--- a/benefit_indexing.xlsx
+++ b/benefit_indexing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/BryanMak/Documents/RawClaimMCR-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{708E0673-4AFE-A045-AEAF-F7214D05CF8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6A52DF-937E-6143-BB97-0D6008D3FC67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20060" yWindow="-21000" windowWidth="38400" windowHeight="21000" xr2:uid="{A0161F8B-45E3-674F-BD1A-B040F75BC5F2}"/>
+    <workbookView xWindow="-18340" yWindow="-21600" windowWidth="38400" windowHeight="21600" xr2:uid="{A0161F8B-45E3-674F-BD1A-B040F75BC5F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="663">
   <si>
     <t>Daily Room &amp; Board</t>
   </si>
@@ -1950,6 +1950,81 @@
   </si>
   <si>
     <t>Specialist's Fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surgeon Fees - Minor </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attending Doctor's Fee </t>
+  </si>
+  <si>
+    <t xml:space="preserve">X-Ray &amp; Laboratory Tests </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wellness </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miscellaneous Charges </t>
+  </si>
+  <si>
+    <t>Post-Hospitalisation / Day Surgery Outpatient Care</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anaesthetist's fee - Minor </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Room &amp; Board </t>
+  </si>
+  <si>
+    <t>Ineligible Benefit Type (HSBC)</t>
+  </si>
+  <si>
+    <t>Ineligible Benefit Type</t>
+  </si>
+  <si>
+    <t>Daily Cash Benefit For Second Claim</t>
+  </si>
+  <si>
+    <t>Pre-Hospitalisation / Day Surgery Outpatient Care</t>
+  </si>
+  <si>
+    <t>Emergency Treatment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surgeon Fees - Major </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anaesthetist's fee - Major </t>
+  </si>
+  <si>
+    <t>Operating Theater - Major</t>
+  </si>
+  <si>
+    <t>Day Surgery Cash Benefit</t>
+  </si>
+  <si>
+    <t>Government Hospital Cash</t>
+  </si>
+  <si>
+    <t>Surgeon Fees - Inter</t>
+  </si>
+  <si>
+    <t>Anaesthetist's fee - Inter</t>
+  </si>
+  <si>
+    <t>Operating Theater - Inter</t>
+  </si>
+  <si>
+    <t>Psychiatric Outpatient Treatment</t>
+  </si>
+  <si>
+    <t>Chiropractic Treatment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surgeon Fees - Complex </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prescription Benefit </t>
   </si>
 </sst>
 </file>
@@ -2384,7 +2459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4FDC71E-C596-D04E-840B-E0EAE83F6708}">
-  <dimension ref="A1:S180"/>
+  <dimension ref="A1:S189"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
@@ -2546,6 +2621,9 @@
       <c r="L3" t="s">
         <v>325</v>
       </c>
+      <c r="M3" t="s">
+        <v>645</v>
+      </c>
       <c r="O3" t="s">
         <v>497</v>
       </c>
@@ -2634,6 +2712,9 @@
       <c r="K5" t="s">
         <v>215</v>
       </c>
+      <c r="M5" t="s">
+        <v>639</v>
+      </c>
       <c r="N5" s="10" t="s">
         <v>579</v>
       </c>
@@ -2728,6 +2809,9 @@
       </c>
       <c r="L7" t="s">
         <v>326</v>
+      </c>
+      <c r="M7" t="s">
+        <v>642</v>
       </c>
       <c r="O7" t="s">
         <v>499</v>
@@ -2855,6 +2939,9 @@
       <c r="E13" t="s">
         <v>48</v>
       </c>
+      <c r="M13" t="s">
+        <v>661</v>
+      </c>
       <c r="N13" s="10" t="s">
         <v>580</v>
       </c>
@@ -2913,6 +3000,9 @@
       <c r="K15" t="s">
         <v>215</v>
       </c>
+      <c r="M15" t="s">
+        <v>651</v>
+      </c>
     </row>
     <row r="16" spans="1:19">
       <c r="A16" s="1" t="s">
@@ -2968,6 +3058,9 @@
       <c r="K17" t="s">
         <v>215</v>
       </c>
+      <c r="M17" t="s">
+        <v>656</v>
+      </c>
     </row>
     <row r="18" spans="1:19">
       <c r="A18" s="1" t="s">
@@ -3027,6 +3120,9 @@
       <c r="K19" t="s">
         <v>215</v>
       </c>
+      <c r="M19" t="s">
+        <v>638</v>
+      </c>
     </row>
     <row r="20" spans="1:19">
       <c r="A20" s="1" t="s">
@@ -3096,48 +3192,22 @@
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D23" t="s">
-        <v>57</v>
-      </c>
-      <c r="E23" t="s">
-        <v>48</v>
-      </c>
-      <c r="H23" t="s">
-        <v>200</v>
-      </c>
-      <c r="I23" t="s">
-        <v>236</v>
-      </c>
-      <c r="J23" t="s">
-        <v>203</v>
-      </c>
-      <c r="K23" t="s">
-        <v>215</v>
-      </c>
-      <c r="L23" t="s">
-        <v>340</v>
-      </c>
-      <c r="M23" t="s">
-        <v>387</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="N23" s="10"/>
     </row>
     <row r="24" spans="1:19">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E24" t="s">
         <v>48</v>
@@ -3146,7 +3216,7 @@
         <v>200</v>
       </c>
       <c r="I24" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J24" t="s">
         <v>203</v>
@@ -3155,10 +3225,10 @@
         <v>215</v>
       </c>
       <c r="L24" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="M24" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -3166,37 +3236,10 @@
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" t="s">
-        <v>62</v>
-      </c>
-      <c r="E25" t="s">
-        <v>48</v>
-      </c>
-      <c r="H25" t="s">
-        <v>200</v>
-      </c>
-      <c r="I25" t="s">
-        <v>238</v>
-      </c>
-      <c r="J25" t="s">
-        <v>203</v>
-      </c>
-      <c r="K25" t="s">
-        <v>215</v>
-      </c>
-      <c r="L25" t="s">
-        <v>337</v>
+        <v>8</v>
       </c>
       <c r="M25" t="s">
-        <v>389</v>
-      </c>
-      <c r="N25" s="10" t="s">
-        <v>430</v>
+        <v>652</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -3204,29 +3247,34 @@
         <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="F26" t="s">
-        <v>158</v>
-      </c>
-      <c r="G26" t="s">
-        <v>173</v>
-      </c>
-      <c r="N26" s="10"/>
-      <c r="O26" s="10" t="s">
-        <v>444</v>
-      </c>
-      <c r="P26" t="s">
-        <v>517</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>563</v>
-      </c>
-      <c r="R26" t="s">
-        <v>597</v>
-      </c>
-      <c r="S26" t="s">
-        <v>598</v>
+        <v>9</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D26" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26" t="s">
+        <v>48</v>
+      </c>
+      <c r="H26" t="s">
+        <v>200</v>
+      </c>
+      <c r="I26" t="s">
+        <v>237</v>
+      </c>
+      <c r="J26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K26" t="s">
+        <v>215</v>
+      </c>
+      <c r="L26" t="s">
+        <v>323</v>
+      </c>
+      <c r="M26" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -3234,31 +3282,48 @@
         <v>23</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="N27" s="10"/>
-      <c r="O27" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="17" customHeight="1">
+        <v>9</v>
+      </c>
+      <c r="M27" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19">
       <c r="A28" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D28" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="E28" t="s">
         <v>48</v>
       </c>
+      <c r="H28" t="s">
+        <v>200</v>
+      </c>
+      <c r="I28" t="s">
+        <v>238</v>
+      </c>
+      <c r="J28" t="s">
+        <v>203</v>
+      </c>
+      <c r="K28" t="s">
+        <v>215</v>
+      </c>
+      <c r="L28" t="s">
+        <v>337</v>
+      </c>
+      <c r="M28" t="s">
+        <v>389</v>
+      </c>
       <c r="N28" s="10" t="s">
-        <v>581</v>
+        <v>430</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -3266,54 +3331,41 @@
         <v>23</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D29" t="s">
-        <v>59</v>
-      </c>
-      <c r="E29" t="s">
-        <v>48</v>
-      </c>
-      <c r="H29" t="s">
-        <v>200</v>
-      </c>
-      <c r="I29" t="s">
-        <v>239</v>
-      </c>
-      <c r="J29" t="s">
-        <v>203</v>
-      </c>
-      <c r="K29" t="s">
-        <v>215</v>
-      </c>
-      <c r="L29" t="s">
-        <v>333</v>
+        <v>10</v>
       </c>
       <c r="M29" t="s">
-        <v>395</v>
-      </c>
+        <v>644</v>
+      </c>
+      <c r="N29" s="10"/>
     </row>
     <row r="30" spans="1:19">
       <c r="A30" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H30" t="s">
-        <v>200</v>
-      </c>
-      <c r="I30" t="s">
-        <v>240</v>
-      </c>
-      <c r="J30" t="s">
-        <v>203</v>
-      </c>
-      <c r="K30" t="s">
-        <v>215</v>
+        <v>595</v>
+      </c>
+      <c r="F30" t="s">
+        <v>158</v>
+      </c>
+      <c r="G30" t="s">
+        <v>173</v>
+      </c>
+      <c r="N30" s="10"/>
+      <c r="O30" s="10" t="s">
+        <v>444</v>
+      </c>
+      <c r="P30" t="s">
+        <v>517</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>563</v>
+      </c>
+      <c r="R30" t="s">
+        <v>597</v>
+      </c>
+      <c r="S30" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -3321,54 +3373,31 @@
         <v>23</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D31" t="s">
-        <v>60</v>
-      </c>
-      <c r="E31" t="s">
-        <v>48</v>
-      </c>
-      <c r="H31" t="s">
-        <v>200</v>
-      </c>
-      <c r="I31" t="s">
-        <v>241</v>
-      </c>
-      <c r="J31" t="s">
-        <v>203</v>
-      </c>
-      <c r="K31" t="s">
-        <v>215</v>
-      </c>
-      <c r="L31" t="s">
-        <v>324</v>
-      </c>
-      <c r="M31" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19">
+        <v>595</v>
+      </c>
+      <c r="N31" s="10"/>
+      <c r="O31" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="17" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H32" t="s">
-        <v>200</v>
-      </c>
-      <c r="I32" t="s">
-        <v>242</v>
-      </c>
-      <c r="J32" t="s">
-        <v>203</v>
-      </c>
-      <c r="K32" t="s">
-        <v>215</v>
+        <v>11</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D32" t="s">
+        <v>88</v>
+      </c>
+      <c r="E32" t="s">
+        <v>48</v>
+      </c>
+      <c r="N32" s="10" t="s">
+        <v>581</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -3376,13 +3405,13 @@
         <v>23</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D33" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E33" t="s">
         <v>48</v>
@@ -3391,7 +3420,7 @@
         <v>200</v>
       </c>
       <c r="I33" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="J33" t="s">
         <v>203</v>
@@ -3400,13 +3429,10 @@
         <v>215</v>
       </c>
       <c r="L33" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="M33" t="s">
-        <v>396</v>
-      </c>
-      <c r="N33" s="10" t="s">
-        <v>428</v>
+        <v>395</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -3414,19 +3440,22 @@
         <v>23</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H34" t="s">
         <v>200</v>
       </c>
       <c r="I34" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="J34" t="s">
         <v>203</v>
       </c>
       <c r="K34" t="s">
         <v>215</v>
+      </c>
+      <c r="M34" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -3434,28 +3463,34 @@
         <v>23</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="F35" t="s">
-        <v>159</v>
-      </c>
-      <c r="G35" t="s">
-        <v>173</v>
-      </c>
-      <c r="O35" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="P35" t="s">
-        <v>518</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>159</v>
-      </c>
-      <c r="R35" t="s">
-        <v>592</v>
-      </c>
-      <c r="S35" t="s">
-        <v>593</v>
+        <v>13</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D35" t="s">
+        <v>60</v>
+      </c>
+      <c r="E35" t="s">
+        <v>48</v>
+      </c>
+      <c r="H35" t="s">
+        <v>200</v>
+      </c>
+      <c r="I35" t="s">
+        <v>241</v>
+      </c>
+      <c r="J35" t="s">
+        <v>203</v>
+      </c>
+      <c r="K35" t="s">
+        <v>215</v>
+      </c>
+      <c r="L35" t="s">
+        <v>324</v>
+      </c>
+      <c r="M35" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -3463,10 +3498,22 @@
         <v>23</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="O36" t="s">
-        <v>505</v>
+        <v>13</v>
+      </c>
+      <c r="H36" t="s">
+        <v>200</v>
+      </c>
+      <c r="I36" t="s">
+        <v>242</v>
+      </c>
+      <c r="J36" t="s">
+        <v>203</v>
+      </c>
+      <c r="K36" t="s">
+        <v>215</v>
+      </c>
+      <c r="M36" t="s">
+        <v>658</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -3474,28 +3521,22 @@
         <v>23</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D37" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="E37" t="s">
         <v>48</v>
       </c>
-      <c r="F37" t="s">
-        <v>167</v>
-      </c>
-      <c r="G37" t="s">
-        <v>173</v>
-      </c>
       <c r="H37" t="s">
         <v>200</v>
       </c>
       <c r="I37" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="J37" t="s">
         <v>203</v>
@@ -3504,25 +3545,13 @@
         <v>215</v>
       </c>
       <c r="L37" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="M37" t="s">
-        <v>401</v>
-      </c>
-      <c r="N37" t="s">
-        <v>637</v>
-      </c>
-      <c r="P37" t="s">
-        <v>519</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>572</v>
-      </c>
-      <c r="R37" t="s">
-        <v>622</v>
-      </c>
-      <c r="S37" t="s">
-        <v>623</v>
+        <v>396</v>
+      </c>
+      <c r="N37" s="10" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -3530,25 +3559,22 @@
         <v>23</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F38" t="s">
-        <v>348</v>
-      </c>
-      <c r="G38" t="s">
-        <v>173</v>
+        <v>14</v>
       </c>
       <c r="H38" t="s">
         <v>200</v>
       </c>
       <c r="I38" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="J38" t="s">
         <v>203</v>
       </c>
       <c r="K38" t="s">
         <v>215</v>
+      </c>
+      <c r="M38" t="s">
+        <v>645</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -3556,25 +3582,28 @@
         <v>23</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="D39" t="s">
-        <v>465</v>
-      </c>
-      <c r="E39" t="s">
-        <v>48</v>
+        <v>594</v>
       </c>
       <c r="F39" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G39" t="s">
         <v>173</v>
       </c>
-      <c r="L39" t="s">
-        <v>343</v>
+      <c r="O39" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="P39" t="s">
+        <v>518</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>159</v>
+      </c>
+      <c r="R39" t="s">
+        <v>592</v>
+      </c>
+      <c r="S39" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="40" spans="1:19">
@@ -3582,34 +3611,10 @@
         <v>23</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="D40" t="s">
-        <v>133</v>
-      </c>
-      <c r="E40" t="s">
-        <v>48</v>
-      </c>
-      <c r="F40" t="s">
-        <v>356</v>
-      </c>
-      <c r="G40" t="s">
-        <v>173</v>
-      </c>
-      <c r="H40" t="s">
-        <v>200</v>
-      </c>
-      <c r="I40" t="s">
-        <v>247</v>
-      </c>
-      <c r="J40" t="s">
-        <v>203</v>
-      </c>
-      <c r="K40" t="s">
-        <v>215</v>
+        <v>594</v>
+      </c>
+      <c r="O40" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="41" spans="1:19">
@@ -3617,17 +3622,55 @@
         <v>23</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C41" s="7"/>
+        <v>15</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D41" t="s">
+        <v>85</v>
+      </c>
+      <c r="E41" t="s">
+        <v>48</v>
+      </c>
       <c r="F41" t="s">
-        <v>476</v>
+        <v>167</v>
       </c>
       <c r="G41" t="s">
         <v>173</v>
       </c>
       <c r="H41" t="s">
         <v>200</v>
+      </c>
+      <c r="I41" t="s">
+        <v>245</v>
+      </c>
+      <c r="J41" t="s">
+        <v>203</v>
+      </c>
+      <c r="K41" t="s">
+        <v>215</v>
+      </c>
+      <c r="L41" t="s">
+        <v>341</v>
+      </c>
+      <c r="M41" t="s">
+        <v>401</v>
+      </c>
+      <c r="N41" t="s">
+        <v>637</v>
+      </c>
+      <c r="P41" t="s">
+        <v>519</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>572</v>
+      </c>
+      <c r="R41" t="s">
+        <v>622</v>
+      </c>
+      <c r="S41" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="42" spans="1:19">
@@ -3635,22 +3678,25 @@
         <v>23</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="D42" t="s">
-        <v>130</v>
-      </c>
-      <c r="E42" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="F42" t="s">
-        <v>172</v>
+        <v>348</v>
       </c>
       <c r="G42" t="s">
         <v>173</v>
+      </c>
+      <c r="H42" t="s">
+        <v>200</v>
+      </c>
+      <c r="I42" t="s">
+        <v>246</v>
+      </c>
+      <c r="J42" t="s">
+        <v>203</v>
+      </c>
+      <c r="K42" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="43" spans="1:19">
@@ -3658,20 +3704,25 @@
         <v>23</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="C43" s="7"/>
-      <c r="H43" t="s">
-        <v>200</v>
-      </c>
-      <c r="I43" t="s">
-        <v>229</v>
-      </c>
-      <c r="J43" t="s">
-        <v>203</v>
-      </c>
-      <c r="K43" t="s">
-        <v>215</v>
+        <v>16</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="D43" t="s">
+        <v>465</v>
+      </c>
+      <c r="E43" t="s">
+        <v>48</v>
+      </c>
+      <c r="F43" t="s">
+        <v>164</v>
+      </c>
+      <c r="G43" t="s">
+        <v>173</v>
+      </c>
+      <c r="L43" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="44" spans="1:19">
@@ -3679,23 +3730,34 @@
         <v>23</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="C44" s="7"/>
+        <v>17</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D44" t="s">
+        <v>133</v>
+      </c>
+      <c r="E44" t="s">
+        <v>48</v>
+      </c>
+      <c r="F44" t="s">
+        <v>356</v>
+      </c>
+      <c r="G44" t="s">
+        <v>173</v>
+      </c>
       <c r="H44" t="s">
         <v>200</v>
       </c>
       <c r="I44" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="J44" t="s">
         <v>203</v>
       </c>
       <c r="K44" t="s">
         <v>215</v>
-      </c>
-      <c r="O44" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="45" spans="1:19">
@@ -3703,23 +3765,17 @@
         <v>23</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>368</v>
+        <v>18</v>
       </c>
       <c r="C45" s="7"/>
+      <c r="F45" t="s">
+        <v>476</v>
+      </c>
+      <c r="G45" t="s">
+        <v>173</v>
+      </c>
       <c r="H45" t="s">
         <v>200</v>
-      </c>
-      <c r="I45" t="s">
-        <v>225</v>
-      </c>
-      <c r="J45" t="s">
-        <v>203</v>
-      </c>
-      <c r="K45" t="s">
-        <v>215</v>
-      </c>
-      <c r="M45" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="46" spans="1:19">
@@ -3727,23 +3783,22 @@
         <v>23</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="C46" s="7"/>
-      <c r="H46" t="s">
-        <v>200</v>
-      </c>
-      <c r="I46" t="s">
-        <v>226</v>
-      </c>
-      <c r="J46" t="s">
-        <v>203</v>
-      </c>
-      <c r="K46" t="s">
-        <v>215</v>
-      </c>
-      <c r="M46" t="s">
-        <v>399</v>
+        <v>367</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D46" t="s">
+        <v>130</v>
+      </c>
+      <c r="E46" t="s">
+        <v>48</v>
+      </c>
+      <c r="F46" t="s">
+        <v>172</v>
+      </c>
+      <c r="G46" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="47" spans="1:19">
@@ -3751,14 +3806,14 @@
         <v>23</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>368</v>
+        <v>511</v>
       </c>
       <c r="C47" s="7"/>
       <c r="H47" t="s">
         <v>200</v>
       </c>
       <c r="I47" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J47" t="s">
         <v>203</v>
@@ -3767,7 +3822,7 @@
         <v>215</v>
       </c>
       <c r="M47" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
     </row>
     <row r="48" spans="1:19">
@@ -3775,52 +3830,11 @@
         <v>23</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C48" s="6">
-        <v>210</v>
-      </c>
-      <c r="D48" t="s">
-        <v>83</v>
-      </c>
-      <c r="E48" t="s">
-        <v>48</v>
-      </c>
-      <c r="F48" t="s">
-        <v>165</v>
-      </c>
-      <c r="G48" t="s">
-        <v>173</v>
-      </c>
-      <c r="H48" t="s">
-        <v>200</v>
-      </c>
-      <c r="I48" t="s">
-        <v>248</v>
-      </c>
-      <c r="J48" t="s">
-        <v>203</v>
-      </c>
-      <c r="K48" t="s">
-        <v>215</v>
-      </c>
-      <c r="L48" t="s">
-        <v>317</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="C48" s="7"/>
       <c r="M48" t="s">
-        <v>390</v>
-      </c>
-      <c r="N48" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="O48" t="s">
-        <v>496</v>
-      </c>
-      <c r="R48" t="s">
-        <v>626</v>
-      </c>
-      <c r="S48" t="s">
-        <v>627</v>
+        <v>649</v>
       </c>
     </row>
     <row r="49" spans="1:19">
@@ -3828,28 +3842,14 @@
         <v>23</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C49" s="6">
-        <v>220</v>
-      </c>
-      <c r="D49" t="s">
-        <v>134</v>
-      </c>
-      <c r="E49" t="s">
-        <v>48</v>
-      </c>
-      <c r="F49" t="s">
-        <v>170</v>
-      </c>
-      <c r="G49" t="s">
-        <v>173</v>
-      </c>
+        <v>509</v>
+      </c>
+      <c r="C49" s="7"/>
       <c r="H49" t="s">
         <v>200</v>
       </c>
       <c r="I49" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="J49" t="s">
         <v>203</v>
@@ -3857,11 +3857,11 @@
       <c r="K49" t="s">
         <v>215</v>
       </c>
-      <c r="L49" t="s">
-        <v>335</v>
-      </c>
       <c r="M49" t="s">
-        <v>391</v>
+        <v>643</v>
+      </c>
+      <c r="O49" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="50" spans="1:19">
@@ -3869,25 +3869,11 @@
         <v>23</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F50" t="s">
-        <v>359</v>
-      </c>
-      <c r="G50" t="s">
-        <v>173</v>
-      </c>
-      <c r="H50" t="s">
-        <v>200</v>
-      </c>
-      <c r="I50" t="s">
-        <v>250</v>
-      </c>
-      <c r="J50" t="s">
-        <v>203</v>
-      </c>
-      <c r="K50" t="s">
-        <v>215</v>
+        <v>509</v>
+      </c>
+      <c r="C50" s="7"/>
+      <c r="M50" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="51" spans="1:19">
@@ -3895,19 +3881,23 @@
         <v>23</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>19</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="C51" s="7"/>
       <c r="H51" t="s">
         <v>200</v>
       </c>
       <c r="I51" t="s">
-        <v>421</v>
+        <v>225</v>
       </c>
       <c r="J51" t="s">
         <v>203</v>
       </c>
       <c r="K51" t="s">
         <v>215</v>
+      </c>
+      <c r="M51" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="52" spans="1:19">
@@ -3915,7 +3905,20 @@
         <v>23</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>636</v>
+        <v>368</v>
+      </c>
+      <c r="C52" s="7"/>
+      <c r="H52" t="s">
+        <v>200</v>
+      </c>
+      <c r="I52" t="s">
+        <v>226</v>
+      </c>
+      <c r="J52" t="s">
+        <v>203</v>
+      </c>
+      <c r="K52" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="53" spans="1:19">
@@ -3923,55 +3926,20 @@
         <v>23</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C53" s="6">
-        <v>230</v>
-      </c>
-      <c r="D53" t="s">
-        <v>131</v>
-      </c>
-      <c r="E53" t="s">
-        <v>48</v>
-      </c>
-      <c r="F53" t="s">
-        <v>163</v>
-      </c>
-      <c r="G53" t="s">
-        <v>173</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="C53" s="7"/>
       <c r="H53" t="s">
         <v>200</v>
       </c>
       <c r="I53" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="J53" t="s">
         <v>203</v>
       </c>
       <c r="K53" t="s">
         <v>215</v>
-      </c>
-      <c r="L53" t="s">
-        <v>342</v>
-      </c>
-      <c r="M53" t="s">
-        <v>392</v>
-      </c>
-      <c r="N53" s="10" t="s">
-        <v>583</v>
-      </c>
-      <c r="O53" t="s">
-        <v>512</v>
-      </c>
-      <c r="P53" t="s">
-        <v>544</v>
-      </c>
-      <c r="R53" t="s">
-        <v>634</v>
-      </c>
-      <c r="S53" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="54" spans="1:19">
@@ -3979,13 +3947,52 @@
         <v>23</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
+      </c>
+      <c r="C54" s="6">
+        <v>210</v>
+      </c>
+      <c r="D54" t="s">
+        <v>83</v>
+      </c>
+      <c r="E54" t="s">
+        <v>48</v>
       </c>
       <c r="F54" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G54" t="s">
         <v>173</v>
+      </c>
+      <c r="H54" t="s">
+        <v>200</v>
+      </c>
+      <c r="I54" t="s">
+        <v>248</v>
+      </c>
+      <c r="J54" t="s">
+        <v>203</v>
+      </c>
+      <c r="K54" t="s">
+        <v>215</v>
+      </c>
+      <c r="L54" t="s">
+        <v>317</v>
+      </c>
+      <c r="M54" t="s">
+        <v>390</v>
+      </c>
+      <c r="N54" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="O54" t="s">
+        <v>496</v>
+      </c>
+      <c r="R54" t="s">
+        <v>626</v>
+      </c>
+      <c r="S54" t="s">
+        <v>627</v>
       </c>
     </row>
     <row r="55" spans="1:19">
@@ -3993,22 +4000,40 @@
         <v>23</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>408</v>
+        <v>19</v>
+      </c>
+      <c r="C55" s="6">
+        <v>220</v>
+      </c>
+      <c r="D55" t="s">
+        <v>134</v>
+      </c>
+      <c r="E55" t="s">
+        <v>48</v>
+      </c>
+      <c r="F55" t="s">
+        <v>170</v>
+      </c>
+      <c r="G55" t="s">
+        <v>173</v>
+      </c>
+      <c r="H55" t="s">
+        <v>200</v>
+      </c>
+      <c r="I55" t="s">
+        <v>249</v>
+      </c>
+      <c r="J55" t="s">
+        <v>203</v>
+      </c>
+      <c r="K55" t="s">
+        <v>215</v>
       </c>
       <c r="L55" t="s">
         <v>335</v>
       </c>
       <c r="M55" t="s">
-        <v>409</v>
-      </c>
-      <c r="O55" t="s">
-        <v>504</v>
-      </c>
-      <c r="R55" t="s">
-        <v>618</v>
-      </c>
-      <c r="S55" t="s">
-        <v>619</v>
+        <v>391</v>
       </c>
     </row>
     <row r="56" spans="1:19">
@@ -4016,13 +4041,28 @@
         <v>23</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="R56" t="s">
-        <v>630</v>
-      </c>
-      <c r="S56" t="s">
-        <v>631</v>
+        <v>19</v>
+      </c>
+      <c r="F56" t="s">
+        <v>359</v>
+      </c>
+      <c r="G56" t="s">
+        <v>173</v>
+      </c>
+      <c r="H56" t="s">
+        <v>200</v>
+      </c>
+      <c r="I56" t="s">
+        <v>250</v>
+      </c>
+      <c r="J56" t="s">
+        <v>203</v>
+      </c>
+      <c r="K56" t="s">
+        <v>215</v>
+      </c>
+      <c r="M56" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="57" spans="1:19">
@@ -4030,13 +4070,19 @@
         <v>23</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="R57" t="s">
-        <v>632</v>
-      </c>
-      <c r="S57" t="s">
-        <v>633</v>
+        <v>19</v>
+      </c>
+      <c r="H57" t="s">
+        <v>200</v>
+      </c>
+      <c r="I57" t="s">
+        <v>421</v>
+      </c>
+      <c r="J57" t="s">
+        <v>203</v>
+      </c>
+      <c r="K57" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="58" spans="1:19">
@@ -4044,7 +4090,7 @@
         <v>23</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>21</v>
+        <v>636</v>
       </c>
     </row>
     <row r="59" spans="1:19">
@@ -4052,16 +4098,55 @@
         <v>23</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>127</v>
+        <v>20</v>
+      </c>
+      <c r="C59" s="6">
+        <v>230</v>
       </c>
       <c r="D59" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E59" t="s">
         <v>48</v>
+      </c>
+      <c r="F59" t="s">
+        <v>163</v>
+      </c>
+      <c r="G59" t="s">
+        <v>173</v>
+      </c>
+      <c r="H59" t="s">
+        <v>200</v>
+      </c>
+      <c r="I59" t="s">
+        <v>251</v>
+      </c>
+      <c r="J59" t="s">
+        <v>203</v>
+      </c>
+      <c r="K59" t="s">
+        <v>215</v>
+      </c>
+      <c r="L59" t="s">
+        <v>342</v>
+      </c>
+      <c r="M59" t="s">
+        <v>392</v>
+      </c>
+      <c r="N59" s="10" t="s">
+        <v>583</v>
+      </c>
+      <c r="O59" t="s">
+        <v>512</v>
+      </c>
+      <c r="P59" t="s">
+        <v>544</v>
+      </c>
+      <c r="R59" t="s">
+        <v>634</v>
+      </c>
+      <c r="S59" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="60" spans="1:19">
@@ -4069,11 +4154,16 @@
         <v>23</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="C60" s="7"/>
-      <c r="O60" t="s">
-        <v>532</v>
+        <v>20</v>
+      </c>
+      <c r="F60" t="s">
+        <v>171</v>
+      </c>
+      <c r="G60" t="s">
+        <v>173</v>
+      </c>
+      <c r="M60" t="s">
+        <v>648</v>
       </c>
     </row>
     <row r="61" spans="1:19">
@@ -4081,11 +4171,22 @@
         <v>23</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="C61" s="7"/>
-      <c r="Q61" t="s">
-        <v>567</v>
+        <v>408</v>
+      </c>
+      <c r="L61" t="s">
+        <v>335</v>
+      </c>
+      <c r="M61" t="s">
+        <v>409</v>
+      </c>
+      <c r="O61" t="s">
+        <v>504</v>
+      </c>
+      <c r="R61" t="s">
+        <v>618</v>
+      </c>
+      <c r="S61" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="62" spans="1:19">
@@ -4093,272 +4194,178 @@
         <v>23</v>
       </c>
       <c r="B62" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="M62" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" ht="17" customHeight="1">
+      <c r="A63" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="R63" t="s">
+        <v>630</v>
+      </c>
+      <c r="S63" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19">
+      <c r="A64" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="R64" t="s">
+        <v>632</v>
+      </c>
+      <c r="S64" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19">
+      <c r="A65" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19">
+      <c r="A66" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D66" t="s">
+        <v>128</v>
+      </c>
+      <c r="E66" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19">
+      <c r="A67" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C67" s="7"/>
+      <c r="O67" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19">
+      <c r="A68" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="C68" s="7"/>
+      <c r="Q68" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19">
+      <c r="A69" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="C62" s="7"/>
-    </row>
-    <row r="63" spans="1:19">
-      <c r="A63" s="2" t="s">
+      <c r="C69" s="7"/>
+    </row>
+    <row r="70" spans="1:19">
+      <c r="A70" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B70" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C70" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D70" t="s">
         <v>65</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E70" t="s">
         <v>48</v>
       </c>
-      <c r="F63" t="s">
+      <c r="F70" t="s">
         <v>168</v>
       </c>
-      <c r="G63" t="s">
+      <c r="G70" t="s">
         <v>173</v>
       </c>
-      <c r="H63" t="s">
+      <c r="H70" t="s">
         <v>200</v>
       </c>
-      <c r="I63" t="s">
+      <c r="I70" t="s">
         <v>252</v>
       </c>
-      <c r="J63" t="s">
+      <c r="J70" t="s">
         <v>207</v>
       </c>
-      <c r="K63" t="s">
+      <c r="K70" t="s">
         <v>216</v>
       </c>
-      <c r="L63" t="s">
+      <c r="L70" t="s">
         <v>329</v>
       </c>
-      <c r="M63" t="s">
+      <c r="M70" t="s">
         <v>370</v>
       </c>
-      <c r="P63" t="s">
+      <c r="P70" t="s">
         <v>168</v>
       </c>
-      <c r="Q63" t="s">
+      <c r="Q70" t="s">
         <v>168</v>
       </c>
-      <c r="R63" t="s">
+      <c r="R70" t="s">
         <v>614</v>
       </c>
-      <c r="S63" t="s">
+      <c r="S70" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="64" spans="1:19">
-      <c r="A64" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D64" t="s">
-        <v>67</v>
-      </c>
-      <c r="E64" t="s">
-        <v>49</v>
-      </c>
-      <c r="F64" t="s">
-        <v>143</v>
-      </c>
-      <c r="G64" t="s">
-        <v>148</v>
-      </c>
-      <c r="H64" t="s">
-        <v>201</v>
-      </c>
-      <c r="I64" t="s">
-        <v>253</v>
-      </c>
-      <c r="J64" t="s">
-        <v>204</v>
-      </c>
-      <c r="K64" t="s">
-        <v>218</v>
-      </c>
-      <c r="L64" t="s">
-        <v>312</v>
-      </c>
-      <c r="M64" t="s">
-        <v>379</v>
-      </c>
-      <c r="N64" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="O64" s="10" t="s">
-        <v>434</v>
-      </c>
-      <c r="P64" t="s">
-        <v>520</v>
-      </c>
-      <c r="Q64" t="s">
-        <v>520</v>
-      </c>
-      <c r="R64" t="s">
-        <v>586</v>
-      </c>
-      <c r="S64" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15">
-      <c r="A65" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F65" t="s">
-        <v>144</v>
-      </c>
-      <c r="G65" t="s">
-        <v>148</v>
-      </c>
-      <c r="H65" t="s">
-        <v>201</v>
-      </c>
-      <c r="I65" t="s">
-        <v>254</v>
-      </c>
-      <c r="J65" t="s">
-        <v>204</v>
-      </c>
-      <c r="K65" t="s">
-        <v>218</v>
-      </c>
-      <c r="L65" t="s">
-        <v>450</v>
-      </c>
-      <c r="M65" t="s">
-        <v>384</v>
-      </c>
-      <c r="O65" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15">
-      <c r="A66" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H66" t="s">
-        <v>201</v>
-      </c>
-      <c r="I66" t="s">
-        <v>255</v>
-      </c>
-      <c r="J66" t="s">
-        <v>204</v>
-      </c>
-      <c r="K66" t="s">
-        <v>218</v>
-      </c>
-      <c r="O66" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15">
-      <c r="A67" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H67" t="s">
-        <v>201</v>
-      </c>
-      <c r="I67" t="s">
-        <v>256</v>
-      </c>
-      <c r="J67" t="s">
-        <v>204</v>
-      </c>
-      <c r="K67" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15">
-      <c r="A68" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H68" t="s">
-        <v>201</v>
-      </c>
-      <c r="I68" t="s">
-        <v>350</v>
-      </c>
-      <c r="J68" t="s">
-        <v>204</v>
-      </c>
-      <c r="K68" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15">
-      <c r="A69" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H69" t="s">
-        <v>201</v>
-      </c>
-      <c r="I69" t="s">
-        <v>351</v>
-      </c>
-      <c r="J69" t="s">
-        <v>204</v>
-      </c>
-      <c r="K69" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15">
-      <c r="A70" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H70" t="s">
-        <v>201</v>
-      </c>
-      <c r="I70" t="s">
-        <v>354</v>
-      </c>
-      <c r="J70" t="s">
-        <v>204</v>
-      </c>
-      <c r="K70" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15">
+    <row r="71" spans="1:19">
       <c r="A71" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="C71" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D71" t="s">
+        <v>67</v>
+      </c>
+      <c r="E71" t="s">
+        <v>49</v>
+      </c>
+      <c r="F71" t="s">
+        <v>143</v>
+      </c>
+      <c r="G71" t="s">
+        <v>148</v>
+      </c>
       <c r="H71" t="s">
         <v>201</v>
       </c>
       <c r="I71" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="J71" t="s">
         <v>204</v>
@@ -4366,19 +4373,49 @@
       <c r="K71" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="72" spans="1:15">
+      <c r="L71" t="s">
+        <v>312</v>
+      </c>
+      <c r="M71" t="s">
+        <v>379</v>
+      </c>
+      <c r="N71" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="O71" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="P71" t="s">
+        <v>520</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>520</v>
+      </c>
+      <c r="R71" t="s">
+        <v>586</v>
+      </c>
+      <c r="S71" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19">
       <c r="A72" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="F72" t="s">
+        <v>144</v>
+      </c>
+      <c r="G72" t="s">
+        <v>148</v>
+      </c>
       <c r="H72" t="s">
         <v>201</v>
       </c>
       <c r="I72" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="J72" t="s">
         <v>204</v>
@@ -4386,8 +4423,17 @@
       <c r="K72" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="73" spans="1:15">
+      <c r="L72" t="s">
+        <v>450</v>
+      </c>
+      <c r="M72" t="s">
+        <v>384</v>
+      </c>
+      <c r="O72" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19">
       <c r="A73" s="3" t="s">
         <v>24</v>
       </c>
@@ -4398,7 +4444,7 @@
         <v>201</v>
       </c>
       <c r="I73" t="s">
-        <v>413</v>
+        <v>255</v>
       </c>
       <c r="J73" t="s">
         <v>204</v>
@@ -4406,8 +4452,11 @@
       <c r="K73" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="74" spans="1:15">
+      <c r="O73" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19">
       <c r="A74" s="3" t="s">
         <v>24</v>
       </c>
@@ -4418,7 +4467,7 @@
         <v>201</v>
       </c>
       <c r="I74" t="s">
-        <v>414</v>
+        <v>256</v>
       </c>
       <c r="J74" t="s">
         <v>204</v>
@@ -4427,7 +4476,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="75" spans="1:15">
+    <row r="75" spans="1:19">
       <c r="A75" s="3" t="s">
         <v>24</v>
       </c>
@@ -4438,7 +4487,7 @@
         <v>201</v>
       </c>
       <c r="I75" t="s">
-        <v>416</v>
+        <v>350</v>
       </c>
       <c r="J75" t="s">
         <v>204</v>
@@ -4447,7 +4496,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="76" spans="1:15">
+    <row r="76" spans="1:19">
       <c r="A76" s="3" t="s">
         <v>24</v>
       </c>
@@ -4458,7 +4507,7 @@
         <v>201</v>
       </c>
       <c r="I76" t="s">
-        <v>415</v>
+        <v>351</v>
       </c>
       <c r="J76" t="s">
         <v>204</v>
@@ -4467,15 +4516,18 @@
         <v>218</v>
       </c>
     </row>
-    <row r="77" spans="1:15">
+    <row r="77" spans="1:19">
       <c r="A77" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="H77" t="s">
+        <v>201</v>
+      </c>
       <c r="I77" t="s">
-        <v>483</v>
+        <v>354</v>
       </c>
       <c r="J77" t="s">
         <v>204</v>
@@ -4484,15 +4536,18 @@
         <v>218</v>
       </c>
     </row>
-    <row r="78" spans="1:15">
+    <row r="78" spans="1:19">
       <c r="A78" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="H78" t="s">
+        <v>201</v>
+      </c>
       <c r="I78" t="s">
-        <v>484</v>
+        <v>257</v>
       </c>
       <c r="J78" t="s">
         <v>204</v>
@@ -4501,7 +4556,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="79" spans="1:15">
+    <row r="79" spans="1:19">
       <c r="A79" s="3" t="s">
         <v>24</v>
       </c>
@@ -4512,7 +4567,7 @@
         <v>201</v>
       </c>
       <c r="I79" t="s">
-        <v>479</v>
+        <v>258</v>
       </c>
       <c r="J79" t="s">
         <v>204</v>
@@ -4521,7 +4576,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="80" spans="1:15">
+    <row r="80" spans="1:19">
       <c r="A80" s="3" t="s">
         <v>24</v>
       </c>
@@ -4532,7 +4587,7 @@
         <v>201</v>
       </c>
       <c r="I80" t="s">
-        <v>349</v>
+        <v>413</v>
       </c>
       <c r="J80" t="s">
         <v>204</v>
@@ -4552,7 +4607,7 @@
         <v>201</v>
       </c>
       <c r="I81" t="s">
-        <v>257</v>
+        <v>414</v>
       </c>
       <c r="J81" t="s">
         <v>204</v>
@@ -4566,25 +4621,13 @@
         <v>24</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D82" t="s">
-        <v>68</v>
-      </c>
-      <c r="E82" t="s">
-        <v>49</v>
-      </c>
-      <c r="F82" t="s">
-        <v>145</v>
-      </c>
-      <c r="G82" t="s">
-        <v>148</v>
+        <v>25</v>
       </c>
       <c r="H82" t="s">
         <v>201</v>
+      </c>
+      <c r="I82" t="s">
+        <v>416</v>
       </c>
       <c r="J82" t="s">
         <v>204</v>
@@ -4592,43 +4635,19 @@
       <c r="K82" t="s">
         <v>218</v>
       </c>
-      <c r="L82" t="s">
-        <v>314</v>
-      </c>
-      <c r="M82" t="s">
-        <v>246</v>
-      </c>
-      <c r="N82" s="10" t="s">
-        <v>423</v>
-      </c>
-      <c r="O82" s="10" t="s">
-        <v>442</v>
-      </c>
-      <c r="P82" t="s">
-        <v>521</v>
-      </c>
-      <c r="Q82" t="s">
-        <v>546</v>
-      </c>
-      <c r="R82" t="s">
-        <v>606</v>
-      </c>
-      <c r="S82" t="s">
-        <v>607</v>
-      </c>
     </row>
     <row r="83" spans="1:19">
       <c r="A83" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H83" t="s">
         <v>201</v>
       </c>
       <c r="I83" t="s">
-        <v>259</v>
+        <v>415</v>
       </c>
       <c r="J83" t="s">
         <v>204</v>
@@ -4636,28 +4655,16 @@
       <c r="K83" t="s">
         <v>218</v>
       </c>
-      <c r="O83" t="s">
-        <v>498</v>
-      </c>
     </row>
     <row r="84" spans="1:19">
       <c r="A84" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F84" t="s">
-        <v>146</v>
-      </c>
-      <c r="G84" t="s">
-        <v>148</v>
-      </c>
-      <c r="H84" t="s">
-        <v>201</v>
+        <v>25</v>
       </c>
       <c r="I84" t="s">
-        <v>260</v>
+        <v>483</v>
       </c>
       <c r="J84" t="s">
         <v>204</v>
@@ -4665,22 +4672,16 @@
       <c r="K84" t="s">
         <v>218</v>
       </c>
-      <c r="O84" t="s">
-        <v>521</v>
-      </c>
     </row>
     <row r="85" spans="1:19">
       <c r="A85" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H85" t="s">
-        <v>201</v>
+        <v>25</v>
       </c>
       <c r="I85" t="s">
-        <v>261</v>
+        <v>484</v>
       </c>
       <c r="J85" t="s">
         <v>204</v>
@@ -4694,13 +4695,13 @@
         <v>24</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H86" t="s">
         <v>201</v>
       </c>
       <c r="I86" t="s">
-        <v>262</v>
+        <v>479</v>
       </c>
       <c r="J86" t="s">
         <v>204</v>
@@ -4714,13 +4715,13 @@
         <v>24</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H87" t="s">
         <v>201</v>
       </c>
       <c r="I87" t="s">
-        <v>263</v>
+        <v>349</v>
       </c>
       <c r="J87" t="s">
         <v>204</v>
@@ -4734,13 +4735,13 @@
         <v>24</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H88" t="s">
         <v>201</v>
       </c>
       <c r="I88" t="s">
-        <v>480</v>
+        <v>257</v>
       </c>
       <c r="J88" t="s">
         <v>204</v>
@@ -4756,11 +4757,23 @@
       <c r="B89" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="C89" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D89" t="s">
+        <v>68</v>
+      </c>
+      <c r="E89" t="s">
+        <v>49</v>
+      </c>
+      <c r="F89" t="s">
+        <v>145</v>
+      </c>
+      <c r="G89" t="s">
+        <v>148</v>
+      </c>
       <c r="H89" t="s">
         <v>201</v>
-      </c>
-      <c r="I89" t="s">
-        <v>352</v>
       </c>
       <c r="J89" t="s">
         <v>204</v>
@@ -4768,6 +4781,30 @@
       <c r="K89" t="s">
         <v>218</v>
       </c>
+      <c r="L89" t="s">
+        <v>314</v>
+      </c>
+      <c r="M89" t="s">
+        <v>246</v>
+      </c>
+      <c r="N89" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="O89" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="P89" t="s">
+        <v>521</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>546</v>
+      </c>
+      <c r="R89" t="s">
+        <v>606</v>
+      </c>
+      <c r="S89" t="s">
+        <v>607</v>
+      </c>
     </row>
     <row r="90" spans="1:19">
       <c r="A90" s="3" t="s">
@@ -4780,7 +4817,7 @@
         <v>201</v>
       </c>
       <c r="I90" t="s">
-        <v>355</v>
+        <v>259</v>
       </c>
       <c r="J90" t="s">
         <v>204</v>
@@ -4788,6 +4825,9 @@
       <c r="K90" t="s">
         <v>218</v>
       </c>
+      <c r="O90" t="s">
+        <v>498</v>
+      </c>
     </row>
     <row r="91" spans="1:19">
       <c r="A91" s="3" t="s">
@@ -4796,11 +4836,17 @@
       <c r="B91" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="F91" t="s">
+        <v>146</v>
+      </c>
+      <c r="G91" t="s">
+        <v>148</v>
+      </c>
       <c r="H91" t="s">
         <v>201</v>
       </c>
       <c r="I91" t="s">
-        <v>417</v>
+        <v>260</v>
       </c>
       <c r="J91" t="s">
         <v>204</v>
@@ -4808,6 +4854,9 @@
       <c r="K91" t="s">
         <v>218</v>
       </c>
+      <c r="O91" t="s">
+        <v>521</v>
+      </c>
     </row>
     <row r="92" spans="1:19">
       <c r="A92" s="3" t="s">
@@ -4820,7 +4869,7 @@
         <v>201</v>
       </c>
       <c r="I92" t="s">
-        <v>418</v>
+        <v>261</v>
       </c>
       <c r="J92" t="s">
         <v>204</v>
@@ -4840,7 +4889,7 @@
         <v>201</v>
       </c>
       <c r="I93" t="s">
-        <v>419</v>
+        <v>262</v>
       </c>
       <c r="J93" t="s">
         <v>204</v>
@@ -4860,7 +4909,7 @@
         <v>201</v>
       </c>
       <c r="I94" t="s">
-        <v>478</v>
+        <v>263</v>
       </c>
       <c r="J94" t="s">
         <v>204</v>
@@ -4880,7 +4929,7 @@
         <v>201</v>
       </c>
       <c r="I95" t="s">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="J95" t="s">
         <v>204</v>
@@ -4896,8 +4945,11 @@
       <c r="B96" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="H96" t="s">
+        <v>201</v>
+      </c>
       <c r="I96" t="s">
-        <v>482</v>
+        <v>352</v>
       </c>
       <c r="J96" t="s">
         <v>204</v>
@@ -4913,8 +4965,11 @@
       <c r="B97" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="H97" t="s">
+        <v>201</v>
+      </c>
       <c r="I97" t="s">
-        <v>485</v>
+        <v>355</v>
       </c>
       <c r="J97" t="s">
         <v>204</v>
@@ -4930,8 +4985,11 @@
       <c r="B98" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="H98" t="s">
+        <v>201</v>
+      </c>
       <c r="I98" t="s">
-        <v>486</v>
+        <v>417</v>
       </c>
       <c r="J98" t="s">
         <v>204</v>
@@ -4951,7 +5009,7 @@
         <v>201</v>
       </c>
       <c r="I99" t="s">
-        <v>205</v>
+        <v>418</v>
       </c>
       <c r="J99" t="s">
         <v>204</v>
@@ -4971,7 +5029,7 @@
         <v>201</v>
       </c>
       <c r="I100" t="s">
-        <v>279</v>
+        <v>419</v>
       </c>
       <c r="J100" t="s">
         <v>204</v>
@@ -4991,7 +5049,7 @@
         <v>201</v>
       </c>
       <c r="I101" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J101" t="s">
         <v>204</v>
@@ -5005,28 +5063,13 @@
         <v>24</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C102" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D102" t="s">
-        <v>69</v>
-      </c>
-      <c r="E102" t="s">
-        <v>49</v>
-      </c>
-      <c r="F102" t="s">
-        <v>151</v>
-      </c>
-      <c r="G102" t="s">
-        <v>148</v>
+        <v>26</v>
       </c>
       <c r="H102" t="s">
         <v>201</v>
       </c>
       <c r="I102" t="s">
-        <v>264</v>
+        <v>420</v>
       </c>
       <c r="J102" t="s">
         <v>204</v>
@@ -5034,37 +5077,16 @@
       <c r="K102" t="s">
         <v>218</v>
       </c>
-      <c r="L102" t="s">
-        <v>331</v>
-      </c>
-      <c r="M102" t="s">
-        <v>266</v>
-      </c>
-      <c r="O102" s="10" t="s">
-        <v>443</v>
-      </c>
-      <c r="P102" t="s">
-        <v>524</v>
-      </c>
-      <c r="R102" t="s">
-        <v>590</v>
-      </c>
-      <c r="S102" t="s">
-        <v>591</v>
-      </c>
     </row>
     <row r="103" spans="1:19">
       <c r="A103" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H103" t="s">
-        <v>201</v>
+        <v>26</v>
       </c>
       <c r="I103" t="s">
-        <v>265</v>
+        <v>482</v>
       </c>
       <c r="J103" t="s">
         <v>204</v>
@@ -5072,28 +5094,16 @@
       <c r="K103" t="s">
         <v>218</v>
       </c>
-      <c r="O103" t="s">
-        <v>541</v>
-      </c>
     </row>
     <row r="104" spans="1:19">
       <c r="A104" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F104" t="s">
-        <v>152</v>
-      </c>
-      <c r="G104" t="s">
-        <v>148</v>
-      </c>
-      <c r="H104" t="s">
-        <v>201</v>
+        <v>26</v>
       </c>
       <c r="I104" t="s">
-        <v>266</v>
+        <v>485</v>
       </c>
       <c r="J104" t="s">
         <v>204</v>
@@ -5107,19 +5117,10 @@
         <v>24</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="F105" t="s">
-        <v>189</v>
-      </c>
-      <c r="G105" t="s">
-        <v>148</v>
-      </c>
-      <c r="H105" t="s">
-        <v>201</v>
+        <v>26</v>
       </c>
       <c r="I105" t="s">
-        <v>267</v>
+        <v>486</v>
       </c>
       <c r="J105" t="s">
         <v>204</v>
@@ -5127,43 +5128,19 @@
       <c r="K105" t="s">
         <v>218</v>
       </c>
-      <c r="N105" s="10" t="s">
-        <v>427</v>
-      </c>
-      <c r="O105" t="s">
-        <v>500</v>
-      </c>
-      <c r="Q105" t="s">
-        <v>569</v>
-      </c>
     </row>
     <row r="106" spans="1:19">
       <c r="A106" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D106" t="s">
-        <v>84</v>
-      </c>
-      <c r="E106" t="s">
-        <v>49</v>
-      </c>
-      <c r="F106" t="s">
-        <v>149</v>
-      </c>
-      <c r="G106" t="s">
-        <v>148</v>
+        <v>26</v>
       </c>
       <c r="H106" t="s">
         <v>201</v>
       </c>
       <c r="I106" t="s">
-        <v>84</v>
+        <v>205</v>
       </c>
       <c r="J106" t="s">
         <v>204</v>
@@ -5171,31 +5148,25 @@
       <c r="K106" t="s">
         <v>218</v>
       </c>
-      <c r="L106" t="s">
-        <v>318</v>
-      </c>
-      <c r="M106" t="s">
-        <v>374</v>
-      </c>
-      <c r="P106" t="s">
-        <v>523</v>
-      </c>
-      <c r="R106" t="s">
-        <v>624</v>
-      </c>
-      <c r="S106" t="s">
-        <v>625</v>
-      </c>
     </row>
     <row r="107" spans="1:19">
       <c r="A107" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L107" t="s">
-        <v>464</v>
+        <v>26</v>
+      </c>
+      <c r="H107" t="s">
+        <v>201</v>
+      </c>
+      <c r="I107" t="s">
+        <v>279</v>
+      </c>
+      <c r="J107" t="s">
+        <v>204</v>
+      </c>
+      <c r="K107" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="108" spans="1:19">
@@ -5203,28 +5174,13 @@
         <v>24</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D108" t="s">
-        <v>72</v>
-      </c>
-      <c r="E108" t="s">
-        <v>49</v>
-      </c>
-      <c r="F108" t="s">
-        <v>150</v>
-      </c>
-      <c r="G108" t="s">
-        <v>148</v>
+        <v>26</v>
       </c>
       <c r="H108" t="s">
         <v>201</v>
       </c>
       <c r="I108" t="s">
-        <v>268</v>
+        <v>477</v>
       </c>
       <c r="J108" t="s">
         <v>204</v>
@@ -5232,49 +5188,25 @@
       <c r="K108" t="s">
         <v>218</v>
       </c>
-      <c r="L108" t="s">
-        <v>311</v>
-      </c>
-      <c r="M108" t="s">
-        <v>371</v>
-      </c>
-      <c r="N108" s="10" t="s">
-        <v>425</v>
-      </c>
-      <c r="O108" s="10" t="s">
-        <v>436</v>
-      </c>
-      <c r="P108" t="s">
-        <v>522</v>
-      </c>
-      <c r="Q108" t="s">
-        <v>548</v>
-      </c>
-      <c r="R108" t="s">
-        <v>588</v>
-      </c>
-      <c r="S108" t="s">
-        <v>589</v>
-      </c>
     </row>
     <row r="109" spans="1:19">
       <c r="A109" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>535</v>
+        <v>27</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D109" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E109" t="s">
         <v>49</v>
       </c>
       <c r="F109" t="s">
-        <v>194</v>
+        <v>151</v>
       </c>
       <c r="G109" t="s">
         <v>148</v>
@@ -5283,7 +5215,7 @@
         <v>201</v>
       </c>
       <c r="I109" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="J109" t="s">
         <v>204</v>
@@ -5292,16 +5224,22 @@
         <v>218</v>
       </c>
       <c r="L109" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="M109" t="s">
-        <v>372</v>
-      </c>
-      <c r="O109" t="s">
-        <v>494</v>
-      </c>
-      <c r="Q109" t="s">
-        <v>566</v>
+        <v>266</v>
+      </c>
+      <c r="O109" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="P109" t="s">
+        <v>524</v>
+      </c>
+      <c r="R109" t="s">
+        <v>590</v>
+      </c>
+      <c r="S109" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="110" spans="1:19">
@@ -5309,19 +5247,13 @@
         <v>24</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="F110" t="s">
-        <v>187</v>
-      </c>
-      <c r="G110" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="H110" t="s">
         <v>201</v>
       </c>
       <c r="I110" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="J110" t="s">
         <v>204</v>
@@ -5329,17 +5261,8 @@
       <c r="K110" t="s">
         <v>218</v>
       </c>
-      <c r="L110" t="s">
-        <v>321</v>
-      </c>
-      <c r="M110" t="s">
-        <v>373</v>
-      </c>
       <c r="O110" t="s">
-        <v>536</v>
-      </c>
-      <c r="Q110" t="s">
-        <v>571</v>
+        <v>541</v>
       </c>
     </row>
     <row r="111" spans="1:19">
@@ -5347,10 +5270,10 @@
         <v>24</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>535</v>
+        <v>27</v>
       </c>
       <c r="F111" t="s">
-        <v>347</v>
+        <v>152</v>
       </c>
       <c r="G111" t="s">
         <v>148</v>
@@ -5359,13 +5282,13 @@
         <v>201</v>
       </c>
       <c r="I111" t="s">
-        <v>490</v>
-      </c>
-      <c r="L111" t="s">
-        <v>460</v>
-      </c>
-      <c r="M111" t="s">
-        <v>383</v>
+        <v>266</v>
+      </c>
+      <c r="J111" t="s">
+        <v>204</v>
+      </c>
+      <c r="K111" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="112" spans="1:19">
@@ -5373,10 +5296,10 @@
         <v>24</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>535</v>
+        <v>501</v>
       </c>
       <c r="F112" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G112" t="s">
         <v>148</v>
@@ -5385,7 +5308,7 @@
         <v>201</v>
       </c>
       <c r="I112" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J112" t="s">
         <v>204</v>
@@ -5393,8 +5316,14 @@
       <c r="K112" t="s">
         <v>218</v>
       </c>
-      <c r="M112" t="s">
-        <v>410</v>
+      <c r="N112" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="O112" t="s">
+        <v>500</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="113" spans="1:19">
@@ -5402,10 +5331,19 @@
         <v>24</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>535</v>
+        <v>28</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D113" t="s">
+        <v>84</v>
+      </c>
+      <c r="E113" t="s">
+        <v>49</v>
       </c>
       <c r="F113" t="s">
-        <v>193</v>
+        <v>149</v>
       </c>
       <c r="G113" t="s">
         <v>148</v>
@@ -5414,7 +5352,7 @@
         <v>201</v>
       </c>
       <c r="I113" t="s">
-        <v>272</v>
+        <v>84</v>
       </c>
       <c r="J113" t="s">
         <v>204</v>
@@ -5422,25 +5360,34 @@
       <c r="K113" t="s">
         <v>218</v>
       </c>
+      <c r="L113" t="s">
+        <v>318</v>
+      </c>
+      <c r="M113" t="s">
+        <v>374</v>
+      </c>
+      <c r="P113" t="s">
+        <v>523</v>
+      </c>
+      <c r="R113" t="s">
+        <v>624</v>
+      </c>
+      <c r="S113" t="s">
+        <v>625</v>
+      </c>
     </row>
     <row r="114" spans="1:19">
       <c r="A114" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="F114" t="s">
-        <v>358</v>
-      </c>
-      <c r="G114" t="s">
-        <v>148</v>
-      </c>
-      <c r="H114" t="s">
-        <v>201</v>
-      </c>
-      <c r="I114" t="s">
-        <v>491</v>
+        <v>28</v>
+      </c>
+      <c r="L114" t="s">
+        <v>464</v>
+      </c>
+      <c r="M114" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="115" spans="1:19">
@@ -5450,8 +5397,17 @@
       <c r="B115" s="3" t="s">
         <v>535</v>
       </c>
+      <c r="C115" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D115" t="s">
+        <v>72</v>
+      </c>
+      <c r="E115" t="s">
+        <v>49</v>
+      </c>
       <c r="F115" t="s">
-        <v>361</v>
+        <v>150</v>
       </c>
       <c r="G115" t="s">
         <v>148</v>
@@ -5460,7 +5416,37 @@
         <v>201</v>
       </c>
       <c r="I115" t="s">
-        <v>492</v>
+        <v>268</v>
+      </c>
+      <c r="J115" t="s">
+        <v>204</v>
+      </c>
+      <c r="K115" t="s">
+        <v>218</v>
+      </c>
+      <c r="L115" t="s">
+        <v>311</v>
+      </c>
+      <c r="M115" t="s">
+        <v>371</v>
+      </c>
+      <c r="N115" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="O115" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="P115" t="s">
+        <v>522</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>548</v>
+      </c>
+      <c r="R115" t="s">
+        <v>588</v>
+      </c>
+      <c r="S115" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="116" spans="1:19">
@@ -5470,8 +5456,17 @@
       <c r="B116" s="3" t="s">
         <v>535</v>
       </c>
+      <c r="C116" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D116" t="s">
+        <v>73</v>
+      </c>
+      <c r="E116" t="s">
+        <v>49</v>
+      </c>
       <c r="F116" t="s">
-        <v>573</v>
+        <v>194</v>
       </c>
       <c r="G116" t="s">
         <v>148</v>
@@ -5480,7 +5475,25 @@
         <v>201</v>
       </c>
       <c r="I116" t="s">
-        <v>73</v>
+        <v>269</v>
+      </c>
+      <c r="J116" t="s">
+        <v>204</v>
+      </c>
+      <c r="K116" t="s">
+        <v>218</v>
+      </c>
+      <c r="L116" t="s">
+        <v>320</v>
+      </c>
+      <c r="M116" t="s">
+        <v>372</v>
+      </c>
+      <c r="O116" t="s">
+        <v>494</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="117" spans="1:19">
@@ -5491,11 +5504,35 @@
         <v>535</v>
       </c>
       <c r="F117" t="s">
-        <v>574</v>
+        <v>187</v>
       </c>
       <c r="G117" t="s">
         <v>148</v>
       </c>
+      <c r="H117" t="s">
+        <v>201</v>
+      </c>
+      <c r="I117" t="s">
+        <v>270</v>
+      </c>
+      <c r="J117" t="s">
+        <v>204</v>
+      </c>
+      <c r="K117" t="s">
+        <v>218</v>
+      </c>
+      <c r="L117" t="s">
+        <v>321</v>
+      </c>
+      <c r="M117" t="s">
+        <v>373</v>
+      </c>
+      <c r="O117" t="s">
+        <v>536</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>571</v>
+      </c>
     </row>
     <row r="118" spans="1:19">
       <c r="A118" s="3" t="s">
@@ -5504,25 +5541,34 @@
       <c r="B118" s="3" t="s">
         <v>535</v>
       </c>
+      <c r="F118" t="s">
+        <v>347</v>
+      </c>
+      <c r="G118" t="s">
+        <v>148</v>
+      </c>
+      <c r="H118" t="s">
+        <v>201</v>
+      </c>
+      <c r="I118" t="s">
+        <v>490</v>
+      </c>
+      <c r="L118" t="s">
+        <v>460</v>
+      </c>
+      <c r="M118" t="s">
+        <v>383</v>
+      </c>
     </row>
     <row r="119" spans="1:19">
       <c r="A119" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C119" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D119" t="s">
-        <v>74</v>
-      </c>
-      <c r="E119" t="s">
-        <v>49</v>
+        <v>535</v>
       </c>
       <c r="F119" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="G119" t="s">
         <v>148</v>
@@ -5531,7 +5577,7 @@
         <v>201</v>
       </c>
       <c r="I119" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="J119" t="s">
         <v>204</v>
@@ -5540,13 +5586,7 @@
         <v>218</v>
       </c>
       <c r="M119" t="s">
-        <v>382</v>
-      </c>
-      <c r="N119" s="10" t="s">
-        <v>432</v>
-      </c>
-      <c r="O119" s="10" t="s">
-        <v>448</v>
+        <v>410</v>
       </c>
     </row>
     <row r="120" spans="1:19">
@@ -5554,11 +5594,25 @@
         <v>24</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N120" s="10"/>
-      <c r="O120" t="s">
-        <v>197</v>
+        <v>535</v>
+      </c>
+      <c r="F120" t="s">
+        <v>193</v>
+      </c>
+      <c r="G120" t="s">
+        <v>148</v>
+      </c>
+      <c r="H120" t="s">
+        <v>201</v>
+      </c>
+      <c r="I120" t="s">
+        <v>272</v>
+      </c>
+      <c r="J120" t="s">
+        <v>204</v>
+      </c>
+      <c r="K120" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="121" spans="1:19">
@@ -5566,28 +5620,19 @@
         <v>24</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C121" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D121" t="s">
-        <v>92</v>
-      </c>
-      <c r="E121" t="s">
-        <v>49</v>
+        <v>535</v>
+      </c>
+      <c r="F121" t="s">
+        <v>358</v>
+      </c>
+      <c r="G121" t="s">
+        <v>148</v>
       </c>
       <c r="H121" t="s">
         <v>201</v>
       </c>
       <c r="I121" t="s">
-        <v>274</v>
-      </c>
-      <c r="J121" t="s">
-        <v>204</v>
-      </c>
-      <c r="K121" t="s">
-        <v>218</v>
+        <v>491</v>
       </c>
     </row>
     <row r="122" spans="1:19">
@@ -5595,7 +5640,19 @@
         <v>24</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>31</v>
+        <v>535</v>
+      </c>
+      <c r="F122" t="s">
+        <v>361</v>
+      </c>
+      <c r="G122" t="s">
+        <v>148</v>
+      </c>
+      <c r="H122" t="s">
+        <v>201</v>
+      </c>
+      <c r="I122" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="123" spans="1:19">
@@ -5603,19 +5660,10 @@
         <v>24</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C123" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D123" t="s">
-        <v>71</v>
-      </c>
-      <c r="E123" t="s">
-        <v>49</v>
+        <v>535</v>
       </c>
       <c r="F123" t="s">
-        <v>154</v>
+        <v>573</v>
       </c>
       <c r="G123" t="s">
         <v>148</v>
@@ -5624,37 +5672,7 @@
         <v>201</v>
       </c>
       <c r="I123" t="s">
-        <v>275</v>
-      </c>
-      <c r="J123" t="s">
-        <v>204</v>
-      </c>
-      <c r="K123" t="s">
-        <v>218</v>
-      </c>
-      <c r="L123" t="s">
-        <v>315</v>
-      </c>
-      <c r="M123" t="s">
-        <v>385</v>
-      </c>
-      <c r="N123" s="10" t="s">
-        <v>424</v>
-      </c>
-      <c r="O123" s="10" t="s">
-        <v>438</v>
-      </c>
-      <c r="P123" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q123" t="s">
-        <v>551</v>
-      </c>
-      <c r="R123" t="s">
-        <v>608</v>
-      </c>
-      <c r="S123" t="s">
-        <v>609</v>
+        <v>73</v>
       </c>
     </row>
     <row r="124" spans="1:19">
@@ -5662,51 +5680,21 @@
         <v>24</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>32</v>
+        <v>535</v>
       </c>
       <c r="F124" t="s">
-        <v>155</v>
+        <v>574</v>
       </c>
       <c r="G124" t="s">
         <v>148</v>
       </c>
-      <c r="H124" t="s">
-        <v>201</v>
-      </c>
-      <c r="I124" t="s">
-        <v>276</v>
-      </c>
-      <c r="J124" t="s">
-        <v>204</v>
-      </c>
-      <c r="K124" t="s">
-        <v>218</v>
-      </c>
-      <c r="L124" t="s">
-        <v>449</v>
-      </c>
-      <c r="O124" t="s">
-        <v>502</v>
-      </c>
     </row>
     <row r="125" spans="1:19">
       <c r="A125" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F125" t="s">
-        <v>363</v>
-      </c>
-      <c r="G125" t="s">
-        <v>148</v>
-      </c>
-      <c r="H125" t="s">
-        <v>201</v>
-      </c>
-      <c r="O125" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="126" spans="1:19">
@@ -5714,19 +5702,19 @@
         <v>24</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D126" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E126" t="s">
         <v>49</v>
       </c>
       <c r="F126" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="G126" t="s">
         <v>148</v>
@@ -5735,7 +5723,7 @@
         <v>201</v>
       </c>
       <c r="I126" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="J126" t="s">
         <v>204</v>
@@ -5743,20 +5731,14 @@
       <c r="K126" t="s">
         <v>218</v>
       </c>
-      <c r="L126" t="s">
-        <v>334</v>
-      </c>
       <c r="M126" t="s">
-        <v>381</v>
-      </c>
-      <c r="O126" t="s">
-        <v>540</v>
-      </c>
-      <c r="P126" t="s">
-        <v>543</v>
-      </c>
-      <c r="Q126" t="s">
-        <v>547</v>
+        <v>382</v>
+      </c>
+      <c r="N126" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="O126" s="10" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="127" spans="1:19">
@@ -5764,34 +5746,14 @@
         <v>24</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C127" s="6">
-        <v>253</v>
-      </c>
-      <c r="D127" t="s">
-        <v>90</v>
-      </c>
-      <c r="E127" t="s">
-        <v>49</v>
-      </c>
-      <c r="F127" t="s">
-        <v>220</v>
-      </c>
-      <c r="G127" t="s">
-        <v>148</v>
-      </c>
-      <c r="H127" t="s">
-        <v>201</v>
-      </c>
-      <c r="I127" t="s">
-        <v>278</v>
-      </c>
-      <c r="J127" t="s">
-        <v>204</v>
-      </c>
-      <c r="K127" t="s">
-        <v>218</v>
+        <v>29</v>
+      </c>
+      <c r="M127" t="s">
+        <v>659</v>
+      </c>
+      <c r="N127" s="10"/>
+      <c r="O127" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="128" spans="1:19">
@@ -5799,19 +5761,28 @@
         <v>24</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F128" t="s">
-        <v>196</v>
-      </c>
-      <c r="G128" t="s">
-        <v>148</v>
+        <v>30</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D128" t="s">
+        <v>92</v>
+      </c>
+      <c r="E128" t="s">
+        <v>49</v>
       </c>
       <c r="H128" t="s">
         <v>201</v>
       </c>
       <c r="I128" t="s">
-        <v>481</v>
+        <v>274</v>
+      </c>
+      <c r="J128" t="s">
+        <v>204</v>
+      </c>
+      <c r="K128" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="129" spans="1:19">
@@ -5819,49 +5790,7 @@
         <v>24</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C129" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="D129" t="s">
-        <v>34</v>
-      </c>
-      <c r="E129" t="s">
-        <v>49</v>
-      </c>
-      <c r="F129" t="s">
-        <v>475</v>
-      </c>
-      <c r="G129" t="s">
-        <v>148</v>
-      </c>
-      <c r="H129" t="s">
-        <v>201</v>
-      </c>
-      <c r="I129" t="s">
-        <v>34</v>
-      </c>
-      <c r="J129" t="s">
-        <v>204</v>
-      </c>
-      <c r="K129" t="s">
-        <v>213</v>
-      </c>
-      <c r="L129" t="s">
-        <v>463</v>
-      </c>
-      <c r="M129" t="s">
-        <v>34</v>
-      </c>
-      <c r="N129" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="O129" s="10" t="s">
-        <v>447</v>
-      </c>
-      <c r="Q129" t="s">
-        <v>570</v>
+        <v>31</v>
       </c>
     </row>
     <row r="130" spans="1:19">
@@ -5869,10 +5798,58 @@
         <v>24</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D130" t="s">
+        <v>71</v>
+      </c>
+      <c r="E130" t="s">
+        <v>49</v>
+      </c>
+      <c r="F130" t="s">
+        <v>154</v>
+      </c>
+      <c r="G130" t="s">
+        <v>148</v>
+      </c>
+      <c r="H130" t="s">
+        <v>201</v>
+      </c>
+      <c r="I130" t="s">
+        <v>275</v>
+      </c>
+      <c r="J130" t="s">
+        <v>204</v>
+      </c>
+      <c r="K130" t="s">
+        <v>218</v>
+      </c>
+      <c r="L130" t="s">
+        <v>315</v>
+      </c>
+      <c r="M130" t="s">
+        <v>385</v>
+      </c>
+      <c r="N130" s="10" t="s">
+        <v>424</v>
       </c>
       <c r="O130" s="10" t="s">
-        <v>542</v>
+        <v>438</v>
+      </c>
+      <c r="P130" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>551</v>
+      </c>
+      <c r="R130" t="s">
+        <v>608</v>
+      </c>
+      <c r="S130" t="s">
+        <v>609</v>
       </c>
     </row>
     <row r="131" spans="1:19">
@@ -5880,19 +5857,10 @@
         <v>24</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C131" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="D131" t="s">
-        <v>89</v>
-      </c>
-      <c r="E131" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="F131" t="s">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="G131" t="s">
         <v>148</v>
@@ -5901,34 +5869,22 @@
         <v>201</v>
       </c>
       <c r="I131" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="J131" t="s">
         <v>204</v>
       </c>
       <c r="K131" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="L131" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="M131" t="s">
-        <v>380</v>
-      </c>
-      <c r="N131" s="10" t="s">
-        <v>577</v>
+        <v>640</v>
       </c>
       <c r="O131" t="s">
-        <v>507</v>
-      </c>
-      <c r="Q131" t="s">
-        <v>539</v>
-      </c>
-      <c r="R131" t="s">
-        <v>616</v>
-      </c>
-      <c r="S131" t="s">
-        <v>617</v>
+        <v>502</v>
       </c>
     </row>
     <row r="132" spans="1:19">
@@ -5936,10 +5892,10 @@
         <v>24</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F132" t="s">
-        <v>191</v>
+        <v>363</v>
       </c>
       <c r="G132" t="s">
         <v>148</v>
@@ -5947,17 +5903,8 @@
       <c r="H132" t="s">
         <v>201</v>
       </c>
-      <c r="I132" t="s">
-        <v>281</v>
-      </c>
-      <c r="J132" t="s">
-        <v>204</v>
-      </c>
-      <c r="K132" t="s">
-        <v>218</v>
-      </c>
       <c r="O132" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="133" spans="1:19">
@@ -5965,10 +5912,19 @@
         <v>24</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D133" t="s">
+        <v>70</v>
+      </c>
+      <c r="E133" t="s">
+        <v>49</v>
       </c>
       <c r="F133" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="G133" t="s">
         <v>148</v>
@@ -5976,25 +5932,58 @@
       <c r="H133" t="s">
         <v>201</v>
       </c>
+      <c r="I133" t="s">
+        <v>277</v>
+      </c>
+      <c r="J133" t="s">
+        <v>204</v>
+      </c>
+      <c r="K133" t="s">
+        <v>218</v>
+      </c>
+      <c r="L133" t="s">
+        <v>334</v>
+      </c>
+      <c r="M133" t="s">
+        <v>381</v>
+      </c>
+      <c r="O133" t="s">
+        <v>540</v>
+      </c>
+      <c r="P133" t="s">
+        <v>543</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>547</v>
+      </c>
     </row>
     <row r="134" spans="1:19">
       <c r="A134" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C134" s="6">
-        <v>311</v>
+        <v>253</v>
       </c>
       <c r="D134" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="E134" t="s">
-        <v>51</v>
+        <v>49</v>
+      </c>
+      <c r="F134" t="s">
+        <v>220</v>
+      </c>
+      <c r="G134" t="s">
+        <v>148</v>
+      </c>
+      <c r="H134" t="s">
+        <v>201</v>
       </c>
       <c r="I134" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="J134" t="s">
         <v>204</v>
@@ -6003,13 +5992,7 @@
         <v>218</v>
       </c>
       <c r="M134" t="s">
-        <v>376</v>
-      </c>
-      <c r="O134" s="10" t="s">
-        <v>437</v>
-      </c>
-      <c r="P134" t="s">
-        <v>525</v>
+        <v>662</v>
       </c>
     </row>
     <row r="135" spans="1:19">
@@ -6017,19 +6000,19 @@
         <v>24</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C135" s="6">
-        <v>312</v>
-      </c>
-      <c r="D135" t="s">
-        <v>135</v>
-      </c>
-      <c r="E135" t="s">
-        <v>51</v>
-      </c>
-      <c r="O135" t="s">
-        <v>565</v>
+        <v>33</v>
+      </c>
+      <c r="F135" t="s">
+        <v>196</v>
+      </c>
+      <c r="G135" t="s">
+        <v>148</v>
+      </c>
+      <c r="H135" t="s">
+        <v>201</v>
+      </c>
+      <c r="I135" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="136" spans="1:19">
@@ -6037,19 +6020,49 @@
         <v>24</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>304</v>
+        <v>34</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>305</v>
+        <v>120</v>
       </c>
       <c r="D136" t="s">
-        <v>304</v>
+        <v>34</v>
       </c>
       <c r="E136" t="s">
         <v>49</v>
       </c>
+      <c r="F136" t="s">
+        <v>475</v>
+      </c>
+      <c r="G136" t="s">
+        <v>148</v>
+      </c>
+      <c r="H136" t="s">
+        <v>201</v>
+      </c>
+      <c r="I136" t="s">
+        <v>34</v>
+      </c>
+      <c r="J136" t="s">
+        <v>204</v>
+      </c>
+      <c r="K136" t="s">
+        <v>213</v>
+      </c>
+      <c r="L136" t="s">
+        <v>463</v>
+      </c>
       <c r="M136" t="s">
-        <v>375</v>
+        <v>34</v>
+      </c>
+      <c r="N136" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="O136" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="137" spans="1:19">
@@ -6057,10 +6070,10 @@
         <v>24</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="M137" t="s">
-        <v>378</v>
+        <v>34</v>
+      </c>
+      <c r="O137" s="10" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="138" spans="1:19">
@@ -6068,19 +6081,19 @@
         <v>24</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>308</v>
+        <v>35</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>307</v>
+        <v>121</v>
       </c>
       <c r="D138" t="s">
-        <v>306</v>
+        <v>89</v>
       </c>
       <c r="E138" t="s">
         <v>49</v>
       </c>
       <c r="F138" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="G138" t="s">
         <v>148</v>
@@ -6089,13 +6102,34 @@
         <v>201</v>
       </c>
       <c r="I138" t="s">
-        <v>353</v>
+        <v>280</v>
       </c>
       <c r="J138" t="s">
         <v>204</v>
       </c>
       <c r="K138" t="s">
-        <v>218</v>
+        <v>213</v>
+      </c>
+      <c r="L138" t="s">
+        <v>462</v>
+      </c>
+      <c r="M138" t="s">
+        <v>380</v>
+      </c>
+      <c r="N138" s="10" t="s">
+        <v>577</v>
+      </c>
+      <c r="O138" t="s">
+        <v>507</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>539</v>
+      </c>
+      <c r="R138" t="s">
+        <v>616</v>
+      </c>
+      <c r="S138" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="139" spans="1:19">
@@ -6103,10 +6137,10 @@
         <v>24</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>345</v>
+        <v>35</v>
       </c>
       <c r="F139" t="s">
-        <v>344</v>
+        <v>191</v>
       </c>
       <c r="G139" t="s">
         <v>148</v>
@@ -6114,8 +6148,17 @@
       <c r="H139" t="s">
         <v>201</v>
       </c>
-      <c r="L139" t="s">
-        <v>330</v>
+      <c r="I139" t="s">
+        <v>281</v>
+      </c>
+      <c r="J139" t="s">
+        <v>204</v>
+      </c>
+      <c r="K139" t="s">
+        <v>218</v>
+      </c>
+      <c r="O139" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="140" spans="1:19">
@@ -6123,10 +6166,10 @@
         <v>24</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>455</v>
+        <v>35</v>
       </c>
       <c r="F140" t="s">
-        <v>472</v>
+        <v>192</v>
       </c>
       <c r="G140" t="s">
         <v>148</v>
@@ -6134,31 +6177,25 @@
       <c r="H140" t="s">
         <v>201</v>
       </c>
-      <c r="I140" t="s">
-        <v>488</v>
-      </c>
-      <c r="J140" t="s">
-        <v>204</v>
-      </c>
-      <c r="K140" t="s">
-        <v>218</v>
-      </c>
-      <c r="L140" t="s">
-        <v>456</v>
-      </c>
     </row>
     <row r="141" spans="1:19">
       <c r="A141" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="H141" t="s">
-        <v>201</v>
+        <v>36</v>
+      </c>
+      <c r="C141" s="6">
+        <v>311</v>
+      </c>
+      <c r="D141" t="s">
+        <v>75</v>
+      </c>
+      <c r="E141" t="s">
+        <v>51</v>
       </c>
       <c r="I141" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J141" t="s">
         <v>204</v>
@@ -6167,19 +6204,13 @@
         <v>218</v>
       </c>
       <c r="M141" t="s">
-        <v>287</v>
-      </c>
-      <c r="N141" s="10" t="s">
-        <v>287</v>
+        <v>376</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>435</v>
-      </c>
-      <c r="R141" t="s">
-        <v>604</v>
-      </c>
-      <c r="S141" t="s">
-        <v>605</v>
+        <v>437</v>
+      </c>
+      <c r="P141" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="142" spans="1:19">
@@ -6187,11 +6218,19 @@
         <v>24</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="N142" s="10"/>
-      <c r="O142" s="10" t="s">
-        <v>537</v>
+        <v>36</v>
+      </c>
+      <c r="C142" s="6">
+        <v>312</v>
+      </c>
+      <c r="D142" t="s">
+        <v>135</v>
+      </c>
+      <c r="E142" t="s">
+        <v>51</v>
+      </c>
+      <c r="O142" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="143" spans="1:19">
@@ -6199,10 +6238,19 @@
         <v>24</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>407</v>
+        <v>304</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="D143" t="s">
+        <v>304</v>
+      </c>
+      <c r="E143" t="s">
+        <v>49</v>
       </c>
       <c r="M143" t="s">
-        <v>38</v>
+        <v>375</v>
       </c>
     </row>
     <row r="144" spans="1:19">
@@ -6210,342 +6258,256 @@
         <v>24</v>
       </c>
       <c r="B144" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="M144" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="145" spans="1:19">
+      <c r="A145" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="M145" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="146" spans="1:19">
+      <c r="A146" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="D146" t="s">
+        <v>306</v>
+      </c>
+      <c r="E146" t="s">
+        <v>49</v>
+      </c>
+      <c r="F146" t="s">
+        <v>188</v>
+      </c>
+      <c r="G146" t="s">
+        <v>148</v>
+      </c>
+      <c r="H146" t="s">
+        <v>201</v>
+      </c>
+      <c r="I146" t="s">
+        <v>353</v>
+      </c>
+      <c r="J146" t="s">
+        <v>204</v>
+      </c>
+      <c r="K146" t="s">
+        <v>218</v>
+      </c>
+      <c r="M146" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="147" spans="1:19">
+      <c r="A147" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="F147" t="s">
+        <v>344</v>
+      </c>
+      <c r="G147" t="s">
+        <v>148</v>
+      </c>
+      <c r="H147" t="s">
+        <v>201</v>
+      </c>
+      <c r="L147" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="148" spans="1:19">
+      <c r="A148" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="F148" t="s">
+        <v>472</v>
+      </c>
+      <c r="G148" t="s">
+        <v>148</v>
+      </c>
+      <c r="H148" t="s">
+        <v>201</v>
+      </c>
+      <c r="I148" t="s">
+        <v>488</v>
+      </c>
+      <c r="J148" t="s">
+        <v>204</v>
+      </c>
+      <c r="K148" t="s">
+        <v>218</v>
+      </c>
+      <c r="L148" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="149" spans="1:19">
+      <c r="A149" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="H149" t="s">
+        <v>201</v>
+      </c>
+      <c r="I149" t="s">
+        <v>283</v>
+      </c>
+      <c r="J149" t="s">
+        <v>204</v>
+      </c>
+      <c r="K149" t="s">
+        <v>218</v>
+      </c>
+      <c r="M149" t="s">
+        <v>287</v>
+      </c>
+      <c r="N149" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="O149" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="R149" t="s">
+        <v>604</v>
+      </c>
+      <c r="S149" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="150" spans="1:19">
+      <c r="A150" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="N150" s="10"/>
+      <c r="O150" s="10" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="151" spans="1:19">
+      <c r="A151" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="M151" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="152" spans="1:19">
+      <c r="A152" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B152" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="R144" t="s">
+      <c r="R152" t="s">
         <v>602</v>
       </c>
-      <c r="S144" t="s">
+      <c r="S152" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="145" spans="1:17">
-      <c r="A145" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B145" s="3" t="s">
+    <row r="153" spans="1:19">
+      <c r="A153" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B153" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="F145" t="s">
+      <c r="F153" t="s">
         <v>470</v>
       </c>
-      <c r="G145" t="s">
+      <c r="G153" t="s">
         <v>148</v>
       </c>
-      <c r="H145" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="146" spans="1:17">
-      <c r="A146" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B146" s="3" t="s">
+      <c r="H153" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="154" spans="1:19">
+      <c r="A154" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B154" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="O146" t="s">
+      <c r="O154" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="147" spans="1:17">
-      <c r="A147" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B147" s="3" t="s">
+    <row r="155" spans="1:19">
+      <c r="A155" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B155" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="Q147" t="s">
+      <c r="Q155" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="148" spans="1:17">
-      <c r="A148" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B148" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C148" s="6">
-        <v>511</v>
-      </c>
-      <c r="D148" t="s">
-        <v>81</v>
-      </c>
-      <c r="E148" t="s">
-        <v>50</v>
-      </c>
-      <c r="F148" t="s">
-        <v>181</v>
-      </c>
-      <c r="G148" t="s">
-        <v>186</v>
-      </c>
-      <c r="H148" t="s">
-        <v>201</v>
-      </c>
-      <c r="J148" t="s">
-        <v>206</v>
-      </c>
-      <c r="K148" t="s">
-        <v>217</v>
-      </c>
-      <c r="L148" t="s">
-        <v>313</v>
-      </c>
-      <c r="N148" s="10" t="s">
-        <v>575</v>
-      </c>
-      <c r="P148" t="s">
-        <v>526</v>
-      </c>
-      <c r="Q148" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="149" spans="1:17">
-      <c r="A149" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B149" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F149" t="s">
-        <v>179</v>
-      </c>
-      <c r="G149" t="s">
-        <v>186</v>
-      </c>
-      <c r="H149" t="s">
-        <v>201</v>
-      </c>
-      <c r="I149" t="s">
-        <v>284</v>
-      </c>
-      <c r="J149" t="s">
-        <v>206</v>
-      </c>
-      <c r="K149" t="s">
-        <v>217</v>
-      </c>
-      <c r="L149" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="150" spans="1:17">
-      <c r="A150" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B150" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C150" s="6">
-        <v>513</v>
-      </c>
-      <c r="D150" t="s">
-        <v>82</v>
-      </c>
-      <c r="E150" t="s">
-        <v>50</v>
-      </c>
-      <c r="F150" t="s">
-        <v>177</v>
-      </c>
-      <c r="G150" t="s">
-        <v>186</v>
-      </c>
-      <c r="H150" t="s">
-        <v>201</v>
-      </c>
-      <c r="I150" t="s">
-        <v>285</v>
-      </c>
-      <c r="J150" t="s">
-        <v>206</v>
-      </c>
-      <c r="K150" t="s">
-        <v>217</v>
-      </c>
-      <c r="L150" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="151" spans="1:17">
-      <c r="A151" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B151" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F151" t="s">
-        <v>176</v>
-      </c>
-      <c r="G151" t="s">
-        <v>186</v>
-      </c>
-      <c r="H151" t="s">
-        <v>201</v>
-      </c>
-      <c r="I151" t="s">
-        <v>286</v>
-      </c>
-      <c r="J151" t="s">
-        <v>206</v>
-      </c>
-      <c r="K151" t="s">
-        <v>217</v>
-      </c>
-      <c r="L151" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="152" spans="1:17">
-      <c r="A152" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B152" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F152" t="s">
-        <v>37</v>
-      </c>
-      <c r="G152" t="s">
-        <v>186</v>
-      </c>
-      <c r="H152" t="s">
-        <v>201</v>
-      </c>
-      <c r="I152" t="s">
-        <v>287</v>
-      </c>
-      <c r="J152" t="s">
-        <v>206</v>
-      </c>
-      <c r="K152" t="s">
-        <v>213</v>
-      </c>
-      <c r="L152" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="153" spans="1:17">
-      <c r="A153" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B153" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F153" t="s">
-        <v>182</v>
-      </c>
-      <c r="G153" t="s">
-        <v>186</v>
-      </c>
-      <c r="H153" t="s">
-        <v>201</v>
-      </c>
-      <c r="I153" t="s">
-        <v>38</v>
-      </c>
-      <c r="J153" t="s">
-        <v>206</v>
-      </c>
-      <c r="K153" t="s">
-        <v>217</v>
-      </c>
-      <c r="L153" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="154" spans="1:17" ht="17" customHeight="1">
-      <c r="A154" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B154" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F154" t="s">
-        <v>357</v>
-      </c>
-      <c r="G154" t="s">
-        <v>186</v>
-      </c>
-      <c r="H154" t="s">
-        <v>201</v>
-      </c>
-      <c r="I154" t="s">
-        <v>288</v>
-      </c>
-      <c r="J154" t="s">
-        <v>206</v>
-      </c>
-      <c r="K154" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="155" spans="1:17" ht="17" customHeight="1">
-      <c r="A155" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B155" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F155" t="s">
-        <v>473</v>
-      </c>
-      <c r="G155" t="s">
-        <v>186</v>
-      </c>
-      <c r="H155" t="s">
-        <v>201</v>
-      </c>
-      <c r="I155" t="s">
-        <v>289</v>
-      </c>
-      <c r="J155" t="s">
-        <v>206</v>
-      </c>
-      <c r="K155" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="156" spans="1:17" ht="17" customHeight="1">
-      <c r="A156" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B156" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F156" t="s">
-        <v>474</v>
-      </c>
-      <c r="G156" t="s">
-        <v>186</v>
-      </c>
-      <c r="H156" t="s">
-        <v>201</v>
-      </c>
-      <c r="I156" t="s">
-        <v>290</v>
-      </c>
-      <c r="J156" t="s">
-        <v>206</v>
-      </c>
-      <c r="K156" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="157" spans="1:17" ht="17" customHeight="1">
+    <row r="156" spans="1:19">
+      <c r="A156" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="M156" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="157" spans="1:19">
       <c r="A157" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>38</v>
       </c>
+      <c r="C157" s="6">
+        <v>511</v>
+      </c>
+      <c r="D157" t="s">
+        <v>81</v>
+      </c>
+      <c r="E157" t="s">
+        <v>50</v>
+      </c>
+      <c r="F157" t="s">
+        <v>181</v>
+      </c>
+      <c r="G157" t="s">
+        <v>186</v>
+      </c>
       <c r="H157" t="s">
         <v>201</v>
-      </c>
-      <c r="I157" t="s">
-        <v>291</v>
       </c>
       <c r="J157" t="s">
         <v>206</v>
@@ -6553,8 +6515,20 @@
       <c r="K157" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="158" spans="1:17" ht="17" customHeight="1">
+      <c r="L157" t="s">
+        <v>313</v>
+      </c>
+      <c r="N157" s="10" t="s">
+        <v>575</v>
+      </c>
+      <c r="P157" t="s">
+        <v>526</v>
+      </c>
+      <c r="Q157" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="158" spans="1:19">
       <c r="A158" s="4" t="s">
         <v>37</v>
       </c>
@@ -6562,7 +6536,7 @@
         <v>38</v>
       </c>
       <c r="F158" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G158" t="s">
         <v>186</v>
@@ -6571,7 +6545,7 @@
         <v>201</v>
       </c>
       <c r="I158" t="s">
-        <v>487</v>
+        <v>284</v>
       </c>
       <c r="J158" t="s">
         <v>206</v>
@@ -6579,16 +6553,28 @@
       <c r="K158" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="159" spans="1:17" ht="17" customHeight="1">
+      <c r="L158" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="159" spans="1:19">
       <c r="A159" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B159" s="4" t="s">
         <v>38</v>
       </c>
+      <c r="C159" s="6">
+        <v>513</v>
+      </c>
+      <c r="D159" t="s">
+        <v>82</v>
+      </c>
+      <c r="E159" t="s">
+        <v>50</v>
+      </c>
       <c r="F159" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="G159" t="s">
         <v>186</v>
@@ -6597,7 +6583,7 @@
         <v>201</v>
       </c>
       <c r="I159" t="s">
-        <v>212</v>
+        <v>285</v>
       </c>
       <c r="J159" t="s">
         <v>206</v>
@@ -6605,19 +6591,28 @@
       <c r="K159" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="160" spans="1:17" ht="17" customHeight="1">
+      <c r="L159" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="160" spans="1:19">
       <c r="A160" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B160" s="4" t="s">
         <v>38</v>
       </c>
+      <c r="F160" t="s">
+        <v>176</v>
+      </c>
+      <c r="G160" t="s">
+        <v>186</v>
+      </c>
       <c r="H160" t="s">
         <v>201</v>
       </c>
       <c r="I160" t="s">
-        <v>489</v>
+        <v>286</v>
       </c>
       <c r="J160" t="s">
         <v>206</v>
@@ -6625,25 +6620,37 @@
       <c r="K160" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="161" spans="1:17" ht="17" customHeight="1">
+      <c r="L160" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17">
       <c r="A161" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>38</v>
       </c>
+      <c r="F161" t="s">
+        <v>37</v>
+      </c>
+      <c r="G161" t="s">
+        <v>186</v>
+      </c>
       <c r="H161" t="s">
         <v>201</v>
       </c>
       <c r="I161" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="J161" t="s">
         <v>206</v>
       </c>
       <c r="K161" t="s">
-        <v>217</v>
+        <v>213</v>
+      </c>
+      <c r="L161" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="162" spans="1:17">
@@ -6651,10 +6658,10 @@
         <v>37</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F162" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="G162" t="s">
         <v>186</v>
@@ -6663,7 +6670,7 @@
         <v>201</v>
       </c>
       <c r="I162" t="s">
-        <v>293</v>
+        <v>38</v>
       </c>
       <c r="J162" t="s">
         <v>206</v>
@@ -6672,27 +6679,18 @@
         <v>217</v>
       </c>
       <c r="L162" t="s">
-        <v>458</v>
-      </c>
-      <c r="N162" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="P162" t="s">
-        <v>527</v>
-      </c>
-      <c r="Q162" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="163" spans="1:17">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17" ht="17" customHeight="1">
       <c r="A163" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F163" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="G163" t="s">
         <v>186</v>
@@ -6701,7 +6699,7 @@
         <v>201</v>
       </c>
       <c r="I163" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J163" t="s">
         <v>206</v>
@@ -6710,18 +6708,24 @@
         <v>217</v>
       </c>
     </row>
-    <row r="164" spans="1:17">
+    <row r="164" spans="1:17" ht="17" customHeight="1">
       <c r="A164" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="F164" t="s">
+        <v>473</v>
+      </c>
+      <c r="G164" t="s">
+        <v>186</v>
       </c>
       <c r="H164" t="s">
         <v>201</v>
       </c>
       <c r="I164" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="J164" t="s">
         <v>206</v>
@@ -6730,15 +6734,15 @@
         <v>217</v>
       </c>
     </row>
-    <row r="165" spans="1:17">
+    <row r="165" spans="1:17" ht="17" customHeight="1">
       <c r="A165" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F165" t="s">
-        <v>178</v>
+        <v>474</v>
       </c>
       <c r="G165" t="s">
         <v>186</v>
@@ -6747,7 +6751,7 @@
         <v>201</v>
       </c>
       <c r="I165" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="J165" t="s">
         <v>206</v>
@@ -6755,34 +6759,19 @@
       <c r="K165" t="s">
         <v>217</v>
       </c>
-      <c r="L165" t="s">
-        <v>459</v>
-      </c>
-      <c r="N165" s="10" t="s">
-        <v>578</v>
-      </c>
-      <c r="P165" t="s">
-        <v>528</v>
-      </c>
-      <c r="Q165" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="166" spans="1:17">
+    </row>
+    <row r="166" spans="1:17" ht="17" customHeight="1">
       <c r="A166" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F166" t="s">
-        <v>360</v>
+        <v>38</v>
       </c>
       <c r="H166" t="s">
         <v>201</v>
       </c>
       <c r="I166" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="J166" t="s">
         <v>206</v>
@@ -6791,15 +6780,15 @@
         <v>217</v>
       </c>
     </row>
-    <row r="167" spans="1:17">
+    <row r="167" spans="1:17" ht="17" customHeight="1">
       <c r="A167" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>530</v>
+        <v>38</v>
       </c>
       <c r="F167" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="G167" t="s">
         <v>186</v>
@@ -6808,7 +6797,7 @@
         <v>201</v>
       </c>
       <c r="I167" t="s">
-        <v>298</v>
+        <v>487</v>
       </c>
       <c r="J167" t="s">
         <v>206</v>
@@ -6816,28 +6805,16 @@
       <c r="K167" t="s">
         <v>217</v>
       </c>
-      <c r="L167" t="s">
-        <v>452</v>
-      </c>
-      <c r="N167" s="10" t="s">
-        <v>530</v>
-      </c>
-      <c r="P167" t="s">
-        <v>529</v>
-      </c>
-      <c r="Q167" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="168" spans="1:17">
+    </row>
+    <row r="168" spans="1:17" ht="17" customHeight="1">
       <c r="A168" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>530</v>
+        <v>38</v>
       </c>
       <c r="F168" t="s">
-        <v>471</v>
+        <v>184</v>
       </c>
       <c r="G168" t="s">
         <v>186</v>
@@ -6846,7 +6823,7 @@
         <v>201</v>
       </c>
       <c r="I168" t="s">
-        <v>41</v>
+        <v>212</v>
       </c>
       <c r="J168" t="s">
         <v>206</v>
@@ -6855,18 +6832,18 @@
         <v>217</v>
       </c>
     </row>
-    <row r="169" spans="1:17">
+    <row r="169" spans="1:17" ht="17" customHeight="1">
       <c r="A169" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>530</v>
+        <v>38</v>
       </c>
       <c r="H169" t="s">
         <v>201</v>
       </c>
       <c r="I169" t="s">
-        <v>211</v>
+        <v>489</v>
       </c>
       <c r="J169" t="s">
         <v>206</v>
@@ -6875,18 +6852,18 @@
         <v>217</v>
       </c>
     </row>
-    <row r="170" spans="1:17">
+    <row r="170" spans="1:17" ht="17" customHeight="1">
       <c r="A170" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>530</v>
+        <v>38</v>
       </c>
       <c r="H170" t="s">
         <v>201</v>
       </c>
       <c r="I170" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="J170" t="s">
         <v>206</v>
@@ -6900,10 +6877,37 @@
         <v>37</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>555</v>
+        <v>39</v>
+      </c>
+      <c r="F171" t="s">
+        <v>175</v>
+      </c>
+      <c r="G171" t="s">
+        <v>186</v>
+      </c>
+      <c r="H171" t="s">
+        <v>201</v>
+      </c>
+      <c r="I171" t="s">
+        <v>293</v>
+      </c>
+      <c r="J171" t="s">
+        <v>206</v>
+      </c>
+      <c r="K171" t="s">
+        <v>217</v>
+      </c>
+      <c r="L171" t="s">
+        <v>458</v>
+      </c>
+      <c r="N171" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="P171" t="s">
+        <v>527</v>
       </c>
       <c r="Q171" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="172" spans="1:17">
@@ -6911,10 +6915,25 @@
         <v>37</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>556</v>
-      </c>
-      <c r="Q172" t="s">
-        <v>558</v>
+        <v>39</v>
+      </c>
+      <c r="F172" t="s">
+        <v>362</v>
+      </c>
+      <c r="G172" t="s">
+        <v>186</v>
+      </c>
+      <c r="H172" t="s">
+        <v>201</v>
+      </c>
+      <c r="I172" t="s">
+        <v>294</v>
+      </c>
+      <c r="J172" t="s">
+        <v>206</v>
+      </c>
+      <c r="K172" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="173" spans="1:17">
@@ -6922,30 +6941,30 @@
         <v>37</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q173" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="174" spans="1:17" ht="17" customHeight="1">
+        <v>39</v>
+      </c>
+      <c r="H173" t="s">
+        <v>201</v>
+      </c>
+      <c r="I173" t="s">
+        <v>295</v>
+      </c>
+      <c r="J173" t="s">
+        <v>206</v>
+      </c>
+      <c r="K173" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="174" spans="1:17">
       <c r="A174" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C174" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="D174" t="s">
-        <v>467</v>
-      </c>
-      <c r="E174" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F174" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="G174" t="s">
         <v>186</v>
@@ -6954,13 +6973,25 @@
         <v>201</v>
       </c>
       <c r="I174" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="J174" t="s">
         <v>206</v>
       </c>
       <c r="K174" t="s">
         <v>217</v>
+      </c>
+      <c r="L174" t="s">
+        <v>459</v>
+      </c>
+      <c r="N174" s="10" t="s">
+        <v>578</v>
+      </c>
+      <c r="P174" t="s">
+        <v>528</v>
+      </c>
+      <c r="Q174" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="175" spans="1:17">
@@ -6968,151 +6999,346 @@
         <v>37</v>
       </c>
       <c r="B175" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F175" t="s">
+        <v>360</v>
+      </c>
+      <c r="H175" t="s">
+        <v>201</v>
+      </c>
+      <c r="I175" t="s">
+        <v>297</v>
+      </c>
+      <c r="J175" t="s">
+        <v>206</v>
+      </c>
+      <c r="K175" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="176" spans="1:17">
+      <c r="A176" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="F176" t="s">
+        <v>174</v>
+      </c>
+      <c r="G176" t="s">
+        <v>186</v>
+      </c>
+      <c r="H176" t="s">
+        <v>201</v>
+      </c>
+      <c r="I176" t="s">
+        <v>298</v>
+      </c>
+      <c r="J176" t="s">
+        <v>206</v>
+      </c>
+      <c r="K176" t="s">
+        <v>217</v>
+      </c>
+      <c r="L176" t="s">
+        <v>452</v>
+      </c>
+      <c r="N176" s="10" t="s">
+        <v>530</v>
+      </c>
+      <c r="P176" t="s">
+        <v>529</v>
+      </c>
+      <c r="Q176" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="177" spans="1:17">
+      <c r="A177" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="F177" t="s">
+        <v>471</v>
+      </c>
+      <c r="G177" t="s">
+        <v>186</v>
+      </c>
+      <c r="H177" t="s">
+        <v>201</v>
+      </c>
+      <c r="I177" t="s">
+        <v>41</v>
+      </c>
+      <c r="J177" t="s">
+        <v>206</v>
+      </c>
+      <c r="K177" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="178" spans="1:17">
+      <c r="A178" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="H178" t="s">
+        <v>201</v>
+      </c>
+      <c r="I178" t="s">
+        <v>211</v>
+      </c>
+      <c r="J178" t="s">
+        <v>206</v>
+      </c>
+      <c r="K178" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="179" spans="1:17">
+      <c r="A179" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="H179" t="s">
+        <v>201</v>
+      </c>
+      <c r="I179" t="s">
+        <v>299</v>
+      </c>
+      <c r="J179" t="s">
+        <v>206</v>
+      </c>
+      <c r="K179" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="180" spans="1:17">
+      <c r="A180" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="Q180" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="181" spans="1:17">
+      <c r="A181" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="Q181" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="182" spans="1:17">
+      <c r="A182" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q182" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="183" spans="1:17" ht="17" customHeight="1">
+      <c r="A183" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B183" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F175" t="s">
+      <c r="C183" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="D183" t="s">
+        <v>467</v>
+      </c>
+      <c r="E183" t="s">
+        <v>50</v>
+      </c>
+      <c r="F183" t="s">
+        <v>185</v>
+      </c>
+      <c r="G183" t="s">
+        <v>186</v>
+      </c>
+      <c r="H183" t="s">
+        <v>201</v>
+      </c>
+      <c r="I183" t="s">
+        <v>300</v>
+      </c>
+      <c r="J183" t="s">
+        <v>206</v>
+      </c>
+      <c r="K183" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="184" spans="1:17">
+      <c r="A184" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F184" t="s">
         <v>183</v>
       </c>
-      <c r="G175" t="s">
+      <c r="G184" t="s">
         <v>186</v>
       </c>
-      <c r="H175" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="176" spans="1:17">
-      <c r="A176" s="5" t="s">
+      <c r="H184" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="185" spans="1:17">
+      <c r="A185" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B176" s="5" t="s">
+      <c r="B185" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E176" t="s">
+      <c r="E185" t="s">
         <v>52</v>
       </c>
-      <c r="H176" t="s">
+      <c r="H185" t="s">
         <v>200</v>
       </c>
-      <c r="I176" t="s">
+      <c r="I185" t="s">
         <v>301</v>
       </c>
-      <c r="J176" t="s">
+      <c r="J185" t="s">
         <v>209</v>
       </c>
-      <c r="K176" t="s">
+      <c r="K185" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="177" spans="1:11">
-      <c r="A177" s="5" t="s">
+    <row r="186" spans="1:17">
+      <c r="A186" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B177" s="5" t="s">
+      <c r="B186" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="H177" t="s">
+      <c r="H186" t="s">
         <v>200</v>
       </c>
-      <c r="I177" t="s">
+      <c r="I186" t="s">
         <v>208</v>
       </c>
-      <c r="J177" t="s">
+      <c r="J186" t="s">
         <v>209</v>
       </c>
-      <c r="K177" t="s">
+      <c r="K186" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="178" spans="1:11">
-      <c r="A178" s="5" t="s">
+    <row r="187" spans="1:17">
+      <c r="A187" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B178" s="5" t="s">
+      <c r="B187" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C178" s="6" t="s">
+      <c r="C187" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="D178" t="s">
+      <c r="D187" t="s">
         <v>45</v>
       </c>
-      <c r="E178" t="s">
+      <c r="E187" t="s">
         <v>52</v>
       </c>
-      <c r="F178" t="s">
+      <c r="F187" t="s">
         <v>161</v>
       </c>
-      <c r="G178" t="s">
+      <c r="G187" t="s">
         <v>173</v>
       </c>
-      <c r="H178" t="s">
+      <c r="H187" t="s">
         <v>200</v>
       </c>
-      <c r="I178" t="s">
+      <c r="I187" t="s">
         <v>45</v>
       </c>
-      <c r="J178" t="s">
+      <c r="J187" t="s">
         <v>209</v>
       </c>
-      <c r="K178" t="s">
+      <c r="K187" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="179" spans="1:11">
-      <c r="A179" s="5" t="s">
+    <row r="188" spans="1:17">
+      <c r="A188" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B179" s="5" t="s">
+      <c r="B188" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C179" s="6" t="s">
+      <c r="C188" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="D179" t="s">
+      <c r="D188" t="s">
         <v>91</v>
       </c>
-      <c r="E179" t="s">
+      <c r="E188" t="s">
         <v>52</v>
       </c>
-      <c r="H179" t="s">
+      <c r="H188" t="s">
         <v>200</v>
       </c>
-      <c r="I179" t="s">
+      <c r="I188" t="s">
         <v>302</v>
       </c>
-      <c r="J179" t="s">
+      <c r="J188" t="s">
         <v>209</v>
       </c>
-      <c r="K179" t="s">
+      <c r="K188" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="180" spans="1:11">
-      <c r="A180" s="5" t="s">
+    <row r="189" spans="1:17">
+      <c r="A189" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B180" s="5" t="s">
+      <c r="B189" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C180" s="6" t="s">
+      <c r="C189" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="D180" t="s">
+      <c r="D189" t="s">
         <v>47</v>
       </c>
-      <c r="E180" t="s">
+      <c r="E189" t="s">
         <v>52</v>
       </c>
-      <c r="H180" t="s">
+      <c r="H189" t="s">
         <v>200</v>
       </c>
-      <c r="I180" t="s">
+      <c r="I189" t="s">
         <v>303</v>
       </c>
-      <c r="J180" t="s">
+      <c r="J189" t="s">
         <v>209</v>
       </c>
-      <c r="K180" t="s">
+      <c r="K189" t="s">
         <v>214</v>
       </c>
     </row>

--- a/benefit_indexing.xlsx
+++ b/benefit_indexing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/BryanMak/Documents/RawClaimMCR-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6A52DF-937E-6143-BB97-0D6008D3FC67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1197D49A-2257-7D42-AA2C-C66BA9AB8428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-18340" yWindow="-21600" windowWidth="38400" windowHeight="21600" xr2:uid="{A0161F8B-45E3-674F-BD1A-B040F75BC5F2}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{A0161F8B-45E3-674F-BD1A-B040F75BC5F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="663">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1486" uniqueCount="666">
   <si>
     <t>Daily Room &amp; Board</t>
   </si>
@@ -2025,6 +2025,15 @@
   </si>
   <si>
     <t xml:space="preserve">Prescription Benefit </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dental Treatment </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physiotherapy </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplementary Major Medical </t>
   </si>
 </sst>
 </file>
@@ -2459,7 +2468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4FDC71E-C596-D04E-840B-E0EAE83F6708}">
-  <dimension ref="A1:S189"/>
+  <dimension ref="A1:S190"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
@@ -4340,62 +4349,14 @@
       </c>
     </row>
     <row r="71" spans="1:19">
-      <c r="A71" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D71" t="s">
-        <v>67</v>
-      </c>
-      <c r="E71" t="s">
-        <v>49</v>
-      </c>
-      <c r="F71" t="s">
-        <v>143</v>
-      </c>
-      <c r="G71" t="s">
-        <v>148</v>
-      </c>
-      <c r="H71" t="s">
-        <v>201</v>
-      </c>
-      <c r="I71" t="s">
-        <v>253</v>
-      </c>
-      <c r="J71" t="s">
-        <v>204</v>
-      </c>
-      <c r="K71" t="s">
-        <v>218</v>
-      </c>
-      <c r="L71" t="s">
-        <v>312</v>
+      <c r="A71" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="M71" t="s">
-        <v>379</v>
-      </c>
-      <c r="N71" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="O71" s="10" t="s">
-        <v>434</v>
-      </c>
-      <c r="P71" t="s">
-        <v>520</v>
-      </c>
-      <c r="Q71" t="s">
-        <v>520</v>
-      </c>
-      <c r="R71" t="s">
-        <v>586</v>
-      </c>
-      <c r="S71" t="s">
-        <v>587</v>
+        <v>665</v>
       </c>
     </row>
     <row r="72" spans="1:19">
@@ -4405,8 +4366,17 @@
       <c r="B72" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="C72" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D72" t="s">
+        <v>67</v>
+      </c>
+      <c r="E72" t="s">
+        <v>49</v>
+      </c>
       <c r="F72" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G72" t="s">
         <v>148</v>
@@ -4415,7 +4385,7 @@
         <v>201</v>
       </c>
       <c r="I72" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J72" t="s">
         <v>204</v>
@@ -4424,13 +4394,28 @@
         <v>218</v>
       </c>
       <c r="L72" t="s">
-        <v>450</v>
+        <v>312</v>
       </c>
       <c r="M72" t="s">
-        <v>384</v>
-      </c>
-      <c r="O72" t="s">
-        <v>495</v>
+        <v>379</v>
+      </c>
+      <c r="N72" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="O72" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="P72" t="s">
+        <v>520</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>520</v>
+      </c>
+      <c r="R72" t="s">
+        <v>586</v>
+      </c>
+      <c r="S72" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="73" spans="1:19">
@@ -4440,11 +4425,17 @@
       <c r="B73" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="F73" t="s">
+        <v>144</v>
+      </c>
+      <c r="G73" t="s">
+        <v>148</v>
+      </c>
       <c r="H73" t="s">
         <v>201</v>
       </c>
       <c r="I73" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J73" t="s">
         <v>204</v>
@@ -4452,8 +4443,14 @@
       <c r="K73" t="s">
         <v>218</v>
       </c>
+      <c r="L73" t="s">
+        <v>450</v>
+      </c>
+      <c r="M73" t="s">
+        <v>384</v>
+      </c>
       <c r="O73" t="s">
-        <v>520</v>
+        <v>495</v>
       </c>
     </row>
     <row r="74" spans="1:19">
@@ -4467,7 +4464,7 @@
         <v>201</v>
       </c>
       <c r="I74" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J74" t="s">
         <v>204</v>
@@ -4475,6 +4472,9 @@
       <c r="K74" t="s">
         <v>218</v>
       </c>
+      <c r="O74" t="s">
+        <v>520</v>
+      </c>
     </row>
     <row r="75" spans="1:19">
       <c r="A75" s="3" t="s">
@@ -4487,7 +4487,7 @@
         <v>201</v>
       </c>
       <c r="I75" t="s">
-        <v>350</v>
+        <v>256</v>
       </c>
       <c r="J75" t="s">
         <v>204</v>
@@ -4507,7 +4507,7 @@
         <v>201</v>
       </c>
       <c r="I76" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J76" t="s">
         <v>204</v>
@@ -4527,7 +4527,7 @@
         <v>201</v>
       </c>
       <c r="I77" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="J77" t="s">
         <v>204</v>
@@ -4547,7 +4547,7 @@
         <v>201</v>
       </c>
       <c r="I78" t="s">
-        <v>257</v>
+        <v>354</v>
       </c>
       <c r="J78" t="s">
         <v>204</v>
@@ -4567,7 +4567,7 @@
         <v>201</v>
       </c>
       <c r="I79" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J79" t="s">
         <v>204</v>
@@ -4587,7 +4587,7 @@
         <v>201</v>
       </c>
       <c r="I80" t="s">
-        <v>413</v>
+        <v>258</v>
       </c>
       <c r="J80" t="s">
         <v>204</v>
@@ -4607,7 +4607,7 @@
         <v>201</v>
       </c>
       <c r="I81" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J81" t="s">
         <v>204</v>
@@ -4627,7 +4627,7 @@
         <v>201</v>
       </c>
       <c r="I82" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="J82" t="s">
         <v>204</v>
@@ -4647,7 +4647,7 @@
         <v>201</v>
       </c>
       <c r="I83" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J83" t="s">
         <v>204</v>
@@ -4663,8 +4663,11 @@
       <c r="B84" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="H84" t="s">
+        <v>201</v>
+      </c>
       <c r="I84" t="s">
-        <v>483</v>
+        <v>415</v>
       </c>
       <c r="J84" t="s">
         <v>204</v>
@@ -4681,7 +4684,7 @@
         <v>25</v>
       </c>
       <c r="I85" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="J85" t="s">
         <v>204</v>
@@ -4697,11 +4700,8 @@
       <c r="B86" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H86" t="s">
-        <v>201</v>
-      </c>
       <c r="I86" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="J86" t="s">
         <v>204</v>
@@ -4721,7 +4721,7 @@
         <v>201</v>
       </c>
       <c r="I87" t="s">
-        <v>349</v>
+        <v>479</v>
       </c>
       <c r="J87" t="s">
         <v>204</v>
@@ -4741,7 +4741,7 @@
         <v>201</v>
       </c>
       <c r="I88" t="s">
-        <v>257</v>
+        <v>349</v>
       </c>
       <c r="J88" t="s">
         <v>204</v>
@@ -4755,25 +4755,13 @@
         <v>24</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D89" t="s">
-        <v>68</v>
-      </c>
-      <c r="E89" t="s">
-        <v>49</v>
-      </c>
-      <c r="F89" t="s">
-        <v>145</v>
-      </c>
-      <c r="G89" t="s">
-        <v>148</v>
+        <v>25</v>
       </c>
       <c r="H89" t="s">
         <v>201</v>
+      </c>
+      <c r="I89" t="s">
+        <v>257</v>
       </c>
       <c r="J89" t="s">
         <v>204</v>
@@ -4781,30 +4769,6 @@
       <c r="K89" t="s">
         <v>218</v>
       </c>
-      <c r="L89" t="s">
-        <v>314</v>
-      </c>
-      <c r="M89" t="s">
-        <v>246</v>
-      </c>
-      <c r="N89" s="10" t="s">
-        <v>423</v>
-      </c>
-      <c r="O89" s="10" t="s">
-        <v>442</v>
-      </c>
-      <c r="P89" t="s">
-        <v>521</v>
-      </c>
-      <c r="Q89" t="s">
-        <v>546</v>
-      </c>
-      <c r="R89" t="s">
-        <v>606</v>
-      </c>
-      <c r="S89" t="s">
-        <v>607</v>
-      </c>
     </row>
     <row r="90" spans="1:19">
       <c r="A90" s="3" t="s">
@@ -4813,11 +4777,23 @@
       <c r="B90" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="C90" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D90" t="s">
+        <v>68</v>
+      </c>
+      <c r="E90" t="s">
+        <v>49</v>
+      </c>
+      <c r="F90" t="s">
+        <v>145</v>
+      </c>
+      <c r="G90" t="s">
+        <v>148</v>
+      </c>
       <c r="H90" t="s">
         <v>201</v>
-      </c>
-      <c r="I90" t="s">
-        <v>259</v>
       </c>
       <c r="J90" t="s">
         <v>204</v>
@@ -4825,8 +4801,29 @@
       <c r="K90" t="s">
         <v>218</v>
       </c>
-      <c r="O90" t="s">
-        <v>498</v>
+      <c r="L90" t="s">
+        <v>314</v>
+      </c>
+      <c r="M90" t="s">
+        <v>246</v>
+      </c>
+      <c r="N90" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="O90" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="P90" t="s">
+        <v>521</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>546</v>
+      </c>
+      <c r="R90" t="s">
+        <v>606</v>
+      </c>
+      <c r="S90" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="91" spans="1:19">
@@ -4836,17 +4833,11 @@
       <c r="B91" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F91" t="s">
-        <v>146</v>
-      </c>
-      <c r="G91" t="s">
-        <v>148</v>
-      </c>
       <c r="H91" t="s">
         <v>201</v>
       </c>
       <c r="I91" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J91" t="s">
         <v>204</v>
@@ -4855,7 +4846,7 @@
         <v>218</v>
       </c>
       <c r="O91" t="s">
-        <v>521</v>
+        <v>498</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -4865,11 +4856,17 @@
       <c r="B92" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="F92" t="s">
+        <v>146</v>
+      </c>
+      <c r="G92" t="s">
+        <v>148</v>
+      </c>
       <c r="H92" t="s">
         <v>201</v>
       </c>
       <c r="I92" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J92" t="s">
         <v>204</v>
@@ -4877,6 +4874,9 @@
       <c r="K92" t="s">
         <v>218</v>
       </c>
+      <c r="O92" t="s">
+        <v>521</v>
+      </c>
     </row>
     <row r="93" spans="1:19">
       <c r="A93" s="3" t="s">
@@ -4889,7 +4889,7 @@
         <v>201</v>
       </c>
       <c r="I93" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J93" t="s">
         <v>204</v>
@@ -4909,7 +4909,7 @@
         <v>201</v>
       </c>
       <c r="I94" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J94" t="s">
         <v>204</v>
@@ -4929,7 +4929,7 @@
         <v>201</v>
       </c>
       <c r="I95" t="s">
-        <v>480</v>
+        <v>263</v>
       </c>
       <c r="J95" t="s">
         <v>204</v>
@@ -4949,7 +4949,7 @@
         <v>201</v>
       </c>
       <c r="I96" t="s">
-        <v>352</v>
+        <v>480</v>
       </c>
       <c r="J96" t="s">
         <v>204</v>
@@ -4969,7 +4969,7 @@
         <v>201</v>
       </c>
       <c r="I97" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J97" t="s">
         <v>204</v>
@@ -4989,7 +4989,7 @@
         <v>201</v>
       </c>
       <c r="I98" t="s">
-        <v>417</v>
+        <v>355</v>
       </c>
       <c r="J98" t="s">
         <v>204</v>
@@ -5009,7 +5009,7 @@
         <v>201</v>
       </c>
       <c r="I99" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="J99" t="s">
         <v>204</v>
@@ -5029,7 +5029,7 @@
         <v>201</v>
       </c>
       <c r="I100" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J100" t="s">
         <v>204</v>
@@ -5049,7 +5049,7 @@
         <v>201</v>
       </c>
       <c r="I101" t="s">
-        <v>478</v>
+        <v>419</v>
       </c>
       <c r="J101" t="s">
         <v>204</v>
@@ -5069,7 +5069,7 @@
         <v>201</v>
       </c>
       <c r="I102" t="s">
-        <v>420</v>
+        <v>478</v>
       </c>
       <c r="J102" t="s">
         <v>204</v>
@@ -5085,8 +5085,11 @@
       <c r="B103" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="H103" t="s">
+        <v>201</v>
+      </c>
       <c r="I103" t="s">
-        <v>482</v>
+        <v>420</v>
       </c>
       <c r="J103" t="s">
         <v>204</v>
@@ -5103,7 +5106,7 @@
         <v>26</v>
       </c>
       <c r="I104" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="J104" t="s">
         <v>204</v>
@@ -5120,7 +5123,7 @@
         <v>26</v>
       </c>
       <c r="I105" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="J105" t="s">
         <v>204</v>
@@ -5136,11 +5139,8 @@
       <c r="B106" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H106" t="s">
-        <v>201</v>
-      </c>
       <c r="I106" t="s">
-        <v>205</v>
+        <v>486</v>
       </c>
       <c r="J106" t="s">
         <v>204</v>
@@ -5160,7 +5160,7 @@
         <v>201</v>
       </c>
       <c r="I107" t="s">
-        <v>279</v>
+        <v>205</v>
       </c>
       <c r="J107" t="s">
         <v>204</v>
@@ -5180,7 +5180,7 @@
         <v>201</v>
       </c>
       <c r="I108" t="s">
-        <v>477</v>
+        <v>279</v>
       </c>
       <c r="J108" t="s">
         <v>204</v>
@@ -5194,28 +5194,13 @@
         <v>24</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C109" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D109" t="s">
-        <v>69</v>
-      </c>
-      <c r="E109" t="s">
-        <v>49</v>
-      </c>
-      <c r="F109" t="s">
-        <v>151</v>
-      </c>
-      <c r="G109" t="s">
-        <v>148</v>
+        <v>26</v>
       </c>
       <c r="H109" t="s">
         <v>201</v>
       </c>
       <c r="I109" t="s">
-        <v>264</v>
+        <v>477</v>
       </c>
       <c r="J109" t="s">
         <v>204</v>
@@ -5223,24 +5208,6 @@
       <c r="K109" t="s">
         <v>218</v>
       </c>
-      <c r="L109" t="s">
-        <v>331</v>
-      </c>
-      <c r="M109" t="s">
-        <v>266</v>
-      </c>
-      <c r="O109" s="10" t="s">
-        <v>443</v>
-      </c>
-      <c r="P109" t="s">
-        <v>524</v>
-      </c>
-      <c r="R109" t="s">
-        <v>590</v>
-      </c>
-      <c r="S109" t="s">
-        <v>591</v>
-      </c>
     </row>
     <row r="110" spans="1:19">
       <c r="A110" s="3" t="s">
@@ -5249,11 +5216,26 @@
       <c r="B110" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="C110" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D110" t="s">
+        <v>69</v>
+      </c>
+      <c r="E110" t="s">
+        <v>49</v>
+      </c>
+      <c r="F110" t="s">
+        <v>151</v>
+      </c>
+      <c r="G110" t="s">
+        <v>148</v>
+      </c>
       <c r="H110" t="s">
         <v>201</v>
       </c>
       <c r="I110" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J110" t="s">
         <v>204</v>
@@ -5261,8 +5243,23 @@
       <c r="K110" t="s">
         <v>218</v>
       </c>
-      <c r="O110" t="s">
-        <v>541</v>
+      <c r="L110" t="s">
+        <v>331</v>
+      </c>
+      <c r="M110" t="s">
+        <v>266</v>
+      </c>
+      <c r="O110" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="P110" t="s">
+        <v>524</v>
+      </c>
+      <c r="R110" t="s">
+        <v>590</v>
+      </c>
+      <c r="S110" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="111" spans="1:19">
@@ -5272,17 +5269,11 @@
       <c r="B111" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F111" t="s">
-        <v>152</v>
-      </c>
-      <c r="G111" t="s">
-        <v>148</v>
-      </c>
       <c r="H111" t="s">
         <v>201</v>
       </c>
       <c r="I111" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J111" t="s">
         <v>204</v>
@@ -5290,16 +5281,22 @@
       <c r="K111" t="s">
         <v>218</v>
       </c>
+      <c r="M111" t="s">
+        <v>664</v>
+      </c>
+      <c r="O111" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="112" spans="1:19">
       <c r="A112" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>501</v>
+        <v>27</v>
       </c>
       <c r="F112" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="G112" t="s">
         <v>148</v>
@@ -5308,7 +5305,7 @@
         <v>201</v>
       </c>
       <c r="I112" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J112" t="s">
         <v>204</v>
@@ -5316,34 +5313,16 @@
       <c r="K112" t="s">
         <v>218</v>
       </c>
-      <c r="N112" s="10" t="s">
-        <v>427</v>
-      </c>
-      <c r="O112" t="s">
-        <v>500</v>
-      </c>
-      <c r="Q112" t="s">
-        <v>569</v>
-      </c>
     </row>
     <row r="113" spans="1:19">
       <c r="A113" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C113" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D113" t="s">
-        <v>84</v>
-      </c>
-      <c r="E113" t="s">
-        <v>49</v>
+        <v>501</v>
       </c>
       <c r="F113" t="s">
-        <v>149</v>
+        <v>189</v>
       </c>
       <c r="G113" t="s">
         <v>148</v>
@@ -5352,7 +5331,7 @@
         <v>201</v>
       </c>
       <c r="I113" t="s">
-        <v>84</v>
+        <v>267</v>
       </c>
       <c r="J113" t="s">
         <v>204</v>
@@ -5360,20 +5339,14 @@
       <c r="K113" t="s">
         <v>218</v>
       </c>
-      <c r="L113" t="s">
-        <v>318</v>
-      </c>
-      <c r="M113" t="s">
-        <v>374</v>
-      </c>
-      <c r="P113" t="s">
-        <v>523</v>
-      </c>
-      <c r="R113" t="s">
-        <v>624</v>
-      </c>
-      <c r="S113" t="s">
-        <v>625</v>
+      <c r="N113" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="O113" t="s">
+        <v>500</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="114" spans="1:19">
@@ -5383,11 +5356,47 @@
       <c r="B114" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="C114" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D114" t="s">
+        <v>84</v>
+      </c>
+      <c r="E114" t="s">
+        <v>49</v>
+      </c>
+      <c r="F114" t="s">
+        <v>149</v>
+      </c>
+      <c r="G114" t="s">
+        <v>148</v>
+      </c>
+      <c r="H114" t="s">
+        <v>201</v>
+      </c>
+      <c r="I114" t="s">
+        <v>84</v>
+      </c>
+      <c r="J114" t="s">
+        <v>204</v>
+      </c>
+      <c r="K114" t="s">
+        <v>218</v>
+      </c>
       <c r="L114" t="s">
-        <v>464</v>
+        <v>318</v>
       </c>
       <c r="M114" t="s">
-        <v>660</v>
+        <v>374</v>
+      </c>
+      <c r="P114" t="s">
+        <v>523</v>
+      </c>
+      <c r="R114" t="s">
+        <v>624</v>
+      </c>
+      <c r="S114" t="s">
+        <v>625</v>
       </c>
     </row>
     <row r="115" spans="1:19">
@@ -5395,58 +5404,13 @@
         <v>24</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="C115" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D115" t="s">
-        <v>72</v>
-      </c>
-      <c r="E115" t="s">
-        <v>49</v>
-      </c>
-      <c r="F115" t="s">
-        <v>150</v>
-      </c>
-      <c r="G115" t="s">
-        <v>148</v>
-      </c>
-      <c r="H115" t="s">
-        <v>201</v>
-      </c>
-      <c r="I115" t="s">
-        <v>268</v>
-      </c>
-      <c r="J115" t="s">
-        <v>204</v>
-      </c>
-      <c r="K115" t="s">
-        <v>218</v>
+        <v>28</v>
       </c>
       <c r="L115" t="s">
-        <v>311</v>
+        <v>464</v>
       </c>
       <c r="M115" t="s">
-        <v>371</v>
-      </c>
-      <c r="N115" s="10" t="s">
-        <v>425</v>
-      </c>
-      <c r="O115" s="10" t="s">
-        <v>436</v>
-      </c>
-      <c r="P115" t="s">
-        <v>522</v>
-      </c>
-      <c r="Q115" t="s">
-        <v>548</v>
-      </c>
-      <c r="R115" t="s">
-        <v>588</v>
-      </c>
-      <c r="S115" t="s">
-        <v>589</v>
+        <v>660</v>
       </c>
     </row>
     <row r="116" spans="1:19">
@@ -5457,16 +5421,16 @@
         <v>535</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D116" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E116" t="s">
         <v>49</v>
       </c>
       <c r="F116" t="s">
-        <v>194</v>
+        <v>150</v>
       </c>
       <c r="G116" t="s">
         <v>148</v>
@@ -5475,7 +5439,7 @@
         <v>201</v>
       </c>
       <c r="I116" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J116" t="s">
         <v>204</v>
@@ -5484,16 +5448,28 @@
         <v>218</v>
       </c>
       <c r="L116" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="M116" t="s">
-        <v>372</v>
-      </c>
-      <c r="O116" t="s">
-        <v>494</v>
+        <v>371</v>
+      </c>
+      <c r="N116" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="O116" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="P116" t="s">
+        <v>522</v>
       </c>
       <c r="Q116" t="s">
-        <v>566</v>
+        <v>548</v>
+      </c>
+      <c r="R116" t="s">
+        <v>588</v>
+      </c>
+      <c r="S116" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="117" spans="1:19">
@@ -5503,8 +5479,17 @@
       <c r="B117" s="3" t="s">
         <v>535</v>
       </c>
+      <c r="C117" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D117" t="s">
+        <v>73</v>
+      </c>
+      <c r="E117" t="s">
+        <v>49</v>
+      </c>
       <c r="F117" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="G117" t="s">
         <v>148</v>
@@ -5513,7 +5498,7 @@
         <v>201</v>
       </c>
       <c r="I117" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J117" t="s">
         <v>204</v>
@@ -5522,16 +5507,16 @@
         <v>218</v>
       </c>
       <c r="L117" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M117" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O117" t="s">
-        <v>536</v>
+        <v>494</v>
       </c>
       <c r="Q117" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
     </row>
     <row r="118" spans="1:19">
@@ -5542,7 +5527,7 @@
         <v>535</v>
       </c>
       <c r="F118" t="s">
-        <v>347</v>
+        <v>187</v>
       </c>
       <c r="G118" t="s">
         <v>148</v>
@@ -5551,13 +5536,25 @@
         <v>201</v>
       </c>
       <c r="I118" t="s">
-        <v>490</v>
+        <v>270</v>
+      </c>
+      <c r="J118" t="s">
+        <v>204</v>
+      </c>
+      <c r="K118" t="s">
+        <v>218</v>
       </c>
       <c r="L118" t="s">
-        <v>460</v>
+        <v>321</v>
       </c>
       <c r="M118" t="s">
-        <v>383</v>
+        <v>373</v>
+      </c>
+      <c r="O118" t="s">
+        <v>536</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>571</v>
       </c>
     </row>
     <row r="119" spans="1:19">
@@ -5568,7 +5565,7 @@
         <v>535</v>
       </c>
       <c r="F119" t="s">
-        <v>190</v>
+        <v>347</v>
       </c>
       <c r="G119" t="s">
         <v>148</v>
@@ -5577,16 +5574,13 @@
         <v>201</v>
       </c>
       <c r="I119" t="s">
-        <v>271</v>
-      </c>
-      <c r="J119" t="s">
-        <v>204</v>
-      </c>
-      <c r="K119" t="s">
-        <v>218</v>
+        <v>490</v>
+      </c>
+      <c r="L119" t="s">
+        <v>460</v>
       </c>
       <c r="M119" t="s">
-        <v>410</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:19">
@@ -5597,7 +5591,7 @@
         <v>535</v>
       </c>
       <c r="F120" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G120" t="s">
         <v>148</v>
@@ -5606,7 +5600,7 @@
         <v>201</v>
       </c>
       <c r="I120" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J120" t="s">
         <v>204</v>
@@ -5614,6 +5608,9 @@
       <c r="K120" t="s">
         <v>218</v>
       </c>
+      <c r="M120" t="s">
+        <v>410</v>
+      </c>
     </row>
     <row r="121" spans="1:19">
       <c r="A121" s="3" t="s">
@@ -5623,7 +5620,7 @@
         <v>535</v>
       </c>
       <c r="F121" t="s">
-        <v>358</v>
+        <v>193</v>
       </c>
       <c r="G121" t="s">
         <v>148</v>
@@ -5632,7 +5629,13 @@
         <v>201</v>
       </c>
       <c r="I121" t="s">
-        <v>491</v>
+        <v>272</v>
+      </c>
+      <c r="J121" t="s">
+        <v>204</v>
+      </c>
+      <c r="K121" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="122" spans="1:19">
@@ -5643,7 +5646,7 @@
         <v>535</v>
       </c>
       <c r="F122" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="G122" t="s">
         <v>148</v>
@@ -5652,7 +5655,7 @@
         <v>201</v>
       </c>
       <c r="I122" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="123" spans="1:19">
@@ -5663,7 +5666,7 @@
         <v>535</v>
       </c>
       <c r="F123" t="s">
-        <v>573</v>
+        <v>361</v>
       </c>
       <c r="G123" t="s">
         <v>148</v>
@@ -5672,7 +5675,7 @@
         <v>201</v>
       </c>
       <c r="I123" t="s">
-        <v>73</v>
+        <v>492</v>
       </c>
     </row>
     <row r="124" spans="1:19">
@@ -5683,11 +5686,17 @@
         <v>535</v>
       </c>
       <c r="F124" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="G124" t="s">
         <v>148</v>
       </c>
+      <c r="H124" t="s">
+        <v>201</v>
+      </c>
+      <c r="I124" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="125" spans="1:19">
       <c r="A125" s="3" t="s">
@@ -5696,49 +5705,19 @@
       <c r="B125" s="3" t="s">
         <v>535</v>
       </c>
+      <c r="F125" t="s">
+        <v>574</v>
+      </c>
+      <c r="G125" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="126" spans="1:19">
       <c r="A126" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C126" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D126" t="s">
-        <v>74</v>
-      </c>
-      <c r="E126" t="s">
-        <v>49</v>
-      </c>
-      <c r="F126" t="s">
-        <v>197</v>
-      </c>
-      <c r="G126" t="s">
-        <v>148</v>
-      </c>
-      <c r="H126" t="s">
-        <v>201</v>
-      </c>
-      <c r="I126" t="s">
-        <v>273</v>
-      </c>
-      <c r="J126" t="s">
-        <v>204</v>
-      </c>
-      <c r="K126" t="s">
-        <v>218</v>
-      </c>
-      <c r="M126" t="s">
-        <v>382</v>
-      </c>
-      <c r="N126" s="10" t="s">
-        <v>432</v>
-      </c>
-      <c r="O126" s="10" t="s">
-        <v>448</v>
+        <v>535</v>
       </c>
     </row>
     <row r="127" spans="1:19">
@@ -5748,12 +5727,41 @@
       <c r="B127" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="C127" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D127" t="s">
+        <v>74</v>
+      </c>
+      <c r="E127" t="s">
+        <v>49</v>
+      </c>
+      <c r="F127" t="s">
+        <v>197</v>
+      </c>
+      <c r="G127" t="s">
+        <v>148</v>
+      </c>
+      <c r="H127" t="s">
+        <v>201</v>
+      </c>
+      <c r="I127" t="s">
+        <v>273</v>
+      </c>
+      <c r="J127" t="s">
+        <v>204</v>
+      </c>
+      <c r="K127" t="s">
+        <v>218</v>
+      </c>
       <c r="M127" t="s">
-        <v>659</v>
-      </c>
-      <c r="N127" s="10"/>
-      <c r="O127" t="s">
-        <v>197</v>
+        <v>382</v>
+      </c>
+      <c r="N127" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="O127" s="10" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="128" spans="1:19">
@@ -5761,28 +5769,14 @@
         <v>24</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C128" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D128" t="s">
-        <v>92</v>
-      </c>
-      <c r="E128" t="s">
-        <v>49</v>
-      </c>
-      <c r="H128" t="s">
-        <v>201</v>
-      </c>
-      <c r="I128" t="s">
-        <v>274</v>
-      </c>
-      <c r="J128" t="s">
-        <v>204</v>
-      </c>
-      <c r="K128" t="s">
-        <v>218</v>
+        <v>29</v>
+      </c>
+      <c r="M128" t="s">
+        <v>659</v>
+      </c>
+      <c r="N128" s="10"/>
+      <c r="O128" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="129" spans="1:19">
@@ -5790,7 +5784,28 @@
         <v>24</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D129" t="s">
+        <v>92</v>
+      </c>
+      <c r="E129" t="s">
+        <v>49</v>
+      </c>
+      <c r="H129" t="s">
+        <v>201</v>
+      </c>
+      <c r="I129" t="s">
+        <v>274</v>
+      </c>
+      <c r="J129" t="s">
+        <v>204</v>
+      </c>
+      <c r="K129" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="130" spans="1:19">
@@ -5798,58 +5813,7 @@
         <v>24</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C130" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D130" t="s">
-        <v>71</v>
-      </c>
-      <c r="E130" t="s">
-        <v>49</v>
-      </c>
-      <c r="F130" t="s">
-        <v>154</v>
-      </c>
-      <c r="G130" t="s">
-        <v>148</v>
-      </c>
-      <c r="H130" t="s">
-        <v>201</v>
-      </c>
-      <c r="I130" t="s">
-        <v>275</v>
-      </c>
-      <c r="J130" t="s">
-        <v>204</v>
-      </c>
-      <c r="K130" t="s">
-        <v>218</v>
-      </c>
-      <c r="L130" t="s">
-        <v>315</v>
-      </c>
-      <c r="M130" t="s">
-        <v>385</v>
-      </c>
-      <c r="N130" s="10" t="s">
-        <v>424</v>
-      </c>
-      <c r="O130" s="10" t="s">
-        <v>438</v>
-      </c>
-      <c r="P130" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q130" t="s">
-        <v>551</v>
-      </c>
-      <c r="R130" t="s">
-        <v>608</v>
-      </c>
-      <c r="S130" t="s">
-        <v>609</v>
+        <v>31</v>
       </c>
     </row>
     <row r="131" spans="1:19">
@@ -5859,8 +5823,17 @@
       <c r="B131" s="3" t="s">
         <v>32</v>
       </c>
+      <c r="C131" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D131" t="s">
+        <v>71</v>
+      </c>
+      <c r="E131" t="s">
+        <v>49</v>
+      </c>
       <c r="F131" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G131" t="s">
         <v>148</v>
@@ -5869,7 +5842,7 @@
         <v>201</v>
       </c>
       <c r="I131" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J131" t="s">
         <v>204</v>
@@ -5878,13 +5851,28 @@
         <v>218</v>
       </c>
       <c r="L131" t="s">
-        <v>449</v>
+        <v>315</v>
       </c>
       <c r="M131" t="s">
-        <v>640</v>
-      </c>
-      <c r="O131" t="s">
-        <v>502</v>
+        <v>385</v>
+      </c>
+      <c r="N131" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="O131" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="P131" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>551</v>
+      </c>
+      <c r="R131" t="s">
+        <v>608</v>
+      </c>
+      <c r="S131" t="s">
+        <v>609</v>
       </c>
     </row>
     <row r="132" spans="1:19">
@@ -5895,7 +5883,7 @@
         <v>32</v>
       </c>
       <c r="F132" t="s">
-        <v>363</v>
+        <v>155</v>
       </c>
       <c r="G132" t="s">
         <v>148</v>
@@ -5903,8 +5891,23 @@
       <c r="H132" t="s">
         <v>201</v>
       </c>
+      <c r="I132" t="s">
+        <v>276</v>
+      </c>
+      <c r="J132" t="s">
+        <v>204</v>
+      </c>
+      <c r="K132" t="s">
+        <v>218</v>
+      </c>
+      <c r="L132" t="s">
+        <v>449</v>
+      </c>
+      <c r="M132" t="s">
+        <v>640</v>
+      </c>
       <c r="O132" t="s">
-        <v>538</v>
+        <v>502</v>
       </c>
     </row>
     <row r="133" spans="1:19">
@@ -5912,19 +5915,10 @@
         <v>24</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C133" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D133" t="s">
-        <v>70</v>
-      </c>
-      <c r="E133" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="F133" t="s">
-        <v>153</v>
+        <v>363</v>
       </c>
       <c r="G133" t="s">
         <v>148</v>
@@ -5932,29 +5926,8 @@
       <c r="H133" t="s">
         <v>201</v>
       </c>
-      <c r="I133" t="s">
-        <v>277</v>
-      </c>
-      <c r="J133" t="s">
-        <v>204</v>
-      </c>
-      <c r="K133" t="s">
-        <v>218</v>
-      </c>
-      <c r="L133" t="s">
-        <v>334</v>
-      </c>
-      <c r="M133" t="s">
-        <v>381</v>
-      </c>
       <c r="O133" t="s">
-        <v>540</v>
-      </c>
-      <c r="P133" t="s">
-        <v>543</v>
-      </c>
-      <c r="Q133" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
     </row>
     <row r="134" spans="1:19">
@@ -5964,17 +5937,17 @@
       <c r="B134" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C134" s="6">
-        <v>253</v>
+      <c r="C134" s="6" t="s">
+        <v>119</v>
       </c>
       <c r="D134" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E134" t="s">
         <v>49</v>
       </c>
       <c r="F134" t="s">
-        <v>220</v>
+        <v>153</v>
       </c>
       <c r="G134" t="s">
         <v>148</v>
@@ -5983,7 +5956,7 @@
         <v>201</v>
       </c>
       <c r="I134" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J134" t="s">
         <v>204</v>
@@ -5991,8 +5964,20 @@
       <c r="K134" t="s">
         <v>218</v>
       </c>
+      <c r="L134" t="s">
+        <v>334</v>
+      </c>
       <c r="M134" t="s">
-        <v>662</v>
+        <v>381</v>
+      </c>
+      <c r="O134" t="s">
+        <v>540</v>
+      </c>
+      <c r="P134" t="s">
+        <v>543</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="135" spans="1:19">
@@ -6002,8 +5987,17 @@
       <c r="B135" s="3" t="s">
         <v>33</v>
       </c>
+      <c r="C135" s="6">
+        <v>253</v>
+      </c>
+      <c r="D135" t="s">
+        <v>90</v>
+      </c>
+      <c r="E135" t="s">
+        <v>49</v>
+      </c>
       <c r="F135" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="G135" t="s">
         <v>148</v>
@@ -6012,7 +6006,16 @@
         <v>201</v>
       </c>
       <c r="I135" t="s">
-        <v>481</v>
+        <v>278</v>
+      </c>
+      <c r="J135" t="s">
+        <v>204</v>
+      </c>
+      <c r="K135" t="s">
+        <v>218</v>
+      </c>
+      <c r="M135" t="s">
+        <v>662</v>
       </c>
     </row>
     <row r="136" spans="1:19">
@@ -6020,19 +6023,10 @@
         <v>24</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C136" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="D136" t="s">
-        <v>34</v>
-      </c>
-      <c r="E136" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="F136" t="s">
-        <v>475</v>
+        <v>196</v>
       </c>
       <c r="G136" t="s">
         <v>148</v>
@@ -6041,28 +6035,7 @@
         <v>201</v>
       </c>
       <c r="I136" t="s">
-        <v>34</v>
-      </c>
-      <c r="J136" t="s">
-        <v>204</v>
-      </c>
-      <c r="K136" t="s">
-        <v>213</v>
-      </c>
-      <c r="L136" t="s">
-        <v>463</v>
-      </c>
-      <c r="M136" t="s">
-        <v>34</v>
-      </c>
-      <c r="N136" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="O136" s="10" t="s">
-        <v>447</v>
-      </c>
-      <c r="Q136" t="s">
-        <v>570</v>
+        <v>481</v>
       </c>
     </row>
     <row r="137" spans="1:19">
@@ -6072,8 +6045,47 @@
       <c r="B137" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="C137" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D137" t="s">
+        <v>34</v>
+      </c>
+      <c r="E137" t="s">
+        <v>49</v>
+      </c>
+      <c r="F137" t="s">
+        <v>475</v>
+      </c>
+      <c r="G137" t="s">
+        <v>148</v>
+      </c>
+      <c r="H137" t="s">
+        <v>201</v>
+      </c>
+      <c r="I137" t="s">
+        <v>34</v>
+      </c>
+      <c r="J137" t="s">
+        <v>204</v>
+      </c>
+      <c r="K137" t="s">
+        <v>213</v>
+      </c>
+      <c r="L137" t="s">
+        <v>463</v>
+      </c>
+      <c r="M137" t="s">
+        <v>34</v>
+      </c>
+      <c r="N137" s="10" t="s">
+        <v>34</v>
+      </c>
       <c r="O137" s="10" t="s">
-        <v>542</v>
+        <v>447</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="138" spans="1:19">
@@ -6081,55 +6093,10 @@
         <v>24</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C138" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="D138" t="s">
-        <v>89</v>
-      </c>
-      <c r="E138" t="s">
-        <v>49</v>
-      </c>
-      <c r="F138" t="s">
-        <v>195</v>
-      </c>
-      <c r="G138" t="s">
-        <v>148</v>
-      </c>
-      <c r="H138" t="s">
-        <v>201</v>
-      </c>
-      <c r="I138" t="s">
-        <v>280</v>
-      </c>
-      <c r="J138" t="s">
-        <v>204</v>
-      </c>
-      <c r="K138" t="s">
-        <v>213</v>
-      </c>
-      <c r="L138" t="s">
-        <v>462</v>
-      </c>
-      <c r="M138" t="s">
-        <v>380</v>
-      </c>
-      <c r="N138" s="10" t="s">
-        <v>577</v>
-      </c>
-      <c r="O138" t="s">
-        <v>507</v>
-      </c>
-      <c r="Q138" t="s">
-        <v>539</v>
-      </c>
-      <c r="R138" t="s">
-        <v>616</v>
-      </c>
-      <c r="S138" t="s">
-        <v>617</v>
+        <v>34</v>
+      </c>
+      <c r="O138" s="10" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="139" spans="1:19">
@@ -6139,8 +6106,17 @@
       <c r="B139" s="3" t="s">
         <v>35</v>
       </c>
+      <c r="C139" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D139" t="s">
+        <v>89</v>
+      </c>
+      <c r="E139" t="s">
+        <v>49</v>
+      </c>
       <c r="F139" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G139" t="s">
         <v>148</v>
@@ -6149,16 +6125,34 @@
         <v>201</v>
       </c>
       <c r="I139" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J139" t="s">
         <v>204</v>
       </c>
       <c r="K139" t="s">
-        <v>218</v>
+        <v>213</v>
+      </c>
+      <c r="L139" t="s">
+        <v>462</v>
+      </c>
+      <c r="M139" t="s">
+        <v>380</v>
+      </c>
+      <c r="N139" s="10" t="s">
+        <v>577</v>
       </c>
       <c r="O139" t="s">
+        <v>507</v>
+      </c>
+      <c r="Q139" t="s">
         <v>539</v>
+      </c>
+      <c r="R139" t="s">
+        <v>616</v>
+      </c>
+      <c r="S139" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="140" spans="1:19">
@@ -6169,7 +6163,7 @@
         <v>35</v>
       </c>
       <c r="F140" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G140" t="s">
         <v>148</v>
@@ -6177,40 +6171,34 @@
       <c r="H140" t="s">
         <v>201</v>
       </c>
+      <c r="I140" t="s">
+        <v>281</v>
+      </c>
+      <c r="J140" t="s">
+        <v>204</v>
+      </c>
+      <c r="K140" t="s">
+        <v>218</v>
+      </c>
+      <c r="O140" t="s">
+        <v>539</v>
+      </c>
     </row>
     <row r="141" spans="1:19">
       <c r="A141" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C141" s="6">
-        <v>311</v>
-      </c>
-      <c r="D141" t="s">
-        <v>75</v>
-      </c>
-      <c r="E141" t="s">
-        <v>51</v>
-      </c>
-      <c r="I141" t="s">
-        <v>282</v>
-      </c>
-      <c r="J141" t="s">
-        <v>204</v>
-      </c>
-      <c r="K141" t="s">
-        <v>218</v>
-      </c>
-      <c r="M141" t="s">
-        <v>376</v>
-      </c>
-      <c r="O141" s="10" t="s">
-        <v>437</v>
-      </c>
-      <c r="P141" t="s">
-        <v>525</v>
+        <v>35</v>
+      </c>
+      <c r="F141" t="s">
+        <v>192</v>
+      </c>
+      <c r="G141" t="s">
+        <v>148</v>
+      </c>
+      <c r="H141" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="142" spans="1:19">
@@ -6221,16 +6209,31 @@
         <v>36</v>
       </c>
       <c r="C142" s="6">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D142" t="s">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="E142" t="s">
         <v>51</v>
       </c>
-      <c r="O142" t="s">
-        <v>565</v>
+      <c r="I142" t="s">
+        <v>282</v>
+      </c>
+      <c r="J142" t="s">
+        <v>204</v>
+      </c>
+      <c r="K142" t="s">
+        <v>218</v>
+      </c>
+      <c r="M142" t="s">
+        <v>376</v>
+      </c>
+      <c r="O142" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="P142" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="143" spans="1:19">
@@ -6238,19 +6241,19 @@
         <v>24</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="C143" s="6" t="s">
-        <v>305</v>
+        <v>36</v>
+      </c>
+      <c r="C143" s="6">
+        <v>312</v>
       </c>
       <c r="D143" t="s">
-        <v>304</v>
+        <v>135</v>
       </c>
       <c r="E143" t="s">
-        <v>49</v>
-      </c>
-      <c r="M143" t="s">
-        <v>375</v>
+        <v>51</v>
+      </c>
+      <c r="O143" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="144" spans="1:19">
@@ -6260,8 +6263,17 @@
       <c r="B144" s="3" t="s">
         <v>304</v>
       </c>
+      <c r="C144" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="D144" t="s">
+        <v>304</v>
+      </c>
+      <c r="E144" t="s">
+        <v>49</v>
+      </c>
       <c r="M144" t="s">
-        <v>650</v>
+        <v>375</v>
       </c>
     </row>
     <row r="145" spans="1:19">
@@ -6269,10 +6281,10 @@
         <v>24</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="M145" t="s">
-        <v>378</v>
+        <v>650</v>
       </c>
     </row>
     <row r="146" spans="1:19">
@@ -6280,37 +6292,10 @@
         <v>24</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C146" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="D146" t="s">
-        <v>306</v>
-      </c>
-      <c r="E146" t="s">
-        <v>49</v>
-      </c>
-      <c r="F146" t="s">
-        <v>188</v>
-      </c>
-      <c r="G146" t="s">
-        <v>148</v>
-      </c>
-      <c r="H146" t="s">
-        <v>201</v>
-      </c>
-      <c r="I146" t="s">
-        <v>353</v>
-      </c>
-      <c r="J146" t="s">
-        <v>204</v>
-      </c>
-      <c r="K146" t="s">
-        <v>218</v>
+        <v>377</v>
       </c>
       <c r="M146" t="s">
-        <v>641</v>
+        <v>378</v>
       </c>
     </row>
     <row r="147" spans="1:19">
@@ -6318,10 +6303,19 @@
         <v>24</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>345</v>
+        <v>308</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="D147" t="s">
+        <v>306</v>
+      </c>
+      <c r="E147" t="s">
+        <v>49</v>
       </c>
       <c r="F147" t="s">
-        <v>344</v>
+        <v>188</v>
       </c>
       <c r="G147" t="s">
         <v>148</v>
@@ -6329,8 +6323,17 @@
       <c r="H147" t="s">
         <v>201</v>
       </c>
-      <c r="L147" t="s">
-        <v>330</v>
+      <c r="I147" t="s">
+        <v>353</v>
+      </c>
+      <c r="J147" t="s">
+        <v>204</v>
+      </c>
+      <c r="K147" t="s">
+        <v>218</v>
+      </c>
+      <c r="M147" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="148" spans="1:19">
@@ -6338,10 +6341,10 @@
         <v>24</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>455</v>
+        <v>345</v>
       </c>
       <c r="F148" t="s">
-        <v>472</v>
+        <v>344</v>
       </c>
       <c r="G148" t="s">
         <v>148</v>
@@ -6349,17 +6352,8 @@
       <c r="H148" t="s">
         <v>201</v>
       </c>
-      <c r="I148" t="s">
-        <v>488</v>
-      </c>
-      <c r="J148" t="s">
-        <v>204</v>
-      </c>
-      <c r="K148" t="s">
-        <v>218</v>
-      </c>
       <c r="L148" t="s">
-        <v>456</v>
+        <v>330</v>
       </c>
     </row>
     <row r="149" spans="1:19">
@@ -6367,13 +6361,19 @@
         <v>24</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>406</v>
+        <v>455</v>
+      </c>
+      <c r="F149" t="s">
+        <v>472</v>
+      </c>
+      <c r="G149" t="s">
+        <v>148</v>
       </c>
       <c r="H149" t="s">
         <v>201</v>
       </c>
       <c r="I149" t="s">
-        <v>283</v>
+        <v>488</v>
       </c>
       <c r="J149" t="s">
         <v>204</v>
@@ -6381,20 +6381,8 @@
       <c r="K149" t="s">
         <v>218</v>
       </c>
-      <c r="M149" t="s">
-        <v>287</v>
-      </c>
-      <c r="N149" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="O149" s="10" t="s">
-        <v>435</v>
-      </c>
-      <c r="R149" t="s">
-        <v>604</v>
-      </c>
-      <c r="S149" t="s">
-        <v>605</v>
+      <c r="L149" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="150" spans="1:19">
@@ -6404,9 +6392,32 @@
       <c r="B150" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="N150" s="10"/>
+      <c r="H150" t="s">
+        <v>201</v>
+      </c>
+      <c r="I150" t="s">
+        <v>283</v>
+      </c>
+      <c r="J150" t="s">
+        <v>204</v>
+      </c>
+      <c r="K150" t="s">
+        <v>218</v>
+      </c>
+      <c r="M150" t="s">
+        <v>287</v>
+      </c>
+      <c r="N150" s="10" t="s">
+        <v>287</v>
+      </c>
       <c r="O150" s="10" t="s">
-        <v>537</v>
+        <v>435</v>
+      </c>
+      <c r="R150" t="s">
+        <v>604</v>
+      </c>
+      <c r="S150" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="151" spans="1:19">
@@ -6414,10 +6425,14 @@
         <v>24</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="M151" t="s">
-        <v>38</v>
+        <v>663</v>
+      </c>
+      <c r="N151" s="10"/>
+      <c r="O151" s="10" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="152" spans="1:19">
@@ -6425,13 +6440,10 @@
         <v>24</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="R152" t="s">
-        <v>602</v>
-      </c>
-      <c r="S152" t="s">
-        <v>603</v>
+        <v>407</v>
+      </c>
+      <c r="M152" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="153" spans="1:19">
@@ -6439,16 +6451,13 @@
         <v>24</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="F153" t="s">
-        <v>470</v>
-      </c>
-      <c r="G153" t="s">
-        <v>148</v>
-      </c>
-      <c r="H153" t="s">
-        <v>201</v>
+        <v>601</v>
+      </c>
+      <c r="R153" t="s">
+        <v>602</v>
+      </c>
+      <c r="S153" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="154" spans="1:19">
@@ -6456,10 +6465,16 @@
         <v>24</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>534</v>
-      </c>
-      <c r="O154" t="s">
-        <v>533</v>
+        <v>469</v>
+      </c>
+      <c r="F154" t="s">
+        <v>470</v>
+      </c>
+      <c r="G154" t="s">
+        <v>148</v>
+      </c>
+      <c r="H154" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="155" spans="1:19">
@@ -6467,10 +6482,10 @@
         <v>24</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="Q155" t="s">
-        <v>550</v>
+        <v>534</v>
+      </c>
+      <c r="O155" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="156" spans="1:19">
@@ -6478,54 +6493,21 @@
         <v>24</v>
       </c>
       <c r="B156" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="Q156" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="157" spans="1:19">
+      <c r="A157" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B157" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="M156" t="s">
+      <c r="M157" t="s">
         <v>647</v>
-      </c>
-    </row>
-    <row r="157" spans="1:19">
-      <c r="A157" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B157" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C157" s="6">
-        <v>511</v>
-      </c>
-      <c r="D157" t="s">
-        <v>81</v>
-      </c>
-      <c r="E157" t="s">
-        <v>50</v>
-      </c>
-      <c r="F157" t="s">
-        <v>181</v>
-      </c>
-      <c r="G157" t="s">
-        <v>186</v>
-      </c>
-      <c r="H157" t="s">
-        <v>201</v>
-      </c>
-      <c r="J157" t="s">
-        <v>206</v>
-      </c>
-      <c r="K157" t="s">
-        <v>217</v>
-      </c>
-      <c r="L157" t="s">
-        <v>313</v>
-      </c>
-      <c r="N157" s="10" t="s">
-        <v>575</v>
-      </c>
-      <c r="P157" t="s">
-        <v>526</v>
-      </c>
-      <c r="Q157" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="158" spans="1:19">
@@ -6535,8 +6517,17 @@
       <c r="B158" s="4" t="s">
         <v>38</v>
       </c>
+      <c r="C158" s="6">
+        <v>511</v>
+      </c>
+      <c r="D158" t="s">
+        <v>81</v>
+      </c>
+      <c r="E158" t="s">
+        <v>50</v>
+      </c>
       <c r="F158" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G158" t="s">
         <v>186</v>
@@ -6544,9 +6535,6 @@
       <c r="H158" t="s">
         <v>201</v>
       </c>
-      <c r="I158" t="s">
-        <v>284</v>
-      </c>
       <c r="J158" t="s">
         <v>206</v>
       </c>
@@ -6554,7 +6542,16 @@
         <v>217</v>
       </c>
       <c r="L158" t="s">
-        <v>451</v>
+        <v>313</v>
+      </c>
+      <c r="N158" s="10" t="s">
+        <v>575</v>
+      </c>
+      <c r="P158" t="s">
+        <v>526</v>
+      </c>
+      <c r="Q158" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="159" spans="1:19">
@@ -6564,17 +6561,8 @@
       <c r="B159" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C159" s="6">
-        <v>513</v>
-      </c>
-      <c r="D159" t="s">
-        <v>82</v>
-      </c>
-      <c r="E159" t="s">
-        <v>50</v>
-      </c>
       <c r="F159" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G159" t="s">
         <v>186</v>
@@ -6583,7 +6571,7 @@
         <v>201</v>
       </c>
       <c r="I159" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J159" t="s">
         <v>206</v>
@@ -6592,7 +6580,7 @@
         <v>217</v>
       </c>
       <c r="L159" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="160" spans="1:19">
@@ -6602,8 +6590,17 @@
       <c r="B160" s="4" t="s">
         <v>38</v>
       </c>
+      <c r="C160" s="6">
+        <v>513</v>
+      </c>
+      <c r="D160" t="s">
+        <v>82</v>
+      </c>
+      <c r="E160" t="s">
+        <v>50</v>
+      </c>
       <c r="F160" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G160" t="s">
         <v>186</v>
@@ -6612,7 +6609,7 @@
         <v>201</v>
       </c>
       <c r="I160" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J160" t="s">
         <v>206</v>
@@ -6621,7 +6618,7 @@
         <v>217</v>
       </c>
       <c r="L160" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="161" spans="1:17">
@@ -6632,7 +6629,7 @@
         <v>38</v>
       </c>
       <c r="F161" t="s">
-        <v>37</v>
+        <v>176</v>
       </c>
       <c r="G161" t="s">
         <v>186</v>
@@ -6641,16 +6638,16 @@
         <v>201</v>
       </c>
       <c r="I161" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J161" t="s">
         <v>206</v>
       </c>
       <c r="K161" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="L161" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="162" spans="1:17">
@@ -6661,7 +6658,7 @@
         <v>38</v>
       </c>
       <c r="F162" t="s">
-        <v>182</v>
+        <v>37</v>
       </c>
       <c r="G162" t="s">
         <v>186</v>
@@ -6670,19 +6667,19 @@
         <v>201</v>
       </c>
       <c r="I162" t="s">
-        <v>38</v>
+        <v>287</v>
       </c>
       <c r="J162" t="s">
         <v>206</v>
       </c>
       <c r="K162" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="L162" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="163" spans="1:17" ht="17" customHeight="1">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17">
       <c r="A163" s="4" t="s">
         <v>37</v>
       </c>
@@ -6690,7 +6687,7 @@
         <v>38</v>
       </c>
       <c r="F163" t="s">
-        <v>357</v>
+        <v>182</v>
       </c>
       <c r="G163" t="s">
         <v>186</v>
@@ -6699,13 +6696,16 @@
         <v>201</v>
       </c>
       <c r="I163" t="s">
-        <v>288</v>
+        <v>38</v>
       </c>
       <c r="J163" t="s">
         <v>206</v>
       </c>
       <c r="K163" t="s">
         <v>217</v>
+      </c>
+      <c r="L163" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="164" spans="1:17" ht="17" customHeight="1">
@@ -6716,7 +6716,7 @@
         <v>38</v>
       </c>
       <c r="F164" t="s">
-        <v>473</v>
+        <v>357</v>
       </c>
       <c r="G164" t="s">
         <v>186</v>
@@ -6725,7 +6725,7 @@
         <v>201</v>
       </c>
       <c r="I164" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J164" t="s">
         <v>206</v>
@@ -6742,7 +6742,7 @@
         <v>38</v>
       </c>
       <c r="F165" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="G165" t="s">
         <v>186</v>
@@ -6751,7 +6751,7 @@
         <v>201</v>
       </c>
       <c r="I165" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J165" t="s">
         <v>206</v>
@@ -6767,11 +6767,17 @@
       <c r="B166" s="4" t="s">
         <v>38</v>
       </c>
+      <c r="F166" t="s">
+        <v>474</v>
+      </c>
+      <c r="G166" t="s">
+        <v>186</v>
+      </c>
       <c r="H166" t="s">
         <v>201</v>
       </c>
       <c r="I166" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J166" t="s">
         <v>206</v>
@@ -6787,17 +6793,11 @@
       <c r="B167" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F167" t="s">
-        <v>180</v>
-      </c>
-      <c r="G167" t="s">
-        <v>186</v>
-      </c>
       <c r="H167" t="s">
         <v>201</v>
       </c>
       <c r="I167" t="s">
-        <v>487</v>
+        <v>291</v>
       </c>
       <c r="J167" t="s">
         <v>206</v>
@@ -6814,7 +6814,7 @@
         <v>38</v>
       </c>
       <c r="F168" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G168" t="s">
         <v>186</v>
@@ -6823,7 +6823,7 @@
         <v>201</v>
       </c>
       <c r="I168" t="s">
-        <v>212</v>
+        <v>487</v>
       </c>
       <c r="J168" t="s">
         <v>206</v>
@@ -6839,11 +6839,17 @@
       <c r="B169" s="4" t="s">
         <v>38</v>
       </c>
+      <c r="F169" t="s">
+        <v>184</v>
+      </c>
+      <c r="G169" t="s">
+        <v>186</v>
+      </c>
       <c r="H169" t="s">
         <v>201</v>
       </c>
       <c r="I169" t="s">
-        <v>489</v>
+        <v>212</v>
       </c>
       <c r="J169" t="s">
         <v>206</v>
@@ -6863,7 +6869,7 @@
         <v>201</v>
       </c>
       <c r="I170" t="s">
-        <v>292</v>
+        <v>489</v>
       </c>
       <c r="J170" t="s">
         <v>206</v>
@@ -6872,42 +6878,24 @@
         <v>217</v>
       </c>
     </row>
-    <row r="171" spans="1:17">
+    <row r="171" spans="1:17" ht="17" customHeight="1">
       <c r="A171" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F171" t="s">
-        <v>175</v>
-      </c>
-      <c r="G171" t="s">
-        <v>186</v>
+        <v>38</v>
       </c>
       <c r="H171" t="s">
         <v>201</v>
       </c>
       <c r="I171" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J171" t="s">
         <v>206</v>
       </c>
       <c r="K171" t="s">
         <v>217</v>
-      </c>
-      <c r="L171" t="s">
-        <v>458</v>
-      </c>
-      <c r="N171" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="P171" t="s">
-        <v>527</v>
-      </c>
-      <c r="Q171" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="172" spans="1:17">
@@ -6918,7 +6906,7 @@
         <v>39</v>
       </c>
       <c r="F172" t="s">
-        <v>362</v>
+        <v>175</v>
       </c>
       <c r="G172" t="s">
         <v>186</v>
@@ -6927,13 +6915,25 @@
         <v>201</v>
       </c>
       <c r="I172" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J172" t="s">
         <v>206</v>
       </c>
       <c r="K172" t="s">
         <v>217</v>
+      </c>
+      <c r="L172" t="s">
+        <v>458</v>
+      </c>
+      <c r="N172" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="P172" t="s">
+        <v>527</v>
+      </c>
+      <c r="Q172" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="173" spans="1:17">
@@ -6943,11 +6943,17 @@
       <c r="B173" s="4" t="s">
         <v>39</v>
       </c>
+      <c r="F173" t="s">
+        <v>362</v>
+      </c>
+      <c r="G173" t="s">
+        <v>186</v>
+      </c>
       <c r="H173" t="s">
         <v>201</v>
       </c>
       <c r="I173" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J173" t="s">
         <v>206</v>
@@ -6961,37 +6967,19 @@
         <v>37</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F174" t="s">
-        <v>178</v>
-      </c>
-      <c r="G174" t="s">
-        <v>186</v>
+        <v>39</v>
       </c>
       <c r="H174" t="s">
         <v>201</v>
       </c>
       <c r="I174" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J174" t="s">
         <v>206</v>
       </c>
       <c r="K174" t="s">
         <v>217</v>
-      </c>
-      <c r="L174" t="s">
-        <v>459</v>
-      </c>
-      <c r="N174" s="10" t="s">
-        <v>578</v>
-      </c>
-      <c r="P174" t="s">
-        <v>528</v>
-      </c>
-      <c r="Q174" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="175" spans="1:17">
@@ -7002,19 +6990,34 @@
         <v>40</v>
       </c>
       <c r="F175" t="s">
-        <v>360</v>
+        <v>178</v>
+      </c>
+      <c r="G175" t="s">
+        <v>186</v>
       </c>
       <c r="H175" t="s">
         <v>201</v>
       </c>
       <c r="I175" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J175" t="s">
         <v>206</v>
       </c>
       <c r="K175" t="s">
         <v>217</v>
+      </c>
+      <c r="L175" t="s">
+        <v>459</v>
+      </c>
+      <c r="N175" s="10" t="s">
+        <v>578</v>
+      </c>
+      <c r="P175" t="s">
+        <v>528</v>
+      </c>
+      <c r="Q175" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="176" spans="1:17">
@@ -7022,37 +7025,22 @@
         <v>37</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>530</v>
+        <v>40</v>
       </c>
       <c r="F176" t="s">
-        <v>174</v>
-      </c>
-      <c r="G176" t="s">
-        <v>186</v>
+        <v>360</v>
       </c>
       <c r="H176" t="s">
         <v>201</v>
       </c>
       <c r="I176" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J176" t="s">
         <v>206</v>
       </c>
       <c r="K176" t="s">
         <v>217</v>
-      </c>
-      <c r="L176" t="s">
-        <v>452</v>
-      </c>
-      <c r="N176" s="10" t="s">
-        <v>530</v>
-      </c>
-      <c r="P176" t="s">
-        <v>529</v>
-      </c>
-      <c r="Q176" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="177" spans="1:17">
@@ -7063,7 +7051,7 @@
         <v>530</v>
       </c>
       <c r="F177" t="s">
-        <v>471</v>
+        <v>174</v>
       </c>
       <c r="G177" t="s">
         <v>186</v>
@@ -7072,13 +7060,25 @@
         <v>201</v>
       </c>
       <c r="I177" t="s">
-        <v>41</v>
+        <v>298</v>
       </c>
       <c r="J177" t="s">
         <v>206</v>
       </c>
       <c r="K177" t="s">
         <v>217</v>
+      </c>
+      <c r="L177" t="s">
+        <v>452</v>
+      </c>
+      <c r="N177" s="10" t="s">
+        <v>530</v>
+      </c>
+      <c r="P177" t="s">
+        <v>529</v>
+      </c>
+      <c r="Q177" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="178" spans="1:17">
@@ -7088,11 +7088,17 @@
       <c r="B178" s="4" t="s">
         <v>530</v>
       </c>
+      <c r="F178" t="s">
+        <v>471</v>
+      </c>
+      <c r="G178" t="s">
+        <v>186</v>
+      </c>
       <c r="H178" t="s">
         <v>201</v>
       </c>
       <c r="I178" t="s">
-        <v>211</v>
+        <v>41</v>
       </c>
       <c r="J178" t="s">
         <v>206</v>
@@ -7112,7 +7118,7 @@
         <v>201</v>
       </c>
       <c r="I179" t="s">
-        <v>299</v>
+        <v>211</v>
       </c>
       <c r="J179" t="s">
         <v>206</v>
@@ -7126,10 +7132,19 @@
         <v>37</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>555</v>
-      </c>
-      <c r="Q180" t="s">
-        <v>557</v>
+        <v>530</v>
+      </c>
+      <c r="H180" t="s">
+        <v>201</v>
+      </c>
+      <c r="I180" t="s">
+        <v>299</v>
+      </c>
+      <c r="J180" t="s">
+        <v>206</v>
+      </c>
+      <c r="K180" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="181" spans="1:17">
@@ -7137,10 +7152,10 @@
         <v>37</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="Q181" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="182" spans="1:17">
@@ -7148,56 +7163,41 @@
         <v>37</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>291</v>
+        <v>556</v>
       </c>
       <c r="Q182" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="183" spans="1:17" ht="17" customHeight="1">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="183" spans="1:17">
       <c r="A183" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C183" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="D183" t="s">
-        <v>467</v>
-      </c>
-      <c r="E183" t="s">
-        <v>50</v>
-      </c>
-      <c r="F183" t="s">
-        <v>185</v>
-      </c>
-      <c r="G183" t="s">
-        <v>186</v>
-      </c>
-      <c r="H183" t="s">
-        <v>201</v>
-      </c>
-      <c r="I183" t="s">
-        <v>300</v>
-      </c>
-      <c r="J183" t="s">
-        <v>206</v>
-      </c>
-      <c r="K183" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="184" spans="1:17">
+        <v>291</v>
+      </c>
+      <c r="Q183" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="184" spans="1:17" ht="17" customHeight="1">
       <c r="A184" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B184" s="4" t="s">
         <v>42</v>
       </c>
+      <c r="C184" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="D184" t="s">
+        <v>467</v>
+      </c>
+      <c r="E184" t="s">
+        <v>50</v>
+      </c>
       <c r="F184" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G184" t="s">
         <v>186</v>
@@ -7205,28 +7205,31 @@
       <c r="H184" t="s">
         <v>201</v>
       </c>
+      <c r="I184" t="s">
+        <v>300</v>
+      </c>
+      <c r="J184" t="s">
+        <v>206</v>
+      </c>
+      <c r="K184" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="185" spans="1:17">
-      <c r="A185" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B185" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E185" t="s">
-        <v>52</v>
+      <c r="A185" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F185" t="s">
+        <v>183</v>
+      </c>
+      <c r="G185" t="s">
+        <v>186</v>
       </c>
       <c r="H185" t="s">
-        <v>200</v>
-      </c>
-      <c r="I185" t="s">
-        <v>301</v>
-      </c>
-      <c r="J185" t="s">
-        <v>209</v>
-      </c>
-      <c r="K185" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
     </row>
     <row r="186" spans="1:17">
@@ -7234,13 +7237,16 @@
         <v>43</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="E186" t="s">
+        <v>52</v>
       </c>
       <c r="H186" t="s">
         <v>200</v>
       </c>
       <c r="I186" t="s">
-        <v>208</v>
+        <v>301</v>
       </c>
       <c r="J186" t="s">
         <v>209</v>
@@ -7256,26 +7262,11 @@
       <c r="B187" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C187" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="D187" t="s">
-        <v>45</v>
-      </c>
-      <c r="E187" t="s">
-        <v>52</v>
-      </c>
-      <c r="F187" t="s">
-        <v>161</v>
-      </c>
-      <c r="G187" t="s">
-        <v>173</v>
-      </c>
       <c r="H187" t="s">
         <v>200</v>
       </c>
       <c r="I187" t="s">
-        <v>45</v>
+        <v>208</v>
       </c>
       <c r="J187" t="s">
         <v>209</v>
@@ -7289,22 +7280,28 @@
         <v>43</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D188" t="s">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="E188" t="s">
         <v>52</v>
       </c>
+      <c r="F188" t="s">
+        <v>161</v>
+      </c>
+      <c r="G188" t="s">
+        <v>173</v>
+      </c>
       <c r="H188" t="s">
         <v>200</v>
       </c>
       <c r="I188" t="s">
-        <v>302</v>
+        <v>45</v>
       </c>
       <c r="J188" t="s">
         <v>209</v>
@@ -7318,13 +7315,13 @@
         <v>43</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D189" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="E189" t="s">
         <v>52</v>
@@ -7333,12 +7330,41 @@
         <v>200</v>
       </c>
       <c r="I189" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J189" t="s">
         <v>209</v>
       </c>
       <c r="K189" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="190" spans="1:17">
+      <c r="A190" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C190" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D190" t="s">
+        <v>47</v>
+      </c>
+      <c r="E190" t="s">
+        <v>52</v>
+      </c>
+      <c r="H190" t="s">
+        <v>200</v>
+      </c>
+      <c r="I190" t="s">
+        <v>303</v>
+      </c>
+      <c r="J190" t="s">
+        <v>209</v>
+      </c>
+      <c r="K190" t="s">
         <v>214</v>
       </c>
     </row>

--- a/benefit_indexing.xlsx
+++ b/benefit_indexing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/BryanMak/Documents/RawClaimMCR-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1197D49A-2257-7D42-AA2C-C66BA9AB8428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A6FA59-D0FD-B442-8EB1-2685129E695F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{A0161F8B-45E3-674F-BD1A-B040F75BC5F2}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="16640" windowHeight="18980" xr2:uid="{A0161F8B-45E3-674F-BD1A-B040F75BC5F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1486" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1486" uniqueCount="667">
   <si>
     <t>Daily Room &amp; Board</t>
   </si>
@@ -2034,6 +2034,9 @@
   </si>
   <si>
     <t xml:space="preserve">Supplementary Major Medical </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating Theater - Minor </t>
   </si>
 </sst>
 </file>
@@ -3583,7 +3586,7 @@
         <v>215</v>
       </c>
       <c r="M38" t="s">
-        <v>645</v>
+        <v>666</v>
       </c>
     </row>
     <row r="39" spans="1:19">

--- a/benefit_indexing.xlsx
+++ b/benefit_indexing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/BryanMak/Documents/RawClaimMCR-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A6FA59-D0FD-B442-8EB1-2685129E695F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9D8EE6-1B1E-2E45-ADAF-37C79128B5FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="16640" windowHeight="18980" xr2:uid="{A0161F8B-45E3-674F-BD1A-B040F75BC5F2}"/>
+    <workbookView xWindow="-18340" yWindow="-21600" windowWidth="38400" windowHeight="21600" xr2:uid="{A0161F8B-45E3-674F-BD1A-B040F75BC5F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1486" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="687">
   <si>
     <t>Daily Room &amp; Board</t>
   </si>
@@ -2037,6 +2037,66 @@
   </si>
   <si>
     <t xml:space="preserve">Operating Theater - Minor </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiropractor Practitioner  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emergency Outpatient Treatment </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Psychiatrist Treatment Benefit </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Psychological Counselling </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Specialist Consultation </t>
+  </si>
+  <si>
+    <t>X-Ray &amp; Laboratory Tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anaesthetist's fee - Complex </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anaesthetist's fee - Inter </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hospital Cash Benefit for Second Claim </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hospital Charges </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating Theater - Inter </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating Theater - Major </t>
+  </si>
+  <si>
+    <t>Operating Theater - Minor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physician's Fee </t>
+  </si>
+  <si>
+    <t>Pre-Hospitalisation / Surgical Operation Benefit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-Hospitalisation / Surgical Operation Benefit </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-Hospitalisation / Surgical Operation Benefit </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private Nursing </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Specialist Fee </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surgeon Fees - Inter </t>
   </si>
 </sst>
 </file>
@@ -2471,7 +2531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4FDC71E-C596-D04E-840B-E0EAE83F6708}">
-  <dimension ref="A1:S190"/>
+  <dimension ref="A1:S203"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
@@ -2739,59 +2799,12 @@
         <v>23</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F6" t="s">
-        <v>162</v>
-      </c>
-      <c r="G6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H6" t="s">
-        <v>200</v>
-      </c>
-      <c r="I6" t="s">
-        <v>223</v>
-      </c>
-      <c r="J6" t="s">
-        <v>203</v>
-      </c>
-      <c r="K6" t="s">
-        <v>215</v>
-      </c>
-      <c r="L6" t="s">
-        <v>327</v>
+        <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>393</v>
-      </c>
-      <c r="N6" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="O6" s="10" t="s">
-        <v>439</v>
-      </c>
-      <c r="P6" t="s">
-        <v>515</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>562</v>
-      </c>
-      <c r="R6" t="s">
-        <v>612</v>
-      </c>
-      <c r="S6" t="s">
-        <v>613</v>
-      </c>
+        <v>680</v>
+      </c>
+      <c r="N6" s="10"/>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="1" t="s">
@@ -2800,9 +2813,17 @@
       <c r="B7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="7"/>
+      <c r="C7" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" t="s">
+        <v>48</v>
+      </c>
       <c r="F7" t="s">
-        <v>493</v>
+        <v>162</v>
       </c>
       <c r="G7" t="s">
         <v>173</v>
@@ -2811,7 +2832,7 @@
         <v>200</v>
       </c>
       <c r="I7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J7" t="s">
         <v>203</v>
@@ -2820,13 +2841,28 @@
         <v>215</v>
       </c>
       <c r="L7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M7" t="s">
-        <v>642</v>
-      </c>
-      <c r="O7" t="s">
-        <v>499</v>
+        <v>393</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="P7" t="s">
+        <v>515</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>562</v>
+      </c>
+      <c r="R7" t="s">
+        <v>612</v>
+      </c>
+      <c r="S7" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -2836,11 +2872,33 @@
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
+      <c r="C8" s="7"/>
+      <c r="F8" t="s">
+        <v>493</v>
+      </c>
+      <c r="G8" t="s">
+        <v>173</v>
+      </c>
+      <c r="H8" t="s">
+        <v>200</v>
+      </c>
+      <c r="I8" t="s">
+        <v>224</v>
+      </c>
+      <c r="J8" t="s">
+        <v>203</v>
+      </c>
+      <c r="K8" t="s">
+        <v>215</v>
+      </c>
       <c r="L8" t="s">
-        <v>336</v>
+        <v>326</v>
+      </c>
+      <c r="M8" t="s">
+        <v>676</v>
+      </c>
+      <c r="O8" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -2848,16 +2906,16 @@
         <v>23</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>48</v>
+        <v>2</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="L9" t="s">
+        <v>336</v>
+      </c>
+      <c r="M9" t="s">
+        <v>642</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -2865,97 +2923,91 @@
         <v>23</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>364</v>
+        <v>126</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>137</v>
+        <v>125</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>126</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F10" t="s">
-        <v>219</v>
-      </c>
-      <c r="G10" t="s">
-        <v>173</v>
-      </c>
-      <c r="I10" t="s">
-        <v>412</v>
-      </c>
-      <c r="J10" t="s">
-        <v>411</v>
-      </c>
-      <c r="K10" t="s">
-        <v>411</v>
-      </c>
-      <c r="L10" t="s">
-        <v>339</v>
-      </c>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>66</v>
+        <v>137</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
       </c>
+      <c r="F11" t="s">
+        <v>219</v>
+      </c>
+      <c r="G11" t="s">
+        <v>173</v>
+      </c>
+      <c r="I11" t="s">
+        <v>412</v>
+      </c>
+      <c r="J11" t="s">
+        <v>411</v>
+      </c>
+      <c r="K11" t="s">
+        <v>411</v>
+      </c>
+      <c r="L11" t="s">
+        <v>339</v>
+      </c>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>140</v>
+        <v>66</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F12" t="s">
-        <v>160</v>
-      </c>
-      <c r="G12" t="s">
-        <v>173</v>
-      </c>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D13" t="s">
-        <v>86</v>
-      </c>
-      <c r="E13" t="s">
+        <v>366</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="M13" t="s">
-        <v>661</v>
-      </c>
-      <c r="N13" s="10" t="s">
-        <v>580</v>
+      <c r="F13" t="s">
+        <v>160</v>
+      </c>
+      <c r="G13" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -2963,34 +3015,22 @@
         <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="E14" t="s">
         <v>48</v>
       </c>
-      <c r="H14" t="s">
-        <v>200</v>
-      </c>
-      <c r="I14" t="s">
-        <v>230</v>
-      </c>
-      <c r="J14" t="s">
-        <v>203</v>
-      </c>
-      <c r="K14" t="s">
-        <v>215</v>
-      </c>
-      <c r="L14" t="s">
-        <v>332</v>
-      </c>
       <c r="M14" t="s">
-        <v>403</v>
+        <v>661</v>
+      </c>
+      <c r="N14" s="10" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3000,11 +3040,20 @@
       <c r="B15" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="C15" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" t="s">
+        <v>48</v>
+      </c>
       <c r="H15" t="s">
         <v>200</v>
       </c>
       <c r="I15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J15" t="s">
         <v>203</v>
@@ -3012,8 +3061,11 @@
       <c r="K15" t="s">
         <v>215</v>
       </c>
+      <c r="L15" t="s">
+        <v>332</v>
+      </c>
       <c r="M15" t="s">
-        <v>651</v>
+        <v>403</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3021,22 +3073,13 @@
         <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D16" t="s">
-        <v>55</v>
-      </c>
-      <c r="E16" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H16" t="s">
         <v>200</v>
       </c>
       <c r="I16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J16" t="s">
         <v>203</v>
@@ -3044,11 +3087,8 @@
       <c r="K16" t="s">
         <v>215</v>
       </c>
-      <c r="L16" t="s">
-        <v>322</v>
-      </c>
       <c r="M16" t="s">
-        <v>402</v>
+        <v>651</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3058,11 +3098,20 @@
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="C17" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" t="s">
+        <v>48</v>
+      </c>
       <c r="H17" t="s">
         <v>200</v>
       </c>
       <c r="I17" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J17" t="s">
         <v>203</v>
@@ -3070,8 +3119,11 @@
       <c r="K17" t="s">
         <v>215</v>
       </c>
+      <c r="L17" t="s">
+        <v>322</v>
+      </c>
       <c r="M17" t="s">
-        <v>656</v>
+        <v>402</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -3079,22 +3131,13 @@
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D18" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="H18" t="s">
         <v>200</v>
       </c>
       <c r="I18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J18" t="s">
         <v>203</v>
@@ -3102,38 +3145,19 @@
       <c r="K18" t="s">
         <v>215</v>
       </c>
-      <c r="L18" t="s">
-        <v>319</v>
-      </c>
       <c r="M18" t="s">
-        <v>404</v>
-      </c>
-      <c r="N18" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="O18" s="10"/>
+        <v>656</v>
+      </c>
     </row>
     <row r="19" spans="1:19">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I19" t="s">
-        <v>235</v>
-      </c>
-      <c r="J19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K19" t="s">
-        <v>215</v>
+        <v>5</v>
       </c>
       <c r="M19" t="s">
-        <v>638</v>
+        <v>686</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -3141,39 +3165,61 @@
         <v>23</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="F20" t="s">
-        <v>157</v>
-      </c>
-      <c r="G20" t="s">
-        <v>173</v>
-      </c>
-      <c r="O20" s="10" t="s">
-        <v>440</v>
-      </c>
-      <c r="P20" t="s">
-        <v>516</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>553</v>
-      </c>
-      <c r="R20" t="s">
-        <v>599</v>
-      </c>
-      <c r="S20" t="s">
-        <v>600</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" t="s">
+        <v>48</v>
+      </c>
+      <c r="H20" t="s">
+        <v>200</v>
+      </c>
+      <c r="I20" t="s">
+        <v>234</v>
+      </c>
+      <c r="J20" t="s">
+        <v>203</v>
+      </c>
+      <c r="K20" t="s">
+        <v>215</v>
+      </c>
+      <c r="L20" t="s">
+        <v>319</v>
+      </c>
+      <c r="M20" t="s">
+        <v>404</v>
+      </c>
+      <c r="N20" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="O20" s="10"/>
     </row>
     <row r="21" spans="1:19">
       <c r="A21" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="O21" t="s">
-        <v>506</v>
+        <v>6</v>
+      </c>
+      <c r="H21" t="s">
+        <v>200</v>
+      </c>
+      <c r="I21" t="s">
+        <v>235</v>
+      </c>
+      <c r="J21" t="s">
+        <v>203</v>
+      </c>
+      <c r="K21" t="s">
+        <v>215</v>
+      </c>
+      <c r="M21" t="s">
+        <v>638</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -3181,22 +3227,28 @@
         <v>23</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D22" t="s">
-        <v>87</v>
-      </c>
-      <c r="E22" t="s">
-        <v>48</v>
-      </c>
-      <c r="M22" t="s">
-        <v>386</v>
-      </c>
-      <c r="N22" s="10" t="s">
-        <v>582</v>
+        <v>596</v>
+      </c>
+      <c r="F22" t="s">
+        <v>157</v>
+      </c>
+      <c r="G22" t="s">
+        <v>173</v>
+      </c>
+      <c r="O22" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="P22" t="s">
+        <v>516</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>553</v>
+      </c>
+      <c r="R22" t="s">
+        <v>599</v>
+      </c>
+      <c r="S22" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -3204,43 +3256,33 @@
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="N23" s="10"/>
+        <v>596</v>
+      </c>
+      <c r="O23" t="s">
+        <v>506</v>
+      </c>
     </row>
     <row r="24" spans="1:19">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D24" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="E24" t="s">
         <v>48</v>
       </c>
-      <c r="H24" t="s">
-        <v>200</v>
-      </c>
-      <c r="I24" t="s">
-        <v>236</v>
-      </c>
-      <c r="J24" t="s">
-        <v>203</v>
-      </c>
-      <c r="K24" t="s">
-        <v>215</v>
-      </c>
-      <c r="L24" t="s">
-        <v>340</v>
-      </c>
       <c r="M24" t="s">
-        <v>387</v>
+        <v>386</v>
+      </c>
+      <c r="N24" s="10" t="s">
+        <v>582</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -3248,24 +3290,25 @@
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M25" t="s">
-        <v>652</v>
-      </c>
+        <v>673</v>
+      </c>
+      <c r="N25" s="10"/>
     </row>
     <row r="26" spans="1:19">
       <c r="A26" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E26" t="s">
         <v>48</v>
@@ -3274,7 +3317,7 @@
         <v>200</v>
       </c>
       <c r="I26" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J26" t="s">
         <v>203</v>
@@ -3283,10 +3326,10 @@
         <v>215</v>
       </c>
       <c r="L26" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="M26" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -3294,10 +3337,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M27" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -3305,13 +3348,13 @@
         <v>23</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D28" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E28" t="s">
         <v>48</v>
@@ -3320,7 +3363,7 @@
         <v>200</v>
       </c>
       <c r="I28" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J28" t="s">
         <v>203</v>
@@ -3329,13 +3372,10 @@
         <v>215</v>
       </c>
       <c r="L28" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="M28" t="s">
-        <v>389</v>
-      </c>
-      <c r="N28" s="10" t="s">
-        <v>430</v>
+        <v>388</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -3343,41 +3383,21 @@
         <v>23</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M29" t="s">
-        <v>644</v>
-      </c>
-      <c r="N29" s="10"/>
+        <v>657</v>
+      </c>
     </row>
     <row r="30" spans="1:19">
       <c r="A30" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="F30" t="s">
-        <v>158</v>
-      </c>
-      <c r="G30" t="s">
-        <v>173</v>
-      </c>
-      <c r="N30" s="10"/>
-      <c r="O30" s="10" t="s">
-        <v>444</v>
-      </c>
-      <c r="P30" t="s">
-        <v>517</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>563</v>
-      </c>
-      <c r="R30" t="s">
-        <v>597</v>
-      </c>
-      <c r="S30" t="s">
-        <v>598</v>
+        <v>9</v>
+      </c>
+      <c r="M30" t="s">
+        <v>674</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -3385,66 +3405,79 @@
         <v>23</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="N31" s="10"/>
-      <c r="O31" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" ht="17" customHeight="1">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" t="s">
+        <v>62</v>
+      </c>
+      <c r="E31" t="s">
+        <v>48</v>
+      </c>
+      <c r="H31" t="s">
+        <v>200</v>
+      </c>
+      <c r="I31" t="s">
+        <v>238</v>
+      </c>
+      <c r="J31" t="s">
+        <v>203</v>
+      </c>
+      <c r="K31" t="s">
+        <v>215</v>
+      </c>
+      <c r="L31" t="s">
+        <v>337</v>
+      </c>
+      <c r="M31" t="s">
+        <v>389</v>
+      </c>
+      <c r="N31" s="10" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19">
       <c r="A32" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D32" t="s">
-        <v>88</v>
-      </c>
-      <c r="E32" t="s">
-        <v>48</v>
-      </c>
-      <c r="N32" s="10" t="s">
-        <v>581</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M32" t="s">
+        <v>644</v>
+      </c>
+      <c r="N32" s="10"/>
     </row>
     <row r="33" spans="1:19">
       <c r="A33" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D33" t="s">
-        <v>59</v>
-      </c>
-      <c r="E33" t="s">
-        <v>48</v>
-      </c>
-      <c r="H33" t="s">
-        <v>200</v>
-      </c>
-      <c r="I33" t="s">
-        <v>239</v>
-      </c>
-      <c r="J33" t="s">
-        <v>203</v>
-      </c>
-      <c r="K33" t="s">
-        <v>215</v>
-      </c>
-      <c r="L33" t="s">
-        <v>333</v>
-      </c>
-      <c r="M33" t="s">
-        <v>395</v>
+        <v>595</v>
+      </c>
+      <c r="F33" t="s">
+        <v>158</v>
+      </c>
+      <c r="G33" t="s">
+        <v>173</v>
+      </c>
+      <c r="N33" s="10"/>
+      <c r="O33" s="10" t="s">
+        <v>444</v>
+      </c>
+      <c r="P33" t="s">
+        <v>517</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>563</v>
+      </c>
+      <c r="R33" t="s">
+        <v>597</v>
+      </c>
+      <c r="S33" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -3452,57 +3485,31 @@
         <v>23</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H34" t="s">
-        <v>200</v>
-      </c>
-      <c r="I34" t="s">
-        <v>240</v>
-      </c>
-      <c r="J34" t="s">
-        <v>203</v>
-      </c>
-      <c r="K34" t="s">
-        <v>215</v>
-      </c>
-      <c r="M34" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19">
+        <v>595</v>
+      </c>
+      <c r="N34" s="10"/>
+      <c r="O34" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="17" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D35" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="E35" t="s">
         <v>48</v>
       </c>
-      <c r="H35" t="s">
-        <v>200</v>
-      </c>
-      <c r="I35" t="s">
-        <v>241</v>
-      </c>
-      <c r="J35" t="s">
-        <v>203</v>
-      </c>
-      <c r="K35" t="s">
-        <v>215</v>
-      </c>
-      <c r="L35" t="s">
-        <v>324</v>
-      </c>
-      <c r="M35" t="s">
-        <v>394</v>
+      <c r="N35" s="10" t="s">
+        <v>581</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -3510,13 +3517,22 @@
         <v>23</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D36" t="s">
+        <v>59</v>
+      </c>
+      <c r="E36" t="s">
+        <v>48</v>
       </c>
       <c r="H36" t="s">
         <v>200</v>
       </c>
       <c r="I36" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="J36" t="s">
         <v>203</v>
@@ -3524,8 +3540,11 @@
       <c r="K36" t="s">
         <v>215</v>
       </c>
+      <c r="L36" t="s">
+        <v>333</v>
+      </c>
       <c r="M36" t="s">
-        <v>658</v>
+        <v>395</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -3533,22 +3552,13 @@
         <v>23</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D37" t="s">
-        <v>61</v>
-      </c>
-      <c r="E37" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="H37" t="s">
         <v>200</v>
       </c>
       <c r="I37" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="J37" t="s">
         <v>203</v>
@@ -3556,14 +3566,8 @@
       <c r="K37" t="s">
         <v>215</v>
       </c>
-      <c r="L37" t="s">
-        <v>338</v>
-      </c>
       <c r="M37" t="s">
-        <v>396</v>
-      </c>
-      <c r="N37" s="10" t="s">
-        <v>428</v>
+        <v>653</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -3571,22 +3575,10 @@
         <v>23</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H38" t="s">
-        <v>200</v>
-      </c>
-      <c r="I38" t="s">
-        <v>244</v>
-      </c>
-      <c r="J38" t="s">
-        <v>203</v>
-      </c>
-      <c r="K38" t="s">
-        <v>215</v>
+        <v>12</v>
       </c>
       <c r="M38" t="s">
-        <v>666</v>
+        <v>678</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -3594,28 +3586,34 @@
         <v>23</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="F39" t="s">
-        <v>159</v>
-      </c>
-      <c r="G39" t="s">
-        <v>173</v>
-      </c>
-      <c r="O39" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="P39" t="s">
-        <v>518</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>159</v>
-      </c>
-      <c r="R39" t="s">
-        <v>592</v>
-      </c>
-      <c r="S39" t="s">
-        <v>593</v>
+        <v>13</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D39" t="s">
+        <v>60</v>
+      </c>
+      <c r="E39" t="s">
+        <v>48</v>
+      </c>
+      <c r="H39" t="s">
+        <v>200</v>
+      </c>
+      <c r="I39" t="s">
+        <v>241</v>
+      </c>
+      <c r="J39" t="s">
+        <v>203</v>
+      </c>
+      <c r="K39" t="s">
+        <v>215</v>
+      </c>
+      <c r="L39" t="s">
+        <v>324</v>
+      </c>
+      <c r="M39" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="40" spans="1:19">
@@ -3623,10 +3621,22 @@
         <v>23</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="O40" t="s">
-        <v>505</v>
+        <v>13</v>
+      </c>
+      <c r="H40" t="s">
+        <v>200</v>
+      </c>
+      <c r="I40" t="s">
+        <v>242</v>
+      </c>
+      <c r="J40" t="s">
+        <v>203</v>
+      </c>
+      <c r="K40" t="s">
+        <v>215</v>
+      </c>
+      <c r="M40" t="s">
+        <v>658</v>
       </c>
     </row>
     <row r="41" spans="1:19">
@@ -3634,55 +3644,10 @@
         <v>23</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D41" t="s">
-        <v>85</v>
-      </c>
-      <c r="E41" t="s">
-        <v>48</v>
-      </c>
-      <c r="F41" t="s">
-        <v>167</v>
-      </c>
-      <c r="G41" t="s">
-        <v>173</v>
-      </c>
-      <c r="H41" t="s">
-        <v>200</v>
-      </c>
-      <c r="I41" t="s">
-        <v>245</v>
-      </c>
-      <c r="J41" t="s">
-        <v>203</v>
-      </c>
-      <c r="K41" t="s">
-        <v>215</v>
-      </c>
-      <c r="L41" t="s">
-        <v>341</v>
+        <v>13</v>
       </c>
       <c r="M41" t="s">
-        <v>401</v>
-      </c>
-      <c r="N41" t="s">
-        <v>637</v>
-      </c>
-      <c r="P41" t="s">
-        <v>519</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>572</v>
-      </c>
-      <c r="R41" t="s">
-        <v>622</v>
-      </c>
-      <c r="S41" t="s">
-        <v>623</v>
+        <v>677</v>
       </c>
     </row>
     <row r="42" spans="1:19">
@@ -3690,19 +3655,22 @@
         <v>23</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F42" t="s">
-        <v>348</v>
-      </c>
-      <c r="G42" t="s">
-        <v>173</v>
+        <v>14</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D42" t="s">
+        <v>61</v>
+      </c>
+      <c r="E42" t="s">
+        <v>48</v>
       </c>
       <c r="H42" t="s">
         <v>200</v>
       </c>
       <c r="I42" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="J42" t="s">
         <v>203</v>
@@ -3710,31 +3678,37 @@
       <c r="K42" t="s">
         <v>215</v>
       </c>
+      <c r="L42" t="s">
+        <v>338</v>
+      </c>
+      <c r="M42" t="s">
+        <v>396</v>
+      </c>
+      <c r="N42" s="10" t="s">
+        <v>428</v>
+      </c>
     </row>
     <row r="43" spans="1:19">
       <c r="A43" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="D43" t="s">
-        <v>465</v>
-      </c>
-      <c r="E43" t="s">
-        <v>48</v>
-      </c>
-      <c r="F43" t="s">
-        <v>164</v>
-      </c>
-      <c r="G43" t="s">
-        <v>173</v>
-      </c>
-      <c r="L43" t="s">
-        <v>343</v>
+        <v>14</v>
+      </c>
+      <c r="H43" t="s">
+        <v>200</v>
+      </c>
+      <c r="I43" t="s">
+        <v>244</v>
+      </c>
+      <c r="J43" t="s">
+        <v>203</v>
+      </c>
+      <c r="K43" t="s">
+        <v>215</v>
+      </c>
+      <c r="M43" t="s">
+        <v>679</v>
       </c>
     </row>
     <row r="44" spans="1:19">
@@ -3742,34 +3716,10 @@
         <v>23</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="D44" t="s">
-        <v>133</v>
-      </c>
-      <c r="E44" t="s">
-        <v>48</v>
-      </c>
-      <c r="F44" t="s">
-        <v>356</v>
-      </c>
-      <c r="G44" t="s">
-        <v>173</v>
-      </c>
-      <c r="H44" t="s">
-        <v>200</v>
-      </c>
-      <c r="I44" t="s">
-        <v>247</v>
-      </c>
-      <c r="J44" t="s">
-        <v>203</v>
-      </c>
-      <c r="K44" t="s">
-        <v>215</v>
+        <v>14</v>
+      </c>
+      <c r="M44" t="s">
+        <v>666</v>
       </c>
     </row>
     <row r="45" spans="1:19">
@@ -3777,17 +3727,28 @@
         <v>23</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C45" s="7"/>
+        <v>594</v>
+      </c>
       <c r="F45" t="s">
-        <v>476</v>
+        <v>159</v>
       </c>
       <c r="G45" t="s">
         <v>173</v>
       </c>
-      <c r="H45" t="s">
-        <v>200</v>
+      <c r="O45" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="P45" t="s">
+        <v>518</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>159</v>
+      </c>
+      <c r="R45" t="s">
+        <v>592</v>
+      </c>
+      <c r="S45" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="46" spans="1:19">
@@ -3795,22 +3756,10 @@
         <v>23</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="D46" t="s">
-        <v>130</v>
-      </c>
-      <c r="E46" t="s">
-        <v>48</v>
-      </c>
-      <c r="F46" t="s">
-        <v>172</v>
-      </c>
-      <c r="G46" t="s">
-        <v>173</v>
+        <v>594</v>
+      </c>
+      <c r="O46" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="47" spans="1:19">
@@ -3818,14 +3767,28 @@
         <v>23</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="C47" s="7"/>
+        <v>15</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D47" t="s">
+        <v>85</v>
+      </c>
+      <c r="E47" t="s">
+        <v>48</v>
+      </c>
+      <c r="F47" t="s">
+        <v>167</v>
+      </c>
+      <c r="G47" t="s">
+        <v>173</v>
+      </c>
       <c r="H47" t="s">
         <v>200</v>
       </c>
       <c r="I47" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="J47" t="s">
         <v>203</v>
@@ -3833,8 +3796,26 @@
       <c r="K47" t="s">
         <v>215</v>
       </c>
+      <c r="L47" t="s">
+        <v>341</v>
+      </c>
       <c r="M47" t="s">
-        <v>399</v>
+        <v>401</v>
+      </c>
+      <c r="N47" t="s">
+        <v>637</v>
+      </c>
+      <c r="P47" t="s">
+        <v>519</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>572</v>
+      </c>
+      <c r="R47" t="s">
+        <v>622</v>
+      </c>
+      <c r="S47" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="48" spans="1:19">
@@ -3842,11 +3823,28 @@
         <v>23</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="C48" s="7"/>
+        <v>15</v>
+      </c>
+      <c r="F48" t="s">
+        <v>348</v>
+      </c>
+      <c r="G48" t="s">
+        <v>173</v>
+      </c>
+      <c r="H48" t="s">
+        <v>200</v>
+      </c>
+      <c r="I48" t="s">
+        <v>246</v>
+      </c>
+      <c r="J48" t="s">
+        <v>203</v>
+      </c>
+      <c r="K48" t="s">
+        <v>215</v>
+      </c>
       <c r="M48" t="s">
-        <v>649</v>
+        <v>685</v>
       </c>
     </row>
     <row r="49" spans="1:19">
@@ -3854,26 +3852,25 @@
         <v>23</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="C49" s="7"/>
-      <c r="H49" t="s">
-        <v>200</v>
-      </c>
-      <c r="I49" t="s">
-        <v>227</v>
-      </c>
-      <c r="J49" t="s">
-        <v>203</v>
-      </c>
-      <c r="K49" t="s">
-        <v>215</v>
-      </c>
-      <c r="M49" t="s">
-        <v>643</v>
-      </c>
-      <c r="O49" t="s">
-        <v>510</v>
+        <v>16</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="D49" t="s">
+        <v>465</v>
+      </c>
+      <c r="E49" t="s">
+        <v>48</v>
+      </c>
+      <c r="F49" t="s">
+        <v>164</v>
+      </c>
+      <c r="G49" t="s">
+        <v>173</v>
+      </c>
+      <c r="L49" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="50" spans="1:19">
@@ -3881,11 +3878,37 @@
         <v>23</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="C50" s="7"/>
+        <v>17</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D50" t="s">
+        <v>133</v>
+      </c>
+      <c r="E50" t="s">
+        <v>48</v>
+      </c>
+      <c r="F50" t="s">
+        <v>356</v>
+      </c>
+      <c r="G50" t="s">
+        <v>173</v>
+      </c>
+      <c r="H50" t="s">
+        <v>200</v>
+      </c>
+      <c r="I50" t="s">
+        <v>247</v>
+      </c>
+      <c r="J50" t="s">
+        <v>203</v>
+      </c>
+      <c r="K50" t="s">
+        <v>215</v>
+      </c>
       <c r="M50" t="s">
-        <v>398</v>
+        <v>684</v>
       </c>
     </row>
     <row r="51" spans="1:19">
@@ -3893,44 +3916,40 @@
         <v>23</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>368</v>
+        <v>18</v>
       </c>
       <c r="C51" s="7"/>
+      <c r="F51" t="s">
+        <v>476</v>
+      </c>
+      <c r="G51" t="s">
+        <v>173</v>
+      </c>
       <c r="H51" t="s">
         <v>200</v>
       </c>
-      <c r="I51" t="s">
-        <v>225</v>
-      </c>
-      <c r="J51" t="s">
-        <v>203</v>
-      </c>
-      <c r="K51" t="s">
-        <v>215</v>
-      </c>
-      <c r="M51" t="s">
-        <v>405</v>
-      </c>
     </row>
     <row r="52" spans="1:19">
       <c r="A52" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="C52" s="7"/>
-      <c r="H52" t="s">
-        <v>200</v>
-      </c>
-      <c r="I52" t="s">
-        <v>226</v>
-      </c>
-      <c r="J52" t="s">
-        <v>203</v>
-      </c>
-      <c r="K52" t="s">
-        <v>215</v>
+        <v>367</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D52" t="s">
+        <v>130</v>
+      </c>
+      <c r="E52" t="s">
+        <v>48</v>
+      </c>
+      <c r="F52" t="s">
+        <v>172</v>
+      </c>
+      <c r="G52" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="53" spans="1:19">
@@ -3938,14 +3957,14 @@
         <v>23</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>368</v>
+        <v>511</v>
       </c>
       <c r="C53" s="7"/>
       <c r="H53" t="s">
         <v>200</v>
       </c>
       <c r="I53" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J53" t="s">
         <v>203</v>
@@ -3953,58 +3972,20 @@
       <c r="K53" t="s">
         <v>215</v>
       </c>
+      <c r="M53" t="s">
+        <v>399</v>
+      </c>
     </row>
     <row r="54" spans="1:19">
       <c r="A54" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C54" s="6">
-        <v>210</v>
-      </c>
-      <c r="D54" t="s">
-        <v>83</v>
-      </c>
-      <c r="E54" t="s">
-        <v>48</v>
-      </c>
-      <c r="F54" t="s">
-        <v>165</v>
-      </c>
-      <c r="G54" t="s">
-        <v>173</v>
-      </c>
-      <c r="H54" t="s">
-        <v>200</v>
-      </c>
-      <c r="I54" t="s">
-        <v>248</v>
-      </c>
-      <c r="J54" t="s">
-        <v>203</v>
-      </c>
-      <c r="K54" t="s">
-        <v>215</v>
-      </c>
-      <c r="L54" t="s">
-        <v>317</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="C54" s="7"/>
       <c r="M54" t="s">
-        <v>390</v>
-      </c>
-      <c r="N54" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="O54" t="s">
-        <v>496</v>
-      </c>
-      <c r="R54" t="s">
-        <v>626</v>
-      </c>
-      <c r="S54" t="s">
-        <v>627</v>
+        <v>649</v>
       </c>
     </row>
     <row r="55" spans="1:19">
@@ -4012,40 +3993,11 @@
         <v>23</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C55" s="6">
-        <v>220</v>
-      </c>
-      <c r="D55" t="s">
-        <v>134</v>
-      </c>
-      <c r="E55" t="s">
-        <v>48</v>
-      </c>
-      <c r="F55" t="s">
-        <v>170</v>
-      </c>
-      <c r="G55" t="s">
-        <v>173</v>
-      </c>
-      <c r="H55" t="s">
-        <v>200</v>
-      </c>
-      <c r="I55" t="s">
-        <v>249</v>
-      </c>
-      <c r="J55" t="s">
-        <v>203</v>
-      </c>
-      <c r="K55" t="s">
-        <v>215</v>
-      </c>
-      <c r="L55" t="s">
-        <v>335</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="C55" s="7"/>
       <c r="M55" t="s">
-        <v>391</v>
+        <v>681</v>
       </c>
     </row>
     <row r="56" spans="1:19">
@@ -4053,28 +4005,11 @@
         <v>23</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F56" t="s">
-        <v>359</v>
-      </c>
-      <c r="G56" t="s">
-        <v>173</v>
-      </c>
-      <c r="H56" t="s">
-        <v>200</v>
-      </c>
-      <c r="I56" t="s">
-        <v>250</v>
-      </c>
-      <c r="J56" t="s">
-        <v>203</v>
-      </c>
-      <c r="K56" t="s">
-        <v>215</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="C56" s="7"/>
       <c r="M56" t="s">
-        <v>655</v>
+        <v>682</v>
       </c>
     </row>
     <row r="57" spans="1:19">
@@ -4082,13 +4017,14 @@
         <v>23</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>19</v>
-      </c>
+        <v>509</v>
+      </c>
+      <c r="C57" s="7"/>
       <c r="H57" t="s">
         <v>200</v>
       </c>
       <c r="I57" t="s">
-        <v>421</v>
+        <v>227</v>
       </c>
       <c r="J57" t="s">
         <v>203</v>
@@ -4096,13 +4032,23 @@
       <c r="K57" t="s">
         <v>215</v>
       </c>
+      <c r="M57" t="s">
+        <v>643</v>
+      </c>
+      <c r="O57" t="s">
+        <v>510</v>
+      </c>
     </row>
     <row r="58" spans="1:19">
       <c r="A58" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>636</v>
+        <v>509</v>
+      </c>
+      <c r="C58" s="7"/>
+      <c r="M58" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="59" spans="1:19">
@@ -4110,55 +4056,11 @@
         <v>23</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C59" s="6">
-        <v>230</v>
-      </c>
-      <c r="D59" t="s">
-        <v>131</v>
-      </c>
-      <c r="E59" t="s">
-        <v>48</v>
-      </c>
-      <c r="F59" t="s">
-        <v>163</v>
-      </c>
-      <c r="G59" t="s">
-        <v>173</v>
-      </c>
-      <c r="H59" t="s">
-        <v>200</v>
-      </c>
-      <c r="I59" t="s">
-        <v>251</v>
-      </c>
-      <c r="J59" t="s">
-        <v>203</v>
-      </c>
-      <c r="K59" t="s">
-        <v>215</v>
-      </c>
-      <c r="L59" t="s">
-        <v>342</v>
-      </c>
+        <v>509</v>
+      </c>
+      <c r="C59" s="7"/>
       <c r="M59" t="s">
-        <v>392</v>
-      </c>
-      <c r="N59" s="10" t="s">
-        <v>583</v>
-      </c>
-      <c r="O59" t="s">
-        <v>512</v>
-      </c>
-      <c r="P59" t="s">
-        <v>544</v>
-      </c>
-      <c r="R59" t="s">
-        <v>634</v>
-      </c>
-      <c r="S59" t="s">
-        <v>635</v>
+        <v>683</v>
       </c>
     </row>
     <row r="60" spans="1:19">
@@ -4166,16 +4068,23 @@
         <v>23</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F60" t="s">
-        <v>171</v>
-      </c>
-      <c r="G60" t="s">
-        <v>173</v>
+        <v>368</v>
+      </c>
+      <c r="C60" s="7"/>
+      <c r="H60" t="s">
+        <v>200</v>
+      </c>
+      <c r="I60" t="s">
+        <v>225</v>
+      </c>
+      <c r="J60" t="s">
+        <v>203</v>
+      </c>
+      <c r="K60" t="s">
+        <v>215</v>
       </c>
       <c r="M60" t="s">
-        <v>648</v>
+        <v>405</v>
       </c>
     </row>
     <row r="61" spans="1:19">
@@ -4183,22 +4092,20 @@
         <v>23</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="L61" t="s">
-        <v>335</v>
-      </c>
-      <c r="M61" t="s">
-        <v>409</v>
-      </c>
-      <c r="O61" t="s">
-        <v>504</v>
-      </c>
-      <c r="R61" t="s">
-        <v>618</v>
-      </c>
-      <c r="S61" t="s">
-        <v>619</v>
+        <v>368</v>
+      </c>
+      <c r="C61" s="7"/>
+      <c r="H61" t="s">
+        <v>200</v>
+      </c>
+      <c r="I61" t="s">
+        <v>226</v>
+      </c>
+      <c r="J61" t="s">
+        <v>203</v>
+      </c>
+      <c r="K61" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="62" spans="1:19">
@@ -4206,24 +4113,73 @@
         <v>23</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="M62" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19" ht="17" customHeight="1">
+        <v>368</v>
+      </c>
+      <c r="C62" s="7"/>
+      <c r="H62" t="s">
+        <v>200</v>
+      </c>
+      <c r="I62" t="s">
+        <v>228</v>
+      </c>
+      <c r="J62" t="s">
+        <v>203</v>
+      </c>
+      <c r="K62" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19">
       <c r="A63" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>628</v>
+        <v>19</v>
+      </c>
+      <c r="C63" s="6">
+        <v>210</v>
+      </c>
+      <c r="D63" t="s">
+        <v>83</v>
+      </c>
+      <c r="E63" t="s">
+        <v>48</v>
+      </c>
+      <c r="F63" t="s">
+        <v>165</v>
+      </c>
+      <c r="G63" t="s">
+        <v>173</v>
+      </c>
+      <c r="H63" t="s">
+        <v>200</v>
+      </c>
+      <c r="I63" t="s">
+        <v>248</v>
+      </c>
+      <c r="J63" t="s">
+        <v>203</v>
+      </c>
+      <c r="K63" t="s">
+        <v>215</v>
+      </c>
+      <c r="L63" t="s">
+        <v>317</v>
+      </c>
+      <c r="M63" t="s">
+        <v>390</v>
+      </c>
+      <c r="N63" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="O63" t="s">
+        <v>496</v>
       </c>
       <c r="R63" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="S63" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="64" spans="1:19">
@@ -4231,13 +4187,40 @@
         <v>23</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="R64" t="s">
-        <v>632</v>
-      </c>
-      <c r="S64" t="s">
-        <v>633</v>
+        <v>19</v>
+      </c>
+      <c r="C64" s="6">
+        <v>220</v>
+      </c>
+      <c r="D64" t="s">
+        <v>134</v>
+      </c>
+      <c r="E64" t="s">
+        <v>48</v>
+      </c>
+      <c r="F64" t="s">
+        <v>170</v>
+      </c>
+      <c r="G64" t="s">
+        <v>173</v>
+      </c>
+      <c r="H64" t="s">
+        <v>200</v>
+      </c>
+      <c r="I64" t="s">
+        <v>249</v>
+      </c>
+      <c r="J64" t="s">
+        <v>203</v>
+      </c>
+      <c r="K64" t="s">
+        <v>215</v>
+      </c>
+      <c r="L64" t="s">
+        <v>335</v>
+      </c>
+      <c r="M64" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="65" spans="1:19">
@@ -4245,7 +4228,28 @@
         <v>23</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
+      </c>
+      <c r="F65" t="s">
+        <v>359</v>
+      </c>
+      <c r="G65" t="s">
+        <v>173</v>
+      </c>
+      <c r="H65" t="s">
+        <v>200</v>
+      </c>
+      <c r="I65" t="s">
+        <v>250</v>
+      </c>
+      <c r="J65" t="s">
+        <v>203</v>
+      </c>
+      <c r="K65" t="s">
+        <v>215</v>
+      </c>
+      <c r="M65" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="66" spans="1:19">
@@ -4253,16 +4257,19 @@
         <v>23</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="D66" t="s">
-        <v>128</v>
-      </c>
-      <c r="E66" t="s">
-        <v>48</v>
+        <v>19</v>
+      </c>
+      <c r="H66" t="s">
+        <v>200</v>
+      </c>
+      <c r="I66" t="s">
+        <v>421</v>
+      </c>
+      <c r="J66" t="s">
+        <v>203</v>
+      </c>
+      <c r="K66" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="67" spans="1:19">
@@ -4270,353 +4277,276 @@
         <v>23</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="C67" s="7"/>
-      <c r="O67" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="68" spans="1:19">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" ht="17" customHeight="1">
       <c r="A68" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="C68" s="7"/>
-      <c r="Q68" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="69" spans="1:19">
+        <v>20</v>
+      </c>
+      <c r="C68" s="6">
+        <v>230</v>
+      </c>
+      <c r="D68" t="s">
+        <v>131</v>
+      </c>
+      <c r="E68" t="s">
+        <v>48</v>
+      </c>
+      <c r="F68" t="s">
+        <v>163</v>
+      </c>
+      <c r="G68" t="s">
+        <v>173</v>
+      </c>
+      <c r="H68" t="s">
+        <v>200</v>
+      </c>
+      <c r="I68" t="s">
+        <v>251</v>
+      </c>
+      <c r="J68" t="s">
+        <v>203</v>
+      </c>
+      <c r="K68" t="s">
+        <v>215</v>
+      </c>
+      <c r="L68" t="s">
+        <v>342</v>
+      </c>
+      <c r="M68" t="s">
+        <v>392</v>
+      </c>
+      <c r="N68" s="10" t="s">
+        <v>583</v>
+      </c>
+      <c r="O68" t="s">
+        <v>512</v>
+      </c>
+      <c r="P68" t="s">
+        <v>544</v>
+      </c>
+      <c r="R68" t="s">
+        <v>634</v>
+      </c>
+      <c r="S68" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" ht="17" customHeight="1">
       <c r="A69" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="C69" s="7"/>
-    </row>
-    <row r="70" spans="1:19">
-      <c r="A70" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D70" t="s">
-        <v>65</v>
-      </c>
-      <c r="E70" t="s">
-        <v>48</v>
+        <v>20</v>
+      </c>
+      <c r="M69" t="s">
+        <v>675</v>
+      </c>
+      <c r="N69" s="10"/>
+    </row>
+    <row r="70" spans="1:19" ht="17" customHeight="1">
+      <c r="A70" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F70" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G70" t="s">
         <v>173</v>
       </c>
-      <c r="H70" t="s">
+      <c r="M70" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19">
+      <c r="A71" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="L71" t="s">
+        <v>335</v>
+      </c>
+      <c r="M71" t="s">
+        <v>409</v>
+      </c>
+      <c r="O71" t="s">
+        <v>504</v>
+      </c>
+      <c r="R71" t="s">
+        <v>618</v>
+      </c>
+      <c r="S71" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19">
+      <c r="A72" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="M72" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" ht="17" customHeight="1">
+      <c r="A73" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="R73" t="s">
+        <v>630</v>
+      </c>
+      <c r="S73" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19">
+      <c r="A74" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="R74" t="s">
+        <v>632</v>
+      </c>
+      <c r="S74" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19">
+      <c r="A75" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19">
+      <c r="A76" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D76" t="s">
+        <v>128</v>
+      </c>
+      <c r="E76" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19">
+      <c r="A77" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="C77" s="7"/>
+      <c r="O77" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19">
+      <c r="A78" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="C78" s="7"/>
+      <c r="Q78" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19">
+      <c r="A79" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="C79" s="7"/>
+    </row>
+    <row r="80" spans="1:19">
+      <c r="A80" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D80" t="s">
+        <v>65</v>
+      </c>
+      <c r="E80" t="s">
+        <v>48</v>
+      </c>
+      <c r="F80" t="s">
+        <v>168</v>
+      </c>
+      <c r="G80" t="s">
+        <v>173</v>
+      </c>
+      <c r="H80" t="s">
         <v>200</v>
       </c>
-      <c r="I70" t="s">
+      <c r="I80" t="s">
         <v>252</v>
       </c>
-      <c r="J70" t="s">
+      <c r="J80" t="s">
         <v>207</v>
       </c>
-      <c r="K70" t="s">
+      <c r="K80" t="s">
         <v>216</v>
       </c>
-      <c r="L70" t="s">
+      <c r="L80" t="s">
         <v>329</v>
       </c>
-      <c r="M70" t="s">
+      <c r="M80" t="s">
         <v>370</v>
       </c>
-      <c r="P70" t="s">
+      <c r="P80" t="s">
         <v>168</v>
       </c>
-      <c r="Q70" t="s">
+      <c r="Q80" t="s">
         <v>168</v>
       </c>
-      <c r="R70" t="s">
+      <c r="R80" t="s">
         <v>614</v>
       </c>
-      <c r="S70" t="s">
+      <c r="S80" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="71" spans="1:19">
-      <c r="A71" s="2" t="s">
+    <row r="81" spans="1:19">
+      <c r="A81" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B81" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="M71" t="s">
+      <c r="M81" t="s">
         <v>665</v>
-      </c>
-    </row>
-    <row r="72" spans="1:19">
-      <c r="A72" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C72" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D72" t="s">
-        <v>67</v>
-      </c>
-      <c r="E72" t="s">
-        <v>49</v>
-      </c>
-      <c r="F72" t="s">
-        <v>143</v>
-      </c>
-      <c r="G72" t="s">
-        <v>148</v>
-      </c>
-      <c r="H72" t="s">
-        <v>201</v>
-      </c>
-      <c r="I72" t="s">
-        <v>253</v>
-      </c>
-      <c r="J72" t="s">
-        <v>204</v>
-      </c>
-      <c r="K72" t="s">
-        <v>218</v>
-      </c>
-      <c r="L72" t="s">
-        <v>312</v>
-      </c>
-      <c r="M72" t="s">
-        <v>379</v>
-      </c>
-      <c r="N72" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="O72" s="10" t="s">
-        <v>434</v>
-      </c>
-      <c r="P72" t="s">
-        <v>520</v>
-      </c>
-      <c r="Q72" t="s">
-        <v>520</v>
-      </c>
-      <c r="R72" t="s">
-        <v>586</v>
-      </c>
-      <c r="S72" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="73" spans="1:19">
-      <c r="A73" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F73" t="s">
-        <v>144</v>
-      </c>
-      <c r="G73" t="s">
-        <v>148</v>
-      </c>
-      <c r="H73" t="s">
-        <v>201</v>
-      </c>
-      <c r="I73" t="s">
-        <v>254</v>
-      </c>
-      <c r="J73" t="s">
-        <v>204</v>
-      </c>
-      <c r="K73" t="s">
-        <v>218</v>
-      </c>
-      <c r="L73" t="s">
-        <v>450</v>
-      </c>
-      <c r="M73" t="s">
-        <v>384</v>
-      </c>
-      <c r="O73" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="74" spans="1:19">
-      <c r="A74" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H74" t="s">
-        <v>201</v>
-      </c>
-      <c r="I74" t="s">
-        <v>255</v>
-      </c>
-      <c r="J74" t="s">
-        <v>204</v>
-      </c>
-      <c r="K74" t="s">
-        <v>218</v>
-      </c>
-      <c r="O74" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="75" spans="1:19">
-      <c r="A75" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H75" t="s">
-        <v>201</v>
-      </c>
-      <c r="I75" t="s">
-        <v>256</v>
-      </c>
-      <c r="J75" t="s">
-        <v>204</v>
-      </c>
-      <c r="K75" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="76" spans="1:19">
-      <c r="A76" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H76" t="s">
-        <v>201</v>
-      </c>
-      <c r="I76" t="s">
-        <v>350</v>
-      </c>
-      <c r="J76" t="s">
-        <v>204</v>
-      </c>
-      <c r="K76" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="77" spans="1:19">
-      <c r="A77" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H77" t="s">
-        <v>201</v>
-      </c>
-      <c r="I77" t="s">
-        <v>351</v>
-      </c>
-      <c r="J77" t="s">
-        <v>204</v>
-      </c>
-      <c r="K77" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="78" spans="1:19">
-      <c r="A78" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H78" t="s">
-        <v>201</v>
-      </c>
-      <c r="I78" t="s">
-        <v>354</v>
-      </c>
-      <c r="J78" t="s">
-        <v>204</v>
-      </c>
-      <c r="K78" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19">
-      <c r="A79" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H79" t="s">
-        <v>201</v>
-      </c>
-      <c r="I79" t="s">
-        <v>257</v>
-      </c>
-      <c r="J79" t="s">
-        <v>204</v>
-      </c>
-      <c r="K79" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="80" spans="1:19">
-      <c r="A80" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H80" t="s">
-        <v>201</v>
-      </c>
-      <c r="I80" t="s">
-        <v>258</v>
-      </c>
-      <c r="J80" t="s">
-        <v>204</v>
-      </c>
-      <c r="K80" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="81" spans="1:19">
-      <c r="A81" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H81" t="s">
-        <v>201</v>
-      </c>
-      <c r="I81" t="s">
-        <v>413</v>
-      </c>
-      <c r="J81" t="s">
-        <v>204</v>
-      </c>
-      <c r="K81" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="82" spans="1:19">
@@ -4626,11 +4556,26 @@
       <c r="B82" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="C82" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D82" t="s">
+        <v>67</v>
+      </c>
+      <c r="E82" t="s">
+        <v>49</v>
+      </c>
+      <c r="F82" t="s">
+        <v>143</v>
+      </c>
+      <c r="G82" t="s">
+        <v>148</v>
+      </c>
       <c r="H82" t="s">
         <v>201</v>
       </c>
       <c r="I82" t="s">
-        <v>414</v>
+        <v>253</v>
       </c>
       <c r="J82" t="s">
         <v>204</v>
@@ -4638,6 +4583,30 @@
       <c r="K82" t="s">
         <v>218</v>
       </c>
+      <c r="L82" t="s">
+        <v>312</v>
+      </c>
+      <c r="M82" t="s">
+        <v>379</v>
+      </c>
+      <c r="N82" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="O82" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="P82" t="s">
+        <v>520</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>520</v>
+      </c>
+      <c r="R82" t="s">
+        <v>586</v>
+      </c>
+      <c r="S82" t="s">
+        <v>587</v>
+      </c>
     </row>
     <row r="83" spans="1:19">
       <c r="A83" s="3" t="s">
@@ -4646,11 +4615,17 @@
       <c r="B83" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="F83" t="s">
+        <v>144</v>
+      </c>
+      <c r="G83" t="s">
+        <v>148</v>
+      </c>
       <c r="H83" t="s">
         <v>201</v>
       </c>
       <c r="I83" t="s">
-        <v>416</v>
+        <v>254</v>
       </c>
       <c r="J83" t="s">
         <v>204</v>
@@ -4658,6 +4633,15 @@
       <c r="K83" t="s">
         <v>218</v>
       </c>
+      <c r="L83" t="s">
+        <v>450</v>
+      </c>
+      <c r="M83" t="s">
+        <v>384</v>
+      </c>
+      <c r="O83" t="s">
+        <v>495</v>
+      </c>
     </row>
     <row r="84" spans="1:19">
       <c r="A84" s="3" t="s">
@@ -4670,7 +4654,7 @@
         <v>201</v>
       </c>
       <c r="I84" t="s">
-        <v>415</v>
+        <v>255</v>
       </c>
       <c r="J84" t="s">
         <v>204</v>
@@ -4678,6 +4662,9 @@
       <c r="K84" t="s">
         <v>218</v>
       </c>
+      <c r="O84" t="s">
+        <v>520</v>
+      </c>
     </row>
     <row r="85" spans="1:19">
       <c r="A85" s="3" t="s">
@@ -4686,8 +4673,11 @@
       <c r="B85" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="H85" t="s">
+        <v>201</v>
+      </c>
       <c r="I85" t="s">
-        <v>483</v>
+        <v>256</v>
       </c>
       <c r="J85" t="s">
         <v>204</v>
@@ -4703,8 +4693,11 @@
       <c r="B86" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="H86" t="s">
+        <v>201</v>
+      </c>
       <c r="I86" t="s">
-        <v>484</v>
+        <v>350</v>
       </c>
       <c r="J86" t="s">
         <v>204</v>
@@ -4724,7 +4717,7 @@
         <v>201</v>
       </c>
       <c r="I87" t="s">
-        <v>479</v>
+        <v>351</v>
       </c>
       <c r="J87" t="s">
         <v>204</v>
@@ -4744,7 +4737,7 @@
         <v>201</v>
       </c>
       <c r="I88" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="J88" t="s">
         <v>204</v>
@@ -4778,25 +4771,13 @@
         <v>24</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D90" t="s">
-        <v>68</v>
-      </c>
-      <c r="E90" t="s">
-        <v>49</v>
-      </c>
-      <c r="F90" t="s">
-        <v>145</v>
-      </c>
-      <c r="G90" t="s">
-        <v>148</v>
+        <v>25</v>
       </c>
       <c r="H90" t="s">
         <v>201</v>
+      </c>
+      <c r="I90" t="s">
+        <v>258</v>
       </c>
       <c r="J90" t="s">
         <v>204</v>
@@ -4804,43 +4785,19 @@
       <c r="K90" t="s">
         <v>218</v>
       </c>
-      <c r="L90" t="s">
-        <v>314</v>
-      </c>
-      <c r="M90" t="s">
-        <v>246</v>
-      </c>
-      <c r="N90" s="10" t="s">
-        <v>423</v>
-      </c>
-      <c r="O90" s="10" t="s">
-        <v>442</v>
-      </c>
-      <c r="P90" t="s">
-        <v>521</v>
-      </c>
-      <c r="Q90" t="s">
-        <v>546</v>
-      </c>
-      <c r="R90" t="s">
-        <v>606</v>
-      </c>
-      <c r="S90" t="s">
-        <v>607</v>
-      </c>
     </row>
     <row r="91" spans="1:19">
       <c r="A91" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H91" t="s">
         <v>201</v>
       </c>
       <c r="I91" t="s">
-        <v>259</v>
+        <v>413</v>
       </c>
       <c r="J91" t="s">
         <v>204</v>
@@ -4848,28 +4805,19 @@
       <c r="K91" t="s">
         <v>218</v>
       </c>
-      <c r="O91" t="s">
-        <v>498</v>
-      </c>
     </row>
     <row r="92" spans="1:19">
       <c r="A92" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F92" t="s">
-        <v>146</v>
-      </c>
-      <c r="G92" t="s">
-        <v>148</v>
+        <v>25</v>
       </c>
       <c r="H92" t="s">
         <v>201</v>
       </c>
       <c r="I92" t="s">
-        <v>260</v>
+        <v>414</v>
       </c>
       <c r="J92" t="s">
         <v>204</v>
@@ -4877,22 +4825,19 @@
       <c r="K92" t="s">
         <v>218</v>
       </c>
-      <c r="O92" t="s">
-        <v>521</v>
-      </c>
     </row>
     <row r="93" spans="1:19">
       <c r="A93" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H93" t="s">
         <v>201</v>
       </c>
       <c r="I93" t="s">
-        <v>261</v>
+        <v>416</v>
       </c>
       <c r="J93" t="s">
         <v>204</v>
@@ -4906,13 +4851,13 @@
         <v>24</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H94" t="s">
         <v>201</v>
       </c>
       <c r="I94" t="s">
-        <v>262</v>
+        <v>415</v>
       </c>
       <c r="J94" t="s">
         <v>204</v>
@@ -4926,13 +4871,10 @@
         <v>24</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H95" t="s">
-        <v>201</v>
+        <v>25</v>
       </c>
       <c r="I95" t="s">
-        <v>263</v>
+        <v>483</v>
       </c>
       <c r="J95" t="s">
         <v>204</v>
@@ -4946,13 +4888,10 @@
         <v>24</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H96" t="s">
-        <v>201</v>
+        <v>25</v>
       </c>
       <c r="I96" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="J96" t="s">
         <v>204</v>
@@ -4966,13 +4905,13 @@
         <v>24</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H97" t="s">
         <v>201</v>
       </c>
       <c r="I97" t="s">
-        <v>352</v>
+        <v>479</v>
       </c>
       <c r="J97" t="s">
         <v>204</v>
@@ -4986,13 +4925,13 @@
         <v>24</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H98" t="s">
         <v>201</v>
       </c>
       <c r="I98" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="J98" t="s">
         <v>204</v>
@@ -5006,13 +4945,13 @@
         <v>24</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H99" t="s">
         <v>201</v>
       </c>
       <c r="I99" t="s">
-        <v>417</v>
+        <v>257</v>
       </c>
       <c r="J99" t="s">
         <v>204</v>
@@ -5028,11 +4967,23 @@
       <c r="B100" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="C100" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D100" t="s">
+        <v>68</v>
+      </c>
+      <c r="E100" t="s">
+        <v>49</v>
+      </c>
+      <c r="F100" t="s">
+        <v>145</v>
+      </c>
+      <c r="G100" t="s">
+        <v>148</v>
+      </c>
       <c r="H100" t="s">
         <v>201</v>
-      </c>
-      <c r="I100" t="s">
-        <v>418</v>
       </c>
       <c r="J100" t="s">
         <v>204</v>
@@ -5040,6 +4991,30 @@
       <c r="K100" t="s">
         <v>218</v>
       </c>
+      <c r="L100" t="s">
+        <v>314</v>
+      </c>
+      <c r="M100" t="s">
+        <v>246</v>
+      </c>
+      <c r="N100" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="O100" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="P100" t="s">
+        <v>521</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>546</v>
+      </c>
+      <c r="R100" t="s">
+        <v>606</v>
+      </c>
+      <c r="S100" t="s">
+        <v>607</v>
+      </c>
     </row>
     <row r="101" spans="1:19">
       <c r="A101" s="3" t="s">
@@ -5052,7 +5027,7 @@
         <v>201</v>
       </c>
       <c r="I101" t="s">
-        <v>419</v>
+        <v>259</v>
       </c>
       <c r="J101" t="s">
         <v>204</v>
@@ -5060,6 +5035,12 @@
       <c r="K101" t="s">
         <v>218</v>
       </c>
+      <c r="M101" t="s">
+        <v>671</v>
+      </c>
+      <c r="O101" t="s">
+        <v>498</v>
+      </c>
     </row>
     <row r="102" spans="1:19">
       <c r="A102" s="3" t="s">
@@ -5068,11 +5049,17 @@
       <c r="B102" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="F102" t="s">
+        <v>146</v>
+      </c>
+      <c r="G102" t="s">
+        <v>148</v>
+      </c>
       <c r="H102" t="s">
         <v>201</v>
       </c>
       <c r="I102" t="s">
-        <v>478</v>
+        <v>260</v>
       </c>
       <c r="J102" t="s">
         <v>204</v>
@@ -5080,6 +5067,9 @@
       <c r="K102" t="s">
         <v>218</v>
       </c>
+      <c r="O102" t="s">
+        <v>521</v>
+      </c>
     </row>
     <row r="103" spans="1:19">
       <c r="A103" s="3" t="s">
@@ -5092,7 +5082,7 @@
         <v>201</v>
       </c>
       <c r="I103" t="s">
-        <v>420</v>
+        <v>261</v>
       </c>
       <c r="J103" t="s">
         <v>204</v>
@@ -5108,8 +5098,11 @@
       <c r="B104" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="H104" t="s">
+        <v>201</v>
+      </c>
       <c r="I104" t="s">
-        <v>482</v>
+        <v>262</v>
       </c>
       <c r="J104" t="s">
         <v>204</v>
@@ -5125,8 +5118,11 @@
       <c r="B105" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="H105" t="s">
+        <v>201</v>
+      </c>
       <c r="I105" t="s">
-        <v>485</v>
+        <v>263</v>
       </c>
       <c r="J105" t="s">
         <v>204</v>
@@ -5142,8 +5138,11 @@
       <c r="B106" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="H106" t="s">
+        <v>201</v>
+      </c>
       <c r="I106" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="J106" t="s">
         <v>204</v>
@@ -5163,7 +5162,7 @@
         <v>201</v>
       </c>
       <c r="I107" t="s">
-        <v>205</v>
+        <v>352</v>
       </c>
       <c r="J107" t="s">
         <v>204</v>
@@ -5183,7 +5182,7 @@
         <v>201</v>
       </c>
       <c r="I108" t="s">
-        <v>279</v>
+        <v>355</v>
       </c>
       <c r="J108" t="s">
         <v>204</v>
@@ -5203,7 +5202,7 @@
         <v>201</v>
       </c>
       <c r="I109" t="s">
-        <v>477</v>
+        <v>417</v>
       </c>
       <c r="J109" t="s">
         <v>204</v>
@@ -5217,28 +5216,13 @@
         <v>24</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C110" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D110" t="s">
-        <v>69</v>
-      </c>
-      <c r="E110" t="s">
-        <v>49</v>
-      </c>
-      <c r="F110" t="s">
-        <v>151</v>
-      </c>
-      <c r="G110" t="s">
-        <v>148</v>
+        <v>26</v>
       </c>
       <c r="H110" t="s">
         <v>201</v>
       </c>
       <c r="I110" t="s">
-        <v>264</v>
+        <v>418</v>
       </c>
       <c r="J110" t="s">
         <v>204</v>
@@ -5246,37 +5230,19 @@
       <c r="K110" t="s">
         <v>218</v>
       </c>
-      <c r="L110" t="s">
-        <v>331</v>
-      </c>
-      <c r="M110" t="s">
-        <v>266</v>
-      </c>
-      <c r="O110" s="10" t="s">
-        <v>443</v>
-      </c>
-      <c r="P110" t="s">
-        <v>524</v>
-      </c>
-      <c r="R110" t="s">
-        <v>590</v>
-      </c>
-      <c r="S110" t="s">
-        <v>591</v>
-      </c>
     </row>
     <row r="111" spans="1:19">
       <c r="A111" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H111" t="s">
         <v>201</v>
       </c>
       <c r="I111" t="s">
-        <v>265</v>
+        <v>419</v>
       </c>
       <c r="J111" t="s">
         <v>204</v>
@@ -5284,31 +5250,19 @@
       <c r="K111" t="s">
         <v>218</v>
       </c>
-      <c r="M111" t="s">
-        <v>664</v>
-      </c>
-      <c r="O111" t="s">
-        <v>541</v>
-      </c>
     </row>
     <row r="112" spans="1:19">
       <c r="A112" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F112" t="s">
-        <v>152</v>
-      </c>
-      <c r="G112" t="s">
-        <v>148</v>
+        <v>26</v>
       </c>
       <c r="H112" t="s">
         <v>201</v>
       </c>
       <c r="I112" t="s">
-        <v>266</v>
+        <v>478</v>
       </c>
       <c r="J112" t="s">
         <v>204</v>
@@ -5322,19 +5276,13 @@
         <v>24</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="F113" t="s">
-        <v>189</v>
-      </c>
-      <c r="G113" t="s">
-        <v>148</v>
+        <v>26</v>
       </c>
       <c r="H113" t="s">
         <v>201</v>
       </c>
       <c r="I113" t="s">
-        <v>267</v>
+        <v>420</v>
       </c>
       <c r="J113" t="s">
         <v>204</v>
@@ -5342,43 +5290,16 @@
       <c r="K113" t="s">
         <v>218</v>
       </c>
-      <c r="N113" s="10" t="s">
-        <v>427</v>
-      </c>
-      <c r="O113" t="s">
-        <v>500</v>
-      </c>
-      <c r="Q113" t="s">
-        <v>569</v>
-      </c>
     </row>
     <row r="114" spans="1:19">
       <c r="A114" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C114" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D114" t="s">
-        <v>84</v>
-      </c>
-      <c r="E114" t="s">
-        <v>49</v>
-      </c>
-      <c r="F114" t="s">
-        <v>149</v>
-      </c>
-      <c r="G114" t="s">
-        <v>148</v>
-      </c>
-      <c r="H114" t="s">
-        <v>201</v>
+        <v>26</v>
       </c>
       <c r="I114" t="s">
-        <v>84</v>
+        <v>482</v>
       </c>
       <c r="J114" t="s">
         <v>204</v>
@@ -5386,34 +5307,22 @@
       <c r="K114" t="s">
         <v>218</v>
       </c>
-      <c r="L114" t="s">
-        <v>318</v>
-      </c>
-      <c r="M114" t="s">
-        <v>374</v>
-      </c>
-      <c r="P114" t="s">
-        <v>523</v>
-      </c>
-      <c r="R114" t="s">
-        <v>624</v>
-      </c>
-      <c r="S114" t="s">
-        <v>625</v>
-      </c>
     </row>
     <row r="115" spans="1:19">
       <c r="A115" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L115" t="s">
-        <v>464</v>
-      </c>
-      <c r="M115" t="s">
-        <v>660</v>
+        <v>26</v>
+      </c>
+      <c r="I115" t="s">
+        <v>485</v>
+      </c>
+      <c r="J115" t="s">
+        <v>204</v>
+      </c>
+      <c r="K115" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="116" spans="1:19">
@@ -5421,28 +5330,10 @@
         <v>24</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="C116" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D116" t="s">
-        <v>72</v>
-      </c>
-      <c r="E116" t="s">
-        <v>49</v>
-      </c>
-      <c r="F116" t="s">
-        <v>150</v>
-      </c>
-      <c r="G116" t="s">
-        <v>148</v>
-      </c>
-      <c r="H116" t="s">
-        <v>201</v>
+        <v>26</v>
       </c>
       <c r="I116" t="s">
-        <v>268</v>
+        <v>486</v>
       </c>
       <c r="J116" t="s">
         <v>204</v>
@@ -5450,58 +5341,19 @@
       <c r="K116" t="s">
         <v>218</v>
       </c>
-      <c r="L116" t="s">
-        <v>311</v>
-      </c>
-      <c r="M116" t="s">
-        <v>371</v>
-      </c>
-      <c r="N116" s="10" t="s">
-        <v>425</v>
-      </c>
-      <c r="O116" s="10" t="s">
-        <v>436</v>
-      </c>
-      <c r="P116" t="s">
-        <v>522</v>
-      </c>
-      <c r="Q116" t="s">
-        <v>548</v>
-      </c>
-      <c r="R116" t="s">
-        <v>588</v>
-      </c>
-      <c r="S116" t="s">
-        <v>589</v>
-      </c>
     </row>
     <row r="117" spans="1:19">
       <c r="A117" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="C117" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D117" t="s">
-        <v>73</v>
-      </c>
-      <c r="E117" t="s">
-        <v>49</v>
-      </c>
-      <c r="F117" t="s">
-        <v>194</v>
-      </c>
-      <c r="G117" t="s">
-        <v>148</v>
+        <v>26</v>
       </c>
       <c r="H117" t="s">
         <v>201</v>
       </c>
       <c r="I117" t="s">
-        <v>269</v>
+        <v>205</v>
       </c>
       <c r="J117" t="s">
         <v>204</v>
@@ -5509,37 +5361,19 @@
       <c r="K117" t="s">
         <v>218</v>
       </c>
-      <c r="L117" t="s">
-        <v>320</v>
-      </c>
-      <c r="M117" t="s">
-        <v>372</v>
-      </c>
-      <c r="O117" t="s">
-        <v>494</v>
-      </c>
-      <c r="Q117" t="s">
-        <v>566</v>
-      </c>
     </row>
     <row r="118" spans="1:19">
       <c r="A118" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="F118" t="s">
-        <v>187</v>
-      </c>
-      <c r="G118" t="s">
-        <v>148</v>
+        <v>26</v>
       </c>
       <c r="H118" t="s">
         <v>201</v>
       </c>
       <c r="I118" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="J118" t="s">
         <v>204</v>
@@ -5547,43 +5381,25 @@
       <c r="K118" t="s">
         <v>218</v>
       </c>
-      <c r="L118" t="s">
-        <v>321</v>
-      </c>
-      <c r="M118" t="s">
-        <v>373</v>
-      </c>
-      <c r="O118" t="s">
-        <v>536</v>
-      </c>
-      <c r="Q118" t="s">
-        <v>571</v>
-      </c>
     </row>
     <row r="119" spans="1:19">
       <c r="A119" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="F119" t="s">
-        <v>347</v>
-      </c>
-      <c r="G119" t="s">
-        <v>148</v>
+        <v>26</v>
       </c>
       <c r="H119" t="s">
         <v>201</v>
       </c>
       <c r="I119" t="s">
-        <v>490</v>
-      </c>
-      <c r="L119" t="s">
-        <v>460</v>
-      </c>
-      <c r="M119" t="s">
-        <v>383</v>
+        <v>477</v>
+      </c>
+      <c r="J119" t="s">
+        <v>204</v>
+      </c>
+      <c r="K119" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="120" spans="1:19">
@@ -5591,10 +5407,19 @@
         <v>24</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>535</v>
+        <v>27</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D120" t="s">
+        <v>69</v>
+      </c>
+      <c r="E120" t="s">
+        <v>49</v>
       </c>
       <c r="F120" t="s">
-        <v>190</v>
+        <v>151</v>
       </c>
       <c r="G120" t="s">
         <v>148</v>
@@ -5603,7 +5428,7 @@
         <v>201</v>
       </c>
       <c r="I120" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="J120" t="s">
         <v>204</v>
@@ -5611,8 +5436,23 @@
       <c r="K120" t="s">
         <v>218</v>
       </c>
+      <c r="L120" t="s">
+        <v>331</v>
+      </c>
       <c r="M120" t="s">
-        <v>410</v>
+        <v>266</v>
+      </c>
+      <c r="O120" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="P120" t="s">
+        <v>524</v>
+      </c>
+      <c r="R120" t="s">
+        <v>590</v>
+      </c>
+      <c r="S120" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="121" spans="1:19">
@@ -5620,19 +5460,13 @@
         <v>24</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="F121" t="s">
-        <v>193</v>
-      </c>
-      <c r="G121" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="H121" t="s">
         <v>201</v>
       </c>
       <c r="I121" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="J121" t="s">
         <v>204</v>
@@ -5640,16 +5474,22 @@
       <c r="K121" t="s">
         <v>218</v>
       </c>
+      <c r="M121" t="s">
+        <v>664</v>
+      </c>
+      <c r="O121" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="122" spans="1:19">
       <c r="A122" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>535</v>
+        <v>27</v>
       </c>
       <c r="F122" t="s">
-        <v>358</v>
+        <v>152</v>
       </c>
       <c r="G122" t="s">
         <v>148</v>
@@ -5658,7 +5498,13 @@
         <v>201</v>
       </c>
       <c r="I122" t="s">
-        <v>491</v>
+        <v>266</v>
+      </c>
+      <c r="J122" t="s">
+        <v>204</v>
+      </c>
+      <c r="K122" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="123" spans="1:19">
@@ -5666,10 +5512,10 @@
         <v>24</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>535</v>
+        <v>501</v>
       </c>
       <c r="F123" t="s">
-        <v>361</v>
+        <v>189</v>
       </c>
       <c r="G123" t="s">
         <v>148</v>
@@ -5678,7 +5524,22 @@
         <v>201</v>
       </c>
       <c r="I123" t="s">
-        <v>492</v>
+        <v>267</v>
+      </c>
+      <c r="J123" t="s">
+        <v>204</v>
+      </c>
+      <c r="K123" t="s">
+        <v>218</v>
+      </c>
+      <c r="N123" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="O123" t="s">
+        <v>500</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="124" spans="1:19">
@@ -5686,10 +5547,19 @@
         <v>24</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>535</v>
+        <v>28</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D124" t="s">
+        <v>84</v>
+      </c>
+      <c r="E124" t="s">
+        <v>49</v>
       </c>
       <c r="F124" t="s">
-        <v>573</v>
+        <v>149</v>
       </c>
       <c r="G124" t="s">
         <v>148</v>
@@ -5698,7 +5568,28 @@
         <v>201</v>
       </c>
       <c r="I124" t="s">
-        <v>73</v>
+        <v>84</v>
+      </c>
+      <c r="J124" t="s">
+        <v>204</v>
+      </c>
+      <c r="K124" t="s">
+        <v>218</v>
+      </c>
+      <c r="L124" t="s">
+        <v>318</v>
+      </c>
+      <c r="M124" t="s">
+        <v>374</v>
+      </c>
+      <c r="P124" t="s">
+        <v>523</v>
+      </c>
+      <c r="R124" t="s">
+        <v>624</v>
+      </c>
+      <c r="S124" t="s">
+        <v>625</v>
       </c>
     </row>
     <row r="125" spans="1:19">
@@ -5706,13 +5597,13 @@
         <v>24</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="F125" t="s">
-        <v>574</v>
-      </c>
-      <c r="G125" t="s">
-        <v>148</v>
+        <v>28</v>
+      </c>
+      <c r="L125" t="s">
+        <v>464</v>
+      </c>
+      <c r="M125" t="s">
+        <v>660</v>
       </c>
     </row>
     <row r="126" spans="1:19">
@@ -5720,7 +5611,10 @@
         <v>24</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>535</v>
+        <v>28</v>
+      </c>
+      <c r="M126" t="s">
+        <v>667</v>
       </c>
     </row>
     <row r="127" spans="1:19">
@@ -5728,19 +5622,19 @@
         <v>24</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>29</v>
+        <v>535</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D127" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E127" t="s">
         <v>49</v>
       </c>
       <c r="F127" t="s">
-        <v>197</v>
+        <v>150</v>
       </c>
       <c r="G127" t="s">
         <v>148</v>
@@ -5749,7 +5643,7 @@
         <v>201</v>
       </c>
       <c r="I127" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="J127" t="s">
         <v>204</v>
@@ -5757,14 +5651,29 @@
       <c r="K127" t="s">
         <v>218</v>
       </c>
+      <c r="L127" t="s">
+        <v>311</v>
+      </c>
       <c r="M127" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>448</v>
+        <v>436</v>
+      </c>
+      <c r="P127" t="s">
+        <v>522</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>548</v>
+      </c>
+      <c r="R127" t="s">
+        <v>588</v>
+      </c>
+      <c r="S127" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="128" spans="1:19">
@@ -5772,14 +5681,46 @@
         <v>24</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>29</v>
+        <v>535</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D128" t="s">
+        <v>73</v>
+      </c>
+      <c r="E128" t="s">
+        <v>49</v>
+      </c>
+      <c r="F128" t="s">
+        <v>194</v>
+      </c>
+      <c r="G128" t="s">
+        <v>148</v>
+      </c>
+      <c r="H128" t="s">
+        <v>201</v>
+      </c>
+      <c r="I128" t="s">
+        <v>269</v>
+      </c>
+      <c r="J128" t="s">
+        <v>204</v>
+      </c>
+      <c r="K128" t="s">
+        <v>218</v>
+      </c>
+      <c r="L128" t="s">
+        <v>320</v>
       </c>
       <c r="M128" t="s">
-        <v>659</v>
-      </c>
-      <c r="N128" s="10"/>
+        <v>372</v>
+      </c>
       <c r="O128" t="s">
-        <v>197</v>
+        <v>494</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="129" spans="1:19">
@@ -5787,22 +5728,19 @@
         <v>24</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C129" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D129" t="s">
-        <v>92</v>
-      </c>
-      <c r="E129" t="s">
-        <v>49</v>
+        <v>535</v>
+      </c>
+      <c r="F129" t="s">
+        <v>187</v>
+      </c>
+      <c r="G129" t="s">
+        <v>148</v>
       </c>
       <c r="H129" t="s">
         <v>201</v>
       </c>
       <c r="I129" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="J129" t="s">
         <v>204</v>
@@ -5810,13 +5748,43 @@
       <c r="K129" t="s">
         <v>218</v>
       </c>
+      <c r="L129" t="s">
+        <v>321</v>
+      </c>
+      <c r="M129" t="s">
+        <v>373</v>
+      </c>
+      <c r="O129" t="s">
+        <v>536</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>571</v>
+      </c>
     </row>
     <row r="130" spans="1:19">
       <c r="A130" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>31</v>
+        <v>535</v>
+      </c>
+      <c r="F130" t="s">
+        <v>347</v>
+      </c>
+      <c r="G130" t="s">
+        <v>148</v>
+      </c>
+      <c r="H130" t="s">
+        <v>201</v>
+      </c>
+      <c r="I130" t="s">
+        <v>490</v>
+      </c>
+      <c r="L130" t="s">
+        <v>460</v>
+      </c>
+      <c r="M130" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="131" spans="1:19">
@@ -5824,19 +5792,10 @@
         <v>24</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C131" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D131" t="s">
-        <v>71</v>
-      </c>
-      <c r="E131" t="s">
-        <v>49</v>
+        <v>535</v>
       </c>
       <c r="F131" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="G131" t="s">
         <v>148</v>
@@ -5845,7 +5804,7 @@
         <v>201</v>
       </c>
       <c r="I131" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="J131" t="s">
         <v>204</v>
@@ -5853,29 +5812,8 @@
       <c r="K131" t="s">
         <v>218</v>
       </c>
-      <c r="L131" t="s">
-        <v>315</v>
-      </c>
       <c r="M131" t="s">
-        <v>385</v>
-      </c>
-      <c r="N131" s="10" t="s">
-        <v>424</v>
-      </c>
-      <c r="O131" s="10" t="s">
-        <v>438</v>
-      </c>
-      <c r="P131" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q131" t="s">
-        <v>551</v>
-      </c>
-      <c r="R131" t="s">
-        <v>608</v>
-      </c>
-      <c r="S131" t="s">
-        <v>609</v>
+        <v>410</v>
       </c>
     </row>
     <row r="132" spans="1:19">
@@ -5883,10 +5821,10 @@
         <v>24</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>32</v>
+        <v>535</v>
       </c>
       <c r="F132" t="s">
-        <v>155</v>
+        <v>193</v>
       </c>
       <c r="G132" t="s">
         <v>148</v>
@@ -5895,7 +5833,7 @@
         <v>201</v>
       </c>
       <c r="I132" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="J132" t="s">
         <v>204</v>
@@ -5903,25 +5841,16 @@
       <c r="K132" t="s">
         <v>218</v>
       </c>
-      <c r="L132" t="s">
-        <v>449</v>
-      </c>
-      <c r="M132" t="s">
-        <v>640</v>
-      </c>
-      <c r="O132" t="s">
-        <v>502</v>
-      </c>
     </row>
     <row r="133" spans="1:19">
       <c r="A133" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>32</v>
+        <v>535</v>
       </c>
       <c r="F133" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="G133" t="s">
         <v>148</v>
@@ -5929,8 +5858,8 @@
       <c r="H133" t="s">
         <v>201</v>
       </c>
-      <c r="O133" t="s">
-        <v>538</v>
+      <c r="I133" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="134" spans="1:19">
@@ -5938,19 +5867,10 @@
         <v>24</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C134" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D134" t="s">
-        <v>70</v>
-      </c>
-      <c r="E134" t="s">
-        <v>49</v>
+        <v>535</v>
       </c>
       <c r="F134" t="s">
-        <v>153</v>
+        <v>361</v>
       </c>
       <c r="G134" t="s">
         <v>148</v>
@@ -5959,28 +5879,7 @@
         <v>201</v>
       </c>
       <c r="I134" t="s">
-        <v>277</v>
-      </c>
-      <c r="J134" t="s">
-        <v>204</v>
-      </c>
-      <c r="K134" t="s">
-        <v>218</v>
-      </c>
-      <c r="L134" t="s">
-        <v>334</v>
-      </c>
-      <c r="M134" t="s">
-        <v>381</v>
-      </c>
-      <c r="O134" t="s">
-        <v>540</v>
-      </c>
-      <c r="P134" t="s">
-        <v>543</v>
-      </c>
-      <c r="Q134" t="s">
-        <v>547</v>
+        <v>492</v>
       </c>
     </row>
     <row r="135" spans="1:19">
@@ -5988,19 +5887,10 @@
         <v>24</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C135" s="6">
-        <v>253</v>
-      </c>
-      <c r="D135" t="s">
-        <v>90</v>
-      </c>
-      <c r="E135" t="s">
-        <v>49</v>
+        <v>535</v>
       </c>
       <c r="F135" t="s">
-        <v>220</v>
+        <v>573</v>
       </c>
       <c r="G135" t="s">
         <v>148</v>
@@ -6009,16 +5899,7 @@
         <v>201</v>
       </c>
       <c r="I135" t="s">
-        <v>278</v>
-      </c>
-      <c r="J135" t="s">
-        <v>204</v>
-      </c>
-      <c r="K135" t="s">
-        <v>218</v>
-      </c>
-      <c r="M135" t="s">
-        <v>662</v>
+        <v>73</v>
       </c>
     </row>
     <row r="136" spans="1:19">
@@ -6026,80 +5907,65 @@
         <v>24</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>33</v>
+        <v>535</v>
       </c>
       <c r="F136" t="s">
-        <v>196</v>
+        <v>574</v>
       </c>
       <c r="G136" t="s">
         <v>148</v>
       </c>
-      <c r="H136" t="s">
-        <v>201</v>
-      </c>
-      <c r="I136" t="s">
-        <v>481</v>
-      </c>
     </row>
     <row r="137" spans="1:19">
       <c r="A137" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C137" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="D137" t="s">
-        <v>34</v>
-      </c>
-      <c r="E137" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="138" spans="1:19" ht="17" customHeight="1">
+      <c r="A138" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D138" t="s">
+        <v>74</v>
+      </c>
+      <c r="E138" t="s">
         <v>49</v>
       </c>
-      <c r="F137" t="s">
-        <v>475</v>
-      </c>
-      <c r="G137" t="s">
+      <c r="F138" t="s">
+        <v>197</v>
+      </c>
+      <c r="G138" t="s">
         <v>148</v>
       </c>
-      <c r="H137" t="s">
-        <v>201</v>
-      </c>
-      <c r="I137" t="s">
-        <v>34</v>
-      </c>
-      <c r="J137" t="s">
+      <c r="H138" t="s">
+        <v>201</v>
+      </c>
+      <c r="I138" t="s">
+        <v>273</v>
+      </c>
+      <c r="J138" t="s">
         <v>204</v>
       </c>
-      <c r="K137" t="s">
-        <v>213</v>
-      </c>
-      <c r="L137" t="s">
-        <v>463</v>
-      </c>
-      <c r="M137" t="s">
-        <v>34</v>
-      </c>
-      <c r="N137" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="O137" s="10" t="s">
-        <v>447</v>
-      </c>
-      <c r="Q137" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="138" spans="1:19">
-      <c r="A138" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B138" s="3" t="s">
-        <v>34</v>
+      <c r="K138" t="s">
+        <v>218</v>
+      </c>
+      <c r="M138" t="s">
+        <v>382</v>
+      </c>
+      <c r="N138" s="10" t="s">
+        <v>432</v>
       </c>
       <c r="O138" s="10" t="s">
-        <v>542</v>
+        <v>448</v>
       </c>
     </row>
     <row r="139" spans="1:19">
@@ -6107,55 +5973,14 @@
         <v>24</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C139" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="D139" t="s">
-        <v>89</v>
-      </c>
-      <c r="E139" t="s">
-        <v>49</v>
-      </c>
-      <c r="F139" t="s">
-        <v>195</v>
-      </c>
-      <c r="G139" t="s">
-        <v>148</v>
-      </c>
-      <c r="H139" t="s">
-        <v>201</v>
-      </c>
-      <c r="I139" t="s">
-        <v>280</v>
-      </c>
-      <c r="J139" t="s">
-        <v>204</v>
-      </c>
-      <c r="K139" t="s">
-        <v>213</v>
-      </c>
-      <c r="L139" t="s">
-        <v>462</v>
+        <v>29</v>
       </c>
       <c r="M139" t="s">
-        <v>380</v>
-      </c>
-      <c r="N139" s="10" t="s">
-        <v>577</v>
-      </c>
+        <v>669</v>
+      </c>
+      <c r="N139" s="10"/>
       <c r="O139" t="s">
-        <v>507</v>
-      </c>
-      <c r="Q139" t="s">
-        <v>539</v>
-      </c>
-      <c r="R139" t="s">
-        <v>616</v>
-      </c>
-      <c r="S139" t="s">
-        <v>617</v>
+        <v>197</v>
       </c>
     </row>
     <row r="140" spans="1:19">
@@ -6163,45 +5988,43 @@
         <v>24</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F140" t="s">
-        <v>191</v>
-      </c>
-      <c r="G140" t="s">
-        <v>148</v>
-      </c>
-      <c r="H140" t="s">
-        <v>201</v>
-      </c>
-      <c r="I140" t="s">
-        <v>281</v>
-      </c>
-      <c r="J140" t="s">
-        <v>204</v>
-      </c>
-      <c r="K140" t="s">
-        <v>218</v>
-      </c>
-      <c r="O140" t="s">
-        <v>539</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="M140" t="s">
+        <v>659</v>
+      </c>
+      <c r="N140" s="10"/>
     </row>
     <row r="141" spans="1:19">
       <c r="A141" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F141" t="s">
-        <v>192</v>
-      </c>
-      <c r="G141" t="s">
-        <v>148</v>
+        <v>30</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D141" t="s">
+        <v>92</v>
+      </c>
+      <c r="E141" t="s">
+        <v>49</v>
       </c>
       <c r="H141" t="s">
         <v>201</v>
+      </c>
+      <c r="I141" t="s">
+        <v>274</v>
+      </c>
+      <c r="J141" t="s">
+        <v>204</v>
+      </c>
+      <c r="K141" t="s">
+        <v>218</v>
+      </c>
+      <c r="M141" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="142" spans="1:19">
@@ -6209,34 +6032,7 @@
         <v>24</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C142" s="6">
-        <v>311</v>
-      </c>
-      <c r="D142" t="s">
-        <v>75</v>
-      </c>
-      <c r="E142" t="s">
-        <v>51</v>
-      </c>
-      <c r="I142" t="s">
-        <v>282</v>
-      </c>
-      <c r="J142" t="s">
-        <v>204</v>
-      </c>
-      <c r="K142" t="s">
-        <v>218</v>
-      </c>
-      <c r="M142" t="s">
-        <v>376</v>
-      </c>
-      <c r="O142" s="10" t="s">
-        <v>437</v>
-      </c>
-      <c r="P142" t="s">
-        <v>525</v>
+        <v>31</v>
       </c>
     </row>
     <row r="143" spans="1:19">
@@ -6244,19 +6040,58 @@
         <v>24</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C143" s="6">
-        <v>312</v>
+        <v>32</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>118</v>
       </c>
       <c r="D143" t="s">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="E143" t="s">
-        <v>51</v>
-      </c>
-      <c r="O143" t="s">
-        <v>565</v>
+        <v>49</v>
+      </c>
+      <c r="F143" t="s">
+        <v>154</v>
+      </c>
+      <c r="G143" t="s">
+        <v>148</v>
+      </c>
+      <c r="H143" t="s">
+        <v>201</v>
+      </c>
+      <c r="I143" t="s">
+        <v>275</v>
+      </c>
+      <c r="J143" t="s">
+        <v>204</v>
+      </c>
+      <c r="K143" t="s">
+        <v>218</v>
+      </c>
+      <c r="L143" t="s">
+        <v>315</v>
+      </c>
+      <c r="M143" t="s">
+        <v>385</v>
+      </c>
+      <c r="N143" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="O143" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="P143" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>551</v>
+      </c>
+      <c r="R143" t="s">
+        <v>608</v>
+      </c>
+      <c r="S143" t="s">
+        <v>609</v>
       </c>
     </row>
     <row r="144" spans="1:19">
@@ -6264,19 +6099,34 @@
         <v>24</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="C144" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="D144" t="s">
-        <v>304</v>
-      </c>
-      <c r="E144" t="s">
-        <v>49</v>
+        <v>32</v>
+      </c>
+      <c r="F144" t="s">
+        <v>155</v>
+      </c>
+      <c r="G144" t="s">
+        <v>148</v>
+      </c>
+      <c r="H144" t="s">
+        <v>201</v>
+      </c>
+      <c r="I144" t="s">
+        <v>276</v>
+      </c>
+      <c r="J144" t="s">
+        <v>204</v>
+      </c>
+      <c r="K144" t="s">
+        <v>218</v>
+      </c>
+      <c r="L144" t="s">
+        <v>449</v>
       </c>
       <c r="M144" t="s">
-        <v>375</v>
+        <v>640</v>
+      </c>
+      <c r="O144" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="145" spans="1:19">
@@ -6284,10 +6134,22 @@
         <v>24</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>304</v>
+        <v>32</v>
+      </c>
+      <c r="F145" t="s">
+        <v>363</v>
+      </c>
+      <c r="G145" t="s">
+        <v>148</v>
+      </c>
+      <c r="H145" t="s">
+        <v>201</v>
       </c>
       <c r="M145" t="s">
-        <v>650</v>
+        <v>672</v>
+      </c>
+      <c r="O145" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="146" spans="1:19">
@@ -6295,10 +6157,49 @@
         <v>24</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>377</v>
+        <v>33</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D146" t="s">
+        <v>70</v>
+      </c>
+      <c r="E146" t="s">
+        <v>49</v>
+      </c>
+      <c r="F146" t="s">
+        <v>153</v>
+      </c>
+      <c r="G146" t="s">
+        <v>148</v>
+      </c>
+      <c r="H146" t="s">
+        <v>201</v>
+      </c>
+      <c r="I146" t="s">
+        <v>277</v>
+      </c>
+      <c r="J146" t="s">
+        <v>204</v>
+      </c>
+      <c r="K146" t="s">
+        <v>218</v>
+      </c>
+      <c r="L146" t="s">
+        <v>334</v>
       </c>
       <c r="M146" t="s">
-        <v>378</v>
+        <v>381</v>
+      </c>
+      <c r="O146" t="s">
+        <v>540</v>
+      </c>
+      <c r="P146" t="s">
+        <v>543</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="147" spans="1:19">
@@ -6306,19 +6207,19 @@
         <v>24</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C147" s="6" t="s">
-        <v>307</v>
+        <v>33</v>
+      </c>
+      <c r="C147" s="6">
+        <v>253</v>
       </c>
       <c r="D147" t="s">
-        <v>306</v>
+        <v>90</v>
       </c>
       <c r="E147" t="s">
         <v>49</v>
       </c>
       <c r="F147" t="s">
-        <v>188</v>
+        <v>220</v>
       </c>
       <c r="G147" t="s">
         <v>148</v>
@@ -6327,7 +6228,7 @@
         <v>201</v>
       </c>
       <c r="I147" t="s">
-        <v>353</v>
+        <v>278</v>
       </c>
       <c r="J147" t="s">
         <v>204</v>
@@ -6336,7 +6237,7 @@
         <v>218</v>
       </c>
       <c r="M147" t="s">
-        <v>641</v>
+        <v>662</v>
       </c>
     </row>
     <row r="148" spans="1:19">
@@ -6344,10 +6245,10 @@
         <v>24</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>345</v>
+        <v>33</v>
       </c>
       <c r="F148" t="s">
-        <v>344</v>
+        <v>196</v>
       </c>
       <c r="G148" t="s">
         <v>148</v>
@@ -6355,8 +6256,8 @@
       <c r="H148" t="s">
         <v>201</v>
       </c>
-      <c r="L148" t="s">
-        <v>330</v>
+      <c r="I148" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="149" spans="1:19">
@@ -6364,10 +6265,19 @@
         <v>24</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>455</v>
+        <v>34</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D149" t="s">
+        <v>34</v>
+      </c>
+      <c r="E149" t="s">
+        <v>49</v>
       </c>
       <c r="F149" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="G149" t="s">
         <v>148</v>
@@ -6376,16 +6286,28 @@
         <v>201</v>
       </c>
       <c r="I149" t="s">
-        <v>488</v>
+        <v>34</v>
       </c>
       <c r="J149" t="s">
         <v>204</v>
       </c>
       <c r="K149" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="L149" t="s">
-        <v>456</v>
+        <v>463</v>
+      </c>
+      <c r="M149" t="s">
+        <v>34</v>
+      </c>
+      <c r="N149" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="O149" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="150" spans="1:19">
@@ -6393,34 +6315,10 @@
         <v>24</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="H150" t="s">
-        <v>201</v>
-      </c>
-      <c r="I150" t="s">
-        <v>283</v>
-      </c>
-      <c r="J150" t="s">
-        <v>204</v>
-      </c>
-      <c r="K150" t="s">
-        <v>218</v>
-      </c>
-      <c r="M150" t="s">
-        <v>287</v>
-      </c>
-      <c r="N150" s="10" t="s">
-        <v>287</v>
+        <v>34</v>
       </c>
       <c r="O150" s="10" t="s">
-        <v>435</v>
-      </c>
-      <c r="R150" t="s">
-        <v>604</v>
-      </c>
-      <c r="S150" t="s">
-        <v>605</v>
+        <v>542</v>
       </c>
     </row>
     <row r="151" spans="1:19">
@@ -6428,14 +6326,55 @@
         <v>24</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>406</v>
+        <v>35</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D151" t="s">
+        <v>89</v>
+      </c>
+      <c r="E151" t="s">
+        <v>49</v>
+      </c>
+      <c r="F151" t="s">
+        <v>195</v>
+      </c>
+      <c r="G151" t="s">
+        <v>148</v>
+      </c>
+      <c r="H151" t="s">
+        <v>201</v>
+      </c>
+      <c r="I151" t="s">
+        <v>280</v>
+      </c>
+      <c r="J151" t="s">
+        <v>204</v>
+      </c>
+      <c r="K151" t="s">
+        <v>213</v>
+      </c>
+      <c r="L151" t="s">
+        <v>462</v>
       </c>
       <c r="M151" t="s">
-        <v>663</v>
-      </c>
-      <c r="N151" s="10"/>
-      <c r="O151" s="10" t="s">
-        <v>537</v>
+        <v>380</v>
+      </c>
+      <c r="N151" s="10" t="s">
+        <v>577</v>
+      </c>
+      <c r="O151" t="s">
+        <v>507</v>
+      </c>
+      <c r="Q151" t="s">
+        <v>539</v>
+      </c>
+      <c r="R151" t="s">
+        <v>616</v>
+      </c>
+      <c r="S151" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="152" spans="1:19">
@@ -6443,10 +6382,28 @@
         <v>24</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="M152" t="s">
-        <v>38</v>
+        <v>35</v>
+      </c>
+      <c r="F152" t="s">
+        <v>191</v>
+      </c>
+      <c r="G152" t="s">
+        <v>148</v>
+      </c>
+      <c r="H152" t="s">
+        <v>201</v>
+      </c>
+      <c r="I152" t="s">
+        <v>281</v>
+      </c>
+      <c r="J152" t="s">
+        <v>204</v>
+      </c>
+      <c r="K152" t="s">
+        <v>218</v>
+      </c>
+      <c r="O152" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="153" spans="1:19">
@@ -6454,13 +6411,16 @@
         <v>24</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="R153" t="s">
-        <v>602</v>
-      </c>
-      <c r="S153" t="s">
-        <v>603</v>
+        <v>35</v>
+      </c>
+      <c r="F153" t="s">
+        <v>192</v>
+      </c>
+      <c r="G153" t="s">
+        <v>148</v>
+      </c>
+      <c r="H153" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="154" spans="1:19">
@@ -6468,16 +6428,34 @@
         <v>24</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="F154" t="s">
-        <v>470</v>
-      </c>
-      <c r="G154" t="s">
-        <v>148</v>
-      </c>
-      <c r="H154" t="s">
-        <v>201</v>
+        <v>36</v>
+      </c>
+      <c r="C154" s="6">
+        <v>311</v>
+      </c>
+      <c r="D154" t="s">
+        <v>75</v>
+      </c>
+      <c r="E154" t="s">
+        <v>51</v>
+      </c>
+      <c r="I154" t="s">
+        <v>282</v>
+      </c>
+      <c r="J154" t="s">
+        <v>204</v>
+      </c>
+      <c r="K154" t="s">
+        <v>218</v>
+      </c>
+      <c r="M154" t="s">
+        <v>376</v>
+      </c>
+      <c r="O154" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="P154" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="155" spans="1:19">
@@ -6485,10 +6463,19 @@
         <v>24</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>534</v>
+        <v>36</v>
+      </c>
+      <c r="C155" s="6">
+        <v>312</v>
+      </c>
+      <c r="D155" t="s">
+        <v>135</v>
+      </c>
+      <c r="E155" t="s">
+        <v>51</v>
       </c>
       <c r="O155" t="s">
-        <v>533</v>
+        <v>565</v>
       </c>
     </row>
     <row r="156" spans="1:19">
@@ -6496,10 +6483,19 @@
         <v>24</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="Q156" t="s">
-        <v>550</v>
+        <v>304</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="D156" t="s">
+        <v>304</v>
+      </c>
+      <c r="E156" t="s">
+        <v>49</v>
+      </c>
+      <c r="M156" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="157" spans="1:19">
@@ -6507,392 +6503,270 @@
         <v>24</v>
       </c>
       <c r="B157" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="M157" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="158" spans="1:19">
+      <c r="A158" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="M158" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="159" spans="1:19">
+      <c r="A159" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="M159" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="160" spans="1:19">
+      <c r="A160" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="D160" t="s">
+        <v>306</v>
+      </c>
+      <c r="E160" t="s">
+        <v>49</v>
+      </c>
+      <c r="F160" t="s">
+        <v>188</v>
+      </c>
+      <c r="G160" t="s">
+        <v>148</v>
+      </c>
+      <c r="H160" t="s">
+        <v>201</v>
+      </c>
+      <c r="I160" t="s">
+        <v>353</v>
+      </c>
+      <c r="J160" t="s">
+        <v>204</v>
+      </c>
+      <c r="K160" t="s">
+        <v>218</v>
+      </c>
+      <c r="M160" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="161" spans="1:19">
+      <c r="A161" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="F161" t="s">
+        <v>344</v>
+      </c>
+      <c r="G161" t="s">
+        <v>148</v>
+      </c>
+      <c r="H161" t="s">
+        <v>201</v>
+      </c>
+      <c r="L161" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="162" spans="1:19">
+      <c r="A162" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="F162" t="s">
+        <v>472</v>
+      </c>
+      <c r="G162" t="s">
+        <v>148</v>
+      </c>
+      <c r="H162" t="s">
+        <v>201</v>
+      </c>
+      <c r="I162" t="s">
+        <v>488</v>
+      </c>
+      <c r="J162" t="s">
+        <v>204</v>
+      </c>
+      <c r="K162" t="s">
+        <v>218</v>
+      </c>
+      <c r="L162" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="163" spans="1:19">
+      <c r="A163" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="H163" t="s">
+        <v>201</v>
+      </c>
+      <c r="I163" t="s">
+        <v>283</v>
+      </c>
+      <c r="J163" t="s">
+        <v>204</v>
+      </c>
+      <c r="K163" t="s">
+        <v>218</v>
+      </c>
+      <c r="M163" t="s">
+        <v>287</v>
+      </c>
+      <c r="N163" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="O163" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="R163" t="s">
+        <v>604</v>
+      </c>
+      <c r="S163" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="164" spans="1:19">
+      <c r="A164" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="M164" t="s">
+        <v>663</v>
+      </c>
+      <c r="N164" s="10"/>
+      <c r="O164" s="10" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="165" spans="1:19">
+      <c r="A165" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="M165" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="166" spans="1:19">
+      <c r="A166" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="R166" t="s">
+        <v>602</v>
+      </c>
+      <c r="S166" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="167" spans="1:19">
+      <c r="A167" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="F167" t="s">
+        <v>470</v>
+      </c>
+      <c r="G167" t="s">
+        <v>148</v>
+      </c>
+      <c r="H167" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="168" spans="1:19">
+      <c r="A168" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="O168" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="169" spans="1:19">
+      <c r="A169" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="Q169" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="170" spans="1:19">
+      <c r="A170" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B170" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="M157" t="s">
+      <c r="M170" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="158" spans="1:19">
-      <c r="A158" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B158" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C158" s="6">
-        <v>511</v>
-      </c>
-      <c r="D158" t="s">
-        <v>81</v>
-      </c>
-      <c r="E158" t="s">
-        <v>50</v>
-      </c>
-      <c r="F158" t="s">
-        <v>181</v>
-      </c>
-      <c r="G158" t="s">
-        <v>186</v>
-      </c>
-      <c r="H158" t="s">
-        <v>201</v>
-      </c>
-      <c r="J158" t="s">
-        <v>206</v>
-      </c>
-      <c r="K158" t="s">
-        <v>217</v>
-      </c>
-      <c r="L158" t="s">
-        <v>313</v>
-      </c>
-      <c r="N158" s="10" t="s">
-        <v>575</v>
-      </c>
-      <c r="P158" t="s">
-        <v>526</v>
-      </c>
-      <c r="Q158" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="159" spans="1:19">
-      <c r="A159" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B159" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F159" t="s">
-        <v>179</v>
-      </c>
-      <c r="G159" t="s">
-        <v>186</v>
-      </c>
-      <c r="H159" t="s">
-        <v>201</v>
-      </c>
-      <c r="I159" t="s">
-        <v>284</v>
-      </c>
-      <c r="J159" t="s">
-        <v>206</v>
-      </c>
-      <c r="K159" t="s">
-        <v>217</v>
-      </c>
-      <c r="L159" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="160" spans="1:19">
-      <c r="A160" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B160" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C160" s="6">
-        <v>513</v>
-      </c>
-      <c r="D160" t="s">
-        <v>82</v>
-      </c>
-      <c r="E160" t="s">
-        <v>50</v>
-      </c>
-      <c r="F160" t="s">
-        <v>177</v>
-      </c>
-      <c r="G160" t="s">
-        <v>186</v>
-      </c>
-      <c r="H160" t="s">
-        <v>201</v>
-      </c>
-      <c r="I160" t="s">
-        <v>285</v>
-      </c>
-      <c r="J160" t="s">
-        <v>206</v>
-      </c>
-      <c r="K160" t="s">
-        <v>217</v>
-      </c>
-      <c r="L160" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="161" spans="1:17">
-      <c r="A161" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B161" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F161" t="s">
-        <v>176</v>
-      </c>
-      <c r="G161" t="s">
-        <v>186</v>
-      </c>
-      <c r="H161" t="s">
-        <v>201</v>
-      </c>
-      <c r="I161" t="s">
-        <v>286</v>
-      </c>
-      <c r="J161" t="s">
-        <v>206</v>
-      </c>
-      <c r="K161" t="s">
-        <v>217</v>
-      </c>
-      <c r="L161" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="162" spans="1:17">
-      <c r="A162" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B162" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F162" t="s">
-        <v>37</v>
-      </c>
-      <c r="G162" t="s">
-        <v>186</v>
-      </c>
-      <c r="H162" t="s">
-        <v>201</v>
-      </c>
-      <c r="I162" t="s">
-        <v>287</v>
-      </c>
-      <c r="J162" t="s">
-        <v>206</v>
-      </c>
-      <c r="K162" t="s">
-        <v>213</v>
-      </c>
-      <c r="L162" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="163" spans="1:17">
-      <c r="A163" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B163" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F163" t="s">
-        <v>182</v>
-      </c>
-      <c r="G163" t="s">
-        <v>186</v>
-      </c>
-      <c r="H163" t="s">
-        <v>201</v>
-      </c>
-      <c r="I163" t="s">
-        <v>38</v>
-      </c>
-      <c r="J163" t="s">
-        <v>206</v>
-      </c>
-      <c r="K163" t="s">
-        <v>217</v>
-      </c>
-      <c r="L163" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="164" spans="1:17" ht="17" customHeight="1">
-      <c r="A164" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B164" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F164" t="s">
-        <v>357</v>
-      </c>
-      <c r="G164" t="s">
-        <v>186</v>
-      </c>
-      <c r="H164" t="s">
-        <v>201</v>
-      </c>
-      <c r="I164" t="s">
-        <v>288</v>
-      </c>
-      <c r="J164" t="s">
-        <v>206</v>
-      </c>
-      <c r="K164" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="165" spans="1:17" ht="17" customHeight="1">
-      <c r="A165" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B165" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F165" t="s">
-        <v>473</v>
-      </c>
-      <c r="G165" t="s">
-        <v>186</v>
-      </c>
-      <c r="H165" t="s">
-        <v>201</v>
-      </c>
-      <c r="I165" t="s">
-        <v>289</v>
-      </c>
-      <c r="J165" t="s">
-        <v>206</v>
-      </c>
-      <c r="K165" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="166" spans="1:17" ht="17" customHeight="1">
-      <c r="A166" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B166" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F166" t="s">
-        <v>474</v>
-      </c>
-      <c r="G166" t="s">
-        <v>186</v>
-      </c>
-      <c r="H166" t="s">
-        <v>201</v>
-      </c>
-      <c r="I166" t="s">
-        <v>290</v>
-      </c>
-      <c r="J166" t="s">
-        <v>206</v>
-      </c>
-      <c r="K166" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="167" spans="1:17" ht="17" customHeight="1">
-      <c r="A167" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B167" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H167" t="s">
-        <v>201</v>
-      </c>
-      <c r="I167" t="s">
-        <v>291</v>
-      </c>
-      <c r="J167" t="s">
-        <v>206</v>
-      </c>
-      <c r="K167" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="168" spans="1:17" ht="17" customHeight="1">
-      <c r="A168" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B168" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F168" t="s">
-        <v>180</v>
-      </c>
-      <c r="G168" t="s">
-        <v>186</v>
-      </c>
-      <c r="H168" t="s">
-        <v>201</v>
-      </c>
-      <c r="I168" t="s">
-        <v>487</v>
-      </c>
-      <c r="J168" t="s">
-        <v>206</v>
-      </c>
-      <c r="K168" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="169" spans="1:17" ht="17" customHeight="1">
-      <c r="A169" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B169" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F169" t="s">
-        <v>184</v>
-      </c>
-      <c r="G169" t="s">
-        <v>186</v>
-      </c>
-      <c r="H169" t="s">
-        <v>201</v>
-      </c>
-      <c r="I169" t="s">
-        <v>212</v>
-      </c>
-      <c r="J169" t="s">
-        <v>206</v>
-      </c>
-      <c r="K169" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="170" spans="1:17" ht="17" customHeight="1">
-      <c r="A170" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B170" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H170" t="s">
-        <v>201</v>
-      </c>
-      <c r="I170" t="s">
-        <v>489</v>
-      </c>
-      <c r="J170" t="s">
-        <v>206</v>
-      </c>
-      <c r="K170" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="171" spans="1:17" ht="17" customHeight="1">
+    <row r="171" spans="1:19">
       <c r="A171" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B171" s="4" t="s">
         <v>38</v>
       </c>
+      <c r="C171" s="6">
+        <v>511</v>
+      </c>
+      <c r="D171" t="s">
+        <v>81</v>
+      </c>
+      <c r="E171" t="s">
+        <v>50</v>
+      </c>
+      <c r="F171" t="s">
+        <v>181</v>
+      </c>
+      <c r="G171" t="s">
+        <v>186</v>
+      </c>
       <c r="H171" t="s">
         <v>201</v>
-      </c>
-      <c r="I171" t="s">
-        <v>292</v>
       </c>
       <c r="J171" t="s">
         <v>206</v>
@@ -6900,16 +6774,28 @@
       <c r="K171" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="172" spans="1:17">
+      <c r="L171" t="s">
+        <v>313</v>
+      </c>
+      <c r="N171" s="10" t="s">
+        <v>575</v>
+      </c>
+      <c r="P171" t="s">
+        <v>526</v>
+      </c>
+      <c r="Q171" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="172" spans="1:19">
       <c r="A172" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F172" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="G172" t="s">
         <v>186</v>
@@ -6918,7 +6804,7 @@
         <v>201</v>
       </c>
       <c r="I172" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="J172" t="s">
         <v>206</v>
@@ -6927,27 +6813,27 @@
         <v>217</v>
       </c>
       <c r="L172" t="s">
-        <v>458</v>
-      </c>
-      <c r="N172" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="P172" t="s">
-        <v>527</v>
-      </c>
-      <c r="Q172" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="173" spans="1:17">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="173" spans="1:19">
       <c r="A173" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="C173" s="6">
+        <v>513</v>
+      </c>
+      <c r="D173" t="s">
+        <v>82</v>
+      </c>
+      <c r="E173" t="s">
+        <v>50</v>
       </c>
       <c r="F173" t="s">
-        <v>362</v>
+        <v>177</v>
       </c>
       <c r="G173" t="s">
         <v>186</v>
@@ -6956,7 +6842,7 @@
         <v>201</v>
       </c>
       <c r="I173" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="J173" t="s">
         <v>206</v>
@@ -6964,19 +6850,28 @@
       <c r="K173" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="174" spans="1:17">
+      <c r="L173" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="174" spans="1:19">
       <c r="A174" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="F174" t="s">
+        <v>176</v>
+      </c>
+      <c r="G174" t="s">
+        <v>186</v>
       </c>
       <c r="H174" t="s">
         <v>201</v>
       </c>
       <c r="I174" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="J174" t="s">
         <v>206</v>
@@ -6984,16 +6879,19 @@
       <c r="K174" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="175" spans="1:17">
+      <c r="L174" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="175" spans="1:19">
       <c r="A175" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F175" t="s">
-        <v>178</v>
+        <v>37</v>
       </c>
       <c r="G175" t="s">
         <v>186</v>
@@ -7002,42 +6900,36 @@
         <v>201</v>
       </c>
       <c r="I175" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="J175" t="s">
         <v>206</v>
       </c>
       <c r="K175" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="L175" t="s">
-        <v>459</v>
-      </c>
-      <c r="N175" s="10" t="s">
-        <v>578</v>
-      </c>
-      <c r="P175" t="s">
-        <v>528</v>
-      </c>
-      <c r="Q175" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="176" spans="1:17">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="176" spans="1:19">
       <c r="A176" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F176" t="s">
-        <v>360</v>
+        <v>182</v>
+      </c>
+      <c r="G176" t="s">
+        <v>186</v>
       </c>
       <c r="H176" t="s">
         <v>201</v>
       </c>
       <c r="I176" t="s">
-        <v>297</v>
+        <v>38</v>
       </c>
       <c r="J176" t="s">
         <v>206</v>
@@ -7045,16 +6937,19 @@
       <c r="K176" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="177" spans="1:17">
+      <c r="L176" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="177" spans="1:17" ht="17" customHeight="1">
       <c r="A177" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>530</v>
+        <v>38</v>
       </c>
       <c r="F177" t="s">
-        <v>174</v>
+        <v>357</v>
       </c>
       <c r="G177" t="s">
         <v>186</v>
@@ -7063,7 +6958,7 @@
         <v>201</v>
       </c>
       <c r="I177" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="J177" t="s">
         <v>206</v>
@@ -7071,28 +6966,16 @@
       <c r="K177" t="s">
         <v>217</v>
       </c>
-      <c r="L177" t="s">
-        <v>452</v>
-      </c>
-      <c r="N177" s="10" t="s">
-        <v>530</v>
-      </c>
-      <c r="P177" t="s">
-        <v>529</v>
-      </c>
-      <c r="Q177" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="178" spans="1:17">
+    </row>
+    <row r="178" spans="1:17" ht="17" customHeight="1">
       <c r="A178" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>530</v>
+        <v>38</v>
       </c>
       <c r="F178" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="G178" t="s">
         <v>186</v>
@@ -7101,7 +6984,7 @@
         <v>201</v>
       </c>
       <c r="I178" t="s">
-        <v>41</v>
+        <v>289</v>
       </c>
       <c r="J178" t="s">
         <v>206</v>
@@ -7110,18 +6993,24 @@
         <v>217</v>
       </c>
     </row>
-    <row r="179" spans="1:17">
+    <row r="179" spans="1:17" ht="17" customHeight="1">
       <c r="A179" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>530</v>
+        <v>38</v>
+      </c>
+      <c r="F179" t="s">
+        <v>474</v>
+      </c>
+      <c r="G179" t="s">
+        <v>186</v>
       </c>
       <c r="H179" t="s">
         <v>201</v>
       </c>
       <c r="I179" t="s">
-        <v>211</v>
+        <v>290</v>
       </c>
       <c r="J179" t="s">
         <v>206</v>
@@ -7130,18 +7019,18 @@
         <v>217</v>
       </c>
     </row>
-    <row r="180" spans="1:17">
+    <row r="180" spans="1:17" ht="17" customHeight="1">
       <c r="A180" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>530</v>
+        <v>38</v>
       </c>
       <c r="H180" t="s">
         <v>201</v>
       </c>
       <c r="I180" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="J180" t="s">
         <v>206</v>
@@ -7150,37 +7039,76 @@
         <v>217</v>
       </c>
     </row>
-    <row r="181" spans="1:17">
+    <row r="181" spans="1:17" ht="17" customHeight="1">
       <c r="A181" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>555</v>
-      </c>
-      <c r="Q181" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="182" spans="1:17">
+        <v>38</v>
+      </c>
+      <c r="F181" t="s">
+        <v>180</v>
+      </c>
+      <c r="G181" t="s">
+        <v>186</v>
+      </c>
+      <c r="H181" t="s">
+        <v>201</v>
+      </c>
+      <c r="I181" t="s">
+        <v>487</v>
+      </c>
+      <c r="J181" t="s">
+        <v>206</v>
+      </c>
+      <c r="K181" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="182" spans="1:17" ht="17" customHeight="1">
       <c r="A182" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>556</v>
-      </c>
-      <c r="Q182" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="183" spans="1:17">
+        <v>38</v>
+      </c>
+      <c r="F182" t="s">
+        <v>184</v>
+      </c>
+      <c r="G182" t="s">
+        <v>186</v>
+      </c>
+      <c r="H182" t="s">
+        <v>201</v>
+      </c>
+      <c r="I182" t="s">
+        <v>212</v>
+      </c>
+      <c r="J182" t="s">
+        <v>206</v>
+      </c>
+      <c r="K182" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="183" spans="1:17" ht="17" customHeight="1">
       <c r="A183" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q183" t="s">
-        <v>559</v>
+        <v>38</v>
+      </c>
+      <c r="H183" t="s">
+        <v>201</v>
+      </c>
+      <c r="I183" t="s">
+        <v>489</v>
+      </c>
+      <c r="J183" t="s">
+        <v>206</v>
+      </c>
+      <c r="K183" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="184" spans="1:17" ht="17" customHeight="1">
@@ -7188,28 +7116,13 @@
         <v>37</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C184" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="D184" t="s">
-        <v>467</v>
-      </c>
-      <c r="E184" t="s">
-        <v>50</v>
-      </c>
-      <c r="F184" t="s">
-        <v>185</v>
-      </c>
-      <c r="G184" t="s">
-        <v>186</v>
+        <v>38</v>
       </c>
       <c r="H184" t="s">
         <v>201</v>
       </c>
       <c r="I184" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="J184" t="s">
         <v>206</v>
@@ -7223,10 +7136,10 @@
         <v>37</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F185" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="G185" t="s">
         <v>186</v>
@@ -7234,140 +7147,457 @@
       <c r="H185" t="s">
         <v>201</v>
       </c>
+      <c r="I185" t="s">
+        <v>293</v>
+      </c>
+      <c r="J185" t="s">
+        <v>206</v>
+      </c>
+      <c r="K185" t="s">
+        <v>217</v>
+      </c>
+      <c r="L185" t="s">
+        <v>458</v>
+      </c>
+      <c r="N185" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="P185" t="s">
+        <v>527</v>
+      </c>
+      <c r="Q185" t="s">
+        <v>554</v>
+      </c>
     </row>
     <row r="186" spans="1:17">
-      <c r="A186" s="5" t="s">
+      <c r="A186" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F186" t="s">
+        <v>362</v>
+      </c>
+      <c r="G186" t="s">
+        <v>186</v>
+      </c>
+      <c r="H186" t="s">
+        <v>201</v>
+      </c>
+      <c r="I186" t="s">
+        <v>294</v>
+      </c>
+      <c r="J186" t="s">
+        <v>206</v>
+      </c>
+      <c r="K186" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="187" spans="1:17">
+      <c r="A187" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H187" t="s">
+        <v>201</v>
+      </c>
+      <c r="I187" t="s">
+        <v>295</v>
+      </c>
+      <c r="J187" t="s">
+        <v>206</v>
+      </c>
+      <c r="K187" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="188" spans="1:17">
+      <c r="A188" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F188" t="s">
+        <v>178</v>
+      </c>
+      <c r="G188" t="s">
+        <v>186</v>
+      </c>
+      <c r="H188" t="s">
+        <v>201</v>
+      </c>
+      <c r="I188" t="s">
+        <v>296</v>
+      </c>
+      <c r="J188" t="s">
+        <v>206</v>
+      </c>
+      <c r="K188" t="s">
+        <v>217</v>
+      </c>
+      <c r="L188" t="s">
+        <v>459</v>
+      </c>
+      <c r="N188" s="10" t="s">
+        <v>578</v>
+      </c>
+      <c r="P188" t="s">
+        <v>528</v>
+      </c>
+      <c r="Q188" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="189" spans="1:17">
+      <c r="A189" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F189" t="s">
+        <v>360</v>
+      </c>
+      <c r="H189" t="s">
+        <v>201</v>
+      </c>
+      <c r="I189" t="s">
+        <v>297</v>
+      </c>
+      <c r="J189" t="s">
+        <v>206</v>
+      </c>
+      <c r="K189" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="190" spans="1:17">
+      <c r="A190" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="F190" t="s">
+        <v>174</v>
+      </c>
+      <c r="G190" t="s">
+        <v>186</v>
+      </c>
+      <c r="H190" t="s">
+        <v>201</v>
+      </c>
+      <c r="I190" t="s">
+        <v>298</v>
+      </c>
+      <c r="J190" t="s">
+        <v>206</v>
+      </c>
+      <c r="K190" t="s">
+        <v>217</v>
+      </c>
+      <c r="L190" t="s">
+        <v>452</v>
+      </c>
+      <c r="N190" s="10" t="s">
+        <v>530</v>
+      </c>
+      <c r="P190" t="s">
+        <v>529</v>
+      </c>
+      <c r="Q190" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="191" spans="1:17">
+      <c r="A191" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="F191" t="s">
+        <v>471</v>
+      </c>
+      <c r="G191" t="s">
+        <v>186</v>
+      </c>
+      <c r="H191" t="s">
+        <v>201</v>
+      </c>
+      <c r="I191" t="s">
+        <v>41</v>
+      </c>
+      <c r="J191" t="s">
+        <v>206</v>
+      </c>
+      <c r="K191" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="192" spans="1:17">
+      <c r="A192" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="H192" t="s">
+        <v>201</v>
+      </c>
+      <c r="I192" t="s">
+        <v>211</v>
+      </c>
+      <c r="J192" t="s">
+        <v>206</v>
+      </c>
+      <c r="K192" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="193" spans="1:17">
+      <c r="A193" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="H193" t="s">
+        <v>201</v>
+      </c>
+      <c r="I193" t="s">
+        <v>299</v>
+      </c>
+      <c r="J193" t="s">
+        <v>206</v>
+      </c>
+      <c r="K193" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="194" spans="1:17">
+      <c r="A194" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="Q194" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="195" spans="1:17">
+      <c r="A195" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="Q195" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="196" spans="1:17">
+      <c r="A196" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q196" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="197" spans="1:17" ht="17" customHeight="1">
+      <c r="A197" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C197" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="D197" t="s">
+        <v>467</v>
+      </c>
+      <c r="E197" t="s">
+        <v>50</v>
+      </c>
+      <c r="F197" t="s">
+        <v>185</v>
+      </c>
+      <c r="G197" t="s">
+        <v>186</v>
+      </c>
+      <c r="H197" t="s">
+        <v>201</v>
+      </c>
+      <c r="I197" t="s">
+        <v>300</v>
+      </c>
+      <c r="J197" t="s">
+        <v>206</v>
+      </c>
+      <c r="K197" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="198" spans="1:17">
+      <c r="A198" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F198" t="s">
+        <v>183</v>
+      </c>
+      <c r="G198" t="s">
+        <v>186</v>
+      </c>
+      <c r="H198" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="199" spans="1:17">
+      <c r="A199" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B186" s="5" t="s">
+      <c r="B199" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E186" t="s">
+      <c r="E199" t="s">
         <v>52</v>
       </c>
-      <c r="H186" t="s">
+      <c r="H199" t="s">
         <v>200</v>
       </c>
-      <c r="I186" t="s">
+      <c r="I199" t="s">
         <v>301</v>
       </c>
-      <c r="J186" t="s">
+      <c r="J199" t="s">
         <v>209</v>
       </c>
-      <c r="K186" t="s">
+      <c r="K199" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="187" spans="1:17">
-      <c r="A187" s="5" t="s">
+    <row r="200" spans="1:17">
+      <c r="A200" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B187" s="5" t="s">
+      <c r="B200" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="H187" t="s">
+      <c r="H200" t="s">
         <v>200</v>
       </c>
-      <c r="I187" t="s">
+      <c r="I200" t="s">
         <v>208</v>
       </c>
-      <c r="J187" t="s">
+      <c r="J200" t="s">
         <v>209</v>
       </c>
-      <c r="K187" t="s">
+      <c r="K200" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="188" spans="1:17">
-      <c r="A188" s="5" t="s">
+    <row r="201" spans="1:17">
+      <c r="A201" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B188" s="5" t="s">
+      <c r="B201" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C188" s="6" t="s">
+      <c r="C201" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="D188" t="s">
+      <c r="D201" t="s">
         <v>45</v>
       </c>
-      <c r="E188" t="s">
+      <c r="E201" t="s">
         <v>52</v>
       </c>
-      <c r="F188" t="s">
+      <c r="F201" t="s">
         <v>161</v>
       </c>
-      <c r="G188" t="s">
+      <c r="G201" t="s">
         <v>173</v>
       </c>
-      <c r="H188" t="s">
+      <c r="H201" t="s">
         <v>200</v>
       </c>
-      <c r="I188" t="s">
+      <c r="I201" t="s">
         <v>45</v>
       </c>
-      <c r="J188" t="s">
+      <c r="J201" t="s">
         <v>209</v>
       </c>
-      <c r="K188" t="s">
+      <c r="K201" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="189" spans="1:17">
-      <c r="A189" s="5" t="s">
+    <row r="202" spans="1:17">
+      <c r="A202" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B189" s="5" t="s">
+      <c r="B202" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C189" s="6" t="s">
+      <c r="C202" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="D189" t="s">
+      <c r="D202" t="s">
         <v>91</v>
       </c>
-      <c r="E189" t="s">
+      <c r="E202" t="s">
         <v>52</v>
       </c>
-      <c r="H189" t="s">
+      <c r="H202" t="s">
         <v>200</v>
       </c>
-      <c r="I189" t="s">
+      <c r="I202" t="s">
         <v>302</v>
       </c>
-      <c r="J189" t="s">
+      <c r="J202" t="s">
         <v>209</v>
       </c>
-      <c r="K189" t="s">
+      <c r="K202" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="190" spans="1:17">
-      <c r="A190" s="5" t="s">
+    <row r="203" spans="1:17">
+      <c r="A203" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B190" s="5" t="s">
+      <c r="B203" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C190" s="6" t="s">
+      <c r="C203" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="D190" t="s">
+      <c r="D203" t="s">
         <v>47</v>
       </c>
-      <c r="E190" t="s">
+      <c r="E203" t="s">
         <v>52</v>
       </c>
-      <c r="H190" t="s">
+      <c r="H203" t="s">
         <v>200</v>
       </c>
-      <c r="I190" t="s">
+      <c r="I203" t="s">
         <v>303</v>
       </c>
-      <c r="J190" t="s">
+      <c r="J203" t="s">
         <v>209</v>
       </c>
-      <c r="K190" t="s">
+      <c r="K203" t="s">
         <v>214</v>
       </c>
     </row>

--- a/benefit_indexing.xlsx
+++ b/benefit_indexing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/BryanMak/Documents/RawClaimMCR-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9D8EE6-1B1E-2E45-ADAF-37C79128B5FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21CC6EFB-52F6-824E-8CF4-E156755A4E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-18340" yWindow="-21600" windowWidth="38400" windowHeight="21600" xr2:uid="{A0161F8B-45E3-674F-BD1A-B040F75BC5F2}"/>
+    <workbookView xWindow="-18340" yWindow="-21000" windowWidth="38400" windowHeight="21000" xr2:uid="{A0161F8B-45E3-674F-BD1A-B040F75BC5F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="689">
   <si>
     <t>Daily Room &amp; Board</t>
   </si>
@@ -2097,6 +2097,12 @@
   </si>
   <si>
     <t xml:space="preserve">Surgeon Fees - Inter </t>
+  </si>
+  <si>
+    <t>Specialist Consultation (rw all)</t>
+  </si>
+  <si>
+    <t>Viral Warts &amp; Skin Lesions (EXCLUDE SMM)</t>
   </si>
 </sst>
 </file>
@@ -2531,7 +2537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4FDC71E-C596-D04E-840B-E0EAE83F6708}">
-  <dimension ref="A1:S203"/>
+  <dimension ref="A1:S205"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
@@ -2975,16 +2981,13 @@
         <v>23</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>48</v>
+        <v>364</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="I12" t="s">
+        <v>688</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -2992,45 +2995,39 @@
         <v>23</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>140</v>
+        <v>66</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F13" t="s">
-        <v>160</v>
-      </c>
-      <c r="G13" t="s">
-        <v>173</v>
-      </c>
     </row>
     <row r="14" spans="1:19">
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" t="s">
-        <v>86</v>
-      </c>
-      <c r="E14" t="s">
+        <v>366</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="M14" t="s">
-        <v>661</v>
-      </c>
-      <c r="N14" s="10" t="s">
-        <v>580</v>
+      <c r="F14" t="s">
+        <v>160</v>
+      </c>
+      <c r="G14" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3038,34 +3035,22 @@
         <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="E15" t="s">
         <v>48</v>
       </c>
-      <c r="H15" t="s">
-        <v>200</v>
-      </c>
-      <c r="I15" t="s">
-        <v>230</v>
-      </c>
-      <c r="J15" t="s">
-        <v>203</v>
-      </c>
-      <c r="K15" t="s">
-        <v>215</v>
-      </c>
-      <c r="L15" t="s">
-        <v>332</v>
-      </c>
       <c r="M15" t="s">
-        <v>403</v>
+        <v>661</v>
+      </c>
+      <c r="N15" s="10" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3075,11 +3060,20 @@
       <c r="B16" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="C16" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" t="s">
+        <v>48</v>
+      </c>
       <c r="H16" t="s">
         <v>200</v>
       </c>
       <c r="I16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J16" t="s">
         <v>203</v>
@@ -3087,8 +3081,11 @@
       <c r="K16" t="s">
         <v>215</v>
       </c>
+      <c r="L16" t="s">
+        <v>332</v>
+      </c>
       <c r="M16" t="s">
-        <v>651</v>
+        <v>403</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3096,22 +3093,13 @@
         <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" t="s">
-        <v>55</v>
-      </c>
-      <c r="E17" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H17" t="s">
         <v>200</v>
       </c>
       <c r="I17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J17" t="s">
         <v>203</v>
@@ -3119,11 +3107,8 @@
       <c r="K17" t="s">
         <v>215</v>
       </c>
-      <c r="L17" t="s">
-        <v>322</v>
-      </c>
       <c r="M17" t="s">
-        <v>402</v>
+        <v>651</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -3133,11 +3118,20 @@
       <c r="B18" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="C18" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" t="s">
+        <v>48</v>
+      </c>
       <c r="H18" t="s">
         <v>200</v>
       </c>
       <c r="I18" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J18" t="s">
         <v>203</v>
@@ -3145,8 +3139,11 @@
       <c r="K18" t="s">
         <v>215</v>
       </c>
+      <c r="L18" t="s">
+        <v>322</v>
+      </c>
       <c r="M18" t="s">
-        <v>656</v>
+        <v>402</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -3156,8 +3153,20 @@
       <c r="B19" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="H19" t="s">
+        <v>200</v>
+      </c>
+      <c r="I19" t="s">
+        <v>233</v>
+      </c>
+      <c r="J19" t="s">
+        <v>203</v>
+      </c>
+      <c r="K19" t="s">
+        <v>215</v>
+      </c>
       <c r="M19" t="s">
-        <v>686</v>
+        <v>656</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -3165,39 +3174,11 @@
         <v>23</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D20" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" t="s">
-        <v>48</v>
-      </c>
-      <c r="H20" t="s">
-        <v>200</v>
-      </c>
-      <c r="I20" t="s">
-        <v>234</v>
-      </c>
-      <c r="J20" t="s">
-        <v>203</v>
-      </c>
-      <c r="K20" t="s">
-        <v>215</v>
-      </c>
-      <c r="L20" t="s">
-        <v>319</v>
+        <v>5</v>
       </c>
       <c r="M20" t="s">
-        <v>404</v>
-      </c>
-      <c r="N20" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="O20" s="10"/>
+        <v>686</v>
+      </c>
     </row>
     <row r="21" spans="1:19">
       <c r="A21" s="1" t="s">
@@ -3206,11 +3187,20 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="C21" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" t="s">
+        <v>48</v>
+      </c>
       <c r="H21" t="s">
         <v>200</v>
       </c>
       <c r="I21" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J21" t="s">
         <v>203</v>
@@ -3218,37 +3208,38 @@
       <c r="K21" t="s">
         <v>215</v>
       </c>
+      <c r="L21" t="s">
+        <v>319</v>
+      </c>
       <c r="M21" t="s">
-        <v>638</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="N21" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="O21" s="10"/>
     </row>
     <row r="22" spans="1:19">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="F22" t="s">
-        <v>157</v>
-      </c>
-      <c r="G22" t="s">
-        <v>173</v>
-      </c>
-      <c r="O22" s="10" t="s">
-        <v>440</v>
-      </c>
-      <c r="P22" t="s">
-        <v>516</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>553</v>
-      </c>
-      <c r="R22" t="s">
-        <v>599</v>
-      </c>
-      <c r="S22" t="s">
-        <v>600</v>
+        <v>6</v>
+      </c>
+      <c r="H22" t="s">
+        <v>200</v>
+      </c>
+      <c r="I22" t="s">
+        <v>235</v>
+      </c>
+      <c r="J22" t="s">
+        <v>203</v>
+      </c>
+      <c r="K22" t="s">
+        <v>215</v>
+      </c>
+      <c r="M22" t="s">
+        <v>638</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -3258,8 +3249,26 @@
       <c r="B23" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="O23" t="s">
-        <v>506</v>
+      <c r="F23" t="s">
+        <v>157</v>
+      </c>
+      <c r="G23" t="s">
+        <v>173</v>
+      </c>
+      <c r="O23" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="P23" t="s">
+        <v>516</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>553</v>
+      </c>
+      <c r="R23" t="s">
+        <v>599</v>
+      </c>
+      <c r="S23" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -3267,22 +3276,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D24" t="s">
-        <v>87</v>
-      </c>
-      <c r="E24" t="s">
-        <v>48</v>
-      </c>
-      <c r="M24" t="s">
-        <v>386</v>
-      </c>
-      <c r="N24" s="10" t="s">
-        <v>582</v>
+        <v>596</v>
+      </c>
+      <c r="O24" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -3292,45 +3289,33 @@
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="C25" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" t="s">
+        <v>48</v>
+      </c>
       <c r="M25" t="s">
-        <v>673</v>
-      </c>
-      <c r="N25" s="10"/>
+        <v>386</v>
+      </c>
+      <c r="N25" s="10" t="s">
+        <v>582</v>
+      </c>
     </row>
     <row r="26" spans="1:19">
       <c r="A26" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D26" t="s">
-        <v>57</v>
-      </c>
-      <c r="E26" t="s">
-        <v>48</v>
-      </c>
-      <c r="H26" t="s">
-        <v>200</v>
-      </c>
-      <c r="I26" t="s">
-        <v>236</v>
-      </c>
-      <c r="J26" t="s">
-        <v>203</v>
-      </c>
-      <c r="K26" t="s">
-        <v>215</v>
-      </c>
-      <c r="L26" t="s">
-        <v>340</v>
+        <v>7</v>
       </c>
       <c r="M26" t="s">
-        <v>387</v>
-      </c>
+        <v>673</v>
+      </c>
+      <c r="N26" s="10"/>
     </row>
     <row r="27" spans="1:19">
       <c r="A27" s="1" t="s">
@@ -3339,8 +3324,32 @@
       <c r="B27" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="C27" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D27" t="s">
+        <v>57</v>
+      </c>
+      <c r="E27" t="s">
+        <v>48</v>
+      </c>
+      <c r="H27" t="s">
+        <v>200</v>
+      </c>
+      <c r="I27" t="s">
+        <v>236</v>
+      </c>
+      <c r="J27" t="s">
+        <v>203</v>
+      </c>
+      <c r="K27" t="s">
+        <v>215</v>
+      </c>
+      <c r="L27" t="s">
+        <v>340</v>
+      </c>
       <c r="M27" t="s">
-        <v>652</v>
+        <v>387</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -3348,34 +3357,10 @@
         <v>23</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D28" t="s">
-        <v>58</v>
-      </c>
-      <c r="E28" t="s">
-        <v>48</v>
-      </c>
-      <c r="H28" t="s">
-        <v>200</v>
-      </c>
-      <c r="I28" t="s">
-        <v>237</v>
-      </c>
-      <c r="J28" t="s">
-        <v>203</v>
-      </c>
-      <c r="K28" t="s">
-        <v>215</v>
-      </c>
-      <c r="L28" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="M28" t="s">
-        <v>388</v>
+        <v>652</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -3385,8 +3370,32 @@
       <c r="B29" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="C29" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D29" t="s">
+        <v>58</v>
+      </c>
+      <c r="E29" t="s">
+        <v>48</v>
+      </c>
+      <c r="H29" t="s">
+        <v>200</v>
+      </c>
+      <c r="I29" t="s">
+        <v>237</v>
+      </c>
+      <c r="J29" t="s">
+        <v>203</v>
+      </c>
+      <c r="K29" t="s">
+        <v>215</v>
+      </c>
+      <c r="L29" t="s">
+        <v>323</v>
+      </c>
       <c r="M29" t="s">
-        <v>657</v>
+        <v>388</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -3397,7 +3406,7 @@
         <v>9</v>
       </c>
       <c r="M30" t="s">
-        <v>674</v>
+        <v>657</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -3405,37 +3414,10 @@
         <v>23</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="D31" t="s">
-        <v>62</v>
-      </c>
-      <c r="E31" t="s">
-        <v>48</v>
-      </c>
-      <c r="H31" t="s">
-        <v>200</v>
-      </c>
-      <c r="I31" t="s">
-        <v>238</v>
-      </c>
-      <c r="J31" t="s">
-        <v>203</v>
-      </c>
-      <c r="K31" t="s">
-        <v>215</v>
-      </c>
-      <c r="L31" t="s">
-        <v>337</v>
+        <v>9</v>
       </c>
       <c r="M31" t="s">
-        <v>389</v>
-      </c>
-      <c r="N31" s="10" t="s">
-        <v>430</v>
+        <v>674</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -3445,40 +3427,48 @@
       <c r="B32" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="C32" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D32" t="s">
+        <v>62</v>
+      </c>
+      <c r="E32" t="s">
+        <v>48</v>
+      </c>
+      <c r="H32" t="s">
+        <v>200</v>
+      </c>
+      <c r="I32" t="s">
+        <v>238</v>
+      </c>
+      <c r="J32" t="s">
+        <v>203</v>
+      </c>
+      <c r="K32" t="s">
+        <v>215</v>
+      </c>
+      <c r="L32" t="s">
+        <v>337</v>
+      </c>
       <c r="M32" t="s">
-        <v>644</v>
-      </c>
-      <c r="N32" s="10"/>
+        <v>389</v>
+      </c>
+      <c r="N32" s="10" t="s">
+        <v>430</v>
+      </c>
     </row>
     <row r="33" spans="1:19">
       <c r="A33" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="F33" t="s">
-        <v>158</v>
-      </c>
-      <c r="G33" t="s">
-        <v>173</v>
+        <v>10</v>
+      </c>
+      <c r="M33" t="s">
+        <v>644</v>
       </c>
       <c r="N33" s="10"/>
-      <c r="O33" s="10" t="s">
-        <v>444</v>
-      </c>
-      <c r="P33" t="s">
-        <v>517</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>563</v>
-      </c>
-      <c r="R33" t="s">
-        <v>597</v>
-      </c>
-      <c r="S33" t="s">
-        <v>598</v>
-      </c>
     </row>
     <row r="34" spans="1:19">
       <c r="A34" s="1" t="s">
@@ -3487,64 +3477,59 @@
       <c r="B34" s="1" t="s">
         <v>595</v>
       </c>
+      <c r="F34" t="s">
+        <v>158</v>
+      </c>
+      <c r="G34" t="s">
+        <v>173</v>
+      </c>
       <c r="N34" s="10"/>
-      <c r="O34" t="s">
+      <c r="O34" s="10" t="s">
+        <v>444</v>
+      </c>
+      <c r="P34" t="s">
+        <v>517</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>563</v>
+      </c>
+      <c r="R34" t="s">
+        <v>597</v>
+      </c>
+      <c r="S34" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19">
+      <c r="A35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="N35" s="10"/>
+      <c r="O35" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="17" customHeight="1">
-      <c r="A35" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B35" s="1" t="s">
+    <row r="36" spans="1:19" ht="17" customHeight="1">
+      <c r="A36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C36" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D36" t="s">
         <v>88</v>
-      </c>
-      <c r="E35" t="s">
-        <v>48</v>
-      </c>
-      <c r="N35" s="10" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19">
-      <c r="A36" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D36" t="s">
-        <v>59</v>
       </c>
       <c r="E36" t="s">
         <v>48</v>
       </c>
-      <c r="H36" t="s">
-        <v>200</v>
-      </c>
-      <c r="I36" t="s">
-        <v>239</v>
-      </c>
-      <c r="J36" t="s">
-        <v>203</v>
-      </c>
-      <c r="K36" t="s">
-        <v>215</v>
-      </c>
-      <c r="L36" t="s">
-        <v>333</v>
-      </c>
-      <c r="M36" t="s">
-        <v>395</v>
+      <c r="N36" s="10" t="s">
+        <v>581</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -3554,11 +3539,20 @@
       <c r="B37" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="C37" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D37" t="s">
+        <v>59</v>
+      </c>
+      <c r="E37" t="s">
+        <v>48</v>
+      </c>
       <c r="H37" t="s">
         <v>200</v>
       </c>
       <c r="I37" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J37" t="s">
         <v>203</v>
@@ -3566,8 +3560,11 @@
       <c r="K37" t="s">
         <v>215</v>
       </c>
+      <c r="L37" t="s">
+        <v>333</v>
+      </c>
       <c r="M37" t="s">
-        <v>653</v>
+        <v>395</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -3577,8 +3574,20 @@
       <c r="B38" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="H38" t="s">
+        <v>200</v>
+      </c>
+      <c r="I38" t="s">
+        <v>240</v>
+      </c>
+      <c r="J38" t="s">
+        <v>203</v>
+      </c>
+      <c r="K38" t="s">
+        <v>215</v>
+      </c>
       <c r="M38" t="s">
-        <v>678</v>
+        <v>653</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -3586,34 +3595,10 @@
         <v>23</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D39" t="s">
-        <v>60</v>
-      </c>
-      <c r="E39" t="s">
-        <v>48</v>
-      </c>
-      <c r="H39" t="s">
-        <v>200</v>
-      </c>
-      <c r="I39" t="s">
-        <v>241</v>
-      </c>
-      <c r="J39" t="s">
-        <v>203</v>
-      </c>
-      <c r="K39" t="s">
-        <v>215</v>
-      </c>
-      <c r="L39" t="s">
-        <v>324</v>
+        <v>12</v>
       </c>
       <c r="M39" t="s">
-        <v>394</v>
+        <v>678</v>
       </c>
     </row>
     <row r="40" spans="1:19">
@@ -3623,11 +3608,20 @@
       <c r="B40" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="C40" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D40" t="s">
+        <v>60</v>
+      </c>
+      <c r="E40" t="s">
+        <v>48</v>
+      </c>
       <c r="H40" t="s">
         <v>200</v>
       </c>
       <c r="I40" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J40" t="s">
         <v>203</v>
@@ -3635,8 +3629,11 @@
       <c r="K40" t="s">
         <v>215</v>
       </c>
+      <c r="L40" t="s">
+        <v>324</v>
+      </c>
       <c r="M40" t="s">
-        <v>658</v>
+        <v>394</v>
       </c>
     </row>
     <row r="41" spans="1:19">
@@ -3646,8 +3643,20 @@
       <c r="B41" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="H41" t="s">
+        <v>200</v>
+      </c>
+      <c r="I41" t="s">
+        <v>242</v>
+      </c>
+      <c r="J41" t="s">
+        <v>203</v>
+      </c>
+      <c r="K41" t="s">
+        <v>215</v>
+      </c>
       <c r="M41" t="s">
-        <v>677</v>
+        <v>658</v>
       </c>
     </row>
     <row r="42" spans="1:19">
@@ -3655,37 +3664,10 @@
         <v>23</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D42" t="s">
-        <v>61</v>
-      </c>
-      <c r="E42" t="s">
-        <v>48</v>
-      </c>
-      <c r="H42" t="s">
-        <v>200</v>
-      </c>
-      <c r="I42" t="s">
-        <v>243</v>
-      </c>
-      <c r="J42" t="s">
-        <v>203</v>
-      </c>
-      <c r="K42" t="s">
-        <v>215</v>
-      </c>
-      <c r="L42" t="s">
-        <v>338</v>
+        <v>13</v>
       </c>
       <c r="M42" t="s">
-        <v>396</v>
-      </c>
-      <c r="N42" s="10" t="s">
-        <v>428</v>
+        <v>677</v>
       </c>
     </row>
     <row r="43" spans="1:19">
@@ -3695,11 +3677,20 @@
       <c r="B43" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="C43" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D43" t="s">
+        <v>61</v>
+      </c>
+      <c r="E43" t="s">
+        <v>48</v>
+      </c>
       <c r="H43" t="s">
         <v>200</v>
       </c>
       <c r="I43" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J43" t="s">
         <v>203</v>
@@ -3707,8 +3698,14 @@
       <c r="K43" t="s">
         <v>215</v>
       </c>
+      <c r="L43" t="s">
+        <v>338</v>
+      </c>
       <c r="M43" t="s">
-        <v>679</v>
+        <v>396</v>
+      </c>
+      <c r="N43" s="10" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="44" spans="1:19">
@@ -3718,8 +3715,20 @@
       <c r="B44" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="H44" t="s">
+        <v>200</v>
+      </c>
+      <c r="I44" t="s">
+        <v>244</v>
+      </c>
+      <c r="J44" t="s">
+        <v>203</v>
+      </c>
+      <c r="K44" t="s">
+        <v>215</v>
+      </c>
       <c r="M44" t="s">
-        <v>666</v>
+        <v>679</v>
       </c>
     </row>
     <row r="45" spans="1:19">
@@ -3727,28 +3736,10 @@
         <v>23</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="F45" t="s">
-        <v>159</v>
-      </c>
-      <c r="G45" t="s">
-        <v>173</v>
-      </c>
-      <c r="O45" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="P45" t="s">
-        <v>518</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>159</v>
-      </c>
-      <c r="R45" t="s">
-        <v>592</v>
-      </c>
-      <c r="S45" t="s">
-        <v>593</v>
+        <v>14</v>
+      </c>
+      <c r="M45" t="s">
+        <v>666</v>
       </c>
     </row>
     <row r="46" spans="1:19">
@@ -3758,8 +3749,26 @@
       <c r="B46" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="O46" t="s">
-        <v>505</v>
+      <c r="F46" t="s">
+        <v>159</v>
+      </c>
+      <c r="G46" t="s">
+        <v>173</v>
+      </c>
+      <c r="O46" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="P46" t="s">
+        <v>518</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>159</v>
+      </c>
+      <c r="R46" t="s">
+        <v>592</v>
+      </c>
+      <c r="S46" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="47" spans="1:19">
@@ -3767,55 +3776,10 @@
         <v>23</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D47" t="s">
-        <v>85</v>
-      </c>
-      <c r="E47" t="s">
-        <v>48</v>
-      </c>
-      <c r="F47" t="s">
-        <v>167</v>
-      </c>
-      <c r="G47" t="s">
-        <v>173</v>
-      </c>
-      <c r="H47" t="s">
-        <v>200</v>
-      </c>
-      <c r="I47" t="s">
-        <v>245</v>
-      </c>
-      <c r="J47" t="s">
-        <v>203</v>
-      </c>
-      <c r="K47" t="s">
-        <v>215</v>
-      </c>
-      <c r="L47" t="s">
-        <v>341</v>
-      </c>
-      <c r="M47" t="s">
-        <v>401</v>
-      </c>
-      <c r="N47" t="s">
-        <v>637</v>
-      </c>
-      <c r="P47" t="s">
-        <v>519</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>572</v>
-      </c>
-      <c r="R47" t="s">
-        <v>622</v>
-      </c>
-      <c r="S47" t="s">
-        <v>623</v>
+        <v>594</v>
+      </c>
+      <c r="O47" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="48" spans="1:19">
@@ -3825,8 +3789,17 @@
       <c r="B48" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="C48" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D48" t="s">
+        <v>85</v>
+      </c>
+      <c r="E48" t="s">
+        <v>48</v>
+      </c>
       <c r="F48" t="s">
-        <v>348</v>
+        <v>167</v>
       </c>
       <c r="G48" t="s">
         <v>173</v>
@@ -3835,7 +3808,7 @@
         <v>200</v>
       </c>
       <c r="I48" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J48" t="s">
         <v>203</v>
@@ -3843,8 +3816,26 @@
       <c r="K48" t="s">
         <v>215</v>
       </c>
+      <c r="L48" t="s">
+        <v>341</v>
+      </c>
       <c r="M48" t="s">
-        <v>685</v>
+        <v>401</v>
+      </c>
+      <c r="N48" t="s">
+        <v>637</v>
+      </c>
+      <c r="P48" t="s">
+        <v>519</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>572</v>
+      </c>
+      <c r="R48" t="s">
+        <v>622</v>
+      </c>
+      <c r="S48" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="49" spans="1:19">
@@ -3852,25 +3843,28 @@
         <v>23</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="D49" t="s">
-        <v>465</v>
-      </c>
-      <c r="E49" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="F49" t="s">
-        <v>164</v>
+        <v>348</v>
       </c>
       <c r="G49" t="s">
         <v>173</v>
       </c>
-      <c r="L49" t="s">
-        <v>343</v>
+      <c r="H49" t="s">
+        <v>200</v>
+      </c>
+      <c r="I49" t="s">
+        <v>246</v>
+      </c>
+      <c r="J49" t="s">
+        <v>203</v>
+      </c>
+      <c r="K49" t="s">
+        <v>215</v>
+      </c>
+      <c r="M49" t="s">
+        <v>685</v>
       </c>
     </row>
     <row r="50" spans="1:19">
@@ -3878,37 +3872,28 @@
         <v>23</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>132</v>
+        <v>466</v>
       </c>
       <c r="D50" t="s">
-        <v>133</v>
+        <v>465</v>
       </c>
       <c r="E50" t="s">
         <v>48</v>
       </c>
       <c r="F50" t="s">
-        <v>356</v>
+        <v>164</v>
       </c>
       <c r="G50" t="s">
         <v>173</v>
       </c>
-      <c r="H50" t="s">
-        <v>200</v>
-      </c>
       <c r="I50" t="s">
-        <v>247</v>
-      </c>
-      <c r="J50" t="s">
-        <v>203</v>
-      </c>
-      <c r="K50" t="s">
-        <v>215</v>
-      </c>
-      <c r="M50" t="s">
-        <v>684</v>
+        <v>16</v>
+      </c>
+      <c r="L50" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="51" spans="1:19">
@@ -3916,11 +3901,19 @@
         <v>23</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C51" s="7"/>
+        <v>17</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D51" t="s">
+        <v>133</v>
+      </c>
+      <c r="E51" t="s">
+        <v>48</v>
+      </c>
       <c r="F51" t="s">
-        <v>476</v>
+        <v>356</v>
       </c>
       <c r="G51" t="s">
         <v>173</v>
@@ -3928,52 +3921,58 @@
       <c r="H51" t="s">
         <v>200</v>
       </c>
+      <c r="I51" t="s">
+        <v>247</v>
+      </c>
+      <c r="J51" t="s">
+        <v>203</v>
+      </c>
+      <c r="K51" t="s">
+        <v>215</v>
+      </c>
+      <c r="M51" t="s">
+        <v>684</v>
+      </c>
     </row>
     <row r="52" spans="1:19">
       <c r="A52" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="D52" t="s">
-        <v>130</v>
-      </c>
-      <c r="E52" t="s">
-        <v>48</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="C52" s="7"/>
       <c r="F52" t="s">
-        <v>172</v>
+        <v>476</v>
       </c>
       <c r="G52" t="s">
         <v>173</v>
       </c>
+      <c r="H52" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="53" spans="1:19">
       <c r="A53" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="C53" s="7"/>
-      <c r="H53" t="s">
-        <v>200</v>
-      </c>
-      <c r="I53" t="s">
-        <v>229</v>
-      </c>
-      <c r="J53" t="s">
-        <v>203</v>
-      </c>
-      <c r="K53" t="s">
-        <v>215</v>
-      </c>
-      <c r="M53" t="s">
-        <v>399</v>
+        <v>367</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D53" t="s">
+        <v>130</v>
+      </c>
+      <c r="E53" t="s">
+        <v>48</v>
+      </c>
+      <c r="F53" t="s">
+        <v>172</v>
+      </c>
+      <c r="G53" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="54" spans="1:19">
@@ -3984,8 +3983,20 @@
         <v>511</v>
       </c>
       <c r="C54" s="7"/>
+      <c r="H54" t="s">
+        <v>200</v>
+      </c>
+      <c r="I54" t="s">
+        <v>229</v>
+      </c>
+      <c r="J54" t="s">
+        <v>203</v>
+      </c>
+      <c r="K54" t="s">
+        <v>215</v>
+      </c>
       <c r="M54" t="s">
-        <v>649</v>
+        <v>399</v>
       </c>
     </row>
     <row r="55" spans="1:19">
@@ -3997,7 +4008,7 @@
       </c>
       <c r="C55" s="7"/>
       <c r="M55" t="s">
-        <v>681</v>
+        <v>649</v>
       </c>
     </row>
     <row r="56" spans="1:19">
@@ -4009,7 +4020,7 @@
       </c>
       <c r="C56" s="7"/>
       <c r="M56" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="57" spans="1:19">
@@ -4017,26 +4028,11 @@
         <v>23</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C57" s="7"/>
-      <c r="H57" t="s">
-        <v>200</v>
-      </c>
-      <c r="I57" t="s">
-        <v>227</v>
-      </c>
-      <c r="J57" t="s">
-        <v>203</v>
-      </c>
-      <c r="K57" t="s">
-        <v>215</v>
-      </c>
       <c r="M57" t="s">
-        <v>643</v>
-      </c>
-      <c r="O57" t="s">
-        <v>510</v>
+        <v>682</v>
       </c>
     </row>
     <row r="58" spans="1:19">
@@ -4047,8 +4043,23 @@
         <v>509</v>
       </c>
       <c r="C58" s="7"/>
+      <c r="H58" t="s">
+        <v>200</v>
+      </c>
+      <c r="I58" t="s">
+        <v>227</v>
+      </c>
+      <c r="J58" t="s">
+        <v>203</v>
+      </c>
+      <c r="K58" t="s">
+        <v>215</v>
+      </c>
       <c r="M58" t="s">
-        <v>398</v>
+        <v>643</v>
+      </c>
+      <c r="O58" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="59" spans="1:19">
@@ -4060,7 +4071,7 @@
       </c>
       <c r="C59" s="7"/>
       <c r="M59" t="s">
-        <v>683</v>
+        <v>398</v>
       </c>
     </row>
     <row r="60" spans="1:19">
@@ -4068,23 +4079,11 @@
         <v>23</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>368</v>
+        <v>509</v>
       </c>
       <c r="C60" s="7"/>
-      <c r="H60" t="s">
-        <v>200</v>
-      </c>
-      <c r="I60" t="s">
-        <v>225</v>
-      </c>
-      <c r="J60" t="s">
-        <v>203</v>
-      </c>
-      <c r="K60" t="s">
-        <v>215</v>
-      </c>
       <c r="M60" t="s">
-        <v>405</v>
+        <v>683</v>
       </c>
     </row>
     <row r="61" spans="1:19">
@@ -4099,13 +4098,16 @@
         <v>200</v>
       </c>
       <c r="I61" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J61" t="s">
         <v>203</v>
       </c>
       <c r="K61" t="s">
         <v>215</v>
+      </c>
+      <c r="M61" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="62" spans="1:19">
@@ -4120,7 +4122,7 @@
         <v>200</v>
       </c>
       <c r="I62" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="J62" t="s">
         <v>203</v>
@@ -4134,28 +4136,14 @@
         <v>23</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C63" s="6">
-        <v>210</v>
-      </c>
-      <c r="D63" t="s">
-        <v>83</v>
-      </c>
-      <c r="E63" t="s">
-        <v>48</v>
-      </c>
-      <c r="F63" t="s">
-        <v>165</v>
-      </c>
-      <c r="G63" t="s">
-        <v>173</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="C63" s="7"/>
       <c r="H63" t="s">
         <v>200</v>
       </c>
       <c r="I63" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="J63" t="s">
         <v>203</v>
@@ -4163,24 +4151,6 @@
       <c r="K63" t="s">
         <v>215</v>
       </c>
-      <c r="L63" t="s">
-        <v>317</v>
-      </c>
-      <c r="M63" t="s">
-        <v>390</v>
-      </c>
-      <c r="N63" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="O63" t="s">
-        <v>496</v>
-      </c>
-      <c r="R63" t="s">
-        <v>626</v>
-      </c>
-      <c r="S63" t="s">
-        <v>627</v>
-      </c>
     </row>
     <row r="64" spans="1:19">
       <c r="A64" s="1" t="s">
@@ -4190,16 +4160,16 @@
         <v>19</v>
       </c>
       <c r="C64" s="6">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="D64" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="E64" t="s">
         <v>48</v>
       </c>
       <c r="F64" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G64" t="s">
         <v>173</v>
@@ -4208,7 +4178,7 @@
         <v>200</v>
       </c>
       <c r="I64" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J64" t="s">
         <v>203</v>
@@ -4217,10 +4187,22 @@
         <v>215</v>
       </c>
       <c r="L64" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
       <c r="M64" t="s">
-        <v>391</v>
+        <v>390</v>
+      </c>
+      <c r="N64" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="O64" t="s">
+        <v>496</v>
+      </c>
+      <c r="R64" t="s">
+        <v>626</v>
+      </c>
+      <c r="S64" t="s">
+        <v>627</v>
       </c>
     </row>
     <row r="65" spans="1:19">
@@ -4230,8 +4212,17 @@
       <c r="B65" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="C65" s="6">
+        <v>220</v>
+      </c>
+      <c r="D65" t="s">
+        <v>134</v>
+      </c>
+      <c r="E65" t="s">
+        <v>48</v>
+      </c>
       <c r="F65" t="s">
-        <v>359</v>
+        <v>170</v>
       </c>
       <c r="G65" t="s">
         <v>173</v>
@@ -4240,7 +4231,7 @@
         <v>200</v>
       </c>
       <c r="I65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J65" t="s">
         <v>203</v>
@@ -4248,8 +4239,11 @@
       <c r="K65" t="s">
         <v>215</v>
       </c>
+      <c r="L65" t="s">
+        <v>335</v>
+      </c>
       <c r="M65" t="s">
-        <v>655</v>
+        <v>391</v>
       </c>
     </row>
     <row r="66" spans="1:19">
@@ -4259,11 +4253,17 @@
       <c r="B66" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="F66" t="s">
+        <v>359</v>
+      </c>
+      <c r="G66" t="s">
+        <v>173</v>
+      </c>
       <c r="H66" t="s">
         <v>200</v>
       </c>
       <c r="I66" t="s">
-        <v>421</v>
+        <v>250</v>
       </c>
       <c r="J66" t="s">
         <v>203</v>
@@ -4271,69 +4271,36 @@
       <c r="K66" t="s">
         <v>215</v>
       </c>
+      <c r="M66" t="s">
+        <v>655</v>
+      </c>
     </row>
     <row r="67" spans="1:19">
       <c r="A67" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H67" t="s">
+        <v>200</v>
+      </c>
+      <c r="I67" t="s">
+        <v>421</v>
+      </c>
+      <c r="J67" t="s">
+        <v>203</v>
+      </c>
+      <c r="K67" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19">
+      <c r="A68" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>636</v>
-      </c>
-    </row>
-    <row r="68" spans="1:19" ht="17" customHeight="1">
-      <c r="A68" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C68" s="6">
-        <v>230</v>
-      </c>
-      <c r="D68" t="s">
-        <v>131</v>
-      </c>
-      <c r="E68" t="s">
-        <v>48</v>
-      </c>
-      <c r="F68" t="s">
-        <v>163</v>
-      </c>
-      <c r="G68" t="s">
-        <v>173</v>
-      </c>
-      <c r="H68" t="s">
-        <v>200</v>
-      </c>
-      <c r="I68" t="s">
-        <v>251</v>
-      </c>
-      <c r="J68" t="s">
-        <v>203</v>
-      </c>
-      <c r="K68" t="s">
-        <v>215</v>
-      </c>
-      <c r="L68" t="s">
-        <v>342</v>
-      </c>
-      <c r="M68" t="s">
-        <v>392</v>
-      </c>
-      <c r="N68" s="10" t="s">
-        <v>583</v>
-      </c>
-      <c r="O68" t="s">
-        <v>512</v>
-      </c>
-      <c r="P68" t="s">
-        <v>544</v>
-      </c>
-      <c r="R68" t="s">
-        <v>634</v>
-      </c>
-      <c r="S68" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="69" spans="1:19" ht="17" customHeight="1">
@@ -4343,10 +4310,54 @@
       <c r="B69" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="C69" s="6">
+        <v>230</v>
+      </c>
+      <c r="D69" t="s">
+        <v>131</v>
+      </c>
+      <c r="E69" t="s">
+        <v>48</v>
+      </c>
+      <c r="F69" t="s">
+        <v>163</v>
+      </c>
+      <c r="G69" t="s">
+        <v>173</v>
+      </c>
+      <c r="H69" t="s">
+        <v>200</v>
+      </c>
+      <c r="I69" t="s">
+        <v>251</v>
+      </c>
+      <c r="J69" t="s">
+        <v>203</v>
+      </c>
+      <c r="K69" t="s">
+        <v>215</v>
+      </c>
+      <c r="L69" t="s">
+        <v>342</v>
+      </c>
       <c r="M69" t="s">
-        <v>675</v>
-      </c>
-      <c r="N69" s="10"/>
+        <v>392</v>
+      </c>
+      <c r="N69" s="10" t="s">
+        <v>583</v>
+      </c>
+      <c r="O69" t="s">
+        <v>512</v>
+      </c>
+      <c r="P69" t="s">
+        <v>544</v>
+      </c>
+      <c r="R69" t="s">
+        <v>634</v>
+      </c>
+      <c r="S69" t="s">
+        <v>635</v>
+      </c>
     </row>
     <row r="70" spans="1:19" ht="17" customHeight="1">
       <c r="A70" s="1" t="s">
@@ -4355,37 +4366,26 @@
       <c r="B70" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F70" t="s">
+      <c r="M70" t="s">
+        <v>675</v>
+      </c>
+      <c r="N70" s="10"/>
+    </row>
+    <row r="71" spans="1:19" ht="17" customHeight="1">
+      <c r="A71" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F71" t="s">
         <v>171</v>
       </c>
-      <c r="G70" t="s">
+      <c r="G71" t="s">
         <v>173</v>
       </c>
-      <c r="M70" t="s">
+      <c r="M71" t="s">
         <v>648</v>
-      </c>
-    </row>
-    <row r="71" spans="1:19">
-      <c r="A71" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="L71" t="s">
-        <v>335</v>
-      </c>
-      <c r="M71" t="s">
-        <v>409</v>
-      </c>
-      <c r="O71" t="s">
-        <v>504</v>
-      </c>
-      <c r="R71" t="s">
-        <v>618</v>
-      </c>
-      <c r="S71" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="72" spans="1:19">
@@ -4395,36 +4395,45 @@
       <c r="B72" s="1" t="s">
         <v>408</v>
       </c>
+      <c r="L72" t="s">
+        <v>335</v>
+      </c>
       <c r="M72" t="s">
+        <v>409</v>
+      </c>
+      <c r="O72" t="s">
+        <v>504</v>
+      </c>
+      <c r="R72" t="s">
+        <v>618</v>
+      </c>
+      <c r="S72" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19">
+      <c r="A73" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="M73" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="17" customHeight="1">
-      <c r="A73" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B73" s="1" t="s">
+    <row r="74" spans="1:19" ht="17" customHeight="1">
+      <c r="A74" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="R73" t="s">
+      <c r="R74" t="s">
         <v>630</v>
       </c>
-      <c r="S73" t="s">
+      <c r="S74" t="s">
         <v>631</v>
-      </c>
-    </row>
-    <row r="74" spans="1:19">
-      <c r="A74" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="R74" t="s">
-        <v>632</v>
-      </c>
-      <c r="S74" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="75" spans="1:19">
@@ -4432,7 +4441,13 @@
         <v>23</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>21</v>
+        <v>629</v>
+      </c>
+      <c r="R75" t="s">
+        <v>632</v>
+      </c>
+      <c r="S75" t="s">
+        <v>633</v>
       </c>
     </row>
     <row r="76" spans="1:19">
@@ -4440,16 +4455,7 @@
         <v>23</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="D76" t="s">
-        <v>128</v>
-      </c>
-      <c r="E76" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77" spans="1:19">
@@ -4457,11 +4463,16 @@
         <v>23</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="C77" s="7"/>
-      <c r="O77" t="s">
-        <v>532</v>
+        <v>22</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D77" t="s">
+        <v>128</v>
+      </c>
+      <c r="E77" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="78" spans="1:19">
@@ -4469,11 +4480,11 @@
         <v>23</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>568</v>
+        <v>531</v>
       </c>
       <c r="C78" s="7"/>
-      <c r="Q78" t="s">
-        <v>567</v>
+      <c r="O78" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="79" spans="1:19">
@@ -4481,62 +4492,21 @@
         <v>23</v>
       </c>
       <c r="B79" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="C79" s="7"/>
+      <c r="Q79" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19">
+      <c r="A80" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="C79" s="7"/>
-    </row>
-    <row r="80" spans="1:19">
-      <c r="A80" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D80" t="s">
-        <v>65</v>
-      </c>
-      <c r="E80" t="s">
-        <v>48</v>
-      </c>
-      <c r="F80" t="s">
-        <v>168</v>
-      </c>
-      <c r="G80" t="s">
-        <v>173</v>
-      </c>
-      <c r="H80" t="s">
-        <v>200</v>
-      </c>
-      <c r="I80" t="s">
-        <v>252</v>
-      </c>
-      <c r="J80" t="s">
-        <v>207</v>
-      </c>
-      <c r="K80" t="s">
-        <v>216</v>
-      </c>
-      <c r="L80" t="s">
-        <v>329</v>
-      </c>
-      <c r="M80" t="s">
-        <v>370</v>
-      </c>
-      <c r="P80" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q80" t="s">
-        <v>168</v>
-      </c>
-      <c r="R80" t="s">
-        <v>614</v>
-      </c>
-      <c r="S80" t="s">
-        <v>615</v>
-      </c>
+      <c r="C80" s="7"/>
     </row>
     <row r="81" spans="1:19">
       <c r="A81" s="2" t="s">
@@ -4545,67 +4515,61 @@
       <c r="B81" s="2" t="s">
         <v>141</v>
       </c>
+      <c r="C81" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D81" t="s">
+        <v>65</v>
+      </c>
+      <c r="E81" t="s">
+        <v>48</v>
+      </c>
+      <c r="F81" t="s">
+        <v>168</v>
+      </c>
+      <c r="G81" t="s">
+        <v>173</v>
+      </c>
+      <c r="H81" t="s">
+        <v>200</v>
+      </c>
+      <c r="I81" t="s">
+        <v>252</v>
+      </c>
+      <c r="J81" t="s">
+        <v>207</v>
+      </c>
+      <c r="K81" t="s">
+        <v>216</v>
+      </c>
+      <c r="L81" t="s">
+        <v>329</v>
+      </c>
       <c r="M81" t="s">
+        <v>370</v>
+      </c>
+      <c r="P81" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>168</v>
+      </c>
+      <c r="R81" t="s">
+        <v>614</v>
+      </c>
+      <c r="S81" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19">
+      <c r="A82" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="M82" t="s">
         <v>665</v>
-      </c>
-    </row>
-    <row r="82" spans="1:19">
-      <c r="A82" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D82" t="s">
-        <v>67</v>
-      </c>
-      <c r="E82" t="s">
-        <v>49</v>
-      </c>
-      <c r="F82" t="s">
-        <v>143</v>
-      </c>
-      <c r="G82" t="s">
-        <v>148</v>
-      </c>
-      <c r="H82" t="s">
-        <v>201</v>
-      </c>
-      <c r="I82" t="s">
-        <v>253</v>
-      </c>
-      <c r="J82" t="s">
-        <v>204</v>
-      </c>
-      <c r="K82" t="s">
-        <v>218</v>
-      </c>
-      <c r="L82" t="s">
-        <v>312</v>
-      </c>
-      <c r="M82" t="s">
-        <v>379</v>
-      </c>
-      <c r="N82" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="O82" s="10" t="s">
-        <v>434</v>
-      </c>
-      <c r="P82" t="s">
-        <v>520</v>
-      </c>
-      <c r="Q82" t="s">
-        <v>520</v>
-      </c>
-      <c r="R82" t="s">
-        <v>586</v>
-      </c>
-      <c r="S82" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="83" spans="1:19">
@@ -4615,8 +4579,17 @@
       <c r="B83" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="C83" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D83" t="s">
+        <v>67</v>
+      </c>
+      <c r="E83" t="s">
+        <v>49</v>
+      </c>
       <c r="F83" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G83" t="s">
         <v>148</v>
@@ -4625,7 +4598,7 @@
         <v>201</v>
       </c>
       <c r="I83" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J83" t="s">
         <v>204</v>
@@ -4634,13 +4607,28 @@
         <v>218</v>
       </c>
       <c r="L83" t="s">
-        <v>450</v>
+        <v>312</v>
       </c>
       <c r="M83" t="s">
-        <v>384</v>
-      </c>
-      <c r="O83" t="s">
-        <v>495</v>
+        <v>379</v>
+      </c>
+      <c r="N83" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="O83" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="P83" t="s">
+        <v>520</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>520</v>
+      </c>
+      <c r="R83" t="s">
+        <v>586</v>
+      </c>
+      <c r="S83" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="84" spans="1:19">
@@ -4650,11 +4638,17 @@
       <c r="B84" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="F84" t="s">
+        <v>144</v>
+      </c>
+      <c r="G84" t="s">
+        <v>148</v>
+      </c>
       <c r="H84" t="s">
         <v>201</v>
       </c>
       <c r="I84" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J84" t="s">
         <v>204</v>
@@ -4662,8 +4656,14 @@
       <c r="K84" t="s">
         <v>218</v>
       </c>
+      <c r="L84" t="s">
+        <v>450</v>
+      </c>
+      <c r="M84" t="s">
+        <v>384</v>
+      </c>
       <c r="O84" t="s">
-        <v>520</v>
+        <v>495</v>
       </c>
     </row>
     <row r="85" spans="1:19">
@@ -4677,7 +4677,7 @@
         <v>201</v>
       </c>
       <c r="I85" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J85" t="s">
         <v>204</v>
@@ -4685,6 +4685,9 @@
       <c r="K85" t="s">
         <v>218</v>
       </c>
+      <c r="O85" t="s">
+        <v>520</v>
+      </c>
     </row>
     <row r="86" spans="1:19">
       <c r="A86" s="3" t="s">
@@ -4697,7 +4700,7 @@
         <v>201</v>
       </c>
       <c r="I86" t="s">
-        <v>350</v>
+        <v>256</v>
       </c>
       <c r="J86" t="s">
         <v>204</v>
@@ -4717,7 +4720,7 @@
         <v>201</v>
       </c>
       <c r="I87" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J87" t="s">
         <v>204</v>
@@ -4737,7 +4740,7 @@
         <v>201</v>
       </c>
       <c r="I88" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="J88" t="s">
         <v>204</v>
@@ -4757,7 +4760,7 @@
         <v>201</v>
       </c>
       <c r="I89" t="s">
-        <v>257</v>
+        <v>354</v>
       </c>
       <c r="J89" t="s">
         <v>204</v>
@@ -4777,7 +4780,7 @@
         <v>201</v>
       </c>
       <c r="I90" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J90" t="s">
         <v>204</v>
@@ -4797,7 +4800,7 @@
         <v>201</v>
       </c>
       <c r="I91" t="s">
-        <v>413</v>
+        <v>258</v>
       </c>
       <c r="J91" t="s">
         <v>204</v>
@@ -4817,7 +4820,7 @@
         <v>201</v>
       </c>
       <c r="I92" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J92" t="s">
         <v>204</v>
@@ -4837,7 +4840,7 @@
         <v>201</v>
       </c>
       <c r="I93" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="J93" t="s">
         <v>204</v>
@@ -4857,7 +4860,7 @@
         <v>201</v>
       </c>
       <c r="I94" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J94" t="s">
         <v>204</v>
@@ -4873,8 +4876,11 @@
       <c r="B95" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="H95" t="s">
+        <v>201</v>
+      </c>
       <c r="I95" t="s">
-        <v>483</v>
+        <v>415</v>
       </c>
       <c r="J95" t="s">
         <v>204</v>
@@ -4891,7 +4897,7 @@
         <v>25</v>
       </c>
       <c r="I96" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="J96" t="s">
         <v>204</v>
@@ -4907,11 +4913,8 @@
       <c r="B97" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H97" t="s">
-        <v>201</v>
-      </c>
       <c r="I97" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="J97" t="s">
         <v>204</v>
@@ -4931,7 +4934,7 @@
         <v>201</v>
       </c>
       <c r="I98" t="s">
-        <v>349</v>
+        <v>479</v>
       </c>
       <c r="J98" t="s">
         <v>204</v>
@@ -4951,7 +4954,7 @@
         <v>201</v>
       </c>
       <c r="I99" t="s">
-        <v>257</v>
+        <v>349</v>
       </c>
       <c r="J99" t="s">
         <v>204</v>
@@ -4965,25 +4968,13 @@
         <v>24</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D100" t="s">
-        <v>68</v>
-      </c>
-      <c r="E100" t="s">
-        <v>49</v>
-      </c>
-      <c r="F100" t="s">
-        <v>145</v>
-      </c>
-      <c r="G100" t="s">
-        <v>148</v>
+        <v>25</v>
       </c>
       <c r="H100" t="s">
         <v>201</v>
+      </c>
+      <c r="I100" t="s">
+        <v>257</v>
       </c>
       <c r="J100" t="s">
         <v>204</v>
@@ -4991,30 +4982,6 @@
       <c r="K100" t="s">
         <v>218</v>
       </c>
-      <c r="L100" t="s">
-        <v>314</v>
-      </c>
-      <c r="M100" t="s">
-        <v>246</v>
-      </c>
-      <c r="N100" s="10" t="s">
-        <v>423</v>
-      </c>
-      <c r="O100" s="10" t="s">
-        <v>442</v>
-      </c>
-      <c r="P100" t="s">
-        <v>521</v>
-      </c>
-      <c r="Q100" t="s">
-        <v>546</v>
-      </c>
-      <c r="R100" t="s">
-        <v>606</v>
-      </c>
-      <c r="S100" t="s">
-        <v>607</v>
-      </c>
     </row>
     <row r="101" spans="1:19">
       <c r="A101" s="3" t="s">
@@ -5023,11 +4990,23 @@
       <c r="B101" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="C101" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D101" t="s">
+        <v>68</v>
+      </c>
+      <c r="E101" t="s">
+        <v>49</v>
+      </c>
+      <c r="F101" t="s">
+        <v>145</v>
+      </c>
+      <c r="G101" t="s">
+        <v>148</v>
+      </c>
       <c r="H101" t="s">
         <v>201</v>
-      </c>
-      <c r="I101" t="s">
-        <v>259</v>
       </c>
       <c r="J101" t="s">
         <v>204</v>
@@ -5035,11 +5014,29 @@
       <c r="K101" t="s">
         <v>218</v>
       </c>
+      <c r="L101" t="s">
+        <v>314</v>
+      </c>
       <c r="M101" t="s">
-        <v>671</v>
-      </c>
-      <c r="O101" t="s">
-        <v>498</v>
+        <v>246</v>
+      </c>
+      <c r="N101" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="O101" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="P101" t="s">
+        <v>521</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>546</v>
+      </c>
+      <c r="R101" t="s">
+        <v>606</v>
+      </c>
+      <c r="S101" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="102" spans="1:19">
@@ -5049,17 +5046,11 @@
       <c r="B102" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F102" t="s">
-        <v>146</v>
-      </c>
-      <c r="G102" t="s">
-        <v>148</v>
-      </c>
       <c r="H102" t="s">
         <v>201</v>
       </c>
       <c r="I102" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J102" t="s">
         <v>204</v>
@@ -5067,8 +5058,11 @@
       <c r="K102" t="s">
         <v>218</v>
       </c>
+      <c r="M102" t="s">
+        <v>671</v>
+      </c>
       <c r="O102" t="s">
-        <v>521</v>
+        <v>498</v>
       </c>
     </row>
     <row r="103" spans="1:19">
@@ -5078,11 +5072,17 @@
       <c r="B103" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="F103" t="s">
+        <v>146</v>
+      </c>
+      <c r="G103" t="s">
+        <v>148</v>
+      </c>
       <c r="H103" t="s">
         <v>201</v>
       </c>
       <c r="I103" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J103" t="s">
         <v>204</v>
@@ -5090,6 +5090,9 @@
       <c r="K103" t="s">
         <v>218</v>
       </c>
+      <c r="O103" t="s">
+        <v>521</v>
+      </c>
     </row>
     <row r="104" spans="1:19">
       <c r="A104" s="3" t="s">
@@ -5102,7 +5105,7 @@
         <v>201</v>
       </c>
       <c r="I104" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J104" t="s">
         <v>204</v>
@@ -5122,7 +5125,7 @@
         <v>201</v>
       </c>
       <c r="I105" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J105" t="s">
         <v>204</v>
@@ -5142,7 +5145,7 @@
         <v>201</v>
       </c>
       <c r="I106" t="s">
-        <v>480</v>
+        <v>263</v>
       </c>
       <c r="J106" t="s">
         <v>204</v>
@@ -5162,7 +5165,7 @@
         <v>201</v>
       </c>
       <c r="I107" t="s">
-        <v>352</v>
+        <v>480</v>
       </c>
       <c r="J107" t="s">
         <v>204</v>
@@ -5182,7 +5185,7 @@
         <v>201</v>
       </c>
       <c r="I108" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="J108" t="s">
         <v>204</v>
@@ -5202,7 +5205,7 @@
         <v>201</v>
       </c>
       <c r="I109" t="s">
-        <v>417</v>
+        <v>355</v>
       </c>
       <c r="J109" t="s">
         <v>204</v>
@@ -5222,7 +5225,7 @@
         <v>201</v>
       </c>
       <c r="I110" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="J110" t="s">
         <v>204</v>
@@ -5242,7 +5245,7 @@
         <v>201</v>
       </c>
       <c r="I111" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J111" t="s">
         <v>204</v>
@@ -5262,7 +5265,7 @@
         <v>201</v>
       </c>
       <c r="I112" t="s">
-        <v>478</v>
+        <v>419</v>
       </c>
       <c r="J112" t="s">
         <v>204</v>
@@ -5282,7 +5285,7 @@
         <v>201</v>
       </c>
       <c r="I113" t="s">
-        <v>420</v>
+        <v>478</v>
       </c>
       <c r="J113" t="s">
         <v>204</v>
@@ -5298,8 +5301,11 @@
       <c r="B114" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="H114" t="s">
+        <v>201</v>
+      </c>
       <c r="I114" t="s">
-        <v>482</v>
+        <v>420</v>
       </c>
       <c r="J114" t="s">
         <v>204</v>
@@ -5316,7 +5322,7 @@
         <v>26</v>
       </c>
       <c r="I115" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="J115" t="s">
         <v>204</v>
@@ -5333,7 +5339,7 @@
         <v>26</v>
       </c>
       <c r="I116" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="J116" t="s">
         <v>204</v>
@@ -5349,11 +5355,8 @@
       <c r="B117" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H117" t="s">
-        <v>201</v>
-      </c>
       <c r="I117" t="s">
-        <v>205</v>
+        <v>486</v>
       </c>
       <c r="J117" t="s">
         <v>204</v>
@@ -5373,7 +5376,7 @@
         <v>201</v>
       </c>
       <c r="I118" t="s">
-        <v>279</v>
+        <v>205</v>
       </c>
       <c r="J118" t="s">
         <v>204</v>
@@ -5393,7 +5396,7 @@
         <v>201</v>
       </c>
       <c r="I119" t="s">
-        <v>477</v>
+        <v>279</v>
       </c>
       <c r="J119" t="s">
         <v>204</v>
@@ -5407,28 +5410,13 @@
         <v>24</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C120" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D120" t="s">
-        <v>69</v>
-      </c>
-      <c r="E120" t="s">
-        <v>49</v>
-      </c>
-      <c r="F120" t="s">
-        <v>151</v>
-      </c>
-      <c r="G120" t="s">
-        <v>148</v>
+        <v>26</v>
       </c>
       <c r="H120" t="s">
         <v>201</v>
       </c>
       <c r="I120" t="s">
-        <v>264</v>
+        <v>477</v>
       </c>
       <c r="J120" t="s">
         <v>204</v>
@@ -5436,49 +5424,16 @@
       <c r="K120" t="s">
         <v>218</v>
       </c>
-      <c r="L120" t="s">
-        <v>331</v>
-      </c>
-      <c r="M120" t="s">
-        <v>266</v>
-      </c>
-      <c r="O120" s="10" t="s">
-        <v>443</v>
-      </c>
-      <c r="P120" t="s">
-        <v>524</v>
-      </c>
-      <c r="R120" t="s">
-        <v>590</v>
-      </c>
-      <c r="S120" t="s">
-        <v>591</v>
-      </c>
     </row>
     <row r="121" spans="1:19">
       <c r="A121" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H121" t="s">
-        <v>201</v>
+        <v>26</v>
       </c>
       <c r="I121" t="s">
-        <v>265</v>
-      </c>
-      <c r="J121" t="s">
-        <v>204</v>
-      </c>
-      <c r="K121" t="s">
-        <v>218</v>
-      </c>
-      <c r="M121" t="s">
-        <v>664</v>
-      </c>
-      <c r="O121" t="s">
-        <v>541</v>
+        <v>687</v>
       </c>
     </row>
     <row r="122" spans="1:19">
@@ -5488,8 +5443,17 @@
       <c r="B122" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="C122" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D122" t="s">
+        <v>69</v>
+      </c>
+      <c r="E122" t="s">
+        <v>49</v>
+      </c>
       <c r="F122" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G122" t="s">
         <v>148</v>
@@ -5498,7 +5462,7 @@
         <v>201</v>
       </c>
       <c r="I122" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="J122" t="s">
         <v>204</v>
@@ -5506,25 +5470,37 @@
       <c r="K122" t="s">
         <v>218</v>
       </c>
+      <c r="L122" t="s">
+        <v>331</v>
+      </c>
+      <c r="M122" t="s">
+        <v>266</v>
+      </c>
+      <c r="O122" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="P122" t="s">
+        <v>524</v>
+      </c>
+      <c r="R122" t="s">
+        <v>590</v>
+      </c>
+      <c r="S122" t="s">
+        <v>591</v>
+      </c>
     </row>
     <row r="123" spans="1:19">
       <c r="A123" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="F123" t="s">
-        <v>189</v>
-      </c>
-      <c r="G123" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="H123" t="s">
         <v>201</v>
       </c>
       <c r="I123" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="J123" t="s">
         <v>204</v>
@@ -5532,14 +5508,11 @@
       <c r="K123" t="s">
         <v>218</v>
       </c>
-      <c r="N123" s="10" t="s">
-        <v>427</v>
+      <c r="M123" t="s">
+        <v>664</v>
       </c>
       <c r="O123" t="s">
-        <v>500</v>
-      </c>
-      <c r="Q123" t="s">
-        <v>569</v>
+        <v>541</v>
       </c>
     </row>
     <row r="124" spans="1:19">
@@ -5547,19 +5520,10 @@
         <v>24</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C124" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D124" t="s">
-        <v>84</v>
-      </c>
-      <c r="E124" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="F124" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G124" t="s">
         <v>148</v>
@@ -5568,7 +5532,7 @@
         <v>201</v>
       </c>
       <c r="I124" t="s">
-        <v>84</v>
+        <v>266</v>
       </c>
       <c r="J124" t="s">
         <v>204</v>
@@ -5576,34 +5540,40 @@
       <c r="K124" t="s">
         <v>218</v>
       </c>
-      <c r="L124" t="s">
-        <v>318</v>
-      </c>
-      <c r="M124" t="s">
-        <v>374</v>
-      </c>
-      <c r="P124" t="s">
-        <v>523</v>
-      </c>
-      <c r="R124" t="s">
-        <v>624</v>
-      </c>
-      <c r="S124" t="s">
-        <v>625</v>
-      </c>
     </row>
     <row r="125" spans="1:19">
       <c r="A125" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L125" t="s">
-        <v>464</v>
-      </c>
-      <c r="M125" t="s">
-        <v>660</v>
+        <v>501</v>
+      </c>
+      <c r="F125" t="s">
+        <v>189</v>
+      </c>
+      <c r="G125" t="s">
+        <v>148</v>
+      </c>
+      <c r="H125" t="s">
+        <v>201</v>
+      </c>
+      <c r="I125" t="s">
+        <v>267</v>
+      </c>
+      <c r="J125" t="s">
+        <v>204</v>
+      </c>
+      <c r="K125" t="s">
+        <v>218</v>
+      </c>
+      <c r="N125" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="O125" t="s">
+        <v>500</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="126" spans="1:19">
@@ -5613,8 +5583,47 @@
       <c r="B126" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="C126" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D126" t="s">
+        <v>84</v>
+      </c>
+      <c r="E126" t="s">
+        <v>49</v>
+      </c>
+      <c r="F126" t="s">
+        <v>149</v>
+      </c>
+      <c r="G126" t="s">
+        <v>148</v>
+      </c>
+      <c r="H126" t="s">
+        <v>201</v>
+      </c>
+      <c r="I126" t="s">
+        <v>84</v>
+      </c>
+      <c r="J126" t="s">
+        <v>204</v>
+      </c>
+      <c r="K126" t="s">
+        <v>218</v>
+      </c>
+      <c r="L126" t="s">
+        <v>318</v>
+      </c>
       <c r="M126" t="s">
-        <v>667</v>
+        <v>374</v>
+      </c>
+      <c r="P126" t="s">
+        <v>523</v>
+      </c>
+      <c r="R126" t="s">
+        <v>624</v>
+      </c>
+      <c r="S126" t="s">
+        <v>625</v>
       </c>
     </row>
     <row r="127" spans="1:19">
@@ -5622,58 +5631,13 @@
         <v>24</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="C127" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D127" t="s">
-        <v>72</v>
-      </c>
-      <c r="E127" t="s">
-        <v>49</v>
-      </c>
-      <c r="F127" t="s">
-        <v>150</v>
-      </c>
-      <c r="G127" t="s">
-        <v>148</v>
-      </c>
-      <c r="H127" t="s">
-        <v>201</v>
-      </c>
-      <c r="I127" t="s">
-        <v>268</v>
-      </c>
-      <c r="J127" t="s">
-        <v>204</v>
-      </c>
-      <c r="K127" t="s">
-        <v>218</v>
+        <v>28</v>
       </c>
       <c r="L127" t="s">
-        <v>311</v>
+        <v>464</v>
       </c>
       <c r="M127" t="s">
-        <v>371</v>
-      </c>
-      <c r="N127" s="10" t="s">
-        <v>425</v>
-      </c>
-      <c r="O127" s="10" t="s">
-        <v>436</v>
-      </c>
-      <c r="P127" t="s">
-        <v>522</v>
-      </c>
-      <c r="Q127" t="s">
-        <v>548</v>
-      </c>
-      <c r="R127" t="s">
-        <v>588</v>
-      </c>
-      <c r="S127" t="s">
-        <v>589</v>
+        <v>660</v>
       </c>
     </row>
     <row r="128" spans="1:19">
@@ -5681,46 +5645,10 @@
         <v>24</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="C128" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D128" t="s">
-        <v>73</v>
-      </c>
-      <c r="E128" t="s">
-        <v>49</v>
-      </c>
-      <c r="F128" t="s">
-        <v>194</v>
-      </c>
-      <c r="G128" t="s">
-        <v>148</v>
-      </c>
-      <c r="H128" t="s">
-        <v>201</v>
-      </c>
-      <c r="I128" t="s">
-        <v>269</v>
-      </c>
-      <c r="J128" t="s">
-        <v>204</v>
-      </c>
-      <c r="K128" t="s">
-        <v>218</v>
-      </c>
-      <c r="L128" t="s">
-        <v>320</v>
+        <v>28</v>
       </c>
       <c r="M128" t="s">
-        <v>372</v>
-      </c>
-      <c r="O128" t="s">
-        <v>494</v>
-      </c>
-      <c r="Q128" t="s">
-        <v>566</v>
+        <v>667</v>
       </c>
     </row>
     <row r="129" spans="1:19">
@@ -5730,8 +5658,17 @@
       <c r="B129" s="3" t="s">
         <v>535</v>
       </c>
+      <c r="C129" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D129" t="s">
+        <v>72</v>
+      </c>
+      <c r="E129" t="s">
+        <v>49</v>
+      </c>
       <c r="F129" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="G129" t="s">
         <v>148</v>
@@ -5740,7 +5677,7 @@
         <v>201</v>
       </c>
       <c r="I129" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="J129" t="s">
         <v>204</v>
@@ -5749,16 +5686,28 @@
         <v>218</v>
       </c>
       <c r="L129" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="M129" t="s">
-        <v>373</v>
-      </c>
-      <c r="O129" t="s">
-        <v>536</v>
+        <v>371</v>
+      </c>
+      <c r="N129" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="O129" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="P129" t="s">
+        <v>522</v>
       </c>
       <c r="Q129" t="s">
-        <v>571</v>
+        <v>548</v>
+      </c>
+      <c r="R129" t="s">
+        <v>588</v>
+      </c>
+      <c r="S129" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="130" spans="1:19">
@@ -5768,8 +5717,17 @@
       <c r="B130" s="3" t="s">
         <v>535</v>
       </c>
+      <c r="C130" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D130" t="s">
+        <v>73</v>
+      </c>
+      <c r="E130" t="s">
+        <v>49</v>
+      </c>
       <c r="F130" t="s">
-        <v>347</v>
+        <v>194</v>
       </c>
       <c r="G130" t="s">
         <v>148</v>
@@ -5778,13 +5736,25 @@
         <v>201</v>
       </c>
       <c r="I130" t="s">
-        <v>490</v>
+        <v>269</v>
+      </c>
+      <c r="J130" t="s">
+        <v>204</v>
+      </c>
+      <c r="K130" t="s">
+        <v>218</v>
       </c>
       <c r="L130" t="s">
-        <v>460</v>
+        <v>320</v>
       </c>
       <c r="M130" t="s">
-        <v>383</v>
+        <v>372</v>
+      </c>
+      <c r="O130" t="s">
+        <v>494</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="131" spans="1:19">
@@ -5795,7 +5765,7 @@
         <v>535</v>
       </c>
       <c r="F131" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G131" t="s">
         <v>148</v>
@@ -5804,7 +5774,7 @@
         <v>201</v>
       </c>
       <c r="I131" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J131" t="s">
         <v>204</v>
@@ -5812,8 +5782,17 @@
       <c r="K131" t="s">
         <v>218</v>
       </c>
+      <c r="L131" t="s">
+        <v>321</v>
+      </c>
       <c r="M131" t="s">
-        <v>410</v>
+        <v>373</v>
+      </c>
+      <c r="O131" t="s">
+        <v>536</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>571</v>
       </c>
     </row>
     <row r="132" spans="1:19">
@@ -5824,7 +5803,7 @@
         <v>535</v>
       </c>
       <c r="F132" t="s">
-        <v>193</v>
+        <v>347</v>
       </c>
       <c r="G132" t="s">
         <v>148</v>
@@ -5833,13 +5812,13 @@
         <v>201</v>
       </c>
       <c r="I132" t="s">
-        <v>272</v>
-      </c>
-      <c r="J132" t="s">
-        <v>204</v>
-      </c>
-      <c r="K132" t="s">
-        <v>218</v>
+        <v>490</v>
+      </c>
+      <c r="L132" t="s">
+        <v>460</v>
+      </c>
+      <c r="M132" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="133" spans="1:19">
@@ -5850,7 +5829,7 @@
         <v>535</v>
       </c>
       <c r="F133" t="s">
-        <v>358</v>
+        <v>190</v>
       </c>
       <c r="G133" t="s">
         <v>148</v>
@@ -5859,7 +5838,16 @@
         <v>201</v>
       </c>
       <c r="I133" t="s">
-        <v>491</v>
+        <v>271</v>
+      </c>
+      <c r="J133" t="s">
+        <v>204</v>
+      </c>
+      <c r="K133" t="s">
+        <v>218</v>
+      </c>
+      <c r="M133" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="134" spans="1:19">
@@ -5870,7 +5858,7 @@
         <v>535</v>
       </c>
       <c r="F134" t="s">
-        <v>361</v>
+        <v>193</v>
       </c>
       <c r="G134" t="s">
         <v>148</v>
@@ -5879,7 +5867,13 @@
         <v>201</v>
       </c>
       <c r="I134" t="s">
-        <v>492</v>
+        <v>272</v>
+      </c>
+      <c r="J134" t="s">
+        <v>204</v>
+      </c>
+      <c r="K134" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="135" spans="1:19">
@@ -5890,7 +5884,7 @@
         <v>535</v>
       </c>
       <c r="F135" t="s">
-        <v>573</v>
+        <v>358</v>
       </c>
       <c r="G135" t="s">
         <v>148</v>
@@ -5899,7 +5893,7 @@
         <v>201</v>
       </c>
       <c r="I135" t="s">
-        <v>73</v>
+        <v>491</v>
       </c>
     </row>
     <row r="136" spans="1:19">
@@ -5910,11 +5904,17 @@
         <v>535</v>
       </c>
       <c r="F136" t="s">
-        <v>574</v>
+        <v>361</v>
       </c>
       <c r="G136" t="s">
         <v>148</v>
       </c>
+      <c r="H136" t="s">
+        <v>201</v>
+      </c>
+      <c r="I136" t="s">
+        <v>492</v>
+      </c>
     </row>
     <row r="137" spans="1:19">
       <c r="A137" s="3" t="s">
@@ -5923,108 +5923,98 @@
       <c r="B137" s="3" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="138" spans="1:19" ht="17" customHeight="1">
+      <c r="F137" t="s">
+        <v>573</v>
+      </c>
+      <c r="G137" t="s">
+        <v>148</v>
+      </c>
+      <c r="H137" t="s">
+        <v>201</v>
+      </c>
+      <c r="I137" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="138" spans="1:19">
       <c r="A138" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C138" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D138" t="s">
-        <v>74</v>
-      </c>
-      <c r="E138" t="s">
-        <v>49</v>
+        <v>535</v>
       </c>
       <c r="F138" t="s">
-        <v>197</v>
+        <v>574</v>
       </c>
       <c r="G138" t="s">
         <v>148</v>
       </c>
-      <c r="H138" t="s">
-        <v>201</v>
-      </c>
-      <c r="I138" t="s">
-        <v>273</v>
-      </c>
-      <c r="J138" t="s">
-        <v>204</v>
-      </c>
-      <c r="K138" t="s">
-        <v>218</v>
-      </c>
-      <c r="M138" t="s">
-        <v>382</v>
-      </c>
-      <c r="N138" s="10" t="s">
-        <v>432</v>
-      </c>
-      <c r="O138" s="10" t="s">
-        <v>448</v>
-      </c>
     </row>
     <row r="139" spans="1:19">
       <c r="A139" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M139" t="s">
-        <v>669</v>
-      </c>
-      <c r="N139" s="10"/>
-      <c r="O139" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="140" spans="1:19">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="140" spans="1:19" ht="17" customHeight="1">
       <c r="A140" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="C140" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D140" t="s">
+        <v>74</v>
+      </c>
+      <c r="E140" t="s">
+        <v>49</v>
+      </c>
+      <c r="F140" t="s">
+        <v>197</v>
+      </c>
+      <c r="G140" t="s">
+        <v>148</v>
+      </c>
+      <c r="H140" t="s">
+        <v>201</v>
+      </c>
+      <c r="I140" t="s">
+        <v>273</v>
+      </c>
+      <c r="J140" t="s">
+        <v>204</v>
+      </c>
+      <c r="K140" t="s">
+        <v>218</v>
+      </c>
       <c r="M140" t="s">
-        <v>659</v>
-      </c>
-      <c r="N140" s="10"/>
+        <v>382</v>
+      </c>
+      <c r="N140" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="O140" s="10" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="141" spans="1:19">
       <c r="A141" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C141" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D141" t="s">
-        <v>92</v>
-      </c>
-      <c r="E141" t="s">
-        <v>49</v>
-      </c>
-      <c r="H141" t="s">
-        <v>201</v>
-      </c>
-      <c r="I141" t="s">
-        <v>274</v>
-      </c>
-      <c r="J141" t="s">
-        <v>204</v>
-      </c>
-      <c r="K141" t="s">
-        <v>218</v>
+        <v>29</v>
       </c>
       <c r="M141" t="s">
-        <v>670</v>
+        <v>669</v>
+      </c>
+      <c r="N141" s="10"/>
+      <c r="O141" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="142" spans="1:19">
@@ -6032,36 +6022,34 @@
         <v>24</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>31</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="M142" t="s">
+        <v>659</v>
+      </c>
+      <c r="N142" s="10"/>
     </row>
     <row r="143" spans="1:19">
       <c r="A143" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D143" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="E143" t="s">
         <v>49</v>
       </c>
-      <c r="F143" t="s">
-        <v>154</v>
-      </c>
-      <c r="G143" t="s">
-        <v>148</v>
-      </c>
       <c r="H143" t="s">
         <v>201</v>
       </c>
       <c r="I143" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J143" t="s">
         <v>204</v>
@@ -6069,29 +6057,8 @@
       <c r="K143" t="s">
         <v>218</v>
       </c>
-      <c r="L143" t="s">
-        <v>315</v>
-      </c>
       <c r="M143" t="s">
-        <v>385</v>
-      </c>
-      <c r="N143" s="10" t="s">
-        <v>424</v>
-      </c>
-      <c r="O143" s="10" t="s">
-        <v>438</v>
-      </c>
-      <c r="P143" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q143" t="s">
-        <v>551</v>
-      </c>
-      <c r="R143" t="s">
-        <v>608</v>
-      </c>
-      <c r="S143" t="s">
-        <v>609</v>
+        <v>670</v>
       </c>
     </row>
     <row r="144" spans="1:19">
@@ -6099,34 +6066,7 @@
         <v>24</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F144" t="s">
-        <v>155</v>
-      </c>
-      <c r="G144" t="s">
-        <v>148</v>
-      </c>
-      <c r="H144" t="s">
-        <v>201</v>
-      </c>
-      <c r="I144" t="s">
-        <v>276</v>
-      </c>
-      <c r="J144" t="s">
-        <v>204</v>
-      </c>
-      <c r="K144" t="s">
-        <v>218</v>
-      </c>
-      <c r="L144" t="s">
-        <v>449</v>
-      </c>
-      <c r="M144" t="s">
-        <v>640</v>
-      </c>
-      <c r="O144" t="s">
-        <v>502</v>
+        <v>31</v>
       </c>
     </row>
     <row r="145" spans="1:19">
@@ -6136,8 +6076,17 @@
       <c r="B145" s="3" t="s">
         <v>32</v>
       </c>
+      <c r="C145" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D145" t="s">
+        <v>71</v>
+      </c>
+      <c r="E145" t="s">
+        <v>49</v>
+      </c>
       <c r="F145" t="s">
-        <v>363</v>
+        <v>154</v>
       </c>
       <c r="G145" t="s">
         <v>148</v>
@@ -6145,11 +6094,38 @@
       <c r="H145" t="s">
         <v>201</v>
       </c>
+      <c r="I145" t="s">
+        <v>275</v>
+      </c>
+      <c r="J145" t="s">
+        <v>204</v>
+      </c>
+      <c r="K145" t="s">
+        <v>218</v>
+      </c>
+      <c r="L145" t="s">
+        <v>315</v>
+      </c>
       <c r="M145" t="s">
-        <v>672</v>
-      </c>
-      <c r="O145" t="s">
-        <v>538</v>
+        <v>385</v>
+      </c>
+      <c r="N145" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="O145" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="P145" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>551</v>
+      </c>
+      <c r="R145" t="s">
+        <v>608</v>
+      </c>
+      <c r="S145" t="s">
+        <v>609</v>
       </c>
     </row>
     <row r="146" spans="1:19">
@@ -6157,19 +6133,10 @@
         <v>24</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C146" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D146" t="s">
-        <v>70</v>
-      </c>
-      <c r="E146" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="F146" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G146" t="s">
         <v>148</v>
@@ -6178,7 +6145,7 @@
         <v>201</v>
       </c>
       <c r="I146" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J146" t="s">
         <v>204</v>
@@ -6187,19 +6154,13 @@
         <v>218</v>
       </c>
       <c r="L146" t="s">
-        <v>334</v>
+        <v>449</v>
       </c>
       <c r="M146" t="s">
-        <v>381</v>
+        <v>640</v>
       </c>
       <c r="O146" t="s">
-        <v>540</v>
-      </c>
-      <c r="P146" t="s">
-        <v>543</v>
-      </c>
-      <c r="Q146" t="s">
-        <v>547</v>
+        <v>502</v>
       </c>
     </row>
     <row r="147" spans="1:19">
@@ -6207,19 +6168,10 @@
         <v>24</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C147" s="6">
-        <v>253</v>
-      </c>
-      <c r="D147" t="s">
-        <v>90</v>
-      </c>
-      <c r="E147" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="F147" t="s">
-        <v>220</v>
+        <v>363</v>
       </c>
       <c r="G147" t="s">
         <v>148</v>
@@ -6227,17 +6179,11 @@
       <c r="H147" t="s">
         <v>201</v>
       </c>
-      <c r="I147" t="s">
-        <v>278</v>
-      </c>
-      <c r="J147" t="s">
-        <v>204</v>
-      </c>
-      <c r="K147" t="s">
-        <v>218</v>
-      </c>
       <c r="M147" t="s">
-        <v>662</v>
+        <v>672</v>
+      </c>
+      <c r="O147" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="148" spans="1:19">
@@ -6247,8 +6193,17 @@
       <c r="B148" s="3" t="s">
         <v>33</v>
       </c>
+      <c r="C148" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D148" t="s">
+        <v>70</v>
+      </c>
+      <c r="E148" t="s">
+        <v>49</v>
+      </c>
       <c r="F148" t="s">
-        <v>196</v>
+        <v>153</v>
       </c>
       <c r="G148" t="s">
         <v>148</v>
@@ -6257,7 +6212,28 @@
         <v>201</v>
       </c>
       <c r="I148" t="s">
-        <v>481</v>
+        <v>277</v>
+      </c>
+      <c r="J148" t="s">
+        <v>204</v>
+      </c>
+      <c r="K148" t="s">
+        <v>218</v>
+      </c>
+      <c r="L148" t="s">
+        <v>334</v>
+      </c>
+      <c r="M148" t="s">
+        <v>381</v>
+      </c>
+      <c r="O148" t="s">
+        <v>540</v>
+      </c>
+      <c r="P148" t="s">
+        <v>543</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="149" spans="1:19">
@@ -6265,19 +6241,19 @@
         <v>24</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C149" s="6" t="s">
-        <v>120</v>
+        <v>33</v>
+      </c>
+      <c r="C149" s="6">
+        <v>253</v>
       </c>
       <c r="D149" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="E149" t="s">
         <v>49</v>
       </c>
       <c r="F149" t="s">
-        <v>475</v>
+        <v>220</v>
       </c>
       <c r="G149" t="s">
         <v>148</v>
@@ -6286,28 +6262,16 @@
         <v>201</v>
       </c>
       <c r="I149" t="s">
-        <v>34</v>
+        <v>278</v>
       </c>
       <c r="J149" t="s">
         <v>204</v>
       </c>
       <c r="K149" t="s">
-        <v>213</v>
-      </c>
-      <c r="L149" t="s">
-        <v>463</v>
+        <v>218</v>
       </c>
       <c r="M149" t="s">
-        <v>34</v>
-      </c>
-      <c r="N149" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="O149" s="10" t="s">
-        <v>447</v>
-      </c>
-      <c r="Q149" t="s">
-        <v>570</v>
+        <v>662</v>
       </c>
     </row>
     <row r="150" spans="1:19">
@@ -6315,10 +6279,19 @@
         <v>24</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="O150" s="10" t="s">
-        <v>542</v>
+        <v>33</v>
+      </c>
+      <c r="F150" t="s">
+        <v>196</v>
+      </c>
+      <c r="G150" t="s">
+        <v>148</v>
+      </c>
+      <c r="H150" t="s">
+        <v>201</v>
+      </c>
+      <c r="I150" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="151" spans="1:19">
@@ -6326,19 +6299,19 @@
         <v>24</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D151" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E151" t="s">
         <v>49</v>
       </c>
       <c r="F151" t="s">
-        <v>195</v>
+        <v>475</v>
       </c>
       <c r="G151" t="s">
         <v>148</v>
@@ -6347,7 +6320,7 @@
         <v>201</v>
       </c>
       <c r="I151" t="s">
-        <v>280</v>
+        <v>34</v>
       </c>
       <c r="J151" t="s">
         <v>204</v>
@@ -6356,25 +6329,19 @@
         <v>213</v>
       </c>
       <c r="L151" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M151" t="s">
-        <v>380</v>
+        <v>34</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>577</v>
-      </c>
-      <c r="O151" t="s">
-        <v>507</v>
+        <v>34</v>
+      </c>
+      <c r="O151" s="10" t="s">
+        <v>447</v>
       </c>
       <c r="Q151" t="s">
-        <v>539</v>
-      </c>
-      <c r="R151" t="s">
-        <v>616</v>
-      </c>
-      <c r="S151" t="s">
-        <v>617</v>
+        <v>570</v>
       </c>
     </row>
     <row r="152" spans="1:19">
@@ -6382,28 +6349,10 @@
         <v>24</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F152" t="s">
-        <v>191</v>
-      </c>
-      <c r="G152" t="s">
-        <v>148</v>
-      </c>
-      <c r="H152" t="s">
-        <v>201</v>
-      </c>
-      <c r="I152" t="s">
-        <v>281</v>
-      </c>
-      <c r="J152" t="s">
-        <v>204</v>
-      </c>
-      <c r="K152" t="s">
-        <v>218</v>
-      </c>
-      <c r="O152" t="s">
-        <v>539</v>
+        <v>34</v>
+      </c>
+      <c r="O152" s="10" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="153" spans="1:19">
@@ -6413,8 +6362,17 @@
       <c r="B153" s="3" t="s">
         <v>35</v>
       </c>
+      <c r="C153" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D153" t="s">
+        <v>89</v>
+      </c>
+      <c r="E153" t="s">
+        <v>49</v>
+      </c>
       <c r="F153" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G153" t="s">
         <v>148</v>
@@ -6422,25 +6380,55 @@
       <c r="H153" t="s">
         <v>201</v>
       </c>
+      <c r="I153" t="s">
+        <v>280</v>
+      </c>
+      <c r="J153" t="s">
+        <v>204</v>
+      </c>
+      <c r="K153" t="s">
+        <v>213</v>
+      </c>
+      <c r="L153" t="s">
+        <v>462</v>
+      </c>
+      <c r="M153" t="s">
+        <v>380</v>
+      </c>
+      <c r="N153" s="10" t="s">
+        <v>577</v>
+      </c>
+      <c r="O153" t="s">
+        <v>507</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>539</v>
+      </c>
+      <c r="R153" t="s">
+        <v>616</v>
+      </c>
+      <c r="S153" t="s">
+        <v>617</v>
+      </c>
     </row>
     <row r="154" spans="1:19">
       <c r="A154" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C154" s="6">
-        <v>311</v>
-      </c>
-      <c r="D154" t="s">
-        <v>75</v>
-      </c>
-      <c r="E154" t="s">
-        <v>51</v>
+        <v>35</v>
+      </c>
+      <c r="F154" t="s">
+        <v>191</v>
+      </c>
+      <c r="G154" t="s">
+        <v>148</v>
+      </c>
+      <c r="H154" t="s">
+        <v>201</v>
       </c>
       <c r="I154" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J154" t="s">
         <v>204</v>
@@ -6448,14 +6436,8 @@
       <c r="K154" t="s">
         <v>218</v>
       </c>
-      <c r="M154" t="s">
-        <v>376</v>
-      </c>
-      <c r="O154" s="10" t="s">
-        <v>437</v>
-      </c>
-      <c r="P154" t="s">
-        <v>525</v>
+      <c r="O154" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="155" spans="1:19">
@@ -6463,19 +6445,16 @@
         <v>24</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C155" s="6">
-        <v>312</v>
-      </c>
-      <c r="D155" t="s">
-        <v>135</v>
-      </c>
-      <c r="E155" t="s">
-        <v>51</v>
-      </c>
-      <c r="O155" t="s">
-        <v>565</v>
+        <v>35</v>
+      </c>
+      <c r="F155" t="s">
+        <v>192</v>
+      </c>
+      <c r="G155" t="s">
+        <v>148</v>
+      </c>
+      <c r="H155" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="156" spans="1:19">
@@ -6483,19 +6462,34 @@
         <v>24</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="C156" s="6" t="s">
-        <v>305</v>
+        <v>36</v>
+      </c>
+      <c r="C156" s="6">
+        <v>311</v>
       </c>
       <c r="D156" t="s">
-        <v>304</v>
+        <v>75</v>
       </c>
       <c r="E156" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="I156" t="s">
+        <v>282</v>
+      </c>
+      <c r="J156" t="s">
+        <v>204</v>
+      </c>
+      <c r="K156" t="s">
+        <v>218</v>
       </c>
       <c r="M156" t="s">
-        <v>375</v>
+        <v>376</v>
+      </c>
+      <c r="O156" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="P156" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="157" spans="1:19">
@@ -6503,10 +6497,19 @@
         <v>24</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="M157" t="s">
-        <v>668</v>
+        <v>36</v>
+      </c>
+      <c r="C157" s="6">
+        <v>312</v>
+      </c>
+      <c r="D157" t="s">
+        <v>135</v>
+      </c>
+      <c r="E157" t="s">
+        <v>51</v>
+      </c>
+      <c r="O157" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="158" spans="1:19">
@@ -6516,8 +6519,17 @@
       <c r="B158" s="3" t="s">
         <v>304</v>
       </c>
+      <c r="C158" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="D158" t="s">
+        <v>304</v>
+      </c>
+      <c r="E158" t="s">
+        <v>49</v>
+      </c>
       <c r="M158" t="s">
-        <v>650</v>
+        <v>375</v>
       </c>
     </row>
     <row r="159" spans="1:19">
@@ -6525,10 +6537,10 @@
         <v>24</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>377</v>
+        <v>304</v>
       </c>
       <c r="M159" t="s">
-        <v>378</v>
+        <v>668</v>
       </c>
     </row>
     <row r="160" spans="1:19">
@@ -6536,37 +6548,10 @@
         <v>24</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C160" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="D160" t="s">
-        <v>306</v>
-      </c>
-      <c r="E160" t="s">
-        <v>49</v>
-      </c>
-      <c r="F160" t="s">
-        <v>188</v>
-      </c>
-      <c r="G160" t="s">
-        <v>148</v>
-      </c>
-      <c r="H160" t="s">
-        <v>201</v>
-      </c>
-      <c r="I160" t="s">
-        <v>353</v>
-      </c>
-      <c r="J160" t="s">
-        <v>204</v>
-      </c>
-      <c r="K160" t="s">
-        <v>218</v>
+        <v>304</v>
       </c>
       <c r="M160" t="s">
-        <v>641</v>
+        <v>650</v>
       </c>
     </row>
     <row r="161" spans="1:19">
@@ -6574,19 +6559,10 @@
         <v>24</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="F161" t="s">
-        <v>344</v>
-      </c>
-      <c r="G161" t="s">
-        <v>148</v>
-      </c>
-      <c r="H161" t="s">
-        <v>201</v>
-      </c>
-      <c r="L161" t="s">
-        <v>330</v>
+        <v>377</v>
+      </c>
+      <c r="M161" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="162" spans="1:19">
@@ -6594,10 +6570,19 @@
         <v>24</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>455</v>
+        <v>308</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="D162" t="s">
+        <v>306</v>
+      </c>
+      <c r="E162" t="s">
+        <v>49</v>
       </c>
       <c r="F162" t="s">
-        <v>472</v>
+        <v>188</v>
       </c>
       <c r="G162" t="s">
         <v>148</v>
@@ -6606,7 +6591,7 @@
         <v>201</v>
       </c>
       <c r="I162" t="s">
-        <v>488</v>
+        <v>353</v>
       </c>
       <c r="J162" t="s">
         <v>204</v>
@@ -6614,8 +6599,8 @@
       <c r="K162" t="s">
         <v>218</v>
       </c>
-      <c r="L162" t="s">
-        <v>456</v>
+      <c r="M162" t="s">
+        <v>641</v>
       </c>
     </row>
     <row r="163" spans="1:19">
@@ -6623,34 +6608,19 @@
         <v>24</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>406</v>
+        <v>345</v>
+      </c>
+      <c r="F163" t="s">
+        <v>344</v>
+      </c>
+      <c r="G163" t="s">
+        <v>148</v>
       </c>
       <c r="H163" t="s">
         <v>201</v>
       </c>
-      <c r="I163" t="s">
-        <v>283</v>
-      </c>
-      <c r="J163" t="s">
-        <v>204</v>
-      </c>
-      <c r="K163" t="s">
-        <v>218</v>
-      </c>
-      <c r="M163" t="s">
-        <v>287</v>
-      </c>
-      <c r="N163" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="O163" s="10" t="s">
-        <v>435</v>
-      </c>
-      <c r="R163" t="s">
-        <v>604</v>
-      </c>
-      <c r="S163" t="s">
-        <v>605</v>
+      <c r="L163" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="164" spans="1:19">
@@ -6658,14 +6628,28 @@
         <v>24</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="M164" t="s">
-        <v>663</v>
-      </c>
-      <c r="N164" s="10"/>
-      <c r="O164" s="10" t="s">
-        <v>537</v>
+        <v>455</v>
+      </c>
+      <c r="F164" t="s">
+        <v>472</v>
+      </c>
+      <c r="G164" t="s">
+        <v>148</v>
+      </c>
+      <c r="H164" t="s">
+        <v>201</v>
+      </c>
+      <c r="I164" t="s">
+        <v>488</v>
+      </c>
+      <c r="J164" t="s">
+        <v>204</v>
+      </c>
+      <c r="K164" t="s">
+        <v>218</v>
+      </c>
+      <c r="L164" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="165" spans="1:19">
@@ -6673,10 +6657,34 @@
         <v>24</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
+      </c>
+      <c r="H165" t="s">
+        <v>201</v>
+      </c>
+      <c r="I165" t="s">
+        <v>283</v>
+      </c>
+      <c r="J165" t="s">
+        <v>204</v>
+      </c>
+      <c r="K165" t="s">
+        <v>218</v>
       </c>
       <c r="M165" t="s">
-        <v>38</v>
+        <v>287</v>
+      </c>
+      <c r="N165" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="O165" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="R165" t="s">
+        <v>604</v>
+      </c>
+      <c r="S165" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="166" spans="1:19">
@@ -6684,13 +6692,14 @@
         <v>24</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="R166" t="s">
-        <v>602</v>
-      </c>
-      <c r="S166" t="s">
-        <v>603</v>
+        <v>406</v>
+      </c>
+      <c r="M166" t="s">
+        <v>663</v>
+      </c>
+      <c r="N166" s="10"/>
+      <c r="O166" s="10" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="167" spans="1:19">
@@ -6698,16 +6707,10 @@
         <v>24</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="F167" t="s">
-        <v>470</v>
-      </c>
-      <c r="G167" t="s">
-        <v>148</v>
-      </c>
-      <c r="H167" t="s">
-        <v>201</v>
+        <v>407</v>
+      </c>
+      <c r="M167" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="168" spans="1:19">
@@ -6715,10 +6718,13 @@
         <v>24</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>534</v>
-      </c>
-      <c r="O168" t="s">
-        <v>533</v>
+        <v>601</v>
+      </c>
+      <c r="R168" t="s">
+        <v>602</v>
+      </c>
+      <c r="S168" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="169" spans="1:19">
@@ -6726,10 +6732,16 @@
         <v>24</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="Q169" t="s">
-        <v>550</v>
+        <v>469</v>
+      </c>
+      <c r="F169" t="s">
+        <v>470</v>
+      </c>
+      <c r="G169" t="s">
+        <v>148</v>
+      </c>
+      <c r="H169" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="170" spans="1:19">
@@ -6737,83 +6749,32 @@
         <v>24</v>
       </c>
       <c r="B170" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="O170" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="171" spans="1:19">
+      <c r="A171" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="Q171" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="172" spans="1:19">
+      <c r="A172" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B172" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="M170" t="s">
+      <c r="M172" t="s">
         <v>647</v>
-      </c>
-    </row>
-    <row r="171" spans="1:19">
-      <c r="A171" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B171" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C171" s="6">
-        <v>511</v>
-      </c>
-      <c r="D171" t="s">
-        <v>81</v>
-      </c>
-      <c r="E171" t="s">
-        <v>50</v>
-      </c>
-      <c r="F171" t="s">
-        <v>181</v>
-      </c>
-      <c r="G171" t="s">
-        <v>186</v>
-      </c>
-      <c r="H171" t="s">
-        <v>201</v>
-      </c>
-      <c r="J171" t="s">
-        <v>206</v>
-      </c>
-      <c r="K171" t="s">
-        <v>217</v>
-      </c>
-      <c r="L171" t="s">
-        <v>313</v>
-      </c>
-      <c r="N171" s="10" t="s">
-        <v>575</v>
-      </c>
-      <c r="P171" t="s">
-        <v>526</v>
-      </c>
-      <c r="Q171" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="172" spans="1:19">
-      <c r="A172" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B172" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F172" t="s">
-        <v>179</v>
-      </c>
-      <c r="G172" t="s">
-        <v>186</v>
-      </c>
-      <c r="H172" t="s">
-        <v>201</v>
-      </c>
-      <c r="I172" t="s">
-        <v>284</v>
-      </c>
-      <c r="J172" t="s">
-        <v>206</v>
-      </c>
-      <c r="K172" t="s">
-        <v>217</v>
-      </c>
-      <c r="L172" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="173" spans="1:19">
@@ -6824,16 +6785,16 @@
         <v>38</v>
       </c>
       <c r="C173" s="6">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="D173" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E173" t="s">
         <v>50</v>
       </c>
       <c r="F173" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G173" t="s">
         <v>186</v>
@@ -6841,9 +6802,6 @@
       <c r="H173" t="s">
         <v>201</v>
       </c>
-      <c r="I173" t="s">
-        <v>285</v>
-      </c>
       <c r="J173" t="s">
         <v>206</v>
       </c>
@@ -6851,7 +6809,16 @@
         <v>217</v>
       </c>
       <c r="L173" t="s">
-        <v>453</v>
+        <v>313</v>
+      </c>
+      <c r="N173" s="10" t="s">
+        <v>575</v>
+      </c>
+      <c r="P173" t="s">
+        <v>526</v>
+      </c>
+      <c r="Q173" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="174" spans="1:19">
@@ -6862,7 +6829,7 @@
         <v>38</v>
       </c>
       <c r="F174" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G174" t="s">
         <v>186</v>
@@ -6871,7 +6838,7 @@
         <v>201</v>
       </c>
       <c r="I174" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="J174" t="s">
         <v>206</v>
@@ -6880,7 +6847,7 @@
         <v>217</v>
       </c>
       <c r="L174" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="175" spans="1:19">
@@ -6890,8 +6857,17 @@
       <c r="B175" s="4" t="s">
         <v>38</v>
       </c>
+      <c r="C175" s="6">
+        <v>513</v>
+      </c>
+      <c r="D175" t="s">
+        <v>82</v>
+      </c>
+      <c r="E175" t="s">
+        <v>50</v>
+      </c>
       <c r="F175" t="s">
-        <v>37</v>
+        <v>177</v>
       </c>
       <c r="G175" t="s">
         <v>186</v>
@@ -6900,16 +6876,16 @@
         <v>201</v>
       </c>
       <c r="I175" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="J175" t="s">
         <v>206</v>
       </c>
       <c r="K175" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="L175" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="176" spans="1:19">
@@ -6920,7 +6896,7 @@
         <v>38</v>
       </c>
       <c r="F176" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="G176" t="s">
         <v>186</v>
@@ -6929,7 +6905,7 @@
         <v>201</v>
       </c>
       <c r="I176" t="s">
-        <v>38</v>
+        <v>286</v>
       </c>
       <c r="J176" t="s">
         <v>206</v>
@@ -6938,10 +6914,10 @@
         <v>217</v>
       </c>
       <c r="L176" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="177" spans="1:17" ht="17" customHeight="1">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="177" spans="1:17">
       <c r="A177" s="4" t="s">
         <v>37</v>
       </c>
@@ -6949,7 +6925,7 @@
         <v>38</v>
       </c>
       <c r="F177" t="s">
-        <v>357</v>
+        <v>37</v>
       </c>
       <c r="G177" t="s">
         <v>186</v>
@@ -6958,16 +6934,19 @@
         <v>201</v>
       </c>
       <c r="I177" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J177" t="s">
         <v>206</v>
       </c>
       <c r="K177" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="178" spans="1:17" ht="17" customHeight="1">
+        <v>213</v>
+      </c>
+      <c r="L177" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="178" spans="1:17">
       <c r="A178" s="4" t="s">
         <v>37</v>
       </c>
@@ -6975,7 +6954,7 @@
         <v>38</v>
       </c>
       <c r="F178" t="s">
-        <v>473</v>
+        <v>182</v>
       </c>
       <c r="G178" t="s">
         <v>186</v>
@@ -6984,13 +6963,16 @@
         <v>201</v>
       </c>
       <c r="I178" t="s">
-        <v>289</v>
+        <v>38</v>
       </c>
       <c r="J178" t="s">
         <v>206</v>
       </c>
       <c r="K178" t="s">
         <v>217</v>
+      </c>
+      <c r="L178" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="179" spans="1:17" ht="17" customHeight="1">
@@ -7001,7 +6983,7 @@
         <v>38</v>
       </c>
       <c r="F179" t="s">
-        <v>474</v>
+        <v>357</v>
       </c>
       <c r="G179" t="s">
         <v>186</v>
@@ -7010,7 +6992,7 @@
         <v>201</v>
       </c>
       <c r="I179" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="J179" t="s">
         <v>206</v>
@@ -7026,11 +7008,17 @@
       <c r="B180" s="4" t="s">
         <v>38</v>
       </c>
+      <c r="F180" t="s">
+        <v>473</v>
+      </c>
+      <c r="G180" t="s">
+        <v>186</v>
+      </c>
       <c r="H180" t="s">
         <v>201</v>
       </c>
       <c r="I180" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="J180" t="s">
         <v>206</v>
@@ -7047,7 +7035,7 @@
         <v>38</v>
       </c>
       <c r="F181" t="s">
-        <v>180</v>
+        <v>474</v>
       </c>
       <c r="G181" t="s">
         <v>186</v>
@@ -7056,7 +7044,7 @@
         <v>201</v>
       </c>
       <c r="I181" t="s">
-        <v>487</v>
+        <v>290</v>
       </c>
       <c r="J181" t="s">
         <v>206</v>
@@ -7072,17 +7060,11 @@
       <c r="B182" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F182" t="s">
-        <v>184</v>
-      </c>
-      <c r="G182" t="s">
-        <v>186</v>
-      </c>
       <c r="H182" t="s">
         <v>201</v>
       </c>
       <c r="I182" t="s">
-        <v>212</v>
+        <v>291</v>
       </c>
       <c r="J182" t="s">
         <v>206</v>
@@ -7098,11 +7080,17 @@
       <c r="B183" s="4" t="s">
         <v>38</v>
       </c>
+      <c r="F183" t="s">
+        <v>180</v>
+      </c>
+      <c r="G183" t="s">
+        <v>186</v>
+      </c>
       <c r="H183" t="s">
         <v>201</v>
       </c>
       <c r="I183" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="J183" t="s">
         <v>206</v>
@@ -7118,11 +7106,17 @@
       <c r="B184" s="4" t="s">
         <v>38</v>
       </c>
+      <c r="F184" t="s">
+        <v>184</v>
+      </c>
+      <c r="G184" t="s">
+        <v>186</v>
+      </c>
       <c r="H184" t="s">
         <v>201</v>
       </c>
       <c r="I184" t="s">
-        <v>292</v>
+        <v>212</v>
       </c>
       <c r="J184" t="s">
         <v>206</v>
@@ -7131,24 +7125,18 @@
         <v>217</v>
       </c>
     </row>
-    <row r="185" spans="1:17">
+    <row r="185" spans="1:17" ht="17" customHeight="1">
       <c r="A185" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F185" t="s">
-        <v>175</v>
-      </c>
-      <c r="G185" t="s">
-        <v>186</v>
+        <v>38</v>
       </c>
       <c r="H185" t="s">
         <v>201</v>
       </c>
       <c r="I185" t="s">
-        <v>293</v>
+        <v>489</v>
       </c>
       <c r="J185" t="s">
         <v>206</v>
@@ -7156,37 +7144,19 @@
       <c r="K185" t="s">
         <v>217</v>
       </c>
-      <c r="L185" t="s">
-        <v>458</v>
-      </c>
-      <c r="N185" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="P185" t="s">
-        <v>527</v>
-      </c>
-      <c r="Q185" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="186" spans="1:17">
+    </row>
+    <row r="186" spans="1:17" ht="17" customHeight="1">
       <c r="A186" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F186" t="s">
-        <v>362</v>
-      </c>
-      <c r="G186" t="s">
-        <v>186</v>
+        <v>38</v>
       </c>
       <c r="H186" t="s">
         <v>201</v>
       </c>
       <c r="I186" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="J186" t="s">
         <v>206</v>
@@ -7202,17 +7172,35 @@
       <c r="B187" s="4" t="s">
         <v>39</v>
       </c>
+      <c r="F187" t="s">
+        <v>175</v>
+      </c>
+      <c r="G187" t="s">
+        <v>186</v>
+      </c>
       <c r="H187" t="s">
         <v>201</v>
       </c>
       <c r="I187" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="J187" t="s">
         <v>206</v>
       </c>
       <c r="K187" t="s">
         <v>217</v>
+      </c>
+      <c r="L187" t="s">
+        <v>458</v>
+      </c>
+      <c r="N187" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="P187" t="s">
+        <v>527</v>
+      </c>
+      <c r="Q187" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="188" spans="1:17">
@@ -7220,10 +7208,10 @@
         <v>37</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F188" t="s">
-        <v>178</v>
+        <v>362</v>
       </c>
       <c r="G188" t="s">
         <v>186</v>
@@ -7232,25 +7220,13 @@
         <v>201</v>
       </c>
       <c r="I188" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J188" t="s">
         <v>206</v>
       </c>
       <c r="K188" t="s">
         <v>217</v>
-      </c>
-      <c r="L188" t="s">
-        <v>459</v>
-      </c>
-      <c r="N188" s="10" t="s">
-        <v>578</v>
-      </c>
-      <c r="P188" t="s">
-        <v>528</v>
-      </c>
-      <c r="Q188" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="189" spans="1:17">
@@ -7258,16 +7234,13 @@
         <v>37</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F189" t="s">
-        <v>360</v>
+        <v>39</v>
       </c>
       <c r="H189" t="s">
         <v>201</v>
       </c>
       <c r="I189" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="J189" t="s">
         <v>206</v>
@@ -7281,10 +7254,10 @@
         <v>37</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>530</v>
+        <v>40</v>
       </c>
       <c r="F190" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G190" t="s">
         <v>186</v>
@@ -7293,7 +7266,7 @@
         <v>201</v>
       </c>
       <c r="I190" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J190" t="s">
         <v>206</v>
@@ -7302,16 +7275,16 @@
         <v>217</v>
       </c>
       <c r="L190" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="N190" s="10" t="s">
-        <v>530</v>
+        <v>578</v>
       </c>
       <c r="P190" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="Q190" t="s">
-        <v>471</v>
+        <v>552</v>
       </c>
     </row>
     <row r="191" spans="1:17">
@@ -7319,19 +7292,16 @@
         <v>37</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>530</v>
+        <v>40</v>
       </c>
       <c r="F191" t="s">
-        <v>471</v>
-      </c>
-      <c r="G191" t="s">
-        <v>186</v>
+        <v>360</v>
       </c>
       <c r="H191" t="s">
         <v>201</v>
       </c>
       <c r="I191" t="s">
-        <v>41</v>
+        <v>297</v>
       </c>
       <c r="J191" t="s">
         <v>206</v>
@@ -7347,17 +7317,35 @@
       <c r="B192" s="4" t="s">
         <v>530</v>
       </c>
+      <c r="F192" t="s">
+        <v>174</v>
+      </c>
+      <c r="G192" t="s">
+        <v>186</v>
+      </c>
       <c r="H192" t="s">
         <v>201</v>
       </c>
       <c r="I192" t="s">
-        <v>211</v>
+        <v>298</v>
       </c>
       <c r="J192" t="s">
         <v>206</v>
       </c>
       <c r="K192" t="s">
         <v>217</v>
+      </c>
+      <c r="L192" t="s">
+        <v>452</v>
+      </c>
+      <c r="N192" s="10" t="s">
+        <v>530</v>
+      </c>
+      <c r="P192" t="s">
+        <v>529</v>
+      </c>
+      <c r="Q192" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="193" spans="1:17">
@@ -7367,11 +7355,17 @@
       <c r="B193" s="4" t="s">
         <v>530</v>
       </c>
+      <c r="F193" t="s">
+        <v>471</v>
+      </c>
+      <c r="G193" t="s">
+        <v>186</v>
+      </c>
       <c r="H193" t="s">
         <v>201</v>
       </c>
       <c r="I193" t="s">
-        <v>299</v>
+        <v>41</v>
       </c>
       <c r="J193" t="s">
         <v>206</v>
@@ -7385,10 +7379,19 @@
         <v>37</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>555</v>
-      </c>
-      <c r="Q194" t="s">
-        <v>557</v>
+        <v>530</v>
+      </c>
+      <c r="H194" t="s">
+        <v>201</v>
+      </c>
+      <c r="I194" t="s">
+        <v>211</v>
+      </c>
+      <c r="J194" t="s">
+        <v>206</v>
+      </c>
+      <c r="K194" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="195" spans="1:17">
@@ -7396,10 +7399,19 @@
         <v>37</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>556</v>
-      </c>
-      <c r="Q195" t="s">
-        <v>558</v>
+        <v>530</v>
+      </c>
+      <c r="H195" t="s">
+        <v>201</v>
+      </c>
+      <c r="I195" t="s">
+        <v>299</v>
+      </c>
+      <c r="J195" t="s">
+        <v>206</v>
+      </c>
+      <c r="K195" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="196" spans="1:17">
@@ -7407,45 +7419,21 @@
         <v>37</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>291</v>
+        <v>555</v>
       </c>
       <c r="Q196" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="197" spans="1:17" ht="17" customHeight="1">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="197" spans="1:17">
       <c r="A197" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C197" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="D197" t="s">
-        <v>467</v>
-      </c>
-      <c r="E197" t="s">
-        <v>50</v>
-      </c>
-      <c r="F197" t="s">
-        <v>185</v>
-      </c>
-      <c r="G197" t="s">
-        <v>186</v>
-      </c>
-      <c r="H197" t="s">
-        <v>201</v>
-      </c>
-      <c r="I197" t="s">
-        <v>300</v>
-      </c>
-      <c r="J197" t="s">
-        <v>206</v>
-      </c>
-      <c r="K197" t="s">
-        <v>217</v>
+        <v>556</v>
+      </c>
+      <c r="Q197" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="198" spans="1:17">
@@ -7453,59 +7441,62 @@
         <v>37</v>
       </c>
       <c r="B198" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q198" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="199" spans="1:17" ht="17" customHeight="1">
+      <c r="A199" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B199" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F198" t="s">
+      <c r="C199" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="D199" t="s">
+        <v>467</v>
+      </c>
+      <c r="E199" t="s">
+        <v>50</v>
+      </c>
+      <c r="F199" t="s">
+        <v>185</v>
+      </c>
+      <c r="G199" t="s">
+        <v>186</v>
+      </c>
+      <c r="H199" t="s">
+        <v>201</v>
+      </c>
+      <c r="I199" t="s">
+        <v>300</v>
+      </c>
+      <c r="J199" t="s">
+        <v>206</v>
+      </c>
+      <c r="K199" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="200" spans="1:17">
+      <c r="A200" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F200" t="s">
         <v>183</v>
       </c>
-      <c r="G198" t="s">
+      <c r="G200" t="s">
         <v>186</v>
       </c>
-      <c r="H198" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="199" spans="1:17">
-      <c r="A199" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B199" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E199" t="s">
-        <v>52</v>
-      </c>
-      <c r="H199" t="s">
-        <v>200</v>
-      </c>
-      <c r="I199" t="s">
-        <v>301</v>
-      </c>
-      <c r="J199" t="s">
-        <v>209</v>
-      </c>
-      <c r="K199" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="200" spans="1:17">
-      <c r="A200" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B200" s="5" t="s">
-        <v>45</v>
-      </c>
       <c r="H200" t="s">
-        <v>200</v>
-      </c>
-      <c r="I200" t="s">
-        <v>208</v>
-      </c>
-      <c r="J200" t="s">
-        <v>209</v>
-      </c>
-      <c r="K200" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
     </row>
     <row r="201" spans="1:17">
@@ -7513,28 +7504,16 @@
         <v>43</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C201" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="D201" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E201" t="s">
         <v>52</v>
       </c>
-      <c r="F201" t="s">
-        <v>161</v>
-      </c>
-      <c r="G201" t="s">
-        <v>173</v>
-      </c>
       <c r="H201" t="s">
         <v>200</v>
       </c>
       <c r="I201" t="s">
-        <v>45</v>
+        <v>301</v>
       </c>
       <c r="J201" t="s">
         <v>209</v>
@@ -7548,22 +7527,13 @@
         <v>43</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C202" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="D202" t="s">
-        <v>91</v>
-      </c>
-      <c r="E202" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H202" t="s">
         <v>200</v>
       </c>
       <c r="I202" t="s">
-        <v>302</v>
+        <v>208</v>
       </c>
       <c r="J202" t="s">
         <v>209</v>
@@ -7577,27 +7547,91 @@
         <v>43</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D203" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E203" t="s">
         <v>52</v>
       </c>
+      <c r="F203" t="s">
+        <v>161</v>
+      </c>
+      <c r="G203" t="s">
+        <v>173</v>
+      </c>
       <c r="H203" t="s">
         <v>200</v>
       </c>
       <c r="I203" t="s">
-        <v>303</v>
+        <v>45</v>
       </c>
       <c r="J203" t="s">
         <v>209</v>
       </c>
       <c r="K203" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="204" spans="1:17">
+      <c r="A204" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B204" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C204" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D204" t="s">
+        <v>91</v>
+      </c>
+      <c r="E204" t="s">
+        <v>52</v>
+      </c>
+      <c r="H204" t="s">
+        <v>200</v>
+      </c>
+      <c r="I204" t="s">
+        <v>302</v>
+      </c>
+      <c r="J204" t="s">
+        <v>209</v>
+      </c>
+      <c r="K204" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="205" spans="1:17">
+      <c r="A205" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C205" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D205" t="s">
+        <v>47</v>
+      </c>
+      <c r="E205" t="s">
+        <v>52</v>
+      </c>
+      <c r="H205" t="s">
+        <v>200</v>
+      </c>
+      <c r="I205" t="s">
+        <v>303</v>
+      </c>
+      <c r="J205" t="s">
+        <v>209</v>
+      </c>
+      <c r="K205" t="s">
         <v>214</v>
       </c>
     </row>

--- a/benefit_indexing.xlsx
+++ b/benefit_indexing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/BryanMak/Documents/RawClaimMCR-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21CC6EFB-52F6-824E-8CF4-E156755A4E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F2F09E-E1A1-F548-A013-FCE62EBD9D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-18340" yWindow="-21000" windowWidth="38400" windowHeight="21000" xr2:uid="{A0161F8B-45E3-674F-BD1A-B040F75BC5F2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="691">
   <si>
     <t>Daily Room &amp; Board</t>
   </si>
@@ -1073,9 +1073,6 @@
     <t>E/VAC</t>
   </si>
   <si>
-    <t>Combined Wellness Benefit - Vac&amp;Opt</t>
-  </si>
-  <si>
     <t>PVIN</t>
   </si>
   <si>
@@ -2103,6 +2100,15 @@
   </si>
   <si>
     <t>Viral Warts &amp; Skin Lesions (EXCLUDE SMM)</t>
+  </si>
+  <si>
+    <t>Combined Wellness Benefit - Vac&amp;CheckUp&amp;Optical</t>
+  </si>
+  <si>
+    <t>Combined Wellness Benefit - Vac&amp;Optical</t>
+  </si>
+  <si>
+    <t>VACC/ROUTINE CHECKUP/OPTICAL</t>
   </si>
 </sst>
 </file>
@@ -2537,7 +2543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4FDC71E-C596-D04E-840B-E0EAE83F6708}">
-  <dimension ref="A1:S205"/>
+  <dimension ref="A1:S206"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
@@ -2591,25 +2597,25 @@
         <v>310</v>
       </c>
       <c r="M1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="N1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="O1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="P1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="Q1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="R1" t="s">
+        <v>583</v>
+      </c>
+      <c r="S1" t="s">
         <v>584</v>
-      </c>
-      <c r="S1" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="17" customHeight="1">
@@ -2650,25 +2656,25 @@
         <v>316</v>
       </c>
       <c r="M2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="N2" s="10" t="s">
         <v>53</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="P2" t="s">
         <v>156</v>
       </c>
       <c r="Q2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="R2" t="s">
+        <v>619</v>
+      </c>
+      <c r="S2" t="s">
         <v>620</v>
-      </c>
-      <c r="S2" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="17" customHeight="1">
@@ -2700,10 +2706,10 @@
         <v>325</v>
       </c>
       <c r="M3" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="O3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -2744,25 +2750,25 @@
         <v>328</v>
       </c>
       <c r="M4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O4" s="10" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="P4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Q4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="R4" t="s">
+        <v>609</v>
+      </c>
+      <c r="S4" t="s">
         <v>610</v>
-      </c>
-      <c r="S4" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2773,7 +2779,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G5" t="s">
         <v>173</v>
@@ -2791,13 +2797,13 @@
         <v>215</v>
       </c>
       <c r="M5" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="O5" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2808,7 +2814,7 @@
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="N6" s="10"/>
     </row>
@@ -2850,25 +2856,25 @@
         <v>327</v>
       </c>
       <c r="M7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="N7" s="10" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="O7" s="10" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="P7" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Q7" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="R7" t="s">
+        <v>611</v>
+      </c>
+      <c r="S7" t="s">
         <v>612</v>
-      </c>
-      <c r="S7" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -2880,7 +2886,7 @@
       </c>
       <c r="C8" s="7"/>
       <c r="F8" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G8" t="s">
         <v>173</v>
@@ -2901,10 +2907,10 @@
         <v>326</v>
       </c>
       <c r="M8" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="O8" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -2921,7 +2927,7 @@
         <v>336</v>
       </c>
       <c r="M9" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -2946,7 +2952,7 @@
         <v>23</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>136</v>
@@ -2964,13 +2970,13 @@
         <v>173</v>
       </c>
       <c r="I11" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="J11" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="K11" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L11" t="s">
         <v>339</v>
@@ -2981,13 +2987,13 @@
         <v>23</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="I12" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -2995,7 +3001,7 @@
         <v>23</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>138</v>
@@ -3012,7 +3018,7 @@
         <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>139</v>
@@ -3047,10 +3053,10 @@
         <v>48</v>
       </c>
       <c r="M15" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3085,7 +3091,7 @@
         <v>332</v>
       </c>
       <c r="M16" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3108,7 +3114,7 @@
         <v>215</v>
       </c>
       <c r="M17" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -3143,7 +3149,7 @@
         <v>322</v>
       </c>
       <c r="M18" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -3166,7 +3172,7 @@
         <v>215</v>
       </c>
       <c r="M19" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -3177,7 +3183,7 @@
         <v>5</v>
       </c>
       <c r="M20" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -3212,7 +3218,7 @@
         <v>319</v>
       </c>
       <c r="M21" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="N21" s="10" t="s">
         <v>234</v>
@@ -3239,7 +3245,7 @@
         <v>215</v>
       </c>
       <c r="M22" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -3247,7 +3253,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F23" t="s">
         <v>157</v>
@@ -3256,19 +3262,19 @@
         <v>173</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="P23" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="Q23" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="R23" t="s">
+        <v>598</v>
+      </c>
+      <c r="S23" t="s">
         <v>599</v>
-      </c>
-      <c r="S23" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -3276,10 +3282,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="O24" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -3299,10 +3305,10 @@
         <v>48</v>
       </c>
       <c r="M25" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -3313,7 +3319,7 @@
         <v>7</v>
       </c>
       <c r="M26" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="N26" s="10"/>
     </row>
@@ -3349,7 +3355,7 @@
         <v>340</v>
       </c>
       <c r="M27" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -3360,7 +3366,7 @@
         <v>8</v>
       </c>
       <c r="M28" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -3395,7 +3401,7 @@
         <v>323</v>
       </c>
       <c r="M29" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -3406,7 +3412,7 @@
         <v>9</v>
       </c>
       <c r="M30" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -3417,7 +3423,7 @@
         <v>9</v>
       </c>
       <c r="M31" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -3452,10 +3458,10 @@
         <v>337</v>
       </c>
       <c r="M32" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="N32" s="10" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -3466,7 +3472,7 @@
         <v>10</v>
       </c>
       <c r="M33" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="N33" s="10"/>
     </row>
@@ -3475,7 +3481,7 @@
         <v>23</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="F34" t="s">
         <v>158</v>
@@ -3485,19 +3491,19 @@
       </c>
       <c r="N34" s="10"/>
       <c r="O34" s="10" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="P34" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="Q34" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="R34" t="s">
+        <v>596</v>
+      </c>
+      <c r="S34" t="s">
         <v>597</v>
-      </c>
-      <c r="S34" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -3505,11 +3511,11 @@
         <v>23</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="N35" s="10"/>
       <c r="O35" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="36" spans="1:19" ht="17" customHeight="1">
@@ -3529,7 +3535,7 @@
         <v>48</v>
       </c>
       <c r="N36" s="10" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -3564,7 +3570,7 @@
         <v>333</v>
       </c>
       <c r="M37" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -3587,7 +3593,7 @@
         <v>215</v>
       </c>
       <c r="M38" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -3598,7 +3604,7 @@
         <v>12</v>
       </c>
       <c r="M39" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="40" spans="1:19">
@@ -3633,7 +3639,7 @@
         <v>324</v>
       </c>
       <c r="M40" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="41" spans="1:19">
@@ -3656,7 +3662,7 @@
         <v>215</v>
       </c>
       <c r="M41" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="42" spans="1:19">
@@ -3667,7 +3673,7 @@
         <v>13</v>
       </c>
       <c r="M42" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="43" spans="1:19">
@@ -3702,10 +3708,10 @@
         <v>338</v>
       </c>
       <c r="M43" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="44" spans="1:19">
@@ -3728,7 +3734,7 @@
         <v>215</v>
       </c>
       <c r="M44" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="45" spans="1:19">
@@ -3739,7 +3745,7 @@
         <v>14</v>
       </c>
       <c r="M45" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="46" spans="1:19">
@@ -3747,7 +3753,7 @@
         <v>23</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F46" t="s">
         <v>159</v>
@@ -3756,19 +3762,19 @@
         <v>173</v>
       </c>
       <c r="O46" s="10" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="P46" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="Q46" t="s">
         <v>159</v>
       </c>
       <c r="R46" t="s">
+        <v>591</v>
+      </c>
+      <c r="S46" t="s">
         <v>592</v>
-      </c>
-      <c r="S46" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="47" spans="1:19">
@@ -3776,10 +3782,10 @@
         <v>23</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="O47" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="48" spans="1:19">
@@ -3820,22 +3826,22 @@
         <v>341</v>
       </c>
       <c r="M48" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="N48" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="P48" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="Q48" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="R48" t="s">
+        <v>621</v>
+      </c>
+      <c r="S48" t="s">
         <v>622</v>
-      </c>
-      <c r="S48" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="49" spans="1:19">
@@ -3846,7 +3852,7 @@
         <v>15</v>
       </c>
       <c r="F49" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G49" t="s">
         <v>173</v>
@@ -3864,7 +3870,7 @@
         <v>215</v>
       </c>
       <c r="M49" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="50" spans="1:19">
@@ -3875,10 +3881,10 @@
         <v>16</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D50" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E50" t="s">
         <v>48</v>
@@ -3913,7 +3919,7 @@
         <v>48</v>
       </c>
       <c r="F51" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G51" t="s">
         <v>173</v>
@@ -3931,7 +3937,7 @@
         <v>215</v>
       </c>
       <c r="M51" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="52" spans="1:19">
@@ -3943,7 +3949,7 @@
       </c>
       <c r="C52" s="7"/>
       <c r="F52" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="G52" t="s">
         <v>173</v>
@@ -3957,7 +3963,7 @@
         <v>23</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>129</v>
@@ -3980,7 +3986,7 @@
         <v>23</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C54" s="7"/>
       <c r="H54" t="s">
@@ -3996,7 +4002,7 @@
         <v>215</v>
       </c>
       <c r="M54" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="55" spans="1:19">
@@ -4004,11 +4010,11 @@
         <v>23</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C55" s="7"/>
       <c r="M55" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="56" spans="1:19">
@@ -4016,11 +4022,11 @@
         <v>23</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C56" s="7"/>
       <c r="M56" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="57" spans="1:19">
@@ -4028,11 +4034,11 @@
         <v>23</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C57" s="7"/>
       <c r="M57" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="58" spans="1:19">
@@ -4040,7 +4046,7 @@
         <v>23</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C58" s="7"/>
       <c r="H58" t="s">
@@ -4056,10 +4062,10 @@
         <v>215</v>
       </c>
       <c r="M58" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="O58" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="59" spans="1:19">
@@ -4067,11 +4073,11 @@
         <v>23</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C59" s="7"/>
       <c r="M59" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="60" spans="1:19">
@@ -4079,11 +4085,11 @@
         <v>23</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C60" s="7"/>
       <c r="M60" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="61" spans="1:19">
@@ -4091,7 +4097,7 @@
         <v>23</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C61" s="7"/>
       <c r="H61" t="s">
@@ -4107,7 +4113,7 @@
         <v>215</v>
       </c>
       <c r="M61" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="62" spans="1:19">
@@ -4115,7 +4121,7 @@
         <v>23</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C62" s="7"/>
       <c r="H62" t="s">
@@ -4136,7 +4142,7 @@
         <v>23</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C63" s="7"/>
       <c r="H63" t="s">
@@ -4190,19 +4196,19 @@
         <v>317</v>
       </c>
       <c r="M64" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="N64" s="10" t="s">
         <v>250</v>
       </c>
       <c r="O64" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="R64" t="s">
+        <v>625</v>
+      </c>
+      <c r="S64" t="s">
         <v>626</v>
-      </c>
-      <c r="S64" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="65" spans="1:19">
@@ -4243,7 +4249,7 @@
         <v>335</v>
       </c>
       <c r="M65" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="66" spans="1:19">
@@ -4254,7 +4260,7 @@
         <v>19</v>
       </c>
       <c r="F66" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G66" t="s">
         <v>173</v>
@@ -4272,7 +4278,7 @@
         <v>215</v>
       </c>
       <c r="M66" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="67" spans="1:19">
@@ -4286,7 +4292,7 @@
         <v>200</v>
       </c>
       <c r="I67" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="J67" t="s">
         <v>203</v>
@@ -4300,7 +4306,7 @@
         <v>23</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="69" spans="1:19" ht="17" customHeight="1">
@@ -4341,22 +4347,22 @@
         <v>342</v>
       </c>
       <c r="M69" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="O69" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="P69" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="R69" t="s">
+        <v>633</v>
+      </c>
+      <c r="S69" t="s">
         <v>634</v>
-      </c>
-      <c r="S69" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="70" spans="1:19" ht="17" customHeight="1">
@@ -4367,7 +4373,7 @@
         <v>20</v>
       </c>
       <c r="M70" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="N70" s="10"/>
     </row>
@@ -4385,7 +4391,7 @@
         <v>173</v>
       </c>
       <c r="M71" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="72" spans="1:19">
@@ -4393,22 +4399,22 @@
         <v>23</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="L72" t="s">
         <v>335</v>
       </c>
       <c r="M72" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="O72" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="R72" t="s">
+        <v>617</v>
+      </c>
+      <c r="S72" t="s">
         <v>618</v>
-      </c>
-      <c r="S72" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="73" spans="1:19">
@@ -4416,10 +4422,10 @@
         <v>23</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="M73" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="74" spans="1:19" ht="17" customHeight="1">
@@ -4427,13 +4433,13 @@
         <v>23</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="R74" t="s">
+        <v>629</v>
+      </c>
+      <c r="S74" t="s">
         <v>630</v>
-      </c>
-      <c r="S74" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="75" spans="1:19">
@@ -4441,13 +4447,13 @@
         <v>23</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="R75" t="s">
+        <v>631</v>
+      </c>
+      <c r="S75" t="s">
         <v>632</v>
-      </c>
-      <c r="S75" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="76" spans="1:19">
@@ -4480,11 +4486,11 @@
         <v>23</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C78" s="7"/>
       <c r="O78" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="79" spans="1:19">
@@ -4492,11 +4498,11 @@
         <v>23</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C79" s="7"/>
       <c r="Q79" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="80" spans="1:19">
@@ -4504,7 +4510,7 @@
         <v>23</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C80" s="7"/>
     </row>
@@ -4546,7 +4552,7 @@
         <v>329</v>
       </c>
       <c r="M81" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="P81" t="s">
         <v>168</v>
@@ -4555,10 +4561,10 @@
         <v>168</v>
       </c>
       <c r="R81" t="s">
+        <v>613</v>
+      </c>
+      <c r="S81" t="s">
         <v>614</v>
-      </c>
-      <c r="S81" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="82" spans="1:19">
@@ -4569,7 +4575,7 @@
         <v>141</v>
       </c>
       <c r="M82" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="83" spans="1:19">
@@ -4610,25 +4616,25 @@
         <v>312</v>
       </c>
       <c r="M83" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="P83" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="Q83" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="R83" t="s">
+        <v>585</v>
+      </c>
+      <c r="S83" t="s">
         <v>586</v>
-      </c>
-      <c r="S83" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="84" spans="1:19">
@@ -4657,13 +4663,13 @@
         <v>218</v>
       </c>
       <c r="L84" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="M84" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O84" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="85" spans="1:19">
@@ -4686,7 +4692,7 @@
         <v>218</v>
       </c>
       <c r="O85" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="86" spans="1:19">
@@ -4720,7 +4726,7 @@
         <v>201</v>
       </c>
       <c r="I87" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J87" t="s">
         <v>204</v>
@@ -4740,7 +4746,7 @@
         <v>201</v>
       </c>
       <c r="I88" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J88" t="s">
         <v>204</v>
@@ -4760,7 +4766,7 @@
         <v>201</v>
       </c>
       <c r="I89" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="J89" t="s">
         <v>204</v>
@@ -4820,7 +4826,7 @@
         <v>201</v>
       </c>
       <c r="I92" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="J92" t="s">
         <v>204</v>
@@ -4840,7 +4846,7 @@
         <v>201</v>
       </c>
       <c r="I93" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J93" t="s">
         <v>204</v>
@@ -4860,7 +4866,7 @@
         <v>201</v>
       </c>
       <c r="I94" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="J94" t="s">
         <v>204</v>
@@ -4880,7 +4886,7 @@
         <v>201</v>
       </c>
       <c r="I95" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="J95" t="s">
         <v>204</v>
@@ -4897,7 +4903,7 @@
         <v>25</v>
       </c>
       <c r="I96" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="J96" t="s">
         <v>204</v>
@@ -4914,7 +4920,7 @@
         <v>25</v>
       </c>
       <c r="I97" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="J97" t="s">
         <v>204</v>
@@ -4934,7 +4940,7 @@
         <v>201</v>
       </c>
       <c r="I98" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J98" t="s">
         <v>204</v>
@@ -4954,7 +4960,7 @@
         <v>201</v>
       </c>
       <c r="I99" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J99" t="s">
         <v>204</v>
@@ -5021,22 +5027,22 @@
         <v>246</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="P101" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="Q101" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="R101" t="s">
+        <v>605</v>
+      </c>
+      <c r="S101" t="s">
         <v>606</v>
-      </c>
-      <c r="S101" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="102" spans="1:19">
@@ -5059,10 +5065,10 @@
         <v>218</v>
       </c>
       <c r="M102" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="O102" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="103" spans="1:19">
@@ -5091,7 +5097,7 @@
         <v>218</v>
       </c>
       <c r="O103" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="104" spans="1:19">
@@ -5165,7 +5171,7 @@
         <v>201</v>
       </c>
       <c r="I107" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J107" t="s">
         <v>204</v>
@@ -5185,7 +5191,7 @@
         <v>201</v>
       </c>
       <c r="I108" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J108" t="s">
         <v>204</v>
@@ -5205,7 +5211,7 @@
         <v>201</v>
       </c>
       <c r="I109" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="J109" t="s">
         <v>204</v>
@@ -5225,7 +5231,7 @@
         <v>201</v>
       </c>
       <c r="I110" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="J110" t="s">
         <v>204</v>
@@ -5245,7 +5251,7 @@
         <v>201</v>
       </c>
       <c r="I111" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="J111" t="s">
         <v>204</v>
@@ -5265,7 +5271,7 @@
         <v>201</v>
       </c>
       <c r="I112" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J112" t="s">
         <v>204</v>
@@ -5285,7 +5291,7 @@
         <v>201</v>
       </c>
       <c r="I113" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J113" t="s">
         <v>204</v>
@@ -5305,7 +5311,7 @@
         <v>201</v>
       </c>
       <c r="I114" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="J114" t="s">
         <v>204</v>
@@ -5322,7 +5328,7 @@
         <v>26</v>
       </c>
       <c r="I115" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="J115" t="s">
         <v>204</v>
@@ -5339,7 +5345,7 @@
         <v>26</v>
       </c>
       <c r="I116" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="J116" t="s">
         <v>204</v>
@@ -5356,7 +5362,7 @@
         <v>26</v>
       </c>
       <c r="I117" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="J117" t="s">
         <v>204</v>
@@ -5416,7 +5422,7 @@
         <v>201</v>
       </c>
       <c r="I120" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="J120" t="s">
         <v>204</v>
@@ -5433,7 +5439,7 @@
         <v>26</v>
       </c>
       <c r="I121" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="122" spans="1:19">
@@ -5477,16 +5483,16 @@
         <v>266</v>
       </c>
       <c r="O122" s="10" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="P122" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="R122" t="s">
+        <v>589</v>
+      </c>
+      <c r="S122" t="s">
         <v>590</v>
-      </c>
-      <c r="S122" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="123" spans="1:19">
@@ -5509,10 +5515,10 @@
         <v>218</v>
       </c>
       <c r="M123" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="O123" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="124" spans="1:19">
@@ -5546,7 +5552,7 @@
         <v>24</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F125" t="s">
         <v>189</v>
@@ -5567,13 +5573,13 @@
         <v>218</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="O125" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="Q125" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="126" spans="1:19">
@@ -5614,16 +5620,16 @@
         <v>318</v>
       </c>
       <c r="M126" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="P126" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="R126" t="s">
+        <v>623</v>
+      </c>
+      <c r="S126" t="s">
         <v>624</v>
-      </c>
-      <c r="S126" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="127" spans="1:19">
@@ -5634,10 +5640,10 @@
         <v>28</v>
       </c>
       <c r="L127" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="M127" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="128" spans="1:19">
@@ -5648,7 +5654,7 @@
         <v>28</v>
       </c>
       <c r="M128" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="129" spans="1:19">
@@ -5656,7 +5662,7 @@
         <v>24</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>115</v>
@@ -5689,25 +5695,25 @@
         <v>311</v>
       </c>
       <c r="M129" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P129" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="Q129" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="R129" t="s">
+        <v>587</v>
+      </c>
+      <c r="S129" t="s">
         <v>588</v>
-      </c>
-      <c r="S129" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="130" spans="1:19">
@@ -5715,7 +5721,7 @@
         <v>24</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>113</v>
@@ -5748,13 +5754,13 @@
         <v>320</v>
       </c>
       <c r="M130" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O130" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="Q130" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="131" spans="1:19">
@@ -5762,7 +5768,7 @@
         <v>24</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F131" t="s">
         <v>187</v>
@@ -5786,13 +5792,13 @@
         <v>321</v>
       </c>
       <c r="M131" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O131" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="Q131" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="132" spans="1:19">
@@ -5800,10 +5806,10 @@
         <v>24</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F132" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G132" t="s">
         <v>148</v>
@@ -5812,13 +5818,13 @@
         <v>201</v>
       </c>
       <c r="I132" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="L132" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="M132" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="133" spans="1:19">
@@ -5826,7 +5832,7 @@
         <v>24</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F133" t="s">
         <v>190</v>
@@ -5847,7 +5853,7 @@
         <v>218</v>
       </c>
       <c r="M133" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="134" spans="1:19">
@@ -5855,7 +5861,7 @@
         <v>24</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F134" t="s">
         <v>193</v>
@@ -5881,10 +5887,10 @@
         <v>24</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F135" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G135" t="s">
         <v>148</v>
@@ -5893,7 +5899,7 @@
         <v>201</v>
       </c>
       <c r="I135" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="136" spans="1:19">
@@ -5901,10 +5907,10 @@
         <v>24</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F136" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G136" t="s">
         <v>148</v>
@@ -5913,7 +5919,7 @@
         <v>201</v>
       </c>
       <c r="I136" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="137" spans="1:19">
@@ -5921,10 +5927,10 @@
         <v>24</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F137" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="G137" t="s">
         <v>148</v>
@@ -5941,10 +5947,10 @@
         <v>24</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F138" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="G138" t="s">
         <v>148</v>
@@ -5955,7 +5961,7 @@
         <v>24</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="140" spans="1:19" ht="17" customHeight="1">
@@ -5993,13 +5999,13 @@
         <v>218</v>
       </c>
       <c r="M140" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="N140" s="10" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="O140" s="10" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="141" spans="1:19">
@@ -6010,7 +6016,7 @@
         <v>29</v>
       </c>
       <c r="M141" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="N141" s="10"/>
       <c r="O141" t="s">
@@ -6025,7 +6031,7 @@
         <v>29</v>
       </c>
       <c r="M142" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="N142" s="10"/>
     </row>
@@ -6058,7 +6064,7 @@
         <v>218</v>
       </c>
       <c r="M143" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="144" spans="1:19">
@@ -6107,25 +6113,25 @@
         <v>315</v>
       </c>
       <c r="M145" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="P145" t="s">
         <v>174</v>
       </c>
       <c r="Q145" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="R145" t="s">
+        <v>607</v>
+      </c>
+      <c r="S145" t="s">
         <v>608</v>
-      </c>
-      <c r="S145" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="146" spans="1:19">
@@ -6154,13 +6160,13 @@
         <v>218</v>
       </c>
       <c r="L146" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="M146" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="O146" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="147" spans="1:19">
@@ -6171,7 +6177,7 @@
         <v>32</v>
       </c>
       <c r="F147" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G147" t="s">
         <v>148</v>
@@ -6180,10 +6186,10 @@
         <v>201</v>
       </c>
       <c r="M147" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="O147" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="148" spans="1:19">
@@ -6224,16 +6230,16 @@
         <v>334</v>
       </c>
       <c r="M148" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="O148" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="P148" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="Q148" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="149" spans="1:19">
@@ -6271,7 +6277,7 @@
         <v>218</v>
       </c>
       <c r="M149" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="150" spans="1:19">
@@ -6291,7 +6297,7 @@
         <v>201</v>
       </c>
       <c r="I150" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="151" spans="1:19">
@@ -6311,7 +6317,7 @@
         <v>49</v>
       </c>
       <c r="F151" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G151" t="s">
         <v>148</v>
@@ -6329,7 +6335,7 @@
         <v>213</v>
       </c>
       <c r="L151" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="M151" t="s">
         <v>34</v>
@@ -6338,10 +6344,10 @@
         <v>34</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Q151" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="152" spans="1:19">
@@ -6352,7 +6358,7 @@
         <v>34</v>
       </c>
       <c r="O152" s="10" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="153" spans="1:19">
@@ -6390,25 +6396,25 @@
         <v>213</v>
       </c>
       <c r="L153" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="M153" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="O153" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="Q153" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="R153" t="s">
+        <v>615</v>
+      </c>
+      <c r="S153" t="s">
         <v>616</v>
-      </c>
-      <c r="S153" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="154" spans="1:19">
@@ -6437,7 +6443,7 @@
         <v>218</v>
       </c>
       <c r="O154" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="155" spans="1:19">
@@ -6483,13 +6489,13 @@
         <v>218</v>
       </c>
       <c r="M156" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O156" s="10" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="P156" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="157" spans="1:19">
@@ -6509,7 +6515,7 @@
         <v>51</v>
       </c>
       <c r="O157" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="158" spans="1:19">
@@ -6529,7 +6535,7 @@
         <v>49</v>
       </c>
       <c r="M158" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="159" spans="1:19">
@@ -6540,7 +6546,7 @@
         <v>304</v>
       </c>
       <c r="M159" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="160" spans="1:19">
@@ -6551,7 +6557,7 @@
         <v>304</v>
       </c>
       <c r="M160" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="161" spans="1:19">
@@ -6559,10 +6565,10 @@
         <v>24</v>
       </c>
       <c r="B161" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="M161" t="s">
         <v>377</v>
-      </c>
-      <c r="M161" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="162" spans="1:19">
@@ -6590,9 +6596,6 @@
       <c r="H162" t="s">
         <v>201</v>
       </c>
-      <c r="I162" t="s">
-        <v>353</v>
-      </c>
       <c r="J162" t="s">
         <v>204</v>
       </c>
@@ -6600,7 +6603,7 @@
         <v>218</v>
       </c>
       <c r="M162" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="163" spans="1:19">
@@ -6608,7 +6611,7 @@
         <v>24</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>345</v>
+        <v>689</v>
       </c>
       <c r="F163" t="s">
         <v>344</v>
@@ -6628,10 +6631,10 @@
         <v>24</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F164" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G164" t="s">
         <v>148</v>
@@ -6640,7 +6643,7 @@
         <v>201</v>
       </c>
       <c r="I164" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J164" t="s">
         <v>204</v>
@@ -6649,7 +6652,7 @@
         <v>218</v>
       </c>
       <c r="L164" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="165" spans="1:19">
@@ -6657,34 +6660,13 @@
         <v>24</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="H165" t="s">
-        <v>201</v>
+        <v>688</v>
       </c>
       <c r="I165" t="s">
-        <v>283</v>
-      </c>
-      <c r="J165" t="s">
-        <v>204</v>
-      </c>
-      <c r="K165" t="s">
-        <v>218</v>
-      </c>
-      <c r="M165" t="s">
-        <v>287</v>
-      </c>
-      <c r="N165" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="O165" s="10" t="s">
-        <v>435</v>
-      </c>
-      <c r="R165" t="s">
-        <v>604</v>
-      </c>
-      <c r="S165" t="s">
-        <v>605</v>
+        <v>352</v>
+      </c>
+      <c r="L165" t="s">
+        <v>690</v>
       </c>
     </row>
     <row r="166" spans="1:19">
@@ -6692,14 +6674,34 @@
         <v>24</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
+      </c>
+      <c r="H166" t="s">
+        <v>201</v>
+      </c>
+      <c r="I166" t="s">
+        <v>283</v>
+      </c>
+      <c r="J166" t="s">
+        <v>204</v>
+      </c>
+      <c r="K166" t="s">
+        <v>218</v>
       </c>
       <c r="M166" t="s">
-        <v>663</v>
-      </c>
-      <c r="N166" s="10"/>
+        <v>287</v>
+      </c>
+      <c r="N166" s="10" t="s">
+        <v>287</v>
+      </c>
       <c r="O166" s="10" t="s">
-        <v>537</v>
+        <v>434</v>
+      </c>
+      <c r="R166" t="s">
+        <v>603</v>
+      </c>
+      <c r="S166" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="167" spans="1:19">
@@ -6707,10 +6709,14 @@
         <v>24</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="M167" t="s">
-        <v>38</v>
+        <v>662</v>
+      </c>
+      <c r="N167" s="10"/>
+      <c r="O167" s="10" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="168" spans="1:19">
@@ -6718,13 +6724,10 @@
         <v>24</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="R168" t="s">
-        <v>602</v>
-      </c>
-      <c r="S168" t="s">
-        <v>603</v>
+        <v>406</v>
+      </c>
+      <c r="M168" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="169" spans="1:19">
@@ -6732,16 +6735,13 @@
         <v>24</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="F169" t="s">
-        <v>470</v>
-      </c>
-      <c r="G169" t="s">
-        <v>148</v>
-      </c>
-      <c r="H169" t="s">
-        <v>201</v>
+        <v>600</v>
+      </c>
+      <c r="R169" t="s">
+        <v>601</v>
+      </c>
+      <c r="S169" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="170" spans="1:19">
@@ -6749,10 +6749,16 @@
         <v>24</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>534</v>
-      </c>
-      <c r="O170" t="s">
-        <v>533</v>
+        <v>468</v>
+      </c>
+      <c r="F170" t="s">
+        <v>469</v>
+      </c>
+      <c r="G170" t="s">
+        <v>148</v>
+      </c>
+      <c r="H170" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="171" spans="1:19">
@@ -6760,10 +6766,10 @@
         <v>24</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="Q171" t="s">
-        <v>550</v>
+        <v>533</v>
+      </c>
+      <c r="O171" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="172" spans="1:19">
@@ -6771,54 +6777,21 @@
         <v>24</v>
       </c>
       <c r="B172" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="Q172" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="173" spans="1:19">
+      <c r="A173" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="M173" t="s">
         <v>646</v>
-      </c>
-      <c r="M172" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="173" spans="1:19">
-      <c r="A173" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B173" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C173" s="6">
-        <v>511</v>
-      </c>
-      <c r="D173" t="s">
-        <v>81</v>
-      </c>
-      <c r="E173" t="s">
-        <v>50</v>
-      </c>
-      <c r="F173" t="s">
-        <v>181</v>
-      </c>
-      <c r="G173" t="s">
-        <v>186</v>
-      </c>
-      <c r="H173" t="s">
-        <v>201</v>
-      </c>
-      <c r="J173" t="s">
-        <v>206</v>
-      </c>
-      <c r="K173" t="s">
-        <v>217</v>
-      </c>
-      <c r="L173" t="s">
-        <v>313</v>
-      </c>
-      <c r="N173" s="10" t="s">
-        <v>575</v>
-      </c>
-      <c r="P173" t="s">
-        <v>526</v>
-      </c>
-      <c r="Q173" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="174" spans="1:19">
@@ -6828,8 +6801,17 @@
       <c r="B174" s="4" t="s">
         <v>38</v>
       </c>
+      <c r="C174" s="6">
+        <v>511</v>
+      </c>
+      <c r="D174" t="s">
+        <v>81</v>
+      </c>
+      <c r="E174" t="s">
+        <v>50</v>
+      </c>
       <c r="F174" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G174" t="s">
         <v>186</v>
@@ -6837,9 +6819,6 @@
       <c r="H174" t="s">
         <v>201</v>
       </c>
-      <c r="I174" t="s">
-        <v>284</v>
-      </c>
       <c r="J174" t="s">
         <v>206</v>
       </c>
@@ -6847,7 +6826,16 @@
         <v>217</v>
       </c>
       <c r="L174" t="s">
-        <v>451</v>
+        <v>313</v>
+      </c>
+      <c r="N174" s="10" t="s">
+        <v>574</v>
+      </c>
+      <c r="P174" t="s">
+        <v>525</v>
+      </c>
+      <c r="Q174" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="175" spans="1:19">
@@ -6857,17 +6845,8 @@
       <c r="B175" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C175" s="6">
-        <v>513</v>
-      </c>
-      <c r="D175" t="s">
-        <v>82</v>
-      </c>
-      <c r="E175" t="s">
-        <v>50</v>
-      </c>
       <c r="F175" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G175" t="s">
         <v>186</v>
@@ -6876,7 +6855,7 @@
         <v>201</v>
       </c>
       <c r="I175" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J175" t="s">
         <v>206</v>
@@ -6885,7 +6864,7 @@
         <v>217</v>
       </c>
       <c r="L175" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="176" spans="1:19">
@@ -6895,8 +6874,17 @@
       <c r="B176" s="4" t="s">
         <v>38</v>
       </c>
+      <c r="C176" s="6">
+        <v>513</v>
+      </c>
+      <c r="D176" t="s">
+        <v>82</v>
+      </c>
+      <c r="E176" t="s">
+        <v>50</v>
+      </c>
       <c r="F176" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G176" t="s">
         <v>186</v>
@@ -6905,7 +6893,7 @@
         <v>201</v>
       </c>
       <c r="I176" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J176" t="s">
         <v>206</v>
@@ -6914,7 +6902,7 @@
         <v>217</v>
       </c>
       <c r="L176" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="177" spans="1:17">
@@ -6925,7 +6913,7 @@
         <v>38</v>
       </c>
       <c r="F177" t="s">
-        <v>37</v>
+        <v>176</v>
       </c>
       <c r="G177" t="s">
         <v>186</v>
@@ -6934,16 +6922,16 @@
         <v>201</v>
       </c>
       <c r="I177" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J177" t="s">
         <v>206</v>
       </c>
       <c r="K177" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="L177" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="178" spans="1:17">
@@ -6954,7 +6942,7 @@
         <v>38</v>
       </c>
       <c r="F178" t="s">
-        <v>182</v>
+        <v>37</v>
       </c>
       <c r="G178" t="s">
         <v>186</v>
@@ -6963,19 +6951,19 @@
         <v>201</v>
       </c>
       <c r="I178" t="s">
-        <v>38</v>
+        <v>287</v>
       </c>
       <c r="J178" t="s">
         <v>206</v>
       </c>
       <c r="K178" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="L178" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="179" spans="1:17" ht="17" customHeight="1">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="179" spans="1:17">
       <c r="A179" s="4" t="s">
         <v>37</v>
       </c>
@@ -6983,7 +6971,7 @@
         <v>38</v>
       </c>
       <c r="F179" t="s">
-        <v>357</v>
+        <v>182</v>
       </c>
       <c r="G179" t="s">
         <v>186</v>
@@ -6992,13 +6980,16 @@
         <v>201</v>
       </c>
       <c r="I179" t="s">
-        <v>288</v>
+        <v>38</v>
       </c>
       <c r="J179" t="s">
         <v>206</v>
       </c>
       <c r="K179" t="s">
         <v>217</v>
+      </c>
+      <c r="L179" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="180" spans="1:17" ht="17" customHeight="1">
@@ -7009,7 +7000,7 @@
         <v>38</v>
       </c>
       <c r="F180" t="s">
-        <v>473</v>
+        <v>356</v>
       </c>
       <c r="G180" t="s">
         <v>186</v>
@@ -7018,7 +7009,7 @@
         <v>201</v>
       </c>
       <c r="I180" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J180" t="s">
         <v>206</v>
@@ -7035,7 +7026,7 @@
         <v>38</v>
       </c>
       <c r="F181" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="G181" t="s">
         <v>186</v>
@@ -7044,7 +7035,7 @@
         <v>201</v>
       </c>
       <c r="I181" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J181" t="s">
         <v>206</v>
@@ -7060,11 +7051,17 @@
       <c r="B182" s="4" t="s">
         <v>38</v>
       </c>
+      <c r="F182" t="s">
+        <v>473</v>
+      </c>
+      <c r="G182" t="s">
+        <v>186</v>
+      </c>
       <c r="H182" t="s">
         <v>201</v>
       </c>
       <c r="I182" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J182" t="s">
         <v>206</v>
@@ -7080,17 +7077,11 @@
       <c r="B183" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F183" t="s">
-        <v>180</v>
-      </c>
-      <c r="G183" t="s">
-        <v>186</v>
-      </c>
       <c r="H183" t="s">
         <v>201</v>
       </c>
       <c r="I183" t="s">
-        <v>487</v>
+        <v>291</v>
       </c>
       <c r="J183" t="s">
         <v>206</v>
@@ -7107,7 +7098,7 @@
         <v>38</v>
       </c>
       <c r="F184" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G184" t="s">
         <v>186</v>
@@ -7116,7 +7107,7 @@
         <v>201</v>
       </c>
       <c r="I184" t="s">
-        <v>212</v>
+        <v>486</v>
       </c>
       <c r="J184" t="s">
         <v>206</v>
@@ -7132,11 +7123,17 @@
       <c r="B185" s="4" t="s">
         <v>38</v>
       </c>
+      <c r="F185" t="s">
+        <v>184</v>
+      </c>
+      <c r="G185" t="s">
+        <v>186</v>
+      </c>
       <c r="H185" t="s">
         <v>201</v>
       </c>
       <c r="I185" t="s">
-        <v>489</v>
+        <v>212</v>
       </c>
       <c r="J185" t="s">
         <v>206</v>
@@ -7156,7 +7153,7 @@
         <v>201</v>
       </c>
       <c r="I186" t="s">
-        <v>292</v>
+        <v>488</v>
       </c>
       <c r="J186" t="s">
         <v>206</v>
@@ -7165,42 +7162,24 @@
         <v>217</v>
       </c>
     </row>
-    <row r="187" spans="1:17">
+    <row r="187" spans="1:17" ht="17" customHeight="1">
       <c r="A187" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F187" t="s">
-        <v>175</v>
-      </c>
-      <c r="G187" t="s">
-        <v>186</v>
+        <v>38</v>
       </c>
       <c r="H187" t="s">
         <v>201</v>
       </c>
       <c r="I187" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J187" t="s">
         <v>206</v>
       </c>
       <c r="K187" t="s">
         <v>217</v>
-      </c>
-      <c r="L187" t="s">
-        <v>458</v>
-      </c>
-      <c r="N187" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="P187" t="s">
-        <v>527</v>
-      </c>
-      <c r="Q187" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="188" spans="1:17">
@@ -7211,7 +7190,7 @@
         <v>39</v>
       </c>
       <c r="F188" t="s">
-        <v>362</v>
+        <v>175</v>
       </c>
       <c r="G188" t="s">
         <v>186</v>
@@ -7220,13 +7199,25 @@
         <v>201</v>
       </c>
       <c r="I188" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J188" t="s">
         <v>206</v>
       </c>
       <c r="K188" t="s">
         <v>217</v>
+      </c>
+      <c r="L188" t="s">
+        <v>457</v>
+      </c>
+      <c r="N188" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="P188" t="s">
+        <v>526</v>
+      </c>
+      <c r="Q188" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="189" spans="1:17">
@@ -7236,11 +7227,17 @@
       <c r="B189" s="4" t="s">
         <v>39</v>
       </c>
+      <c r="F189" t="s">
+        <v>361</v>
+      </c>
+      <c r="G189" t="s">
+        <v>186</v>
+      </c>
       <c r="H189" t="s">
         <v>201</v>
       </c>
       <c r="I189" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J189" t="s">
         <v>206</v>
@@ -7254,37 +7251,19 @@
         <v>37</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F190" t="s">
-        <v>178</v>
-      </c>
-      <c r="G190" t="s">
-        <v>186</v>
+        <v>39</v>
       </c>
       <c r="H190" t="s">
         <v>201</v>
       </c>
       <c r="I190" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J190" t="s">
         <v>206</v>
       </c>
       <c r="K190" t="s">
         <v>217</v>
-      </c>
-      <c r="L190" t="s">
-        <v>459</v>
-      </c>
-      <c r="N190" s="10" t="s">
-        <v>578</v>
-      </c>
-      <c r="P190" t="s">
-        <v>528</v>
-      </c>
-      <c r="Q190" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="191" spans="1:17">
@@ -7295,19 +7274,34 @@
         <v>40</v>
       </c>
       <c r="F191" t="s">
-        <v>360</v>
+        <v>178</v>
+      </c>
+      <c r="G191" t="s">
+        <v>186</v>
       </c>
       <c r="H191" t="s">
         <v>201</v>
       </c>
       <c r="I191" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J191" t="s">
         <v>206</v>
       </c>
       <c r="K191" t="s">
         <v>217</v>
+      </c>
+      <c r="L191" t="s">
+        <v>458</v>
+      </c>
+      <c r="N191" s="10" t="s">
+        <v>577</v>
+      </c>
+      <c r="P191" t="s">
+        <v>527</v>
+      </c>
+      <c r="Q191" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="192" spans="1:17">
@@ -7315,37 +7309,22 @@
         <v>37</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>530</v>
+        <v>40</v>
       </c>
       <c r="F192" t="s">
-        <v>174</v>
-      </c>
-      <c r="G192" t="s">
-        <v>186</v>
+        <v>359</v>
       </c>
       <c r="H192" t="s">
         <v>201</v>
       </c>
       <c r="I192" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J192" t="s">
         <v>206</v>
       </c>
       <c r="K192" t="s">
         <v>217</v>
-      </c>
-      <c r="L192" t="s">
-        <v>452</v>
-      </c>
-      <c r="N192" s="10" t="s">
-        <v>530</v>
-      </c>
-      <c r="P192" t="s">
-        <v>529</v>
-      </c>
-      <c r="Q192" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="193" spans="1:17">
@@ -7353,10 +7332,10 @@
         <v>37</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="F193" t="s">
-        <v>471</v>
+        <v>174</v>
       </c>
       <c r="G193" t="s">
         <v>186</v>
@@ -7365,13 +7344,25 @@
         <v>201</v>
       </c>
       <c r="I193" t="s">
-        <v>41</v>
+        <v>298</v>
       </c>
       <c r="J193" t="s">
         <v>206</v>
       </c>
       <c r="K193" t="s">
         <v>217</v>
+      </c>
+      <c r="L193" t="s">
+        <v>451</v>
+      </c>
+      <c r="N193" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="P193" t="s">
+        <v>528</v>
+      </c>
+      <c r="Q193" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="194" spans="1:17">
@@ -7379,13 +7370,19 @@
         <v>37</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
+      </c>
+      <c r="F194" t="s">
+        <v>470</v>
+      </c>
+      <c r="G194" t="s">
+        <v>186</v>
       </c>
       <c r="H194" t="s">
         <v>201</v>
       </c>
       <c r="I194" t="s">
-        <v>211</v>
+        <v>41</v>
       </c>
       <c r="J194" t="s">
         <v>206</v>
@@ -7399,13 +7396,13 @@
         <v>37</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H195" t="s">
         <v>201</v>
       </c>
       <c r="I195" t="s">
-        <v>299</v>
+        <v>211</v>
       </c>
       <c r="J195" t="s">
         <v>206</v>
@@ -7419,10 +7416,19 @@
         <v>37</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>555</v>
-      </c>
-      <c r="Q196" t="s">
-        <v>557</v>
+        <v>529</v>
+      </c>
+      <c r="H196" t="s">
+        <v>201</v>
+      </c>
+      <c r="I196" t="s">
+        <v>299</v>
+      </c>
+      <c r="J196" t="s">
+        <v>206</v>
+      </c>
+      <c r="K196" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="197" spans="1:17">
@@ -7430,10 +7436,10 @@
         <v>37</v>
       </c>
       <c r="B197" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="Q197" t="s">
         <v>556</v>
-      </c>
-      <c r="Q197" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="198" spans="1:17">
@@ -7441,56 +7447,41 @@
         <v>37</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>291</v>
+        <v>555</v>
       </c>
       <c r="Q198" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="199" spans="1:17" ht="17" customHeight="1">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="199" spans="1:17">
       <c r="A199" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C199" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="D199" t="s">
-        <v>467</v>
-      </c>
-      <c r="E199" t="s">
-        <v>50</v>
-      </c>
-      <c r="F199" t="s">
-        <v>185</v>
-      </c>
-      <c r="G199" t="s">
-        <v>186</v>
-      </c>
-      <c r="H199" t="s">
-        <v>201</v>
-      </c>
-      <c r="I199" t="s">
-        <v>300</v>
-      </c>
-      <c r="J199" t="s">
-        <v>206</v>
-      </c>
-      <c r="K199" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="200" spans="1:17">
+        <v>291</v>
+      </c>
+      <c r="Q199" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="200" spans="1:17" ht="17" customHeight="1">
       <c r="A200" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B200" s="4" t="s">
         <v>42</v>
       </c>
+      <c r="C200" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="D200" t="s">
+        <v>466</v>
+      </c>
+      <c r="E200" t="s">
+        <v>50</v>
+      </c>
       <c r="F200" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G200" t="s">
         <v>186</v>
@@ -7498,28 +7489,31 @@
       <c r="H200" t="s">
         <v>201</v>
       </c>
+      <c r="I200" t="s">
+        <v>300</v>
+      </c>
+      <c r="J200" t="s">
+        <v>206</v>
+      </c>
+      <c r="K200" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="201" spans="1:17">
-      <c r="A201" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B201" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E201" t="s">
-        <v>52</v>
+      <c r="A201" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F201" t="s">
+        <v>183</v>
+      </c>
+      <c r="G201" t="s">
+        <v>186</v>
       </c>
       <c r="H201" t="s">
-        <v>200</v>
-      </c>
-      <c r="I201" t="s">
-        <v>301</v>
-      </c>
-      <c r="J201" t="s">
-        <v>209</v>
-      </c>
-      <c r="K201" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
     </row>
     <row r="202" spans="1:17">
@@ -7527,13 +7521,16 @@
         <v>43</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="E202" t="s">
+        <v>52</v>
       </c>
       <c r="H202" t="s">
         <v>200</v>
       </c>
       <c r="I202" t="s">
-        <v>208</v>
+        <v>301</v>
       </c>
       <c r="J202" t="s">
         <v>209</v>
@@ -7549,26 +7546,11 @@
       <c r="B203" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C203" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="D203" t="s">
-        <v>45</v>
-      </c>
-      <c r="E203" t="s">
-        <v>52</v>
-      </c>
-      <c r="F203" t="s">
-        <v>161</v>
-      </c>
-      <c r="G203" t="s">
-        <v>173</v>
-      </c>
       <c r="H203" t="s">
         <v>200</v>
       </c>
       <c r="I203" t="s">
-        <v>45</v>
+        <v>208</v>
       </c>
       <c r="J203" t="s">
         <v>209</v>
@@ -7582,22 +7564,28 @@
         <v>43</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D204" t="s">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="E204" t="s">
         <v>52</v>
       </c>
+      <c r="F204" t="s">
+        <v>161</v>
+      </c>
+      <c r="G204" t="s">
+        <v>173</v>
+      </c>
       <c r="H204" t="s">
         <v>200</v>
       </c>
       <c r="I204" t="s">
-        <v>302</v>
+        <v>45</v>
       </c>
       <c r="J204" t="s">
         <v>209</v>
@@ -7611,13 +7599,13 @@
         <v>43</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D205" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="E205" t="s">
         <v>52</v>
@@ -7626,12 +7614,41 @@
         <v>200</v>
       </c>
       <c r="I205" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J205" t="s">
         <v>209</v>
       </c>
       <c r="K205" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="206" spans="1:17">
+      <c r="A206" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B206" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C206" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D206" t="s">
+        <v>47</v>
+      </c>
+      <c r="E206" t="s">
+        <v>52</v>
+      </c>
+      <c r="H206" t="s">
+        <v>200</v>
+      </c>
+      <c r="I206" t="s">
+        <v>303</v>
+      </c>
+      <c r="J206" t="s">
+        <v>209</v>
+      </c>
+      <c r="K206" t="s">
         <v>214</v>
       </c>
     </row>

--- a/benefit_indexing.xlsx
+++ b/benefit_indexing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/BryanMak/Documents/RawClaimMCR-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F2F09E-E1A1-F548-A013-FCE62EBD9D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F57184-4355-F34F-9AE1-2ACBA9ACEA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-18340" yWindow="-21000" windowWidth="38400" windowHeight="21000" xr2:uid="{A0161F8B-45E3-674F-BD1A-B040F75BC5F2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1551" uniqueCount="698">
   <si>
     <t>Daily Room &amp; Board</t>
   </si>
@@ -2109,6 +2109,27 @@
   </si>
   <si>
     <t>VACC/ROUTINE CHECKUP/OPTICAL</t>
+  </si>
+  <si>
+    <t>Prescribed Medicine OT Clinic</t>
+  </si>
+  <si>
+    <t>Non Claimable Expenses</t>
+  </si>
+  <si>
+    <t>Operating Theatre - Intermediate</t>
+  </si>
+  <si>
+    <t>Pre-Natal Check</t>
+  </si>
+  <si>
+    <t>Maternity (M)</t>
+  </si>
+  <si>
+    <t>Caesarian</t>
+  </si>
+  <si>
+    <t>Anaesthetist's Fee - Intermediate</t>
   </si>
 </sst>
 </file>
@@ -3151,6 +3172,9 @@
       <c r="M18" t="s">
         <v>401</v>
       </c>
+      <c r="N18" s="10" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="19" spans="1:19">
       <c r="A19" s="1" t="s">
@@ -3402,6 +3426,9 @@
       </c>
       <c r="M29" t="s">
         <v>387</v>
+      </c>
+      <c r="N29" s="10" t="s">
+        <v>697</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -3641,6 +3668,9 @@
       <c r="M40" t="s">
         <v>393</v>
       </c>
+      <c r="N40" s="10" t="s">
+        <v>693</v>
+      </c>
     </row>
     <row r="41" spans="1:19">
       <c r="A41" s="1" t="s">
@@ -3980,6 +4010,7 @@
       <c r="G53" t="s">
         <v>173</v>
       </c>
+      <c r="N53" s="10"/>
     </row>
     <row r="54" spans="1:19">
       <c r="A54" s="1" t="s">
@@ -4115,6 +4146,7 @@
       <c r="M61" t="s">
         <v>404</v>
       </c>
+      <c r="N61" s="10"/>
     </row>
     <row r="62" spans="1:19">
       <c r="A62" s="1" t="s">
@@ -4513,6 +4545,9 @@
         <v>575</v>
       </c>
       <c r="C80" s="7"/>
+      <c r="N80" s="10" t="s">
+        <v>692</v>
+      </c>
     </row>
     <row r="81" spans="1:19">
       <c r="A81" s="2" t="s">
@@ -6232,6 +6267,9 @@
       <c r="M148" t="s">
         <v>380</v>
       </c>
+      <c r="N148" s="10" t="s">
+        <v>691</v>
+      </c>
       <c r="O148" t="s">
         <v>539</v>
       </c>
@@ -6490,6 +6528,9 @@
       </c>
       <c r="M156" t="s">
         <v>375</v>
+      </c>
+      <c r="N156" s="10" t="s">
+        <v>36</v>
       </c>
       <c r="O156" s="10" t="s">
         <v>436</v>
@@ -7538,6 +7579,9 @@
       <c r="K202" t="s">
         <v>214</v>
       </c>
+      <c r="N202" s="10" t="s">
+        <v>694</v>
+      </c>
     </row>
     <row r="203" spans="1:17">
       <c r="A203" s="5" t="s">
@@ -7558,6 +7602,9 @@
       <c r="K203" t="s">
         <v>214</v>
       </c>
+      <c r="N203" s="10" t="s">
+        <v>695</v>
+      </c>
     </row>
     <row r="204" spans="1:17">
       <c r="A204" s="5" t="s">
@@ -7621,6 +7668,9 @@
       </c>
       <c r="K205" t="s">
         <v>214</v>
+      </c>
+      <c r="N205" s="10" t="s">
+        <v>696</v>
       </c>
     </row>
     <row r="206" spans="1:17">

--- a/benefit_indexing.xlsx
+++ b/benefit_indexing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/BryanMak/Documents/RawClaimMCR-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F57184-4355-F34F-9AE1-2ACBA9ACEA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A43D660-8E36-4E41-9D1D-1FBEAFB34B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-18340" yWindow="-21000" windowWidth="38400" windowHeight="21000" xr2:uid="{A0161F8B-45E3-674F-BD1A-B040F75BC5F2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1551" uniqueCount="698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="698">
   <si>
     <t>Daily Room &amp; Board</t>
   </si>
@@ -6555,6 +6555,9 @@
       <c r="E157" t="s">
         <v>51</v>
       </c>
+      <c r="N157" t="s">
+        <v>75</v>
+      </c>
       <c r="O157" t="s">
         <v>564</v>
       </c>

--- a/benefit_indexing.xlsx
+++ b/benefit_indexing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/BryanMak/Documents/RawClaimMCR-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A43D660-8E36-4E41-9D1D-1FBEAFB34B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BEC809-D9E5-EC40-BE99-ECF105C787F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-18340" yWindow="-21000" windowWidth="38400" windowHeight="21000" xr2:uid="{A0161F8B-45E3-674F-BD1A-B040F75BC5F2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="700">
   <si>
     <t>Daily Room &amp; Board</t>
   </si>
@@ -2130,6 +2130,12 @@
   </si>
   <si>
     <t>Anaesthetist's Fee - Intermediate</t>
+  </si>
+  <si>
+    <t>HOSP CASH</t>
+  </si>
+  <si>
+    <t>DAY SURGERY CASH ALLOWANCE</t>
   </si>
 </sst>
 </file>
@@ -4236,6 +4242,9 @@
       <c r="O64" t="s">
         <v>495</v>
       </c>
+      <c r="P64" t="s">
+        <v>698</v>
+      </c>
       <c r="R64" t="s">
         <v>625</v>
       </c>
@@ -4441,6 +4450,9 @@
       </c>
       <c r="O72" t="s">
         <v>503</v>
+      </c>
+      <c r="P72" t="s">
+        <v>699</v>
       </c>
       <c r="R72" t="s">
         <v>617</v>
@@ -6740,6 +6752,9 @@
       </c>
       <c r="O166" s="10" t="s">
         <v>434</v>
+      </c>
+      <c r="P166" t="s">
+        <v>313</v>
       </c>
       <c r="R166" t="s">
         <v>603</v>
